--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>League</t>
   </si>
@@ -194,6 +194,102 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Bulgarian A League</t>
+  </si>
+  <si>
+    <t>Finnish Veikkausliiga</t>
+  </si>
+  <si>
+    <t>Slovakian Super League</t>
+  </si>
+  <si>
+    <t>Israeli Premier League</t>
+  </si>
+  <si>
+    <t>Egyptian Premier</t>
+  </si>
+  <si>
+    <t>Swedish Superettan</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>Beroe Stara Za</t>
+  </si>
+  <si>
+    <t>Gnistan</t>
+  </si>
+  <si>
+    <t>Zilina</t>
+  </si>
+  <si>
+    <t>MFk Skalica</t>
+  </si>
+  <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Lokomotiv Sofia</t>
+  </si>
+  <si>
+    <t>Smouha</t>
+  </si>
+  <si>
+    <t>Al Ahly Cairo</t>
+  </si>
+  <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
+    <t>Falkenbergs</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>FC Inter</t>
+  </si>
+  <si>
+    <t>Zemplin</t>
+  </si>
+  <si>
+    <t>FC Kosice</t>
+  </si>
+  <si>
+    <t>Hapoel Petach Tikva</t>
+  </si>
+  <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
+    <t>Zamalek</t>
+  </si>
+  <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
+    <t>Pyramids</t>
+  </si>
+  <si>
+    <t>Norrkoping</t>
+  </si>
+  <si>
+    <t>2026-05-03 02:41:31</t>
   </si>
 </sst>
 </file>
@@ -551,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BH11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:60">
@@ -734,6 +830,1826 @@
       </c>
       <c r="BH1" s="1" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:60">
+      <c r="A2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2">
+        <v>2.04</v>
+      </c>
+      <c r="G2">
+        <v>2.24</v>
+      </c>
+      <c r="H2">
+        <v>4.1</v>
+      </c>
+      <c r="I2">
+        <v>5.4</v>
+      </c>
+      <c r="J2">
+        <v>3.1</v>
+      </c>
+      <c r="K2">
+        <v>3.8</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1.6</v>
+      </c>
+      <c r="Q2">
+        <v>2.38</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <v>0</v>
+      </c>
+      <c r="BB2">
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <v>0</v>
+      </c>
+      <c r="BF2">
+        <v>0</v>
+      </c>
+      <c r="BG2">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:60">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3">
+        <v>5.1</v>
+      </c>
+      <c r="G3">
+        <v>6.4</v>
+      </c>
+      <c r="H3">
+        <v>1.64</v>
+      </c>
+      <c r="I3">
+        <v>1.8</v>
+      </c>
+      <c r="J3">
+        <v>3.95</v>
+      </c>
+      <c r="K3">
+        <v>4.7</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>2.08</v>
+      </c>
+      <c r="Q3">
+        <v>1.76</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:60">
+      <c r="A4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4">
+        <v>1.44</v>
+      </c>
+      <c r="G4">
+        <v>1.56</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
+      </c>
+      <c r="I4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J4">
+        <v>4.8</v>
+      </c>
+      <c r="K4">
+        <v>5.8</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>2.52</v>
+      </c>
+      <c r="Q4">
+        <v>1.52</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:60">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5">
+        <v>2.5</v>
+      </c>
+      <c r="G5">
+        <v>2.94</v>
+      </c>
+      <c r="H5">
+        <v>2.58</v>
+      </c>
+      <c r="I5">
+        <v>3.15</v>
+      </c>
+      <c r="J5">
+        <v>3.6</v>
+      </c>
+      <c r="K5">
+        <v>4.6</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>2.24</v>
+      </c>
+      <c r="Q5">
+        <v>1.64</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:60">
+      <c r="A6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6">
+        <v>1.31</v>
+      </c>
+      <c r="G6">
+        <v>1.55</v>
+      </c>
+      <c r="H6">
+        <v>2.9</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>2.8</v>
+      </c>
+      <c r="K6">
+        <v>85</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>2.2</v>
+      </c>
+      <c r="Q6">
+        <v>1.47</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:60">
+      <c r="A7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7">
+        <v>2.02</v>
+      </c>
+      <c r="G7">
+        <v>2.28</v>
+      </c>
+      <c r="H7">
+        <v>3.65</v>
+      </c>
+      <c r="I7">
+        <v>4.3</v>
+      </c>
+      <c r="J7">
+        <v>3.25</v>
+      </c>
+      <c r="K7">
+        <v>4.4</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.68</v>
+      </c>
+      <c r="Q7">
+        <v>1.84</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:60">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8">
+        <v>4.7</v>
+      </c>
+      <c r="G8">
+        <v>9.6</v>
+      </c>
+      <c r="H8">
+        <v>1.64</v>
+      </c>
+      <c r="I8">
+        <v>1.8</v>
+      </c>
+      <c r="J8">
+        <v>3.05</v>
+      </c>
+      <c r="K8">
+        <v>4.3</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.48</v>
+      </c>
+      <c r="Q8">
+        <v>2.44</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:60">
+      <c r="A9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F9">
+        <v>1.37</v>
+      </c>
+      <c r="G9">
+        <v>1.45</v>
+      </c>
+      <c r="H9">
+        <v>1.23</v>
+      </c>
+      <c r="I9">
+        <v>13.5</v>
+      </c>
+      <c r="J9">
+        <v>4.2</v>
+      </c>
+      <c r="K9">
+        <v>5.2</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1.75</v>
+      </c>
+      <c r="Q9">
+        <v>2.02</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:60">
+      <c r="A10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10">
+        <v>4.6</v>
+      </c>
+      <c r="G10">
+        <v>5.6</v>
+      </c>
+      <c r="H10">
+        <v>1.84</v>
+      </c>
+      <c r="I10">
+        <v>2.04</v>
+      </c>
+      <c r="J10">
+        <v>3.3</v>
+      </c>
+      <c r="K10">
+        <v>4.1</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>1.66</v>
+      </c>
+      <c r="Q10">
+        <v>2.2</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:60">
+      <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11">
+        <v>2.3</v>
+      </c>
+      <c r="G11">
+        <v>3.2</v>
+      </c>
+      <c r="H11">
+        <v>2.32</v>
+      </c>
+      <c r="I11">
+        <v>3.25</v>
+      </c>
+      <c r="J11">
+        <v>3.35</v>
+      </c>
+      <c r="K11">
+        <v>950</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>2.06</v>
+      </c>
+      <c r="Q11">
+        <v>1.54</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -289,7 +289,7 @@
     <t>Norrkoping</t>
   </si>
   <si>
-    <t>2026-05-03 02:41:31</t>
+    <t>2026-05-03 05:10:42</t>
   </si>
 </sst>
 </file>
@@ -852,7 +852,7 @@
         <v>2.04</v>
       </c>
       <c r="G2">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="H2">
         <v>4.1</v>
@@ -864,7 +864,7 @@
         <v>3.1</v>
       </c>
       <c r="K2">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -882,7 +882,7 @@
         <v>1.6</v>
       </c>
       <c r="Q2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>1.64</v>
       </c>
       <c r="I3">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="J3">
         <v>3.95</v>
@@ -1064,7 +1064,7 @@
         <v>2.08</v>
       </c>
       <c r="Q3">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1216,16 +1216,16 @@
         <v>1.44</v>
       </c>
       <c r="G4">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="H4">
         <v>6.8</v>
       </c>
       <c r="I4">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="K4">
         <v>5.8</v>
@@ -1246,7 +1246,7 @@
         <v>2.52</v>
       </c>
       <c r="Q4">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1398,7 +1398,7 @@
         <v>2.5</v>
       </c>
       <c r="G5">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="H5">
         <v>2.58</v>
@@ -1768,7 +1768,7 @@
         <v>3.65</v>
       </c>
       <c r="I7">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J7">
         <v>3.25</v>
@@ -1789,10 +1789,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="Q7">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2308,16 +2308,16 @@
         <v>4.6</v>
       </c>
       <c r="G10">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="H10">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="I10">
         <v>2.04</v>
       </c>
       <c r="J10">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="K10">
         <v>4.1</v>
@@ -2338,7 +2338,7 @@
         <v>1.66</v>
       </c>
       <c r="Q10">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2493,7 +2493,7 @@
         <v>3.2</v>
       </c>
       <c r="H11">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="I11">
         <v>3.25</v>
@@ -2502,7 +2502,7 @@
         <v>3.35</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -289,7 +289,7 @@
     <t>Norrkoping</t>
   </si>
   <si>
-    <t>2026-05-03 05:10:42</t>
+    <t>2026-05-03 07:41:00</t>
   </si>
 </sst>
 </file>
@@ -852,7 +852,7 @@
         <v>2.04</v>
       </c>
       <c r="G2">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="H2">
         <v>4.1</v>
@@ -1064,7 +1064,7 @@
         <v>2.08</v>
       </c>
       <c r="Q3">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1225,7 +1225,7 @@
         <v>9</v>
       </c>
       <c r="J4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K4">
         <v>5.8</v>
@@ -1246,7 +1246,7 @@
         <v>2.52</v>
       </c>
       <c r="Q4">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1768,7 +1768,7 @@
         <v>3.65</v>
       </c>
       <c r="I7">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J7">
         <v>3.25</v>
@@ -2308,16 +2308,16 @@
         <v>4.6</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H10">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="I10">
         <v>2.04</v>
       </c>
       <c r="J10">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K10">
         <v>4.1</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="98">
   <si>
     <t>League</t>
   </si>
@@ -196,6 +196,9 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Chinese Super League</t>
+  </si>
+  <si>
     <t>Bulgarian A League</t>
   </si>
   <si>
@@ -211,12 +214,15 @@
     <t>Egyptian Premier</t>
   </si>
   <si>
-    <t>Swedish Superettan</t>
-  </si>
-  <si>
     <t>2026-05-05</t>
   </si>
   <si>
+    <t>08:00:00</t>
+  </si>
+  <si>
+    <t>08:35:00</t>
+  </si>
+  <si>
     <t>11:30:00</t>
   </si>
   <si>
@@ -229,6 +235,15 @@
     <t>14:00:00</t>
   </si>
   <si>
+    <t>Qingdao Youth Island</t>
+  </si>
+  <si>
+    <t>Shandong Taishan</t>
+  </si>
+  <si>
+    <t>Liaoning Tieren FC</t>
+  </si>
+  <si>
     <t>Beroe Stara Za</t>
   </si>
   <si>
@@ -256,7 +271,13 @@
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
-    <t>Falkenbergs</t>
+    <t>Tianjin Jinmen Tiger FC</t>
+  </si>
+  <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
+    <t>Chengdu Rongcheng</t>
   </si>
   <si>
     <t>Montana</t>
@@ -286,10 +307,7 @@
     <t>Pyramids</t>
   </si>
   <si>
-    <t>Norrkoping</t>
-  </si>
-  <si>
-    <t>2026-05-03 07:41:00</t>
+    <t>2026-05-03 10:11:23</t>
   </si>
 </sst>
 </file>
@@ -647,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH11"/>
+  <dimension ref="A1:BH13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:60">
@@ -843,180 +861,180 @@
         <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F2">
+        <v>2.18</v>
+      </c>
+      <c r="G2">
+        <v>2.4</v>
+      </c>
+      <c r="H2">
+        <v>3.4</v>
+      </c>
+      <c r="I2">
+        <v>3.85</v>
+      </c>
+      <c r="J2">
+        <v>3.25</v>
+      </c>
+      <c r="K2">
+        <v>3.7</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.08</v>
+      </c>
+      <c r="N2">
+        <v>3.3</v>
+      </c>
+      <c r="O2">
+        <v>1.36</v>
+      </c>
+      <c r="P2">
+        <v>1.79</v>
+      </c>
+      <c r="Q2">
         <v>2.04</v>
       </c>
-      <c r="G2">
-        <v>2.24</v>
-      </c>
-      <c r="H2">
-        <v>4.1</v>
-      </c>
-      <c r="I2">
-        <v>5.4</v>
-      </c>
-      <c r="J2">
-        <v>3.1</v>
-      </c>
-      <c r="K2">
-        <v>3.5</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>1.6</v>
-      </c>
-      <c r="Q2">
-        <v>2.4</v>
-      </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW2">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BD2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BE2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:60">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -1025,180 +1043,180 @@
         <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F3">
-        <v>5.1</v>
+        <v>2.78</v>
       </c>
       <c r="G3">
-        <v>6.4</v>
+        <v>2.98</v>
       </c>
       <c r="H3">
-        <v>1.64</v>
+        <v>2.34</v>
       </c>
       <c r="I3">
-        <v>1.78</v>
+        <v>2.56</v>
       </c>
       <c r="J3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>4.7</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P3">
-        <v>2.08</v>
+        <v>2.84</v>
       </c>
       <c r="Q3">
-        <v>1.76</v>
+        <v>1.46</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AZ3">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BF3">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BG3">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BH3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:60">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -1207,210 +1225,210 @@
         <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F4">
-        <v>1.44</v>
+        <v>6.2</v>
       </c>
       <c r="G4">
-        <v>1.59</v>
+        <v>7.8</v>
       </c>
       <c r="H4">
+        <v>1.57</v>
+      </c>
+      <c r="I4">
+        <v>1.66</v>
+      </c>
+      <c r="J4">
+        <v>3.9</v>
+      </c>
+      <c r="K4">
+        <v>4.4</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.06</v>
+      </c>
+      <c r="N4">
+        <v>4</v>
+      </c>
+      <c r="O4">
+        <v>1.28</v>
+      </c>
+      <c r="P4">
+        <v>2.02</v>
+      </c>
+      <c r="Q4">
+        <v>1.8</v>
+      </c>
+      <c r="R4">
+        <v>1.39</v>
+      </c>
+      <c r="S4">
+        <v>3.1</v>
+      </c>
+      <c r="T4">
+        <v>1.83</v>
+      </c>
+      <c r="U4">
+        <v>1.96</v>
+      </c>
+      <c r="V4">
+        <v>2.5</v>
+      </c>
+      <c r="W4">
+        <v>1.14</v>
+      </c>
+      <c r="X4">
+        <v>17</v>
+      </c>
+      <c r="Y4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z4">
+        <v>10.5</v>
+      </c>
+      <c r="AA4">
+        <v>18</v>
+      </c>
+      <c r="AB4">
+        <v>29</v>
+      </c>
+      <c r="AC4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD4">
+        <v>10.5</v>
+      </c>
+      <c r="AE4">
+        <v>17.5</v>
+      </c>
+      <c r="AF4">
+        <v>70</v>
+      </c>
+      <c r="AG4">
+        <v>32</v>
+      </c>
+      <c r="AH4">
+        <v>22</v>
+      </c>
+      <c r="AI4">
+        <v>36</v>
+      </c>
+      <c r="AJ4">
+        <v>230</v>
+      </c>
+      <c r="AK4">
+        <v>120</v>
+      </c>
+      <c r="AL4">
+        <v>110</v>
+      </c>
+      <c r="AM4">
+        <v>130</v>
+      </c>
+      <c r="AN4">
+        <v>140</v>
+      </c>
+      <c r="AO4">
+        <v>10.5</v>
+      </c>
+      <c r="AP4">
+        <v>5.3</v>
+      </c>
+      <c r="AQ4">
+        <v>7.4</v>
+      </c>
+      <c r="AR4">
+        <v>8.4</v>
+      </c>
+      <c r="AS4">
+        <v>13</v>
+      </c>
+      <c r="AT4">
+        <v>20</v>
+      </c>
+      <c r="AU4">
+        <v>4.3</v>
+      </c>
+      <c r="AV4">
+        <v>4.4</v>
+      </c>
+      <c r="AW4">
+        <v>14</v>
+      </c>
+      <c r="AX4">
         <v>6.8</v>
       </c>
-      <c r="I4">
-        <v>9</v>
-      </c>
-      <c r="J4">
-        <v>4.4</v>
-      </c>
-      <c r="K4">
-        <v>5.8</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>2.52</v>
-      </c>
-      <c r="Q4">
-        <v>1.47</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
       <c r="AY4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AZ4">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BA4">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG4">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BH4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:60">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F5">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="G5">
-        <v>2.78</v>
+        <v>2.24</v>
       </c>
       <c r="H5">
-        <v>2.58</v>
+        <v>4.1</v>
       </c>
       <c r="I5">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="J5">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1425,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>2.24</v>
+        <v>1.6</v>
       </c>
       <c r="Q5">
-        <v>1.64</v>
+        <v>2.4</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1557,42 +1575,42 @@
         <v>0</v>
       </c>
       <c r="BH5" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:60">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F6">
-        <v>1.31</v>
+        <v>5.3</v>
       </c>
       <c r="G6">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="H6">
-        <v>2.9</v>
+        <v>1.64</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>1.76</v>
       </c>
       <c r="J6">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>85</v>
+        <v>4.5</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1607,10 +1625,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q6">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -1739,12 +1757,12 @@
         <v>0</v>
       </c>
       <c r="BH6" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:60">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -1753,28 +1771,28 @@
         <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F7">
-        <v>2.02</v>
+        <v>1.43</v>
       </c>
       <c r="G7">
-        <v>2.28</v>
+        <v>1.54</v>
       </c>
       <c r="H7">
-        <v>3.65</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1789,10 +1807,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.79</v>
+        <v>2.52</v>
       </c>
       <c r="Q7">
-        <v>1.99</v>
+        <v>1.54</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -1921,12 +1939,12 @@
         <v>0</v>
       </c>
       <c r="BH7" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:60">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
@@ -1935,47 +1953,47 @@
         <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F8">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="G8">
-        <v>9.6</v>
+        <v>2.78</v>
       </c>
       <c r="H8">
+        <v>2.58</v>
+      </c>
+      <c r="I8">
+        <v>3.15</v>
+      </c>
+      <c r="J8">
+        <v>3.6</v>
+      </c>
+      <c r="K8">
+        <v>4.2</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>2.24</v>
+      </c>
+      <c r="Q8">
         <v>1.64</v>
       </c>
-      <c r="I8">
-        <v>1.8</v>
-      </c>
-      <c r="J8">
-        <v>3.05</v>
-      </c>
-      <c r="K8">
-        <v>4.3</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>1.48</v>
-      </c>
-      <c r="Q8">
-        <v>2.44</v>
-      </c>
       <c r="R8">
         <v>0</v>
       </c>
@@ -2103,7 +2121,7 @@
         <v>0</v>
       </c>
       <c r="BH8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:60">
@@ -2114,31 +2132,31 @@
         <v>66</v>
       </c>
       <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9">
+        <v>1.31</v>
+      </c>
+      <c r="G9">
+        <v>1.55</v>
+      </c>
+      <c r="H9">
+        <v>2.9</v>
+      </c>
+      <c r="I9">
         <v>70</v>
       </c>
-      <c r="D9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F9">
-        <v>1.37</v>
-      </c>
-      <c r="G9">
-        <v>1.45</v>
-      </c>
-      <c r="H9">
-        <v>1.23</v>
-      </c>
-      <c r="I9">
-        <v>13.5</v>
-      </c>
       <c r="J9">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="K9">
-        <v>5.2</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2153,10 +2171,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="Q9">
-        <v>2.02</v>
+        <v>1.47</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2285,42 +2303,42 @@
         <v>0</v>
       </c>
       <c r="BH9" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:60">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s">
         <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F10">
-        <v>4.6</v>
+        <v>2.02</v>
       </c>
       <c r="G10">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="H10">
-        <v>1.84</v>
+        <v>3.65</v>
       </c>
       <c r="I10">
-        <v>2.04</v>
+        <v>4.8</v>
       </c>
       <c r="J10">
         <v>3.25</v>
       </c>
       <c r="K10">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2335,10 +2353,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="Q10">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2467,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="BH10" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:60">
@@ -2478,31 +2496,31 @@
         <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F11">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="G11">
-        <v>3.2</v>
+        <v>9.6</v>
       </c>
       <c r="H11">
-        <v>2.52</v>
+        <v>1.64</v>
       </c>
       <c r="I11">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="J11">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -2517,10 +2535,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>2.06</v>
+        <v>1.48</v>
       </c>
       <c r="Q11">
-        <v>1.54</v>
+        <v>2.44</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2649,7 +2667,371 @@
         <v>0</v>
       </c>
       <c r="BH11" t="s">
-        <v>91</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:60">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12">
+        <v>1.37</v>
+      </c>
+      <c r="G12">
+        <v>1.45</v>
+      </c>
+      <c r="H12">
+        <v>1.24</v>
+      </c>
+      <c r="I12">
+        <v>13.5</v>
+      </c>
+      <c r="J12">
+        <v>4.4</v>
+      </c>
+      <c r="K12">
+        <v>5.2</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1.75</v>
+      </c>
+      <c r="Q12">
+        <v>2.02</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:60">
+      <c r="A13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13">
+        <v>4.6</v>
+      </c>
+      <c r="G13">
+        <v>5.6</v>
+      </c>
+      <c r="H13">
+        <v>1.84</v>
+      </c>
+      <c r="I13">
+        <v>2.04</v>
+      </c>
+      <c r="J13">
+        <v>3.3</v>
+      </c>
+      <c r="K13">
+        <v>3.8</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1.66</v>
+      </c>
+      <c r="Q13">
+        <v>2.22</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="104">
   <si>
     <t>League</t>
   </si>
@@ -202,6 +202,9 @@
     <t>Bulgarian A League</t>
   </si>
   <si>
+    <t>Romanian Liga II</t>
+  </si>
+  <si>
     <t>Finnish Veikkausliiga</t>
   </si>
   <si>
@@ -214,6 +217,9 @@
     <t>Egyptian Premier</t>
   </si>
   <si>
+    <t>Swedish Superettan</t>
+  </si>
+  <si>
     <t>2026-05-05</t>
   </si>
   <si>
@@ -247,6 +253,9 @@
     <t>Beroe Stara Za</t>
   </si>
   <si>
+    <t>Bihor Oradea</t>
+  </si>
+  <si>
     <t>Gnistan</t>
   </si>
   <si>
@@ -271,6 +280,9 @@
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
+    <t>Falkenbergs</t>
+  </si>
+  <si>
     <t>Tianjin Jinmen Tiger FC</t>
   </si>
   <si>
@@ -283,6 +295,9 @@
     <t>Montana</t>
   </si>
   <si>
+    <t>Chindia Targoviste</t>
+  </si>
+  <si>
     <t>FC Inter</t>
   </si>
   <si>
@@ -307,7 +322,10 @@
     <t>Pyramids</t>
   </si>
   <si>
-    <t>2026-05-03 10:11:23</t>
+    <t>Norrkoping</t>
+  </si>
+  <si>
+    <t>2026-05-03 12:38:03</t>
   </si>
 </sst>
 </file>
@@ -665,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH13"/>
+  <dimension ref="A1:BH15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:60">
@@ -855,19 +873,19 @@
         <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F2">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G2">
         <v>2.4</v>
@@ -885,7 +903,7 @@
         <v>3.7</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M2">
         <v>1.08</v>
@@ -930,7 +948,7 @@
         <v>26</v>
       </c>
       <c r="AA2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB2">
         <v>11</v>
@@ -939,7 +957,7 @@
         <v>8</v>
       </c>
       <c r="AD2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE2">
         <v>48</v>
@@ -996,7 +1014,7 @@
         <v>13</v>
       </c>
       <c r="AW2">
-        <v>38</v>
+        <v>7.8</v>
       </c>
       <c r="AX2">
         <v>12</v>
@@ -1008,28 +1026,28 @@
         <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2">
+        <v>7.2</v>
+      </c>
+      <c r="BC2">
         <v>7</v>
       </c>
-      <c r="BC2">
-        <v>6.8</v>
-      </c>
       <c r="BD2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG2">
         <v>7.8</v>
       </c>
       <c r="BH2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -1037,25 +1055,25 @@
         <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F3">
         <v>2.78</v>
       </c>
       <c r="G3">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H3">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I3">
         <v>2.56</v>
@@ -1073,25 +1091,25 @@
         <v>1.03</v>
       </c>
       <c r="N3">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="O3">
         <v>1.15</v>
       </c>
       <c r="P3">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q3">
         <v>1.46</v>
       </c>
       <c r="R3">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="S3">
         <v>2.14</v>
       </c>
       <c r="T3">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="U3">
         <v>2.84</v>
@@ -1106,7 +1124,7 @@
         <v>32</v>
       </c>
       <c r="Y3">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="Z3">
         <v>22</v>
@@ -1121,7 +1139,7 @@
         <v>11</v>
       </c>
       <c r="AD3">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE3">
         <v>23</v>
@@ -1130,10 +1148,10 @@
         <v>25</v>
       </c>
       <c r="AG3">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH3">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AI3">
         <v>27</v>
@@ -1151,58 +1169,58 @@
         <v>46</v>
       </c>
       <c r="AN3">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AO3">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AP3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR3">
+        <v>7.8</v>
+      </c>
+      <c r="AS3">
+        <v>9</v>
+      </c>
+      <c r="AT3">
         <v>7.6</v>
       </c>
-      <c r="AS3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT3">
-        <v>7.4</v>
-      </c>
       <c r="AU3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AV3">
         <v>6.2</v>
       </c>
       <c r="AW3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY3">
         <v>6.4</v>
       </c>
       <c r="AZ3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA3">
+        <v>8.4</v>
+      </c>
+      <c r="BB3">
+        <v>9.4</v>
+      </c>
+      <c r="BC3">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB3">
-        <v>6.6</v>
-      </c>
-      <c r="BC3">
-        <v>8</v>
-      </c>
       <c r="BD3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF3">
         <v>10.5</v>
@@ -1211,7 +1229,7 @@
         <v>8.4</v>
       </c>
       <c r="BH3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -1219,37 +1237,37 @@
         <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="G4">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H4">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="I4">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="J4">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K4">
         <v>4.4</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M4">
         <v>1.06</v>
@@ -1267,7 +1285,7 @@
         <v>1.8</v>
       </c>
       <c r="R4">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S4">
         <v>3.1</v>
@@ -1276,16 +1294,16 @@
         <v>1.83</v>
       </c>
       <c r="U4">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V4">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="W4">
         <v>1.14</v>
       </c>
       <c r="X4">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Y4">
         <v>8.800000000000001</v>
@@ -1297,25 +1315,25 @@
         <v>18</v>
       </c>
       <c r="AB4">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AC4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD4">
         <v>10.5</v>
       </c>
       <c r="AE4">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AF4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG4">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI4">
         <v>36</v>
@@ -1339,7 +1357,7 @@
         <v>10.5</v>
       </c>
       <c r="AP4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AQ4">
         <v>7.4</v>
@@ -1351,49 +1369,49 @@
         <v>13</v>
       </c>
       <c r="AT4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU4">
         <v>4.3</v>
       </c>
       <c r="AV4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AW4">
         <v>14</v>
       </c>
       <c r="AX4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ4">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BA4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB4">
+        <v>7.6</v>
+      </c>
+      <c r="BC4">
         <v>7.4</v>
       </c>
-      <c r="BC4">
-        <v>7.2</v>
-      </c>
       <c r="BD4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG4">
         <v>7.6</v>
       </c>
       <c r="BH4" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:60">
@@ -1401,16 +1419,16 @@
         <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F5">
         <v>2.04</v>
@@ -1431,151 +1449,151 @@
         <v>3.5</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P5">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q5">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BG5">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BH5" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:60">
@@ -1583,181 +1601,181 @@
         <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F6">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="G6">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="H6">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="I6">
-        <v>1.76</v>
+        <v>1000</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="K6">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P6">
-        <v>2.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q6">
-        <v>1.74</v>
+        <v>1.31</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:60">
@@ -1765,34 +1783,34 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F7">
-        <v>1.43</v>
+        <v>5.3</v>
       </c>
       <c r="G7">
-        <v>1.54</v>
+        <v>6.2</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>1.65</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>1.75</v>
       </c>
       <c r="J7">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1807,10 +1825,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>2.52</v>
+        <v>2.06</v>
       </c>
       <c r="Q7">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -1939,42 +1957,42 @@
         <v>0</v>
       </c>
       <c r="BH7" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:60">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F8">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="G8">
-        <v>2.78</v>
+        <v>1.54</v>
       </c>
       <c r="H8">
-        <v>2.58</v>
+        <v>6.8</v>
       </c>
       <c r="I8">
-        <v>3.15</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="K8">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1989,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="Q8">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2121,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="BH8" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:60">
@@ -2129,34 +2147,34 @@
         <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F9">
-        <v>1.31</v>
+        <v>2.5</v>
       </c>
       <c r="G9">
-        <v>1.55</v>
+        <v>2.78</v>
       </c>
       <c r="H9">
-        <v>2.9</v>
+        <v>2.58</v>
       </c>
       <c r="I9">
-        <v>70</v>
+        <v>3.15</v>
       </c>
       <c r="J9">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2171,10 +2189,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q9">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2303,42 +2321,42 @@
         <v>0</v>
       </c>
       <c r="BH9" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:60">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F10">
-        <v>2.02</v>
+        <v>1.36</v>
       </c>
       <c r="G10">
-        <v>2.4</v>
+        <v>1.46</v>
       </c>
       <c r="H10">
-        <v>3.65</v>
+        <v>1.19</v>
       </c>
       <c r="I10">
-        <v>4.8</v>
+        <v>24</v>
       </c>
       <c r="J10">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="K10">
-        <v>3.85</v>
+        <v>85</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2353,10 +2371,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="Q10">
-        <v>1.99</v>
+        <v>1.51</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2485,39 +2503,39 @@
         <v>0</v>
       </c>
       <c r="BH10" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:60">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F11">
-        <v>4.5</v>
+        <v>2.02</v>
       </c>
       <c r="G11">
-        <v>9.6</v>
+        <v>2.28</v>
       </c>
       <c r="H11">
-        <v>1.64</v>
+        <v>3.65</v>
       </c>
       <c r="I11">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="J11">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K11">
         <v>3.85</v>
@@ -2535,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="Q11">
-        <v>2.44</v>
+        <v>1.99</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2667,42 +2685,42 @@
         <v>0</v>
       </c>
       <c r="BH11" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:60">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F12">
-        <v>1.37</v>
+        <v>4.5</v>
       </c>
       <c r="G12">
-        <v>1.45</v>
+        <v>9.6</v>
       </c>
       <c r="H12">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="I12">
-        <v>13.5</v>
+        <v>1.8</v>
       </c>
       <c r="J12">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="K12">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -2717,10 +2735,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="Q12">
-        <v>2.02</v>
+        <v>2.44</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -2849,189 +2867,553 @@
         <v>0</v>
       </c>
       <c r="BH12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:60">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13">
+        <v>1.37</v>
+      </c>
+      <c r="G13">
+        <v>1.45</v>
+      </c>
+      <c r="H13">
+        <v>1.24</v>
+      </c>
+      <c r="I13">
+        <v>13.5</v>
+      </c>
+      <c r="J13">
+        <v>4.4</v>
+      </c>
+      <c r="K13">
+        <v>5.2</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1.75</v>
+      </c>
+      <c r="Q13">
+        <v>2.02</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:60">
+      <c r="A14" t="s">
         <v>66</v>
       </c>
-      <c r="C13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" t="s">
-        <v>96</v>
-      </c>
-      <c r="F13">
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" t="s">
+        <v>101</v>
+      </c>
+      <c r="F14">
         <v>4.6</v>
       </c>
-      <c r="G13">
-        <v>5.6</v>
-      </c>
-      <c r="H13">
-        <v>1.84</v>
-      </c>
-      <c r="I13">
+      <c r="G14">
+        <v>6</v>
+      </c>
+      <c r="H14">
+        <v>1.85</v>
+      </c>
+      <c r="I14">
         <v>2.04</v>
       </c>
-      <c r="J13">
-        <v>3.3</v>
-      </c>
-      <c r="K13">
+      <c r="J14">
+        <v>3.25</v>
+      </c>
+      <c r="K14">
         <v>3.8</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
         <v>1.66</v>
       </c>
-      <c r="Q13">
+      <c r="Q14">
         <v>2.22</v>
       </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>0</v>
-      </c>
-      <c r="AH13">
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13">
-        <v>0</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
-      </c>
-      <c r="AW13">
-        <v>0</v>
-      </c>
-      <c r="AX13">
-        <v>0</v>
-      </c>
-      <c r="AY13">
-        <v>0</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>0</v>
-      </c>
-      <c r="BC13">
-        <v>0</v>
-      </c>
-      <c r="BD13">
-        <v>0</v>
-      </c>
-      <c r="BE13">
-        <v>0</v>
-      </c>
-      <c r="BF13">
-        <v>0</v>
-      </c>
-      <c r="BG13">
-        <v>0</v>
-      </c>
-      <c r="BH13" t="s">
-        <v>97</v>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:60">
+      <c r="A15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" t="s">
+        <v>102</v>
+      </c>
+      <c r="F15">
+        <v>2.56</v>
+      </c>
+      <c r="G15">
+        <v>3.05</v>
+      </c>
+      <c r="H15">
+        <v>2.6</v>
+      </c>
+      <c r="I15">
+        <v>3.1</v>
+      </c>
+      <c r="J15">
+        <v>3.35</v>
+      </c>
+      <c r="K15">
+        <v>4.5</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>2.26</v>
+      </c>
+      <c r="Q15">
+        <v>1.6</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -325,7 +325,7 @@
     <t>Norrkoping</t>
   </si>
   <si>
-    <t>2026-05-03 12:38:03</t>
+    <t>2026-05-03 14:57:17</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1023,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>15.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA2">
         <v>8.199999999999999</v>
@@ -1073,7 +1073,7 @@
         <v>2.96</v>
       </c>
       <c r="H3">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I3">
         <v>2.56</v>
@@ -1082,7 +1082,7 @@
         <v>4</v>
       </c>
       <c r="K3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1220,13 +1220,13 @@
         <v>8.6</v>
       </c>
       <c r="BE3">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BF3">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG3">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH3" t="s">
         <v>103</v>
@@ -1249,91 +1249,91 @@
         <v>91</v>
       </c>
       <c r="F4">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H4">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="I4">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="J4">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K4">
+        <v>4.7</v>
+      </c>
+      <c r="L4">
+        <v>1.3</v>
+      </c>
+      <c r="M4">
+        <v>1.05</v>
+      </c>
+      <c r="N4">
         <v>4.4</v>
       </c>
-      <c r="L4">
-        <v>1.36</v>
-      </c>
-      <c r="M4">
-        <v>1.06</v>
-      </c>
-      <c r="N4">
-        <v>4</v>
-      </c>
       <c r="O4">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P4">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="Q4">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="R4">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S4">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="T4">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U4">
         <v>1.98</v>
       </c>
       <c r="V4">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="W4">
         <v>1.14</v>
       </c>
       <c r="X4">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Y4">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Z4">
         <v>10.5</v>
       </c>
       <c r="AA4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AB4">
         <v>26</v>
       </c>
       <c r="AC4">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AD4">
         <v>10.5</v>
       </c>
       <c r="AE4">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AF4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AG4">
         <v>29</v>
       </c>
       <c r="AH4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI4">
         <v>36</v>
@@ -1342,58 +1342,58 @@
         <v>230</v>
       </c>
       <c r="AK4">
+        <v>110</v>
+      </c>
+      <c r="AL4">
+        <v>100</v>
+      </c>
+      <c r="AM4">
         <v>120</v>
       </c>
-      <c r="AL4">
-        <v>110</v>
-      </c>
-      <c r="AM4">
+      <c r="AN4">
         <v>130</v>
       </c>
-      <c r="AN4">
-        <v>140</v>
-      </c>
       <c r="AO4">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AP4">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="AQ4">
         <v>7.4</v>
       </c>
       <c r="AR4">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT4">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="AU4">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AV4">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="AW4">
-        <v>14</v>
+        <v>5.5</v>
       </c>
       <c r="AX4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY4">
         <v>6.2</v>
       </c>
       <c r="AZ4">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BA4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC4">
         <v>7.4</v>
@@ -1402,13 +1402,13 @@
         <v>7.4</v>
       </c>
       <c r="BE4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG4">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH4" t="s">
         <v>103</v>
@@ -1434,7 +1434,7 @@
         <v>2.04</v>
       </c>
       <c r="G5">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H5">
         <v>4.1</v>
@@ -1449,67 +1449,67 @@
         <v>3.5</v>
       </c>
       <c r="L5">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N5">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="O5">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P5">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q5">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R5">
         <v>1.22</v>
       </c>
       <c r="S5">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="T5">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="U5">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="V5">
         <v>1.23</v>
       </c>
       <c r="W5">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="X5">
         <v>12</v>
       </c>
       <c r="Y5">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Z5">
         <v>38</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5">
         <v>9</v>
       </c>
       <c r="AD5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF5">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AG5">
         <v>13.5</v>
@@ -1527,70 +1527,70 @@
         <v>34</v>
       </c>
       <c r="AL5">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM5">
         <v>200</v>
       </c>
       <c r="AN5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO5">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP5">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ5">
-        <v>3.1</v>
+        <v>10.5</v>
       </c>
       <c r="AR5">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AS5">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AT5">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU5">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>3.25</v>
+        <v>16</v>
       </c>
       <c r="AW5">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AX5">
-        <v>3.1</v>
+        <v>10.5</v>
       </c>
       <c r="AY5">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BA5">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BB5">
-        <v>20</v>
+        <v>3.85</v>
       </c>
       <c r="BC5">
-        <v>19.5</v>
+        <v>3.85</v>
       </c>
       <c r="BD5">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BE5">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BF5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG5">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="s">
         <v>103</v>
@@ -1625,7 +1625,7 @@
         <v>1000</v>
       </c>
       <c r="J6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -1637,13 +1637,13 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O6">
         <v>1.31</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q6">
         <v>1.31</v>
@@ -1795,166 +1795,166 @@
         <v>94</v>
       </c>
       <c r="F7">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="H7">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="I7">
+        <v>1.81</v>
+      </c>
+      <c r="J7">
+        <v>3.95</v>
+      </c>
+      <c r="K7">
+        <v>4.3</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.06</v>
+      </c>
+      <c r="N7">
+        <v>4.1</v>
+      </c>
+      <c r="O7">
+        <v>1.27</v>
+      </c>
+      <c r="P7">
+        <v>2.04</v>
+      </c>
+      <c r="Q7">
         <v>1.75</v>
       </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>4.5</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
+      <c r="R7">
+        <v>1.41</v>
+      </c>
+      <c r="S7">
+        <v>2.92</v>
+      </c>
+      <c r="T7">
+        <v>1.73</v>
+      </c>
+      <c r="U7">
         <v>2.06</v>
       </c>
-      <c r="Q7">
-        <v>1.76</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
       <c r="V7">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BH7" t="s">
         <v>103</v>
@@ -1977,166 +1977,166 @@
         <v>95</v>
       </c>
       <c r="F8">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="G8">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H8">
         <v>6.8</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
         <v>4.8</v>
       </c>
       <c r="K8">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P8">
         <v>2.52</v>
       </c>
       <c r="Q8">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="s">
         <v>103</v>
@@ -2177,16 +2177,16 @@
         <v>4.2</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P9">
         <v>2.24</v>
@@ -2195,130 +2195,130 @@
         <v>1.64</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BH9" t="s">
         <v>103</v>
@@ -2341,166 +2341,166 @@
         <v>97</v>
       </c>
       <c r="F10">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="G10">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="H10">
-        <v>1.19</v>
+        <v>5.4</v>
       </c>
       <c r="I10">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J10">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K10">
-        <v>85</v>
+        <v>6.6</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="Q10">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="s">
         <v>103</v>
@@ -2526,13 +2526,13 @@
         <v>2.02</v>
       </c>
       <c r="G11">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="H11">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I11">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J11">
         <v>3.25</v>
@@ -2541,16 +2541,16 @@
         <v>3.85</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P11">
         <v>1.79</v>
@@ -2559,130 +2559,130 @@
         <v>1.99</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH11" t="s">
         <v>103</v>
@@ -2705,166 +2705,166 @@
         <v>99</v>
       </c>
       <c r="F12">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="G12">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="H12">
         <v>1.64</v>
       </c>
       <c r="I12">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K12">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P12">
         <v>1.48</v>
       </c>
       <c r="Q12">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BH12" t="s">
         <v>103</v>
@@ -2893,7 +2893,7 @@
         <v>1.45</v>
       </c>
       <c r="H13">
-        <v>1.24</v>
+        <v>5.8</v>
       </c>
       <c r="I13">
         <v>13.5</v>
@@ -2902,19 +2902,19 @@
         <v>4.4</v>
       </c>
       <c r="K13">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P13">
         <v>1.75</v>
@@ -2923,130 +2923,130 @@
         <v>2.02</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BH13" t="s">
         <v>103</v>
@@ -3069,166 +3069,166 @@
         <v>101</v>
       </c>
       <c r="F14">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="H14">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="I14">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="J14">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K14">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P14">
         <v>1.66</v>
       </c>
       <c r="Q14">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH14" t="s">
         <v>103</v>
@@ -3251,13 +3251,13 @@
         <v>102</v>
       </c>
       <c r="F15">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G15">
         <v>3.05</v>
       </c>
       <c r="H15">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I15">
         <v>3.1</v>
@@ -3266,151 +3266,151 @@
         <v>3.35</v>
       </c>
       <c r="K15">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P15">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q15">
         <v>1.6</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="s">
         <v>103</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="122">
   <si>
     <t>League</t>
   </si>
@@ -214,10 +214,25 @@
     <t>Israeli Premier League</t>
   </si>
   <si>
+    <t>Swedish Superettan</t>
+  </si>
+  <si>
     <t>Egyptian Premier</t>
   </si>
   <si>
-    <t>Swedish Superettan</t>
+    <t>Saudi Professional League</t>
+  </si>
+  <si>
+    <t>Scottish League Two</t>
+  </si>
+  <si>
+    <t>Scottish Championship</t>
+  </si>
+  <si>
+    <t>Scottish League One</t>
+  </si>
+  <si>
+    <t>UEFA Champions League</t>
   </si>
   <si>
     <t>2026-05-05</t>
@@ -241,6 +256,15 @@
     <t>14:00:00</t>
   </si>
   <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>15:45:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
@@ -268,6 +292,12 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Falkenbergs</t>
+  </si>
+  <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
     <t>Lokomotiv Sofia</t>
   </si>
   <si>
@@ -277,10 +307,19 @@
     <t>Al Ahly Cairo</t>
   </si>
   <si>
-    <t>Ceramica Cleopatra</t>
-  </si>
-  <si>
-    <t>Falkenbergs</t>
+    <t>Al-Khaleej Saihat</t>
+  </si>
+  <si>
+    <t>Clyde</t>
+  </si>
+  <si>
+    <t>Dunfermline</t>
+  </si>
+  <si>
+    <t>Queen of South</t>
+  </si>
+  <si>
+    <t>Arsenal</t>
   </si>
   <si>
     <t>Tianjin Jinmen Tiger FC</t>
@@ -310,6 +349,12 @@
     <t>Hapoel Petach Tikva</t>
   </si>
   <si>
+    <t>Norrkoping</t>
+  </si>
+  <si>
+    <t>Pyramids</t>
+  </si>
+  <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
@@ -319,13 +364,22 @@
     <t>ENPPI</t>
   </si>
   <si>
-    <t>Pyramids</t>
-  </si>
-  <si>
-    <t>Norrkoping</t>
-  </si>
-  <si>
-    <t>2026-05-03 14:57:17</t>
+    <t>Al-Hilal</t>
+  </si>
+  <si>
+    <t>Spartans</t>
+  </si>
+  <si>
+    <t>Arbroath</t>
+  </si>
+  <si>
+    <t>Stenhousemuir</t>
+  </si>
+  <si>
+    <t>Atletico Madrid</t>
+  </si>
+  <si>
+    <t>2026-05-03 17:12:33</t>
   </si>
 </sst>
 </file>
@@ -683,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH15"/>
+  <dimension ref="A1:BH20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:60">
@@ -873,16 +927,16 @@
         <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="F2">
         <v>2.2</v>
@@ -1023,7 +1077,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="BA2">
         <v>8.199999999999999</v>
@@ -1047,7 +1101,7 @@
         <v>7.8</v>
       </c>
       <c r="BH2" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -1055,19 +1109,19 @@
         <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F3">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="G3">
         <v>2.96</v>
@@ -1082,10 +1136,10 @@
         <v>4</v>
       </c>
       <c r="K3">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M3">
         <v>1.03</v>
@@ -1220,16 +1274,16 @@
         <v>8.6</v>
       </c>
       <c r="BE3">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BF3">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG3">
         <v>5.8</v>
       </c>
       <c r="BH3" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -1237,16 +1291,16 @@
         <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F4">
         <v>7</v>
@@ -1258,7 +1312,7 @@
         <v>1.53</v>
       </c>
       <c r="I4">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="J4">
         <v>4.2</v>
@@ -1267,7 +1321,7 @@
         <v>4.7</v>
       </c>
       <c r="L4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M4">
         <v>1.05</v>
@@ -1276,13 +1330,13 @@
         <v>4.4</v>
       </c>
       <c r="O4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P4">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q4">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="R4">
         <v>1.45</v>
@@ -1360,7 +1414,7 @@
         <v>15</v>
       </c>
       <c r="AQ4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR4">
         <v>7.8</v>
@@ -1411,7 +1465,7 @@
         <v>6.6</v>
       </c>
       <c r="BH4" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:60">
@@ -1419,16 +1473,16 @@
         <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="F5">
         <v>2.04</v>
@@ -1440,7 +1494,7 @@
         <v>4.1</v>
       </c>
       <c r="I5">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J5">
         <v>3.1</v>
@@ -1449,37 +1503,37 @@
         <v>3.5</v>
       </c>
       <c r="L5">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M5">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N5">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O5">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P5">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q5">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R5">
         <v>1.22</v>
       </c>
       <c r="S5">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U5">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V5">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="W5">
         <v>1.82</v>
@@ -1494,10 +1548,10 @@
         <v>38</v>
       </c>
       <c r="AA5">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC5">
         <v>9</v>
@@ -1509,7 +1563,7 @@
         <v>90</v>
       </c>
       <c r="AF5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG5">
         <v>13.5</v>
@@ -1533,19 +1587,19 @@
         <v>200</v>
       </c>
       <c r="AN5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO5">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ5">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AS5">
         <v>4.2</v>
@@ -1557,43 +1611,43 @@
         <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AW5">
         <v>4.1</v>
       </c>
       <c r="AX5">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AY5">
         <v>9.6</v>
       </c>
       <c r="AZ5">
+        <v>19</v>
+      </c>
+      <c r="BA5">
+        <v>4.1</v>
+      </c>
+      <c r="BB5">
+        <v>20</v>
+      </c>
+      <c r="BC5">
         <v>19.5</v>
       </c>
-      <c r="BA5">
-        <v>4.2</v>
-      </c>
-      <c r="BB5">
-        <v>3.85</v>
-      </c>
-      <c r="BC5">
-        <v>3.85</v>
-      </c>
       <c r="BD5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BE5">
         <v>4.2</v>
       </c>
       <c r="BF5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BG5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH5" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:60">
@@ -1601,16 +1655,16 @@
         <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="F6">
         <v>1.04</v>
@@ -1637,22 +1691,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O6">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P6">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q6">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="R6">
         <v>1.15</v>
       </c>
       <c r="S6">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -1775,7 +1829,7 @@
         <v>1.01</v>
       </c>
       <c r="BH6" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:60">
@@ -1783,28 +1837,28 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="G7">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H7">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="I7">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="J7">
         <v>3.95</v>
@@ -1825,82 +1879,82 @@
         <v>1.27</v>
       </c>
       <c r="P7">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q7">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="R7">
         <v>1.41</v>
       </c>
       <c r="S7">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="T7">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U7">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V7">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="W7">
         <v>1.22</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP7">
         <v>15</v>
@@ -1927,7 +1981,7 @@
         <v>15</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY7">
         <v>17.5</v>
@@ -1936,28 +1990,28 @@
         <v>16.5</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG7">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH7" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:60">
@@ -1965,16 +2019,16 @@
         <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="F8">
         <v>1.42</v>
@@ -2139,7 +2193,7 @@
         <v>1.01</v>
       </c>
       <c r="BH8" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:60">
@@ -2147,16 +2201,16 @@
         <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="F9">
         <v>2.5</v>
@@ -2207,7 +2261,7 @@
         <v>2.26</v>
       </c>
       <c r="V9">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W9">
         <v>1.56</v>
@@ -2216,7 +2270,7 @@
         <v>24</v>
       </c>
       <c r="Y9">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Z9">
         <v>24</v>
@@ -2225,7 +2279,7 @@
         <v>46</v>
       </c>
       <c r="AB9">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AC9">
         <v>10.5</v>
@@ -2243,7 +2297,7 @@
         <v>14.5</v>
       </c>
       <c r="AH9">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AI9">
         <v>40</v>
@@ -2321,7 +2375,7 @@
         <v>13.5</v>
       </c>
       <c r="BH9" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:60">
@@ -2329,16 +2383,16 @@
         <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F10">
         <v>1.4</v>
@@ -2347,10 +2401,10 @@
         <v>1.52</v>
       </c>
       <c r="H10">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="I10">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="J10">
         <v>4.3</v>
@@ -2359,13 +2413,13 @@
         <v>6.6</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M10">
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>2.36</v>
+        <v>4.6</v>
       </c>
       <c r="O10">
         <v>1.18</v>
@@ -2374,31 +2428,31 @@
         <v>2.36</v>
       </c>
       <c r="Q10">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="R10">
         <v>1.49</v>
       </c>
       <c r="S10">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="T10">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U10">
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W10">
         <v>2.94</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Z10">
         <v>1000</v>
@@ -2407,37 +2461,37 @@
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE10">
         <v>1000</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI10">
         <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM10">
         <v>1000</v>
@@ -2449,10 +2503,10 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
         <v>1.03</v>
@@ -2461,25 +2515,25 @@
         <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU10">
         <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
         <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
         <v>1.03</v>
@@ -2491,7 +2545,7 @@
         <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
         <v>1.03</v>
@@ -2503,735 +2557,735 @@
         <v>1.01</v>
       </c>
       <c r="BH10" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:60">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="F11">
-        <v>2.02</v>
+        <v>2.58</v>
       </c>
       <c r="G11">
+        <v>2.96</v>
+      </c>
+      <c r="H11">
+        <v>2.62</v>
+      </c>
+      <c r="I11">
+        <v>2.9</v>
+      </c>
+      <c r="J11">
+        <v>3.35</v>
+      </c>
+      <c r="K11">
+        <v>4.4</v>
+      </c>
+      <c r="L11">
+        <v>1.29</v>
+      </c>
+      <c r="M11">
+        <v>1.05</v>
+      </c>
+      <c r="N11">
+        <v>4</v>
+      </c>
+      <c r="O11">
+        <v>1.24</v>
+      </c>
+      <c r="P11">
+        <v>2.22</v>
+      </c>
+      <c r="Q11">
+        <v>1.61</v>
+      </c>
+      <c r="R11">
+        <v>1.49</v>
+      </c>
+      <c r="S11">
+        <v>2.56</v>
+      </c>
+      <c r="T11">
+        <v>1.61</v>
+      </c>
+      <c r="U11">
         <v>2.4</v>
       </c>
-      <c r="H11">
-        <v>3.6</v>
-      </c>
-      <c r="I11">
-        <v>4.8</v>
-      </c>
-      <c r="J11">
-        <v>3.25</v>
-      </c>
-      <c r="K11">
-        <v>3.85</v>
-      </c>
-      <c r="L11">
-        <v>1.36</v>
-      </c>
-      <c r="M11">
-        <v>1.06</v>
-      </c>
-      <c r="N11">
-        <v>3</v>
-      </c>
-      <c r="O11">
-        <v>1.34</v>
-      </c>
-      <c r="P11">
-        <v>1.79</v>
-      </c>
-      <c r="Q11">
-        <v>1.99</v>
-      </c>
-      <c r="R11">
-        <v>1.3</v>
-      </c>
-      <c r="S11">
-        <v>3.2</v>
-      </c>
-      <c r="T11">
-        <v>1.68</v>
-      </c>
-      <c r="U11">
-        <v>1.86</v>
-      </c>
       <c r="V11">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="W11">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="X11">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Y11">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Z11">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AA11">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AB11">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC11">
+        <v>10.5</v>
+      </c>
+      <c r="AD11">
+        <v>970</v>
+      </c>
+      <c r="AE11">
+        <v>32</v>
+      </c>
+      <c r="AF11">
+        <v>23</v>
+      </c>
+      <c r="AG11">
+        <v>970</v>
+      </c>
+      <c r="AH11">
+        <v>970</v>
+      </c>
+      <c r="AI11">
+        <v>40</v>
+      </c>
+      <c r="AJ11">
+        <v>44</v>
+      </c>
+      <c r="AK11">
+        <v>32</v>
+      </c>
+      <c r="AL11">
+        <v>48</v>
+      </c>
+      <c r="AM11">
+        <v>80</v>
+      </c>
+      <c r="AN11">
+        <v>21</v>
+      </c>
+      <c r="AO11">
+        <v>22</v>
+      </c>
+      <c r="AP11">
+        <v>4.3</v>
+      </c>
+      <c r="AQ11">
+        <v>10.5</v>
+      </c>
+      <c r="AR11">
+        <v>4.3</v>
+      </c>
+      <c r="AS11">
+        <v>4.7</v>
+      </c>
+      <c r="AT11">
+        <v>10.5</v>
+      </c>
+      <c r="AU11">
+        <v>7</v>
+      </c>
+      <c r="AV11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW11">
+        <v>4.5</v>
+      </c>
+      <c r="AX11">
+        <v>4.3</v>
+      </c>
+      <c r="AY11">
         <v>9.6</v>
       </c>
-      <c r="AD11">
-        <v>20</v>
-      </c>
-      <c r="AE11">
-        <v>65</v>
-      </c>
-      <c r="AF11">
-        <v>16</v>
-      </c>
-      <c r="AG11">
-        <v>13</v>
-      </c>
-      <c r="AH11">
-        <v>23</v>
-      </c>
-      <c r="AI11">
-        <v>75</v>
-      </c>
-      <c r="AJ11">
-        <v>34</v>
-      </c>
-      <c r="AK11">
-        <v>29</v>
-      </c>
-      <c r="AL11">
-        <v>50</v>
-      </c>
-      <c r="AM11">
-        <v>130</v>
-      </c>
-      <c r="AN11">
-        <v>22</v>
-      </c>
-      <c r="AO11">
-        <v>70</v>
-      </c>
-      <c r="AP11">
-        <v>3.4</v>
-      </c>
-      <c r="AQ11">
-        <v>3.4</v>
-      </c>
-      <c r="AR11">
-        <v>3.85</v>
-      </c>
-      <c r="AS11">
-        <v>4.1</v>
-      </c>
-      <c r="AT11">
-        <v>3.1</v>
-      </c>
-      <c r="AU11">
-        <v>2.98</v>
-      </c>
-      <c r="AV11">
-        <v>3.55</v>
-      </c>
-      <c r="AW11">
-        <v>4</v>
-      </c>
-      <c r="AX11">
-        <v>3.4</v>
-      </c>
-      <c r="AY11">
-        <v>3.2</v>
-      </c>
       <c r="AZ11">
-        <v>3.6</v>
+        <v>11.5</v>
       </c>
       <c r="BA11">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BB11">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="BC11">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="BD11">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BE11">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF11">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BG11">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BH11" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:60">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="F12">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="H12">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="I12">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="J12">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K12">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="M12">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N12">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="O12">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="P12">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="Q12">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="R12">
+        <v>1.25</v>
+      </c>
+      <c r="S12">
+        <v>3.5</v>
+      </c>
+      <c r="T12">
+        <v>2.02</v>
+      </c>
+      <c r="U12">
+        <v>1.78</v>
+      </c>
+      <c r="V12">
+        <v>2.12</v>
+      </c>
+      <c r="W12">
         <v>1.17</v>
       </c>
-      <c r="S12">
-        <v>5.5</v>
-      </c>
-      <c r="T12">
-        <v>2.24</v>
-      </c>
-      <c r="U12">
-        <v>1.47</v>
-      </c>
-      <c r="V12">
-        <v>2.26</v>
-      </c>
-      <c r="W12">
-        <v>1.13</v>
-      </c>
       <c r="X12">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="Y12">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="Z12">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AA12">
         <v>22</v>
       </c>
       <c r="AB12">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AD12">
         <v>12</v>
       </c>
       <c r="AE12">
+        <v>25</v>
+      </c>
+      <c r="AF12">
+        <v>55</v>
+      </c>
+      <c r="AG12">
         <v>27</v>
       </c>
-      <c r="AF12">
-        <v>75</v>
-      </c>
-      <c r="AG12">
-        <v>34</v>
-      </c>
       <c r="AH12">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AI12">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AO12">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AP12">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="AQ12">
+        <v>3.15</v>
+      </c>
+      <c r="AR12">
+        <v>3.6</v>
+      </c>
+      <c r="AS12">
+        <v>4.2</v>
+      </c>
+      <c r="AT12">
+        <v>4.1</v>
+      </c>
+      <c r="AU12">
+        <v>3.35</v>
+      </c>
+      <c r="AV12">
+        <v>3.65</v>
+      </c>
+      <c r="AW12">
         <v>4.3</v>
       </c>
-      <c r="AR12">
-        <v>6.2</v>
-      </c>
-      <c r="AS12">
-        <v>4.7</v>
-      </c>
-      <c r="AT12">
-        <v>4.6</v>
-      </c>
-      <c r="AU12">
-        <v>6.4</v>
-      </c>
-      <c r="AV12">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW12">
-        <v>4.9</v>
-      </c>
       <c r="AX12">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AY12">
+        <v>4.4</v>
+      </c>
+      <c r="AZ12">
+        <v>4.4</v>
+      </c>
+      <c r="BA12">
+        <v>4.8</v>
+      </c>
+      <c r="BB12">
         <v>5.1</v>
       </c>
-      <c r="AZ12">
-        <v>5.2</v>
-      </c>
-      <c r="BA12">
-        <v>5.6</v>
-      </c>
-      <c r="BB12">
-        <v>2.32</v>
-      </c>
       <c r="BC12">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="BD12">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="BE12">
-        <v>2.32</v>
+        <v>5.1</v>
       </c>
       <c r="BF12">
-        <v>2.32</v>
+        <v>5.1</v>
       </c>
       <c r="BG12">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BH12" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:60">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="F13">
-        <v>1.37</v>
+        <v>2.02</v>
       </c>
       <c r="G13">
-        <v>1.45</v>
+        <v>2.4</v>
       </c>
       <c r="H13">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="I13">
-        <v>13.5</v>
+        <v>4.3</v>
       </c>
       <c r="J13">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="K13">
-        <v>5.3</v>
+        <v>3.85</v>
       </c>
       <c r="L13">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="M13">
         <v>1.07</v>
       </c>
       <c r="N13">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O13">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P13">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="Q13">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="R13">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S13">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T13">
-        <v>2.44</v>
+        <v>1.8</v>
       </c>
       <c r="U13">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="V13">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="W13">
+        <v>1.71</v>
+      </c>
+      <c r="X13">
+        <v>16</v>
+      </c>
+      <c r="Y13">
+        <v>16.5</v>
+      </c>
+      <c r="Z13">
+        <v>36</v>
+      </c>
+      <c r="AA13">
+        <v>100</v>
+      </c>
+      <c r="AB13">
+        <v>11</v>
+      </c>
+      <c r="AC13">
+        <v>9.6</v>
+      </c>
+      <c r="AD13">
+        <v>20</v>
+      </c>
+      <c r="AE13">
+        <v>65</v>
+      </c>
+      <c r="AF13">
+        <v>16</v>
+      </c>
+      <c r="AG13">
+        <v>13</v>
+      </c>
+      <c r="AH13">
+        <v>23</v>
+      </c>
+      <c r="AI13">
+        <v>75</v>
+      </c>
+      <c r="AJ13">
+        <v>34</v>
+      </c>
+      <c r="AK13">
+        <v>29</v>
+      </c>
+      <c r="AL13">
+        <v>50</v>
+      </c>
+      <c r="AM13">
+        <v>130</v>
+      </c>
+      <c r="AN13">
+        <v>22</v>
+      </c>
+      <c r="AO13">
+        <v>70</v>
+      </c>
+      <c r="AP13">
+        <v>3.4</v>
+      </c>
+      <c r="AQ13">
+        <v>3.4</v>
+      </c>
+      <c r="AR13">
+        <v>3.85</v>
+      </c>
+      <c r="AS13">
+        <v>4.1</v>
+      </c>
+      <c r="AT13">
+        <v>3.1</v>
+      </c>
+      <c r="AU13">
+        <v>2.98</v>
+      </c>
+      <c r="AV13">
+        <v>3.55</v>
+      </c>
+      <c r="AW13">
+        <v>4</v>
+      </c>
+      <c r="AX13">
+        <v>3.4</v>
+      </c>
+      <c r="AY13">
         <v>3.2</v>
       </c>
-      <c r="X13">
-        <v>13.5</v>
-      </c>
-      <c r="Y13">
-        <v>29</v>
-      </c>
-      <c r="Z13">
-        <v>140</v>
-      </c>
-      <c r="AA13">
-        <v>1000</v>
-      </c>
-      <c r="AB13">
-        <v>6.4</v>
-      </c>
-      <c r="AC13">
-        <v>12</v>
-      </c>
-      <c r="AD13">
-        <v>50</v>
-      </c>
-      <c r="AE13">
-        <v>350</v>
-      </c>
-      <c r="AF13">
-        <v>7.2</v>
-      </c>
-      <c r="AG13">
-        <v>11.5</v>
-      </c>
-      <c r="AH13">
-        <v>40</v>
-      </c>
-      <c r="AI13">
-        <v>290</v>
-      </c>
-      <c r="AJ13">
-        <v>12</v>
-      </c>
-      <c r="AK13">
-        <v>19</v>
-      </c>
-      <c r="AL13">
-        <v>70</v>
-      </c>
-      <c r="AM13">
-        <v>370</v>
-      </c>
-      <c r="AN13">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO13">
-        <v>1000</v>
-      </c>
-      <c r="AP13">
-        <v>5.5</v>
-      </c>
-      <c r="AQ13">
-        <v>7</v>
-      </c>
-      <c r="AR13">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS13">
-        <v>9.4</v>
-      </c>
-      <c r="AT13">
+      <c r="AZ13">
+        <v>3.6</v>
+      </c>
+      <c r="BA13">
+        <v>4</v>
+      </c>
+      <c r="BB13">
         <v>3.8</v>
       </c>
-      <c r="AU13">
-        <v>5.2</v>
-      </c>
-      <c r="AV13">
-        <v>7.8</v>
-      </c>
-      <c r="AW13">
-        <v>9</v>
-      </c>
-      <c r="AX13">
+      <c r="BC13">
+        <v>3.75</v>
+      </c>
+      <c r="BD13">
+        <v>3.95</v>
+      </c>
+      <c r="BE13">
+        <v>4.1</v>
+      </c>
+      <c r="BF13">
+        <v>3.6</v>
+      </c>
+      <c r="BG13">
         <v>4</v>
       </c>
-      <c r="AY13">
-        <v>5.1</v>
-      </c>
-      <c r="AZ13">
-        <v>7.6</v>
-      </c>
-      <c r="BA13">
-        <v>9</v>
-      </c>
-      <c r="BB13">
-        <v>5.2</v>
-      </c>
-      <c r="BC13">
-        <v>6.2</v>
-      </c>
-      <c r="BD13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE13">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF13">
-        <v>4.6</v>
-      </c>
-      <c r="BG13">
-        <v>9.4</v>
-      </c>
       <c r="BH13" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:60">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G14">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="H14">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="I14">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="J14">
         <v>3.5</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L14">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N14">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="O14">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="P14">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="Q14">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="R14">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="S14">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="T14">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="U14">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="V14">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="W14">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z14">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AA14">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AB14">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AC14">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD14">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AE14">
         <v>25</v>
       </c>
       <c r="AF14">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AG14">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AH14">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AI14">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AJ14">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AP14">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AQ14">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="AR14">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AS14">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AT14">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AU14">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="AV14">
-        <v>3.65</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW14">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AX14">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AY14">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AZ14">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BA14">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BB14">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="BC14">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="BD14">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="BE14">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="BF14">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="BG14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BH14" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:60">
@@ -3239,181 +3293,1091 @@
         <v>67</v>
       </c>
       <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15">
+        <v>1.37</v>
+      </c>
+      <c r="G15">
+        <v>1.45</v>
+      </c>
+      <c r="H15">
+        <v>6.4</v>
+      </c>
+      <c r="I15">
+        <v>13.5</v>
+      </c>
+      <c r="J15">
+        <v>4.4</v>
+      </c>
+      <c r="K15">
+        <v>5.3</v>
+      </c>
+      <c r="L15">
+        <v>1.38</v>
+      </c>
+      <c r="M15">
+        <v>1.08</v>
+      </c>
+      <c r="N15">
+        <v>3.15</v>
+      </c>
+      <c r="O15">
+        <v>1.36</v>
+      </c>
+      <c r="P15">
+        <v>1.75</v>
+      </c>
+      <c r="Q15">
+        <v>2.02</v>
+      </c>
+      <c r="R15">
+        <v>1.28</v>
+      </c>
+      <c r="S15">
+        <v>3.35</v>
+      </c>
+      <c r="T15">
+        <v>2.44</v>
+      </c>
+      <c r="U15">
+        <v>1.56</v>
+      </c>
+      <c r="V15">
+        <v>1.08</v>
+      </c>
+      <c r="W15">
+        <v>3.2</v>
+      </c>
+      <c r="X15">
+        <v>13.5</v>
+      </c>
+      <c r="Y15">
+        <v>29</v>
+      </c>
+      <c r="Z15">
+        <v>140</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>6.4</v>
+      </c>
+      <c r="AC15">
+        <v>12</v>
+      </c>
+      <c r="AD15">
+        <v>50</v>
+      </c>
+      <c r="AE15">
+        <v>350</v>
+      </c>
+      <c r="AF15">
+        <v>7.2</v>
+      </c>
+      <c r="AG15">
+        <v>11.5</v>
+      </c>
+      <c r="AH15">
+        <v>40</v>
+      </c>
+      <c r="AI15">
+        <v>290</v>
+      </c>
+      <c r="AJ15">
+        <v>12</v>
+      </c>
+      <c r="AK15">
+        <v>19</v>
+      </c>
+      <c r="AL15">
+        <v>70</v>
+      </c>
+      <c r="AM15">
+        <v>370</v>
+      </c>
+      <c r="AN15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>5.5</v>
+      </c>
+      <c r="AQ15">
+        <v>7</v>
+      </c>
+      <c r="AR15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS15">
+        <v>9.4</v>
+      </c>
+      <c r="AT15">
+        <v>3.8</v>
+      </c>
+      <c r="AU15">
+        <v>5.2</v>
+      </c>
+      <c r="AV15">
+        <v>7.8</v>
+      </c>
+      <c r="AW15">
+        <v>9</v>
+      </c>
+      <c r="AX15">
+        <v>4</v>
+      </c>
+      <c r="AY15">
+        <v>5.1</v>
+      </c>
+      <c r="AZ15">
+        <v>7.6</v>
+      </c>
+      <c r="BA15">
+        <v>9</v>
+      </c>
+      <c r="BB15">
+        <v>5.2</v>
+      </c>
+      <c r="BC15">
+        <v>6.2</v>
+      </c>
+      <c r="BD15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF15">
+        <v>4.6</v>
+      </c>
+      <c r="BG15">
+        <v>9.4</v>
+      </c>
+      <c r="BH15" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:60">
+      <c r="A16" t="s">
         <v>68</v>
       </c>
-      <c r="C15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E15" t="s">
-        <v>102</v>
-      </c>
-      <c r="F15">
-        <v>2.58</v>
-      </c>
-      <c r="G15">
-        <v>3.05</v>
-      </c>
-      <c r="H15">
-        <v>2.62</v>
-      </c>
-      <c r="I15">
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" t="s">
+        <v>116</v>
+      </c>
+      <c r="F16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G16">
+        <v>11.5</v>
+      </c>
+      <c r="H16">
+        <v>1.29</v>
+      </c>
+      <c r="I16">
+        <v>1.37</v>
+      </c>
+      <c r="J16">
+        <v>6.2</v>
+      </c>
+      <c r="K16">
+        <v>7.6</v>
+      </c>
+      <c r="L16">
+        <v>1.16</v>
+      </c>
+      <c r="M16">
+        <v>1.02</v>
+      </c>
+      <c r="N16">
+        <v>7.8</v>
+      </c>
+      <c r="O16">
+        <v>1.12</v>
+      </c>
+      <c r="P16">
+        <v>3.25</v>
+      </c>
+      <c r="Q16">
+        <v>1.35</v>
+      </c>
+      <c r="R16">
+        <v>1.92</v>
+      </c>
+      <c r="S16">
+        <v>1.87</v>
+      </c>
+      <c r="T16">
+        <v>1.68</v>
+      </c>
+      <c r="U16">
+        <v>2.16</v>
+      </c>
+      <c r="V16">
+        <v>3.7</v>
+      </c>
+      <c r="W16">
+        <v>1.09</v>
+      </c>
+      <c r="X16">
+        <v>50</v>
+      </c>
+      <c r="Y16">
+        <v>16</v>
+      </c>
+      <c r="Z16">
+        <v>12.5</v>
+      </c>
+      <c r="AA16">
+        <v>13</v>
+      </c>
+      <c r="AB16">
+        <v>55</v>
+      </c>
+      <c r="AC16">
+        <v>17.5</v>
+      </c>
+      <c r="AD16">
+        <v>12.5</v>
+      </c>
+      <c r="AE16">
+        <v>14</v>
+      </c>
+      <c r="AF16">
+        <v>120</v>
+      </c>
+      <c r="AG16">
+        <v>40</v>
+      </c>
+      <c r="AH16">
+        <v>28</v>
+      </c>
+      <c r="AI16">
+        <v>28</v>
+      </c>
+      <c r="AJ16">
+        <v>320</v>
+      </c>
+      <c r="AK16">
+        <v>140</v>
+      </c>
+      <c r="AL16">
+        <v>90</v>
+      </c>
+      <c r="AM16">
+        <v>100</v>
+      </c>
+      <c r="AN16">
+        <v>110</v>
+      </c>
+      <c r="AO16">
+        <v>3.7</v>
+      </c>
+      <c r="AP16">
+        <v>7.2</v>
+      </c>
+      <c r="AQ16">
+        <v>12.5</v>
+      </c>
+      <c r="AR16">
+        <v>10</v>
+      </c>
+      <c r="AS16">
+        <v>10.5</v>
+      </c>
+      <c r="AT16">
+        <v>7.2</v>
+      </c>
+      <c r="AU16">
+        <v>14</v>
+      </c>
+      <c r="AV16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW16">
+        <v>11</v>
+      </c>
+      <c r="AX16">
+        <v>7.8</v>
+      </c>
+      <c r="AY16">
+        <v>6.8</v>
+      </c>
+      <c r="AZ16">
+        <v>20</v>
+      </c>
+      <c r="BA16">
+        <v>6.4</v>
+      </c>
+      <c r="BB16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC16">
+        <v>7.8</v>
+      </c>
+      <c r="BD16">
+        <v>7.6</v>
+      </c>
+      <c r="BE16">
+        <v>7.6</v>
+      </c>
+      <c r="BF16">
+        <v>7.8</v>
+      </c>
+      <c r="BG16">
         <v>3.1</v>
       </c>
-      <c r="J15">
-        <v>3.35</v>
-      </c>
-      <c r="K15">
-        <v>4.4</v>
-      </c>
-      <c r="L15">
+      <c r="BH16" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:60">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17">
+        <v>1.02</v>
+      </c>
+      <c r="G17">
+        <v>1000</v>
+      </c>
+      <c r="H17">
+        <v>1.02</v>
+      </c>
+      <c r="I17">
+        <v>1000</v>
+      </c>
+      <c r="J17">
+        <v>1.02</v>
+      </c>
+      <c r="K17">
+        <v>950</v>
+      </c>
+      <c r="L17">
         <v>1.01</v>
       </c>
-      <c r="M15">
-        <v>1.04</v>
-      </c>
-      <c r="N15">
-        <v>2.22</v>
-      </c>
-      <c r="O15">
-        <v>1.2</v>
-      </c>
-      <c r="P15">
-        <v>2.22</v>
-      </c>
-      <c r="Q15">
-        <v>1.6</v>
-      </c>
-      <c r="R15">
-        <v>1.42</v>
-      </c>
-      <c r="S15">
-        <v>2.34</v>
-      </c>
-      <c r="T15">
+      <c r="M17">
         <v>1.01</v>
       </c>
-      <c r="U15">
+      <c r="N17">
+        <v>1.09</v>
+      </c>
+      <c r="O17">
+        <v>1.31</v>
+      </c>
+      <c r="P17">
+        <v>1.09</v>
+      </c>
+      <c r="Q17">
+        <v>1.31</v>
+      </c>
+      <c r="R17">
+        <v>1.07</v>
+      </c>
+      <c r="S17">
+        <v>1.33</v>
+      </c>
+      <c r="T17">
         <v>1.01</v>
       </c>
-      <c r="V15">
-        <v>1.51</v>
-      </c>
-      <c r="W15">
-        <v>1.52</v>
-      </c>
-      <c r="X15">
-        <v>1000</v>
-      </c>
-      <c r="Y15">
-        <v>1000</v>
-      </c>
-      <c r="Z15">
-        <v>1000</v>
-      </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>1000</v>
-      </c>
-      <c r="AC15">
-        <v>1000</v>
-      </c>
-      <c r="AD15">
-        <v>1000</v>
-      </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
-      <c r="AF15">
-        <v>1000</v>
-      </c>
-      <c r="AG15">
-        <v>1000</v>
-      </c>
-      <c r="AH15">
-        <v>1000</v>
-      </c>
-      <c r="AI15">
-        <v>1000</v>
-      </c>
-      <c r="AJ15">
-        <v>1000</v>
-      </c>
-      <c r="AK15">
-        <v>1000</v>
-      </c>
-      <c r="AL15">
-        <v>1000</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>1000</v>
-      </c>
-      <c r="AO15">
-        <v>1000</v>
-      </c>
-      <c r="AP15">
-        <v>1.03</v>
-      </c>
-      <c r="AQ15">
-        <v>1.03</v>
-      </c>
-      <c r="AR15">
-        <v>1.03</v>
-      </c>
-      <c r="AS15">
-        <v>1.03</v>
-      </c>
-      <c r="AT15">
-        <v>1.03</v>
-      </c>
-      <c r="AU15">
-        <v>1.03</v>
-      </c>
-      <c r="AV15">
-        <v>1.03</v>
-      </c>
-      <c r="AW15">
-        <v>1.03</v>
-      </c>
-      <c r="AX15">
-        <v>1.03</v>
-      </c>
-      <c r="AY15">
-        <v>1.03</v>
-      </c>
-      <c r="AZ15">
-        <v>1.03</v>
-      </c>
-      <c r="BA15">
-        <v>1.03</v>
-      </c>
-      <c r="BB15">
-        <v>1.03</v>
-      </c>
-      <c r="BC15">
-        <v>1.03</v>
-      </c>
-      <c r="BD15">
-        <v>1.03</v>
-      </c>
-      <c r="BE15">
-        <v>1.03</v>
-      </c>
-      <c r="BF15">
+      <c r="U17">
         <v>1.01</v>
       </c>
-      <c r="BG15">
+      <c r="V17">
         <v>1.01</v>
       </c>
-      <c r="BH15" t="s">
-        <v>103</v>
+      <c r="W17">
+        <v>1.01</v>
+      </c>
+      <c r="X17">
+        <v>1000</v>
+      </c>
+      <c r="Y17">
+        <v>1000</v>
+      </c>
+      <c r="Z17">
+        <v>1000</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>1000</v>
+      </c>
+      <c r="AC17">
+        <v>1000</v>
+      </c>
+      <c r="AD17">
+        <v>1000</v>
+      </c>
+      <c r="AE17">
+        <v>1000</v>
+      </c>
+      <c r="AF17">
+        <v>1000</v>
+      </c>
+      <c r="AG17">
+        <v>1000</v>
+      </c>
+      <c r="AH17">
+        <v>1000</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>1000</v>
+      </c>
+      <c r="AK17">
+        <v>1000</v>
+      </c>
+      <c r="AL17">
+        <v>1000</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>1000</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>1.03</v>
+      </c>
+      <c r="AQ17">
+        <v>1.03</v>
+      </c>
+      <c r="AR17">
+        <v>1.03</v>
+      </c>
+      <c r="AS17">
+        <v>1.03</v>
+      </c>
+      <c r="AT17">
+        <v>1.03</v>
+      </c>
+      <c r="AU17">
+        <v>1.03</v>
+      </c>
+      <c r="AV17">
+        <v>1.03</v>
+      </c>
+      <c r="AW17">
+        <v>1.03</v>
+      </c>
+      <c r="AX17">
+        <v>1.03</v>
+      </c>
+      <c r="AY17">
+        <v>1.03</v>
+      </c>
+      <c r="AZ17">
+        <v>1.03</v>
+      </c>
+      <c r="BA17">
+        <v>1.03</v>
+      </c>
+      <c r="BB17">
+        <v>1.03</v>
+      </c>
+      <c r="BC17">
+        <v>1.03</v>
+      </c>
+      <c r="BD17">
+        <v>1.03</v>
+      </c>
+      <c r="BE17">
+        <v>1.03</v>
+      </c>
+      <c r="BF17">
+        <v>1.01</v>
+      </c>
+      <c r="BG17">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:60">
+      <c r="A18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18">
+        <v>2.26</v>
+      </c>
+      <c r="G18">
+        <v>2.28</v>
+      </c>
+      <c r="H18">
+        <v>3.5</v>
+      </c>
+      <c r="I18">
+        <v>3.55</v>
+      </c>
+      <c r="J18">
+        <v>3.55</v>
+      </c>
+      <c r="K18">
+        <v>3.6</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.07</v>
+      </c>
+      <c r="N18">
+        <v>3.6</v>
+      </c>
+      <c r="O18">
+        <v>1.32</v>
+      </c>
+      <c r="P18">
+        <v>1.9</v>
+      </c>
+      <c r="Q18">
+        <v>2.04</v>
+      </c>
+      <c r="R18">
+        <v>1.35</v>
+      </c>
+      <c r="S18">
+        <v>3.4</v>
+      </c>
+      <c r="T18">
+        <v>1.66</v>
+      </c>
+      <c r="U18">
+        <v>2.14</v>
+      </c>
+      <c r="V18">
+        <v>1.39</v>
+      </c>
+      <c r="W18">
+        <v>1.78</v>
+      </c>
+      <c r="X18">
+        <v>14.5</v>
+      </c>
+      <c r="Y18">
+        <v>13.5</v>
+      </c>
+      <c r="Z18">
+        <v>24</v>
+      </c>
+      <c r="AA18">
+        <v>70</v>
+      </c>
+      <c r="AB18">
+        <v>10.5</v>
+      </c>
+      <c r="AC18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD18">
+        <v>14.5</v>
+      </c>
+      <c r="AE18">
+        <v>46</v>
+      </c>
+      <c r="AF18">
+        <v>15.5</v>
+      </c>
+      <c r="AG18">
+        <v>11.5</v>
+      </c>
+      <c r="AH18">
+        <v>17.5</v>
+      </c>
+      <c r="AI18">
+        <v>60</v>
+      </c>
+      <c r="AJ18">
+        <v>38</v>
+      </c>
+      <c r="AK18">
+        <v>30</v>
+      </c>
+      <c r="AL18">
+        <v>44</v>
+      </c>
+      <c r="AM18">
+        <v>110</v>
+      </c>
+      <c r="AN18">
+        <v>19.5</v>
+      </c>
+      <c r="AO18">
+        <v>44</v>
+      </c>
+      <c r="AP18">
+        <v>1.03</v>
+      </c>
+      <c r="AQ18">
+        <v>1.03</v>
+      </c>
+      <c r="AR18">
+        <v>1.03</v>
+      </c>
+      <c r="AS18">
+        <v>1.03</v>
+      </c>
+      <c r="AT18">
+        <v>1.03</v>
+      </c>
+      <c r="AU18">
+        <v>1.03</v>
+      </c>
+      <c r="AV18">
+        <v>1.03</v>
+      </c>
+      <c r="AW18">
+        <v>1.03</v>
+      </c>
+      <c r="AX18">
+        <v>1.03</v>
+      </c>
+      <c r="AY18">
+        <v>1.03</v>
+      </c>
+      <c r="AZ18">
+        <v>1.03</v>
+      </c>
+      <c r="BA18">
+        <v>1.03</v>
+      </c>
+      <c r="BB18">
+        <v>1.03</v>
+      </c>
+      <c r="BC18">
+        <v>1.03</v>
+      </c>
+      <c r="BD18">
+        <v>1.03</v>
+      </c>
+      <c r="BE18">
+        <v>1.03</v>
+      </c>
+      <c r="BF18">
+        <v>14.5</v>
+      </c>
+      <c r="BG18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH18" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:60">
+      <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19">
+        <v>2.36</v>
+      </c>
+      <c r="G19">
+        <v>2.7</v>
+      </c>
+      <c r="H19">
+        <v>2.82</v>
+      </c>
+      <c r="I19">
+        <v>3.5</v>
+      </c>
+      <c r="J19">
+        <v>3</v>
+      </c>
+      <c r="K19">
+        <v>3.7</v>
+      </c>
+      <c r="L19">
+        <v>1.43</v>
+      </c>
+      <c r="M19">
+        <v>1.07</v>
+      </c>
+      <c r="N19">
+        <v>3.15</v>
+      </c>
+      <c r="O19">
+        <v>1.35</v>
+      </c>
+      <c r="P19">
+        <v>1.69</v>
+      </c>
+      <c r="Q19">
+        <v>1.96</v>
+      </c>
+      <c r="R19">
+        <v>1.26</v>
+      </c>
+      <c r="S19">
+        <v>3.4</v>
+      </c>
+      <c r="T19">
+        <v>1.79</v>
+      </c>
+      <c r="U19">
+        <v>2.02</v>
+      </c>
+      <c r="V19">
+        <v>1.4</v>
+      </c>
+      <c r="W19">
+        <v>1.58</v>
+      </c>
+      <c r="X19">
+        <v>14.5</v>
+      </c>
+      <c r="Y19">
+        <v>13.5</v>
+      </c>
+      <c r="Z19">
+        <v>25</v>
+      </c>
+      <c r="AA19">
+        <v>65</v>
+      </c>
+      <c r="AB19">
+        <v>11.5</v>
+      </c>
+      <c r="AC19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD19">
+        <v>16</v>
+      </c>
+      <c r="AE19">
+        <v>46</v>
+      </c>
+      <c r="AF19">
+        <v>18.5</v>
+      </c>
+      <c r="AG19">
+        <v>14</v>
+      </c>
+      <c r="AH19">
+        <v>21</v>
+      </c>
+      <c r="AI19">
+        <v>60</v>
+      </c>
+      <c r="AJ19">
+        <v>42</v>
+      </c>
+      <c r="AK19">
+        <v>34</v>
+      </c>
+      <c r="AL19">
+        <v>55</v>
+      </c>
+      <c r="AM19">
+        <v>120</v>
+      </c>
+      <c r="AN19">
+        <v>30</v>
+      </c>
+      <c r="AO19">
+        <v>46</v>
+      </c>
+      <c r="AP19">
+        <v>1.03</v>
+      </c>
+      <c r="AQ19">
+        <v>1.03</v>
+      </c>
+      <c r="AR19">
+        <v>1.03</v>
+      </c>
+      <c r="AS19">
+        <v>1.03</v>
+      </c>
+      <c r="AT19">
+        <v>1.03</v>
+      </c>
+      <c r="AU19">
+        <v>1.03</v>
+      </c>
+      <c r="AV19">
+        <v>1.03</v>
+      </c>
+      <c r="AW19">
+        <v>1.03</v>
+      </c>
+      <c r="AX19">
+        <v>1.03</v>
+      </c>
+      <c r="AY19">
+        <v>1.03</v>
+      </c>
+      <c r="AZ19">
+        <v>1.03</v>
+      </c>
+      <c r="BA19">
+        <v>1.03</v>
+      </c>
+      <c r="BB19">
+        <v>1.03</v>
+      </c>
+      <c r="BC19">
+        <v>1.03</v>
+      </c>
+      <c r="BD19">
+        <v>1.03</v>
+      </c>
+      <c r="BE19">
+        <v>1.03</v>
+      </c>
+      <c r="BF19">
+        <v>19</v>
+      </c>
+      <c r="BG19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH19" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:60">
+      <c r="A20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" t="s">
+        <v>101</v>
+      </c>
+      <c r="E20" t="s">
+        <v>120</v>
+      </c>
+      <c r="F20">
+        <v>1.7</v>
+      </c>
+      <c r="G20">
+        <v>1.71</v>
+      </c>
+      <c r="H20">
+        <v>5.6</v>
+      </c>
+      <c r="I20">
+        <v>5.8</v>
+      </c>
+      <c r="J20">
+        <v>4.2</v>
+      </c>
+      <c r="K20">
+        <v>4.3</v>
+      </c>
+      <c r="L20">
+        <v>1.4</v>
+      </c>
+      <c r="M20">
+        <v>1.07</v>
+      </c>
+      <c r="N20">
+        <v>3.8</v>
+      </c>
+      <c r="O20">
+        <v>1.33</v>
+      </c>
+      <c r="P20">
+        <v>1.96</v>
+      </c>
+      <c r="Q20">
+        <v>1.97</v>
+      </c>
+      <c r="R20">
+        <v>1.38</v>
+      </c>
+      <c r="S20">
+        <v>3.45</v>
+      </c>
+      <c r="T20">
+        <v>1.99</v>
+      </c>
+      <c r="U20">
+        <v>1.95</v>
+      </c>
+      <c r="V20">
+        <v>1.21</v>
+      </c>
+      <c r="W20">
+        <v>2.4</v>
+      </c>
+      <c r="X20">
+        <v>14</v>
+      </c>
+      <c r="Y20">
+        <v>18.5</v>
+      </c>
+      <c r="Z20">
+        <v>44</v>
+      </c>
+      <c r="AA20">
+        <v>160</v>
+      </c>
+      <c r="AB20">
+        <v>8.4</v>
+      </c>
+      <c r="AC20">
+        <v>9</v>
+      </c>
+      <c r="AD20">
+        <v>22</v>
+      </c>
+      <c r="AE20">
+        <v>80</v>
+      </c>
+      <c r="AF20">
+        <v>9.6</v>
+      </c>
+      <c r="AG20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH20">
+        <v>22</v>
+      </c>
+      <c r="AI20">
+        <v>85</v>
+      </c>
+      <c r="AJ20">
+        <v>16.5</v>
+      </c>
+      <c r="AK20">
+        <v>17.5</v>
+      </c>
+      <c r="AL20">
+        <v>38</v>
+      </c>
+      <c r="AM20">
+        <v>130</v>
+      </c>
+      <c r="AN20">
+        <v>10</v>
+      </c>
+      <c r="AO20">
+        <v>100</v>
+      </c>
+      <c r="AP20">
+        <v>13</v>
+      </c>
+      <c r="AQ20">
+        <v>17.5</v>
+      </c>
+      <c r="AR20">
+        <v>40</v>
+      </c>
+      <c r="AS20">
+        <v>42</v>
+      </c>
+      <c r="AT20">
+        <v>7.8</v>
+      </c>
+      <c r="AU20">
+        <v>8.4</v>
+      </c>
+      <c r="AV20">
+        <v>20</v>
+      </c>
+      <c r="AW20">
+        <v>70</v>
+      </c>
+      <c r="AX20">
+        <v>9</v>
+      </c>
+      <c r="AY20">
+        <v>9.6</v>
+      </c>
+      <c r="AZ20">
+        <v>20</v>
+      </c>
+      <c r="BA20">
+        <v>70</v>
+      </c>
+      <c r="BB20">
+        <v>15.5</v>
+      </c>
+      <c r="BC20">
+        <v>16.5</v>
+      </c>
+      <c r="BD20">
+        <v>34</v>
+      </c>
+      <c r="BE20">
+        <v>110</v>
+      </c>
+      <c r="BF20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG20">
+        <v>80</v>
+      </c>
+      <c r="BH20" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -379,7 +379,7 @@
     <t>Atletico Madrid</t>
   </si>
   <si>
-    <t>2026-05-03 17:12:33</t>
+    <t>2026-05-03 19:26:41</t>
   </si>
 </sst>
 </file>
@@ -1136,7 +1136,7 @@
         <v>4</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L3">
         <v>1.23</v>
@@ -1280,7 +1280,7 @@
         <v>10.5</v>
       </c>
       <c r="BG3">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="BH3" t="s">
         <v>121</v>
@@ -1363,7 +1363,7 @@
         <v>9.4</v>
       </c>
       <c r="Z4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA4">
         <v>16</v>
@@ -1378,7 +1378,7 @@
         <v>10.5</v>
       </c>
       <c r="AE4">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AF4">
         <v>70</v>
@@ -1411,7 +1411,7 @@
         <v>8</v>
       </c>
       <c r="AP4">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AQ4">
         <v>7.8</v>
@@ -1423,43 +1423,43 @@
         <v>12</v>
       </c>
       <c r="AT4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU4">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AV4">
         <v>8.6</v>
       </c>
       <c r="AW4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX4">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY4">
+        <v>6.6</v>
+      </c>
+      <c r="AZ4">
         <v>6.2</v>
       </c>
-      <c r="AZ4">
-        <v>6</v>
-      </c>
       <c r="BA4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC4">
         <v>7.8</v>
       </c>
-      <c r="BC4">
-        <v>7.4</v>
-      </c>
       <c r="BD4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG4">
         <v>6.6</v>
@@ -1494,7 +1494,7 @@
         <v>4.1</v>
       </c>
       <c r="I5">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J5">
         <v>3.1</v>
@@ -1518,7 +1518,7 @@
         <v>1.61</v>
       </c>
       <c r="Q5">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
         <v>1.22</v>
@@ -1533,7 +1533,7 @@
         <v>1.83</v>
       </c>
       <c r="V5">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="W5">
         <v>1.82</v>
@@ -1691,13 +1691,13 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O6">
         <v>1.29</v>
       </c>
       <c r="P6">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q6">
         <v>1.29</v>
@@ -1867,7 +1867,7 @@
         <v>4.3</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M7">
         <v>1.06</v>
@@ -1897,10 +1897,10 @@
         <v>2.1</v>
       </c>
       <c r="V7">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="W7">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X7">
         <v>20</v>
@@ -2216,7 +2216,7 @@
         <v>2.5</v>
       </c>
       <c r="G9">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="H9">
         <v>2.58</v>
@@ -2252,7 +2252,7 @@
         <v>1.49</v>
       </c>
       <c r="S9">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T9">
         <v>1.51</v>
@@ -2261,10 +2261,10 @@
         <v>2.26</v>
       </c>
       <c r="V9">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W9">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X9">
         <v>24</v>
@@ -2327,10 +2327,10 @@
         <v>11</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT9">
         <v>11</v>
@@ -2342,7 +2342,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX9">
         <v>15</v>
@@ -2354,19 +2354,19 @@
         <v>11.5</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF9">
         <v>13</v>
@@ -2398,16 +2398,16 @@
         <v>1.4</v>
       </c>
       <c r="G10">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="H10">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="I10">
         <v>10.5</v>
       </c>
       <c r="J10">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K10">
         <v>6.6</v>
@@ -2428,7 +2428,7 @@
         <v>2.36</v>
       </c>
       <c r="Q10">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="R10">
         <v>1.49</v>
@@ -2446,7 +2446,7 @@
         <v>1.11</v>
       </c>
       <c r="W10">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="X10">
         <v>34</v>
@@ -2580,13 +2580,13 @@
         <v>2.58</v>
       </c>
       <c r="G11">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H11">
         <v>2.62</v>
       </c>
       <c r="I11">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="J11">
         <v>3.35</v>
@@ -2610,7 +2610,7 @@
         <v>2.22</v>
       </c>
       <c r="Q11">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="R11">
         <v>1.49</v>
@@ -2625,10 +2625,10 @@
         <v>2.4</v>
       </c>
       <c r="V11">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W11">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X11">
         <v>23</v>
@@ -2777,7 +2777,7 @@
         <v>4</v>
       </c>
       <c r="L12">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M12">
         <v>1.09</v>
@@ -2798,19 +2798,19 @@
         <v>1.25</v>
       </c>
       <c r="S12">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T12">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U12">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V12">
         <v>2.12</v>
       </c>
       <c r="W12">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X12">
         <v>13.5</v>
@@ -2944,7 +2944,7 @@
         <v>2.02</v>
       </c>
       <c r="G13">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="H13">
         <v>3.6</v>
@@ -2980,7 +2980,7 @@
         <v>1.3</v>
       </c>
       <c r="S13">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T13">
         <v>1.8</v>
@@ -2989,7 +2989,7 @@
         <v>2</v>
       </c>
       <c r="V13">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W13">
         <v>1.71</v>
@@ -3016,7 +3016,7 @@
         <v>20</v>
       </c>
       <c r="AE13">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF13">
         <v>16</v>
@@ -3052,10 +3052,10 @@
         <v>3.4</v>
       </c>
       <c r="AQ13">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AR13">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AS13">
         <v>4.1</v>
@@ -3064,7 +3064,7 @@
         <v>3.1</v>
       </c>
       <c r="AU13">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AV13">
         <v>3.55</v>
@@ -3076,31 +3076,31 @@
         <v>3.4</v>
       </c>
       <c r="AY13">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AZ13">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BA13">
+        <v>4.1</v>
+      </c>
+      <c r="BB13">
+        <v>3.85</v>
+      </c>
+      <c r="BC13">
+        <v>3.8</v>
+      </c>
+      <c r="BD13">
         <v>4</v>
       </c>
-      <c r="BB13">
-        <v>3.8</v>
-      </c>
-      <c r="BC13">
-        <v>3.75</v>
-      </c>
-      <c r="BD13">
-        <v>3.95</v>
-      </c>
       <c r="BE13">
+        <v>4.2</v>
+      </c>
+      <c r="BF13">
+        <v>3.65</v>
+      </c>
+      <c r="BG13">
         <v>4.1</v>
-      </c>
-      <c r="BF13">
-        <v>3.6</v>
-      </c>
-      <c r="BG13">
-        <v>4</v>
       </c>
       <c r="BH13" t="s">
         <v>121</v>
@@ -3323,7 +3323,7 @@
         <v>5.3</v>
       </c>
       <c r="L15">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M15">
         <v>1.08</v>
@@ -3487,58 +3487,58 @@
         <v>116</v>
       </c>
       <c r="F16">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="G16">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="H16">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="I16">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="J16">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="K16">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
         <v>1.02</v>
       </c>
       <c r="N16">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P16">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q16">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="R16">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="S16">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="T16">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="U16">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V16">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="W16">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
         <v>50</v>
@@ -3556,7 +3556,7 @@
         <v>55</v>
       </c>
       <c r="AC16">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AD16">
         <v>12.5</v>
@@ -3568,7 +3568,7 @@
         <v>120</v>
       </c>
       <c r="AG16">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AH16">
         <v>28</v>
@@ -3577,25 +3577,25 @@
         <v>28</v>
       </c>
       <c r="AJ16">
-        <v>320</v>
+        <v>390</v>
       </c>
       <c r="AK16">
         <v>140</v>
       </c>
       <c r="AL16">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AM16">
         <v>100</v>
       </c>
       <c r="AN16">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AO16">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="AP16">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ16">
         <v>12.5</v>
@@ -3604,10 +3604,10 @@
         <v>10</v>
       </c>
       <c r="AS16">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT16">
-        <v>7.2</v>
+        <v>40</v>
       </c>
       <c r="AU16">
         <v>14</v>
@@ -3619,34 +3619,34 @@
         <v>11</v>
       </c>
       <c r="AX16">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY16">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AZ16">
         <v>20</v>
       </c>
       <c r="BA16">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB16">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC16">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD16">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BE16">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BF16">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG16">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="BH16" t="s">
         <v>121</v>
@@ -3693,16 +3693,16 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="O17">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="P17">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q17">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="R17">
         <v>1.07</v>
@@ -3881,7 +3881,7 @@
         <v>1.32</v>
       </c>
       <c r="P18">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q18">
         <v>2.04</v>
@@ -3890,10 +3890,10 @@
         <v>1.35</v>
       </c>
       <c r="S18">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="T18">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="U18">
         <v>2.14</v>
@@ -3905,7 +3905,7 @@
         <v>1.78</v>
       </c>
       <c r="X18">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Y18">
         <v>13.5</v>
@@ -3923,7 +3923,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD18">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE18">
         <v>46</v>
@@ -3935,7 +3935,7 @@
         <v>11.5</v>
       </c>
       <c r="AH18">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AI18">
         <v>60</v>
@@ -3953,64 +3953,64 @@
         <v>110</v>
       </c>
       <c r="AN18">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AO18">
         <v>44</v>
       </c>
       <c r="AP18">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AQ18">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AR18">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AS18">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AT18">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AU18">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AV18">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AW18">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AX18">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AY18">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AZ18">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BA18">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BB18">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BC18">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BD18">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE18">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="BF18">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="BG18">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH18" t="s">
         <v>121</v>
@@ -4054,19 +4054,19 @@
         <v>1.43</v>
       </c>
       <c r="M19">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N19">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O19">
         <v>1.35</v>
       </c>
       <c r="P19">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="Q19">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R19">
         <v>1.26</v>
@@ -4081,10 +4081,10 @@
         <v>2.02</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W19">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="X19">
         <v>14.5</v>
@@ -4141,58 +4141,58 @@
         <v>46</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF19">
-        <v>19</v>
+        <v>4.4</v>
       </c>
       <c r="BG19">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="BH19" t="s">
         <v>121</v>
@@ -4233,31 +4233,31 @@
         <v>4.3</v>
       </c>
       <c r="L20">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M20">
         <v>1.07</v>
       </c>
       <c r="N20">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O20">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P20">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q20">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R20">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S20">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T20">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U20">
         <v>1.95</v>
@@ -4269,7 +4269,7 @@
         <v>2.4</v>
       </c>
       <c r="X20">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y20">
         <v>18.5</v>
@@ -4293,7 +4293,7 @@
         <v>80</v>
       </c>
       <c r="AF20">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG20">
         <v>9.800000000000001</v>
@@ -4305,7 +4305,7 @@
         <v>85</v>
       </c>
       <c r="AJ20">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK20">
         <v>17.5</v>
@@ -4323,7 +4323,7 @@
         <v>100</v>
       </c>
       <c r="AP20">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ20">
         <v>17.5</v>
@@ -4332,16 +4332,16 @@
         <v>40</v>
       </c>
       <c r="AS20">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AT20">
         <v>7.8</v>
       </c>
       <c r="AU20">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV20">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW20">
         <v>70</v>
@@ -4350,13 +4350,13 @@
         <v>9</v>
       </c>
       <c r="AY20">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20">
         <v>20</v>
       </c>
       <c r="BA20">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BB20">
         <v>15.5</v>
@@ -4374,7 +4374,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG20">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BH20" t="s">
         <v>121</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -379,7 +379,7 @@
     <t>Atletico Madrid</t>
   </si>
   <si>
-    <t>2026-05-03 19:26:41</t>
+    <t>2026-05-03 21:42:42</t>
   </si>
 </sst>
 </file>
@@ -975,19 +975,19 @@
         <v>2.04</v>
       </c>
       <c r="R2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S2">
         <v>3.7</v>
       </c>
       <c r="T2">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U2">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
         <v>1.71</v>
@@ -1014,7 +1014,7 @@
         <v>15.5</v>
       </c>
       <c r="AE2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF2">
         <v>15</v>
@@ -1035,7 +1035,7 @@
         <v>27</v>
       </c>
       <c r="AL2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM2">
         <v>130</v>
@@ -1056,7 +1056,7 @@
         <v>21</v>
       </c>
       <c r="AS2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT2">
         <v>8</v>
@@ -1068,7 +1068,7 @@
         <v>13</v>
       </c>
       <c r="AW2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX2">
         <v>12</v>
@@ -1083,7 +1083,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC2">
         <v>7</v>
@@ -1092,13 +1092,13 @@
         <v>7.8</v>
       </c>
       <c r="BE2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF2">
         <v>15.5</v>
       </c>
       <c r="BG2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH2" t="s">
         <v>121</v>
@@ -1157,10 +1157,10 @@
         <v>1.46</v>
       </c>
       <c r="R3">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S3">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T3">
         <v>1.46</v>
@@ -1175,7 +1175,7 @@
         <v>1.51</v>
       </c>
       <c r="X3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y3">
         <v>970</v>
@@ -1232,49 +1232,49 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="AR3">
+        <v>8</v>
+      </c>
+      <c r="AS3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT3">
         <v>7.8</v>
-      </c>
-      <c r="AS3">
-        <v>9</v>
-      </c>
-      <c r="AT3">
-        <v>7.6</v>
       </c>
       <c r="AU3">
         <v>5.8</v>
       </c>
       <c r="AV3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW3">
         <v>8</v>
       </c>
       <c r="AX3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AZ3">
         <v>6.6</v>
       </c>
       <c r="BA3">
+        <v>8.6</v>
+      </c>
+      <c r="BB3">
+        <v>5.6</v>
+      </c>
+      <c r="BC3">
         <v>8.4</v>
       </c>
-      <c r="BB3">
-        <v>9.4</v>
-      </c>
-      <c r="BC3">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BD3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF3">
         <v>10.5</v>
@@ -1303,7 +1303,7 @@
         <v>104</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -1321,7 +1321,7 @@
         <v>4.7</v>
       </c>
       <c r="L4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M4">
         <v>1.05</v>
@@ -1333,10 +1333,10 @@
         <v>1.25</v>
       </c>
       <c r="P4">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q4">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="R4">
         <v>1.45</v>
@@ -1390,7 +1390,7 @@
         <v>24</v>
       </c>
       <c r="AI4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ4">
         <v>230</v>
@@ -1411,7 +1411,7 @@
         <v>8</v>
       </c>
       <c r="AP4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ4">
         <v>7.8</v>
@@ -1420,13 +1420,13 @@
         <v>7.8</v>
       </c>
       <c r="AS4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT4">
         <v>6.4</v>
       </c>
       <c r="AU4">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AV4">
         <v>8.6</v>
@@ -1435,13 +1435,13 @@
         <v>5.6</v>
       </c>
       <c r="AX4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AZ4">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="BA4">
         <v>6.8</v>
@@ -1456,10 +1456,10 @@
         <v>7.8</v>
       </c>
       <c r="BE4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG4">
         <v>6.6</v>
@@ -1503,7 +1503,7 @@
         <v>3.5</v>
       </c>
       <c r="L5">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="M5">
         <v>1.1</v>
@@ -1518,13 +1518,13 @@
         <v>1.61</v>
       </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="R5">
         <v>1.22</v>
       </c>
       <c r="S5">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="T5">
         <v>2.02</v>
@@ -1533,7 +1533,7 @@
         <v>1.83</v>
       </c>
       <c r="V5">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="W5">
         <v>1.82</v>
@@ -1593,7 +1593,7 @@
         <v>120</v>
       </c>
       <c r="AP5">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AQ5">
         <v>9.199999999999999</v>
@@ -1605,7 +1605,7 @@
         <v>4.2</v>
       </c>
       <c r="AT5">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU5">
         <v>6.6</v>
@@ -1620,7 +1620,7 @@
         <v>9</v>
       </c>
       <c r="AY5">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ5">
         <v>19</v>
@@ -2222,7 +2222,7 @@
         <v>2.58</v>
       </c>
       <c r="I9">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="J9">
         <v>3.6</v>
@@ -2580,13 +2580,13 @@
         <v>2.58</v>
       </c>
       <c r="G11">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="H11">
         <v>2.62</v>
       </c>
       <c r="I11">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="J11">
         <v>3.35</v>
@@ -2798,7 +2798,7 @@
         <v>1.25</v>
       </c>
       <c r="S12">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T12">
         <v>2.06</v>
@@ -2810,7 +2810,7 @@
         <v>2.12</v>
       </c>
       <c r="W12">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X12">
         <v>13.5</v>
@@ -2944,7 +2944,7 @@
         <v>2.02</v>
       </c>
       <c r="G13">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="H13">
         <v>3.6</v>
@@ -2989,7 +2989,7 @@
         <v>2</v>
       </c>
       <c r="V13">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W13">
         <v>1.71</v>
@@ -3153,7 +3153,7 @@
         <v>1.51</v>
       </c>
       <c r="P14">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q14">
         <v>2.44</v>
@@ -3401,7 +3401,7 @@
         <v>19</v>
       </c>
       <c r="AL15">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM15">
         <v>370</v>
@@ -3428,28 +3428,28 @@
         <v>3.8</v>
       </c>
       <c r="AU15">
+        <v>5.3</v>
+      </c>
+      <c r="AV15">
+        <v>8</v>
+      </c>
+      <c r="AW15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX15">
+        <v>4.1</v>
+      </c>
+      <c r="AY15">
         <v>5.2</v>
-      </c>
-      <c r="AV15">
-        <v>7.8</v>
-      </c>
-      <c r="AW15">
-        <v>9</v>
-      </c>
-      <c r="AX15">
-        <v>4</v>
-      </c>
-      <c r="AY15">
-        <v>5.1</v>
       </c>
       <c r="AZ15">
         <v>7.6</v>
       </c>
       <c r="BA15">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB15">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC15">
         <v>6.2</v>
@@ -3487,13 +3487,13 @@
         <v>116</v>
       </c>
       <c r="F16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="H16">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="I16">
         <v>1.31</v>
@@ -3511,7 +3511,7 @@
         <v>1.02</v>
       </c>
       <c r="N16">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O16">
         <v>1.11</v>
@@ -3553,7 +3553,7 @@
         <v>13</v>
       </c>
       <c r="AB16">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AC16">
         <v>19</v>
@@ -3607,7 +3607,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AT16">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AU16">
         <v>14</v>
@@ -3619,7 +3619,7 @@
         <v>11</v>
       </c>
       <c r="AX16">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY16">
         <v>8</v>
@@ -3637,13 +3637,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BD16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF16">
         <v>9</v>
-      </c>
-      <c r="BE16">
-        <v>9</v>
-      </c>
-      <c r="BF16">
-        <v>9.199999999999999</v>
       </c>
       <c r="BG16">
         <v>2.88</v>
@@ -3693,7 +3693,7 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="O17">
         <v>1.01</v>
@@ -3705,7 +3705,7 @@
         <v>1.01</v>
       </c>
       <c r="R17">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S17">
         <v>1.33</v>
@@ -4036,7 +4036,7 @@
         <v>2.36</v>
       </c>
       <c r="G19">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="H19">
         <v>2.82</v>
@@ -4081,7 +4081,7 @@
         <v>2.02</v>
       </c>
       <c r="V19">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
         <v>1.53</v>
@@ -4224,7 +4224,7 @@
         <v>5.6</v>
       </c>
       <c r="I20">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J20">
         <v>4.2</v>
@@ -4245,7 +4245,7 @@
         <v>1.32</v>
       </c>
       <c r="P20">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q20">
         <v>1.98</v>
@@ -4269,7 +4269,7 @@
         <v>2.4</v>
       </c>
       <c r="X20">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y20">
         <v>18.5</v>
@@ -4278,7 +4278,7 @@
         <v>44</v>
       </c>
       <c r="AA20">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB20">
         <v>8.4</v>
@@ -4287,7 +4287,7 @@
         <v>9</v>
       </c>
       <c r="AD20">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE20">
         <v>80</v>
@@ -4320,7 +4320,7 @@
         <v>10</v>
       </c>
       <c r="AO20">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AP20">
         <v>14</v>
@@ -4368,7 +4368,7 @@
         <v>34</v>
       </c>
       <c r="BE20">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BF20">
         <v>9.800000000000001</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -379,7 +379,7 @@
     <t>Atletico Madrid</t>
   </si>
   <si>
-    <t>2026-05-03 21:42:42</t>
+    <t>2026-05-03 23:55:10</t>
   </si>
 </sst>
 </file>
@@ -948,7 +948,7 @@
         <v>3.4</v>
       </c>
       <c r="I2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J2">
         <v>3.25</v>
@@ -963,22 +963,22 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q2">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R2">
         <v>1.31</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T2">
         <v>1.82</v>
@@ -990,7 +990,7 @@
         <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X2">
         <v>13</v>
@@ -1121,7 +1121,7 @@
         <v>103</v>
       </c>
       <c r="F3">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G3">
         <v>2.96</v>
@@ -1130,16 +1130,16 @@
         <v>2.4</v>
       </c>
       <c r="I3">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J3">
         <v>4</v>
       </c>
       <c r="K3">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M3">
         <v>1.03</v>
@@ -1148,16 +1148,16 @@
         <v>6.4</v>
       </c>
       <c r="O3">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P3">
         <v>2.82</v>
       </c>
       <c r="Q3">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R3">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S3">
         <v>2.16</v>
@@ -1166,7 +1166,7 @@
         <v>1.46</v>
       </c>
       <c r="U3">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="V3">
         <v>1.64</v>
@@ -1193,7 +1193,7 @@
         <v>11</v>
       </c>
       <c r="AD3">
-        <v>970</v>
+        <v>80</v>
       </c>
       <c r="AE3">
         <v>23</v>
@@ -1223,64 +1223,64 @@
         <v>46</v>
       </c>
       <c r="AN3">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AO3">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="AP3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ3">
         <v>16</v>
       </c>
       <c r="AR3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV3">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AW3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY3">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB3">
+        <v>5.7</v>
+      </c>
+      <c r="BC3">
         <v>8.6</v>
       </c>
-      <c r="BB3">
-        <v>5.6</v>
-      </c>
-      <c r="BC3">
-        <v>8.4</v>
-      </c>
       <c r="BD3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF3">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="BG3">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="BH3" t="s">
         <v>121</v>
@@ -1303,25 +1303,25 @@
         <v>104</v>
       </c>
       <c r="F4">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <v>1.05</v>
@@ -1333,13 +1333,13 @@
         <v>1.25</v>
       </c>
       <c r="P4">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q4">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S4">
         <v>2.8</v>
@@ -1348,121 +1348,121 @@
         <v>1.85</v>
       </c>
       <c r="U4">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="V4">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="W4">
         <v>1.14</v>
       </c>
       <c r="X4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AO4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AP4">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AQ4">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AR4">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AS4">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AT4">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AU4">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AV4">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AW4">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AX4">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AY4">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AZ4">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BA4">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BB4">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BC4">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BD4">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BE4">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BF4">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BG4">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="s">
         <v>121</v>
@@ -1494,10 +1494,10 @@
         <v>4.1</v>
       </c>
       <c r="I5">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="J5">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K5">
         <v>3.5</v>
@@ -1521,7 +1521,7 @@
         <v>2.34</v>
       </c>
       <c r="R5">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S5">
         <v>4.5</v>
@@ -1557,7 +1557,7 @@
         <v>9</v>
       </c>
       <c r="AD5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE5">
         <v>90</v>
@@ -1599,7 +1599,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AS5">
         <v>4.2</v>
@@ -1626,7 +1626,7 @@
         <v>19</v>
       </c>
       <c r="BA5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB5">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>19.5</v>
       </c>
       <c r="BD5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE5">
         <v>4.2</v>
@@ -1644,7 +1644,7 @@
         <v>17.5</v>
       </c>
       <c r="BG5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="s">
         <v>121</v>
@@ -1670,16 +1670,16 @@
         <v>1.04</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H6">
         <v>1.04</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J6">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -1691,7 +1691,7 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O6">
         <v>1.29</v>
@@ -1700,19 +1700,19 @@
         <v>1.24</v>
       </c>
       <c r="Q6">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="R6">
         <v>1.15</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6">
         <v>1.01</v>
@@ -1906,34 +1906,34 @@
         <v>20</v>
       </c>
       <c r="Y7">
+        <v>10</v>
+      </c>
+      <c r="Z7">
+        <v>12</v>
+      </c>
+      <c r="AA7">
+        <v>20</v>
+      </c>
+      <c r="AB7">
+        <v>20</v>
+      </c>
+      <c r="AC7">
+        <v>10.5</v>
+      </c>
+      <c r="AD7">
         <v>11</v>
       </c>
-      <c r="Z7">
-        <v>13.5</v>
-      </c>
-      <c r="AA7">
-        <v>22</v>
-      </c>
-      <c r="AB7">
-        <v>22</v>
-      </c>
-      <c r="AC7">
-        <v>11</v>
-      </c>
-      <c r="AD7">
-        <v>12</v>
-      </c>
       <c r="AE7">
+        <v>19</v>
+      </c>
+      <c r="AF7">
+        <v>42</v>
+      </c>
+      <c r="AG7">
         <v>21</v>
       </c>
-      <c r="AF7">
-        <v>46</v>
-      </c>
-      <c r="AG7">
-        <v>23</v>
-      </c>
       <c r="AH7">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI7">
         <v>38</v>
@@ -1954,7 +1954,7 @@
         <v>80</v>
       </c>
       <c r="AO7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP7">
         <v>15</v>
@@ -1981,7 +1981,7 @@
         <v>15</v>
       </c>
       <c r="AX7">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AY7">
         <v>17.5</v>
@@ -1990,22 +1990,22 @@
         <v>16.5</v>
       </c>
       <c r="BA7">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB7">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BC7">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BD7">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BE7">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF7">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BG7">
         <v>8.800000000000001</v>
@@ -2216,13 +2216,13 @@
         <v>2.5</v>
       </c>
       <c r="G9">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H9">
         <v>2.58</v>
       </c>
       <c r="I9">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="J9">
         <v>3.6</v>
@@ -2252,13 +2252,13 @@
         <v>1.49</v>
       </c>
       <c r="S9">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T9">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="U9">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="V9">
         <v>1.49</v>
@@ -2327,7 +2327,7 @@
         <v>11</v>
       </c>
       <c r="AR9">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="AS9">
         <v>4.6</v>
@@ -2342,7 +2342,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW9">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="AX9">
         <v>15</v>
@@ -2354,13 +2354,13 @@
         <v>11.5</v>
       </c>
       <c r="BA9">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB9">
         <v>4.6</v>
       </c>
       <c r="BC9">
-        <v>4.3</v>
+        <v>19.5</v>
       </c>
       <c r="BD9">
         <v>4.5</v>
@@ -2404,7 +2404,7 @@
         <v>5.4</v>
       </c>
       <c r="I10">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="J10">
         <v>4.5</v>
@@ -2443,7 +2443,7 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W10">
         <v>2.82</v>
@@ -2586,7 +2586,7 @@
         <v>2.62</v>
       </c>
       <c r="I11">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J11">
         <v>3.35</v>
@@ -2628,7 +2628,7 @@
         <v>1.51</v>
       </c>
       <c r="W11">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X11">
         <v>23</v>
@@ -2759,13 +2759,13 @@
         <v>112</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="G12">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H12">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="I12">
         <v>1.89</v>
@@ -2783,28 +2783,28 @@
         <v>1.09</v>
       </c>
       <c r="N12">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="O12">
         <v>1.4</v>
       </c>
       <c r="P12">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="Q12">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R12">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S12">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="T12">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U12">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V12">
         <v>2.12</v>
@@ -2816,13 +2816,13 @@
         <v>13.5</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z12">
         <v>11.5</v>
       </c>
       <c r="AA12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB12">
         <v>19</v>
@@ -2843,13 +2843,13 @@
         <v>27</v>
       </c>
       <c r="AH12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI12">
         <v>55</v>
       </c>
       <c r="AJ12">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AK12">
         <v>120</v>
@@ -2858,67 +2858,67 @@
         <v>120</v>
       </c>
       <c r="AM12">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN12">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AO12">
         <v>17.5</v>
       </c>
       <c r="AP12">
-        <v>3.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ12">
-        <v>3.15</v>
+        <v>5.7</v>
       </c>
       <c r="AR12">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="AS12">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="AT12">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="AU12">
-        <v>3.35</v>
+        <v>6.6</v>
       </c>
       <c r="AV12">
-        <v>3.65</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW12">
-        <v>4.3</v>
+        <v>16.5</v>
       </c>
       <c r="AX12">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AY12">
-        <v>4.4</v>
+        <v>17.5</v>
       </c>
       <c r="AZ12">
-        <v>4.4</v>
+        <v>18</v>
       </c>
       <c r="BA12">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB12">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BC12">
+        <v>4.9</v>
+      </c>
+      <c r="BD12">
+        <v>4.9</v>
+      </c>
+      <c r="BE12">
         <v>5</v>
       </c>
-      <c r="BD12">
+      <c r="BF12">
         <v>5</v>
       </c>
-      <c r="BE12">
-        <v>5.1</v>
-      </c>
-      <c r="BF12">
-        <v>5.1</v>
-      </c>
       <c r="BG12">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="BH12" t="s">
         <v>121</v>
@@ -2944,43 +2944,43 @@
         <v>2.02</v>
       </c>
       <c r="G13">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="H13">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I13">
         <v>4.3</v>
       </c>
       <c r="J13">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K13">
         <v>3.85</v>
       </c>
       <c r="L13">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="M13">
         <v>1.07</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O13">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P13">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q13">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R13">
         <v>1.3</v>
       </c>
       <c r="S13">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T13">
         <v>1.8</v>
@@ -2992,7 +2992,7 @@
         <v>1.3</v>
       </c>
       <c r="W13">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="X13">
         <v>16</v>
@@ -3013,10 +3013,10 @@
         <v>9.6</v>
       </c>
       <c r="AD13">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE13">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF13">
         <v>16</v>
@@ -3037,7 +3037,7 @@
         <v>29</v>
       </c>
       <c r="AL13">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM13">
         <v>130</v>
@@ -3049,46 +3049,46 @@
         <v>70</v>
       </c>
       <c r="AP13">
-        <v>3.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ13">
-        <v>3.45</v>
+        <v>10</v>
       </c>
       <c r="AR13">
-        <v>3.9</v>
+        <v>20</v>
       </c>
       <c r="AS13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT13">
-        <v>3.1</v>
+        <v>7.6</v>
       </c>
       <c r="AU13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV13">
-        <v>3.55</v>
+        <v>11.5</v>
       </c>
       <c r="AW13">
         <v>4</v>
       </c>
       <c r="AX13">
-        <v>3.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY13">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="AZ13">
-        <v>3.65</v>
+        <v>13.5</v>
       </c>
       <c r="BA13">
         <v>4.1</v>
       </c>
       <c r="BB13">
-        <v>3.85</v>
+        <v>19.5</v>
       </c>
       <c r="BC13">
-        <v>3.8</v>
+        <v>17.5</v>
       </c>
       <c r="BD13">
         <v>4</v>
@@ -3097,7 +3097,7 @@
         <v>4.2</v>
       </c>
       <c r="BF13">
-        <v>3.65</v>
+        <v>13</v>
       </c>
       <c r="BG13">
         <v>4.1</v>
@@ -3150,7 +3150,7 @@
         <v>2.58</v>
       </c>
       <c r="O14">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P14">
         <v>1.52</v>
@@ -3231,55 +3231,55 @@
         <v>19</v>
       </c>
       <c r="AP14">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AQ14">
         <v>4.3</v>
       </c>
       <c r="AR14">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AS14">
         <v>11.5</v>
       </c>
       <c r="AT14">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AU14">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AV14">
         <v>8.199999999999999</v>
       </c>
       <c r="AW14">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX14">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AY14">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AZ14">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BA14">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="BB14">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BC14">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BD14">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BE14">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BF14">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="BG14">
         <v>10</v>
@@ -3305,13 +3305,13 @@
         <v>115</v>
       </c>
       <c r="F15">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G15">
         <v>1.45</v>
       </c>
       <c r="H15">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="I15">
         <v>13.5</v>
@@ -3323,19 +3323,19 @@
         <v>5.3</v>
       </c>
       <c r="L15">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="M15">
         <v>1.08</v>
       </c>
       <c r="N15">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O15">
         <v>1.36</v>
       </c>
       <c r="P15">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q15">
         <v>2.02</v>
@@ -3350,7 +3350,7 @@
         <v>2.44</v>
       </c>
       <c r="U15">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V15">
         <v>1.08</v>
@@ -3380,7 +3380,7 @@
         <v>50</v>
       </c>
       <c r="AE15">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AF15">
         <v>7.2</v>
@@ -3392,7 +3392,7 @@
         <v>40</v>
       </c>
       <c r="AI15">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AJ15">
         <v>12</v>
@@ -3401,10 +3401,10 @@
         <v>19</v>
       </c>
       <c r="AL15">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM15">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AN15">
         <v>9.199999999999999</v>
@@ -3413,34 +3413,34 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AQ15">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR15">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS15">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT15">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="AU15">
-        <v>5.3</v>
+        <v>9.6</v>
       </c>
       <c r="AV15">
         <v>8</v>
       </c>
       <c r="AW15">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX15">
         <v>4.1</v>
       </c>
       <c r="AY15">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
         <v>7.6</v>
@@ -3449,22 +3449,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BB15">
-        <v>5.3</v>
+        <v>9.6</v>
       </c>
       <c r="BC15">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD15">
         <v>8.199999999999999</v>
       </c>
       <c r="BE15">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF15">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG15">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH15" t="s">
         <v>121</v>
@@ -3493,7 +3493,7 @@
         <v>13</v>
       </c>
       <c r="H16">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="I16">
         <v>1.31</v>
@@ -3625,7 +3625,7 @@
         <v>8</v>
       </c>
       <c r="AZ16">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="BA16">
         <v>7.2</v>
@@ -3854,16 +3854,16 @@
         <v>2.26</v>
       </c>
       <c r="G18">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H18">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I18">
         <v>3.55</v>
       </c>
       <c r="J18">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K18">
         <v>3.6</v>
@@ -3902,7 +3902,7 @@
         <v>1.39</v>
       </c>
       <c r="W18">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X18">
         <v>970</v>
@@ -4051,7 +4051,7 @@
         <v>3.7</v>
       </c>
       <c r="L19">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="M19">
         <v>1.08</v>
@@ -4063,10 +4063,10 @@
         <v>1.35</v>
       </c>
       <c r="P19">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q19">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R19">
         <v>1.26</v>
@@ -4081,10 +4081,10 @@
         <v>2.02</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W19">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="X19">
         <v>14.5</v>
@@ -4215,7 +4215,7 @@
         <v>120</v>
       </c>
       <c r="F20">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G20">
         <v>1.71</v>
@@ -4224,7 +4224,7 @@
         <v>5.6</v>
       </c>
       <c r="I20">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J20">
         <v>4.2</v>
@@ -4263,7 +4263,7 @@
         <v>1.95</v>
       </c>
       <c r="V20">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W20">
         <v>2.4</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -379,7 +379,7 @@
     <t>Atletico Madrid</t>
   </si>
   <si>
-    <t>2026-05-03 23:55:10</t>
+    <t>2026-05-04 02:07:34</t>
   </si>
 </sst>
 </file>
@@ -939,10 +939,10 @@
         <v>102</v>
       </c>
       <c r="F2">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G2">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H2">
         <v>3.4</v>
@@ -951,7 +951,7 @@
         <v>3.8</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
         <v>3.7</v>
@@ -969,7 +969,7 @@
         <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q2">
         <v>2.06</v>
@@ -981,7 +981,7 @@
         <v>3.75</v>
       </c>
       <c r="T2">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U2">
         <v>2.04</v>
@@ -1068,7 +1068,7 @@
         <v>13</v>
       </c>
       <c r="AW2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2">
         <v>12</v>
@@ -1083,10 +1083,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD2">
         <v>7.8</v>
@@ -1130,7 +1130,7 @@
         <v>2.4</v>
       </c>
       <c r="I3">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -1169,7 +1169,7 @@
         <v>2.88</v>
       </c>
       <c r="V3">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W3">
         <v>1.51</v>
@@ -1229,7 +1229,7 @@
         <v>44</v>
       </c>
       <c r="AP3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3">
         <v>16</v>
@@ -1241,7 +1241,7 @@
         <v>9.4</v>
       </c>
       <c r="AT3">
-        <v>8.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="AU3">
         <v>8.800000000000001</v>
@@ -1250,7 +1250,7 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX3">
         <v>8.6</v>
@@ -1259,16 +1259,16 @@
         <v>11.5</v>
       </c>
       <c r="AZ3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA3">
         <v>8.800000000000001</v>
       </c>
       <c r="BB3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD3">
         <v>9</v>
@@ -1277,10 +1277,10 @@
         <v>10</v>
       </c>
       <c r="BF3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG3">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BH3" t="s">
         <v>121</v>
@@ -1303,25 +1303,25 @@
         <v>104</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M4">
         <v>1.05</v>
@@ -1339,7 +1339,7 @@
         <v>1.75</v>
       </c>
       <c r="R4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S4">
         <v>2.8</v>
@@ -1357,112 +1357,112 @@
         <v>1.14</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AO4">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AZ4">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA4">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BG4">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BH4" t="s">
         <v>121</v>
@@ -1494,10 +1494,10 @@
         <v>4.1</v>
       </c>
       <c r="I5">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="J5">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K5">
         <v>3.5</v>
@@ -1515,16 +1515,16 @@
         <v>1.45</v>
       </c>
       <c r="P5">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="Q5">
         <v>2.34</v>
       </c>
       <c r="R5">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S5">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
         <v>2.02</v>
@@ -1533,7 +1533,7 @@
         <v>1.83</v>
       </c>
       <c r="V5">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="W5">
         <v>1.82</v>
@@ -1587,16 +1587,16 @@
         <v>200</v>
       </c>
       <c r="AN5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO5">
         <v>120</v>
       </c>
       <c r="AP5">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR5">
         <v>3.9</v>
@@ -1605,10 +1605,10 @@
         <v>4.2</v>
       </c>
       <c r="AT5">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AU5">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="AV5">
         <v>13</v>
@@ -1620,13 +1620,13 @@
         <v>9</v>
       </c>
       <c r="AY5">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BB5">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>19.5</v>
       </c>
       <c r="BD5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BE5">
         <v>4.2</v>
@@ -1691,7 +1691,7 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="O6">
         <v>1.29</v>
@@ -1849,7 +1849,7 @@
         <v>107</v>
       </c>
       <c r="F7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G7">
         <v>5.4</v>
@@ -1858,16 +1858,16 @@
         <v>1.77</v>
       </c>
       <c r="I7">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="J7">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K7">
         <v>4.3</v>
       </c>
       <c r="L7">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
         <v>1.06</v>
@@ -1879,13 +1879,13 @@
         <v>1.27</v>
       </c>
       <c r="P7">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q7">
         <v>1.79</v>
       </c>
       <c r="R7">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S7">
         <v>2.98</v>
@@ -1897,7 +1897,7 @@
         <v>2.1</v>
       </c>
       <c r="V7">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W7">
         <v>1.23</v>
@@ -1954,7 +1954,7 @@
         <v>80</v>
       </c>
       <c r="AO7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP7">
         <v>15</v>
@@ -1981,7 +1981,7 @@
         <v>15</v>
       </c>
       <c r="AX7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY7">
         <v>17.5</v>
@@ -1990,22 +1990,22 @@
         <v>16.5</v>
       </c>
       <c r="BA7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB7">
+        <v>7.4</v>
+      </c>
+      <c r="BC7">
+        <v>7</v>
+      </c>
+      <c r="BD7">
+        <v>7</v>
+      </c>
+      <c r="BE7">
+        <v>7.4</v>
+      </c>
+      <c r="BF7">
         <v>7.2</v>
-      </c>
-      <c r="BC7">
-        <v>6.8</v>
-      </c>
-      <c r="BD7">
-        <v>6.8</v>
-      </c>
-      <c r="BE7">
-        <v>7.2</v>
-      </c>
-      <c r="BF7">
-        <v>6.8</v>
       </c>
       <c r="BG7">
         <v>8.800000000000001</v>
@@ -2115,7 +2115,7 @@
         <v>11</v>
       </c>
       <c r="AH8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI8">
         <v>90</v>
@@ -2213,22 +2213,22 @@
         <v>109</v>
       </c>
       <c r="F9">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G9">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="H9">
         <v>2.58</v>
       </c>
       <c r="I9">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="J9">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L9">
         <v>1.28</v>
@@ -2246,10 +2246,10 @@
         <v>2.24</v>
       </c>
       <c r="Q9">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R9">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S9">
         <v>2.6</v>
@@ -2261,16 +2261,16 @@
         <v>2.42</v>
       </c>
       <c r="V9">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="X9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y9">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Z9">
         <v>24</v>
@@ -2315,31 +2315,31 @@
         <v>75</v>
       </c>
       <c r="AN9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO9">
         <v>21</v>
       </c>
       <c r="AP9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR9">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS9">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="AT9">
         <v>11</v>
       </c>
       <c r="AU9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV9">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AW9">
         <v>20</v>
@@ -2354,22 +2354,22 @@
         <v>11.5</v>
       </c>
       <c r="BA9">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB9">
-        <v>4.6</v>
+        <v>28</v>
       </c>
       <c r="BC9">
         <v>19.5</v>
       </c>
       <c r="BD9">
-        <v>4.5</v>
+        <v>24</v>
       </c>
       <c r="BE9">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG9">
         <v>13.5</v>
@@ -2428,25 +2428,25 @@
         <v>2.36</v>
       </c>
       <c r="Q10">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R10">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S10">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T10">
         <v>1.61</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10">
         <v>1.1</v>
       </c>
       <c r="W10">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="X10">
         <v>34</v>
@@ -2586,7 +2586,7 @@
         <v>2.62</v>
       </c>
       <c r="I11">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="J11">
         <v>3.35</v>
@@ -2622,13 +2622,13 @@
         <v>1.61</v>
       </c>
       <c r="U11">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V11">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W11">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X11">
         <v>23</v>
@@ -2759,16 +2759,16 @@
         <v>112</v>
       </c>
       <c r="F12">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="G12">
         <v>6.8</v>
       </c>
       <c r="H12">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="I12">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="J12">
         <v>3.5</v>
@@ -2783,37 +2783,37 @@
         <v>1.09</v>
       </c>
       <c r="N12">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O12">
         <v>1.4</v>
       </c>
       <c r="P12">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q12">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R12">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S12">
         <v>4.1</v>
       </c>
       <c r="T12">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U12">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V12">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="W12">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y12">
         <v>8.199999999999999</v>
@@ -2825,7 +2825,7 @@
         <v>23</v>
       </c>
       <c r="AB12">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC12">
         <v>9.6</v>
@@ -2834,7 +2834,7 @@
         <v>12</v>
       </c>
       <c r="AE12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF12">
         <v>55</v>
@@ -2843,7 +2843,7 @@
         <v>27</v>
       </c>
       <c r="AH12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI12">
         <v>55</v>
@@ -2852,7 +2852,7 @@
         <v>200</v>
       </c>
       <c r="AK12">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AL12">
         <v>120</v>
@@ -2864,28 +2864,28 @@
         <v>170</v>
       </c>
       <c r="AO12">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AP12">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ12">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AR12">
         <v>7.6</v>
       </c>
       <c r="AS12">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU12">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV12">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AW12">
         <v>16.5</v>
@@ -2918,7 +2918,7 @@
         <v>5</v>
       </c>
       <c r="BG12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH12" t="s">
         <v>121</v>
@@ -2980,7 +2980,7 @@
         <v>1.3</v>
       </c>
       <c r="S13">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="T13">
         <v>1.8</v>
@@ -3049,7 +3049,7 @@
         <v>70</v>
       </c>
       <c r="AP13">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AQ13">
         <v>10</v>
@@ -3064,7 +3064,7 @@
         <v>7.6</v>
       </c>
       <c r="AU13">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV13">
         <v>11.5</v>
@@ -3076,10 +3076,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY13">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA13">
         <v>4.1</v>
@@ -3088,7 +3088,7 @@
         <v>19.5</v>
       </c>
       <c r="BC13">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BD13">
         <v>4</v>
@@ -3123,25 +3123,25 @@
         <v>114</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="G14">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H14">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="I14">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="J14">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K14">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M14">
         <v>1.11</v>
@@ -3150,40 +3150,40 @@
         <v>2.58</v>
       </c>
       <c r="O14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P14">
         <v>1.52</v>
       </c>
       <c r="Q14">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="R14">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S14">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="T14">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="U14">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="V14">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="W14">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X14">
         <v>970</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AA14">
         <v>970</v>
@@ -3192,7 +3192,7 @@
         <v>970</v>
       </c>
       <c r="AC14">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD14">
         <v>970</v>
@@ -3204,7 +3204,7 @@
         <v>80</v>
       </c>
       <c r="AG14">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AH14">
         <v>44</v>
@@ -3228,61 +3228,61 @@
         <v>1000</v>
       </c>
       <c r="AO14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP14">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ14">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AR14">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AS14">
         <v>11.5</v>
       </c>
       <c r="AT14">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU14">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AV14">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="AW14">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AX14">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AY14">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AZ14">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BA14">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BB14">
-        <v>3.95</v>
+        <v>1.94</v>
       </c>
       <c r="BC14">
-        <v>3.95</v>
+        <v>2.42</v>
       </c>
       <c r="BD14">
-        <v>3.95</v>
+        <v>2.42</v>
       </c>
       <c r="BE14">
-        <v>3.95</v>
+        <v>1.94</v>
       </c>
       <c r="BF14">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="BG14">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="BH14" t="s">
         <v>121</v>
@@ -3305,10 +3305,10 @@
         <v>115</v>
       </c>
       <c r="F15">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="G15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H15">
         <v>11</v>
@@ -3317,10 +3317,10 @@
         <v>13.5</v>
       </c>
       <c r="J15">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K15">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L15">
         <v>1.37</v>
@@ -3329,19 +3329,19 @@
         <v>1.08</v>
       </c>
       <c r="N15">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O15">
         <v>1.36</v>
       </c>
       <c r="P15">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q15">
         <v>2.02</v>
       </c>
       <c r="R15">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S15">
         <v>3.35</v>
@@ -3350,13 +3350,13 @@
         <v>2.44</v>
       </c>
       <c r="U15">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V15">
         <v>1.08</v>
       </c>
       <c r="W15">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="X15">
         <v>13.5</v>
@@ -3365,7 +3365,7 @@
         <v>29</v>
       </c>
       <c r="Z15">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA15">
         <v>1000</v>
@@ -3380,7 +3380,7 @@
         <v>50</v>
       </c>
       <c r="AE15">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AF15">
         <v>7.2</v>
@@ -3392,7 +3392,7 @@
         <v>40</v>
       </c>
       <c r="AI15">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AJ15">
         <v>12</v>
@@ -3404,7 +3404,7 @@
         <v>60</v>
       </c>
       <c r="AM15">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="AN15">
         <v>9.199999999999999</v>
@@ -3443,10 +3443,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA15">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB15">
         <v>9.6</v>
@@ -3455,7 +3455,7 @@
         <v>6.4</v>
       </c>
       <c r="BD15">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE15">
         <v>9.4</v>
@@ -3505,7 +3505,7 @@
         <v>8</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M16">
         <v>1.02</v>
@@ -3672,7 +3672,7 @@
         <v>1.02</v>
       </c>
       <c r="G17">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H17">
         <v>1.02</v>
@@ -3681,7 +3681,7 @@
         <v>1000</v>
       </c>
       <c r="J17">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K17">
         <v>950</v>
@@ -3693,7 +3693,7 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O17">
         <v>1.01</v>
@@ -3702,7 +3702,7 @@
         <v>1.08</v>
       </c>
       <c r="Q17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R17">
         <v>1.08</v>
@@ -3711,10 +3711,10 @@
         <v>1.33</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17">
         <v>1.01</v>
@@ -4036,7 +4036,7 @@
         <v>2.36</v>
       </c>
       <c r="G19">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="H19">
         <v>2.82</v>
@@ -4051,7 +4051,7 @@
         <v>3.7</v>
       </c>
       <c r="L19">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M19">
         <v>1.08</v>
@@ -4069,7 +4069,7 @@
         <v>1.94</v>
       </c>
       <c r="R19">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S19">
         <v>3.4</v>
@@ -4084,7 +4084,7 @@
         <v>1.37</v>
       </c>
       <c r="W19">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="X19">
         <v>14.5</v>
@@ -4215,7 +4215,7 @@
         <v>120</v>
       </c>
       <c r="F20">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G20">
         <v>1.71</v>
@@ -4263,7 +4263,7 @@
         <v>1.95</v>
       </c>
       <c r="V20">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W20">
         <v>2.4</v>
@@ -4278,7 +4278,7 @@
         <v>44</v>
       </c>
       <c r="AA20">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AB20">
         <v>8.4</v>
@@ -4320,7 +4320,7 @@
         <v>10</v>
       </c>
       <c r="AO20">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AP20">
         <v>14</v>
@@ -4341,7 +4341,7 @@
         <v>8.6</v>
       </c>
       <c r="AV20">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW20">
         <v>70</v>
@@ -4359,10 +4359,10 @@
         <v>55</v>
       </c>
       <c r="BB20">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC20">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD20">
         <v>34</v>
@@ -4371,7 +4371,7 @@
         <v>100</v>
       </c>
       <c r="BF20">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BG20">
         <v>70</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="129">
   <si>
     <t>League</t>
   </si>
@@ -205,6 +205,9 @@
     <t>Romanian Liga II</t>
   </si>
   <si>
+    <t>Lithuanian A Lyga</t>
+  </si>
+  <si>
     <t>Finnish Veikkausliiga</t>
   </si>
   <si>
@@ -214,24 +217,24 @@
     <t>Israeli Premier League</t>
   </si>
   <si>
+    <t>Egyptian Premier</t>
+  </si>
+  <si>
     <t>Swedish Superettan</t>
   </si>
   <si>
-    <t>Egyptian Premier</t>
-  </si>
-  <si>
     <t>Saudi Professional League</t>
   </si>
   <si>
+    <t>Scottish Championship</t>
+  </si>
+  <si>
+    <t>Scottish League One</t>
+  </si>
+  <si>
     <t>Scottish League Two</t>
   </si>
   <si>
-    <t>Scottish Championship</t>
-  </si>
-  <si>
-    <t>Scottish League One</t>
-  </si>
-  <si>
     <t>UEFA Champions League</t>
   </si>
   <si>
@@ -247,6 +250,12 @@
     <t>11:30:00</t>
   </si>
   <si>
+    <t>12:30:00</t>
+  </si>
+  <si>
+    <t>12:45:00</t>
+  </si>
+  <si>
     <t>13:00:00</t>
   </si>
   <si>
@@ -280,6 +289,12 @@
     <t>Bihor Oradea</t>
   </si>
   <si>
+    <t>Riteriai</t>
+  </si>
+  <si>
+    <t>FK Kauno Zalgiris</t>
+  </si>
+  <si>
     <t>Gnistan</t>
   </si>
   <si>
@@ -292,33 +307,33 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Lokomotiv Sofia</t>
+  </si>
+  <si>
+    <t>Smouha</t>
+  </si>
+  <si>
+    <t>Al Ahly Cairo</t>
+  </si>
+  <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
     <t>Falkenbergs</t>
   </si>
   <si>
-    <t>Ceramica Cleopatra</t>
-  </si>
-  <si>
-    <t>Lokomotiv Sofia</t>
-  </si>
-  <si>
-    <t>Smouha</t>
-  </si>
-  <si>
-    <t>Al Ahly Cairo</t>
-  </si>
-  <si>
     <t>Al-Khaleej Saihat</t>
   </si>
   <si>
+    <t>Dunfermline</t>
+  </si>
+  <si>
+    <t>Queen of South</t>
+  </si>
+  <si>
     <t>Clyde</t>
   </si>
   <si>
-    <t>Dunfermline</t>
-  </si>
-  <si>
-    <t>Queen of South</t>
-  </si>
-  <si>
     <t>Arsenal</t>
   </si>
   <si>
@@ -337,6 +352,12 @@
     <t>Chindia Targoviste</t>
   </si>
   <si>
+    <t>FK Banga Gargzdu</t>
+  </si>
+  <si>
+    <t>FC Dziugas</t>
+  </si>
+  <si>
     <t>FC Inter</t>
   </si>
   <si>
@@ -349,37 +370,37 @@
     <t>Hapoel Petach Tikva</t>
   </si>
   <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
+    <t>Zamalek</t>
+  </si>
+  <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
+    <t>Pyramids</t>
+  </si>
+  <si>
     <t>Norrkoping</t>
   </si>
   <si>
-    <t>Pyramids</t>
-  </si>
-  <si>
-    <t>Botev Vratsa</t>
-  </si>
-  <si>
-    <t>Zamalek</t>
-  </si>
-  <si>
-    <t>ENPPI</t>
-  </si>
-  <si>
     <t>Al-Hilal</t>
   </si>
   <si>
+    <t>Arbroath</t>
+  </si>
+  <si>
+    <t>Stenhousemuir</t>
+  </si>
+  <si>
     <t>Spartans</t>
   </si>
   <si>
-    <t>Arbroath</t>
-  </si>
-  <si>
-    <t>Stenhousemuir</t>
-  </si>
-  <si>
     <t>Atletico Madrid</t>
   </si>
   <si>
-    <t>2026-05-04 02:07:34</t>
+    <t>2026-05-04 04:18:46</t>
   </si>
 </sst>
 </file>
@@ -737,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH20"/>
+  <dimension ref="A1:BH22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:60">
@@ -927,34 +948,34 @@
         <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F2">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="G2">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="H2">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="I2">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K2">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L2">
         <v>1.36</v>
@@ -972,76 +993,76 @@
         <v>1.81</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R2">
         <v>1.31</v>
       </c>
       <c r="S2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T2">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U2">
         <v>2.04</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W2">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="X2">
         <v>13</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z2">
         <v>26</v>
       </c>
       <c r="AA2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE2">
         <v>46</v>
       </c>
       <c r="AF2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
         <v>19</v>
       </c>
       <c r="AI2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM2">
         <v>130</v>
       </c>
       <c r="AN2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO2">
         <v>50</v>
@@ -1053,55 +1074,55 @@
         <v>10.5</v>
       </c>
       <c r="AR2">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AS2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT2">
         <v>8.4</v>
-      </c>
-      <c r="AT2">
-        <v>8</v>
       </c>
       <c r="AU2">
         <v>6.8</v>
       </c>
       <c r="AV2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
-        <v>15.5</v>
+        <v>7.4</v>
       </c>
       <c r="BA2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB2">
+        <v>7.4</v>
+      </c>
+      <c r="BC2">
+        <v>7</v>
+      </c>
+      <c r="BD2">
         <v>7.6</v>
       </c>
-      <c r="BC2">
-        <v>7.2</v>
-      </c>
-      <c r="BD2">
+      <c r="BE2">
+        <v>8.6</v>
+      </c>
+      <c r="BF2">
+        <v>18.5</v>
+      </c>
+      <c r="BG2">
         <v>7.8</v>
       </c>
-      <c r="BE2">
-        <v>9</v>
-      </c>
-      <c r="BF2">
-        <v>15.5</v>
-      </c>
-      <c r="BG2">
-        <v>8</v>
-      </c>
       <c r="BH2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -1109,28 +1130,28 @@
         <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F3">
         <v>2.78</v>
       </c>
       <c r="G3">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I3">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -1139,13 +1160,13 @@
         <v>4.2</v>
       </c>
       <c r="L3">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M3">
         <v>1.03</v>
       </c>
       <c r="N3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O3">
         <v>1.16</v>
@@ -1157,25 +1178,25 @@
         <v>1.48</v>
       </c>
       <c r="R3">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="S3">
         <v>2.16</v>
       </c>
       <c r="T3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U3">
         <v>2.88</v>
       </c>
       <c r="V3">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W3">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X3">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="Y3">
         <v>970</v>
@@ -1187,7 +1208,7 @@
         <v>34</v>
       </c>
       <c r="AB3">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AC3">
         <v>11</v>
@@ -1226,22 +1247,22 @@
         <v>14.5</v>
       </c>
       <c r="AO3">
-        <v>44</v>
+        <v>11.5</v>
       </c>
       <c r="AP3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ3">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AR3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT3">
-        <v>17.5</v>
+        <v>8.4</v>
       </c>
       <c r="AU3">
         <v>8.800000000000001</v>
@@ -1250,10 +1271,10 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY3">
         <v>11.5</v>
@@ -1262,28 +1283,28 @@
         <v>7</v>
       </c>
       <c r="BA3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BC3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BD3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BG3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -1291,25 +1312,25 @@
         <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H4">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="I4">
         <v>1.58</v>
@@ -1327,22 +1348,22 @@
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O4">
         <v>1.25</v>
       </c>
       <c r="P4">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q4">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="R4">
         <v>1.47</v>
       </c>
       <c r="S4">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="T4">
         <v>1.85</v>
@@ -1366,10 +1387,10 @@
         <v>10</v>
       </c>
       <c r="AA4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB4">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AC4">
         <v>10.5</v>
@@ -1384,13 +1405,13 @@
         <v>70</v>
       </c>
       <c r="AG4">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AH4">
         <v>24</v>
       </c>
       <c r="AI4">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ4">
         <v>230</v>
@@ -1399,7 +1420,7 @@
         <v>110</v>
       </c>
       <c r="AL4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AM4">
         <v>120</v>
@@ -1411,10 +1432,10 @@
         <v>7.6</v>
       </c>
       <c r="AP4">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="AQ4">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="AR4">
         <v>8.6</v>
@@ -1429,43 +1450,43 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AW4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX4">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY4">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AZ4">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB4">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BC4">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BD4">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BE4">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF4">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH4" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:60">
@@ -1473,16 +1494,16 @@
         <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F5">
         <v>2.04</v>
@@ -1494,7 +1515,7 @@
         <v>4.1</v>
       </c>
       <c r="I5">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="J5">
         <v>3.1</v>
@@ -1533,7 +1554,7 @@
         <v>1.83</v>
       </c>
       <c r="V5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W5">
         <v>1.82</v>
@@ -1593,7 +1614,7 @@
         <v>120</v>
       </c>
       <c r="AP5">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AQ5">
         <v>9</v>
@@ -1605,10 +1626,10 @@
         <v>4.2</v>
       </c>
       <c r="AT5">
+        <v>5.6</v>
+      </c>
+      <c r="AU5">
         <v>6.6</v>
-      </c>
-      <c r="AU5">
-        <v>5.7</v>
       </c>
       <c r="AV5">
         <v>13</v>
@@ -1620,10 +1641,10 @@
         <v>9</v>
       </c>
       <c r="AY5">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BA5">
         <v>4.1</v>
@@ -1647,7 +1668,7 @@
         <v>4.2</v>
       </c>
       <c r="BH5" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:60">
@@ -1655,16 +1676,16 @@
         <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F6">
         <v>1.04</v>
@@ -1775,52 +1796,52 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
         <v>1.01</v>
@@ -1829,7 +1850,7 @@
         <v>1.01</v>
       </c>
       <c r="BH6" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:60">
@@ -1837,363 +1858,363 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F7">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="G7">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="H7">
-        <v>1.77</v>
+        <v>1.04</v>
       </c>
       <c r="I7">
-        <v>1.81</v>
+        <v>1000</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="K7">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>4.1</v>
+        <v>1.25</v>
       </c>
       <c r="O7">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="P7">
-        <v>2.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q7">
-        <v>1.79</v>
+        <v>1.31</v>
       </c>
       <c r="R7">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="S7">
-        <v>2.98</v>
+        <v>1.31</v>
       </c>
       <c r="T7">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="U7">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="W7">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:60">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F8">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="G8">
-        <v>1.53</v>
+        <v>1000</v>
       </c>
       <c r="H8">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="I8">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="K8">
-        <v>5.7</v>
+        <v>950</v>
       </c>
       <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>1.25</v>
+      </c>
+      <c r="O8">
+        <v>1.29</v>
+      </c>
+      <c r="P8">
         <v>1.24</v>
       </c>
-      <c r="M8">
-        <v>1.01</v>
-      </c>
-      <c r="N8">
-        <v>5.5</v>
-      </c>
-      <c r="O8">
+      <c r="Q8">
+        <v>1.29</v>
+      </c>
+      <c r="R8">
         <v>1.18</v>
       </c>
-      <c r="P8">
-        <v>2.52</v>
-      </c>
-      <c r="Q8">
-        <v>1.54</v>
-      </c>
-      <c r="R8">
-        <v>1.61</v>
-      </c>
       <c r="S8">
-        <v>2.34</v>
+        <v>1.29</v>
       </c>
       <c r="T8">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
         <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
         <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
         <v>1.01</v>
       </c>
       <c r="BH8" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:60">
@@ -2201,181 +2222,181 @@
         <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F9">
-        <v>2.48</v>
+        <v>4.9</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="H9">
-        <v>2.58</v>
+        <v>1.77</v>
       </c>
       <c r="I9">
-        <v>2.98</v>
+        <v>1.81</v>
       </c>
       <c r="J9">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <v>4.3</v>
       </c>
       <c r="L9">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="M9">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="O9">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="P9">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q9">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="R9">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S9">
-        <v>2.6</v>
+        <v>2.98</v>
       </c>
       <c r="T9">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="U9">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>2.22</v>
       </c>
       <c r="W9">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="X9">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Y9">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AA9">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="AB9">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AC9">
         <v>10.5</v>
       </c>
       <c r="AD9">
+        <v>11</v>
+      </c>
+      <c r="AE9">
+        <v>19</v>
+      </c>
+      <c r="AF9">
+        <v>42</v>
+      </c>
+      <c r="AG9">
+        <v>21</v>
+      </c>
+      <c r="AH9">
+        <v>20</v>
+      </c>
+      <c r="AI9">
+        <v>38</v>
+      </c>
+      <c r="AJ9">
+        <v>140</v>
+      </c>
+      <c r="AK9">
+        <v>75</v>
+      </c>
+      <c r="AL9">
+        <v>75</v>
+      </c>
+      <c r="AM9">
+        <v>110</v>
+      </c>
+      <c r="AN9">
+        <v>80</v>
+      </c>
+      <c r="AO9">
+        <v>10.5</v>
+      </c>
+      <c r="AP9">
         <v>15</v>
       </c>
-      <c r="AE9">
-        <v>32</v>
-      </c>
-      <c r="AF9">
-        <v>23</v>
-      </c>
-      <c r="AG9">
-        <v>14.5</v>
-      </c>
-      <c r="AH9">
-        <v>970</v>
-      </c>
-      <c r="AI9">
-        <v>40</v>
-      </c>
-      <c r="AJ9">
-        <v>44</v>
-      </c>
-      <c r="AK9">
-        <v>30</v>
-      </c>
-      <c r="AL9">
-        <v>38</v>
-      </c>
-      <c r="AM9">
-        <v>75</v>
-      </c>
-      <c r="AN9">
-        <v>19</v>
-      </c>
-      <c r="AO9">
-        <v>21</v>
-      </c>
-      <c r="AP9">
-        <v>16</v>
-      </c>
       <c r="AQ9">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR9">
+        <v>9.4</v>
+      </c>
+      <c r="AS9">
+        <v>15</v>
+      </c>
+      <c r="AT9">
         <v>16.5</v>
       </c>
-      <c r="AS9">
-        <v>30</v>
-      </c>
-      <c r="AT9">
-        <v>11</v>
-      </c>
       <c r="AU9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV9">
+        <v>8.6</v>
+      </c>
+      <c r="AW9">
+        <v>15</v>
+      </c>
+      <c r="AX9">
+        <v>6.6</v>
+      </c>
+      <c r="AY9">
+        <v>17.5</v>
+      </c>
+      <c r="AZ9">
+        <v>16.5</v>
+      </c>
+      <c r="BA9">
+        <v>6.4</v>
+      </c>
+      <c r="BB9">
+        <v>7.4</v>
+      </c>
+      <c r="BC9">
+        <v>7</v>
+      </c>
+      <c r="BD9">
+        <v>7</v>
+      </c>
+      <c r="BE9">
+        <v>7.4</v>
+      </c>
+      <c r="BF9">
         <v>7.2</v>
       </c>
-      <c r="AV9">
-        <v>11</v>
-      </c>
-      <c r="AW9">
-        <v>20</v>
-      </c>
-      <c r="AX9">
-        <v>15</v>
-      </c>
-      <c r="AY9">
-        <v>9.6</v>
-      </c>
-      <c r="AZ9">
-        <v>11.5</v>
-      </c>
-      <c r="BA9">
-        <v>4.5</v>
-      </c>
-      <c r="BB9">
-        <v>28</v>
-      </c>
-      <c r="BC9">
-        <v>19.5</v>
-      </c>
-      <c r="BD9">
-        <v>24</v>
-      </c>
-      <c r="BE9">
-        <v>4.7</v>
-      </c>
-      <c r="BF9">
-        <v>12.5</v>
-      </c>
       <c r="BG9">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH9" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:60">
@@ -2383,545 +2404,545 @@
         <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F10">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G10">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H10">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="I10">
-        <v>16</v>
+        <v>8.4</v>
       </c>
       <c r="J10">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="K10">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="L10">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="M10">
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="O10">
         <v>1.18</v>
       </c>
       <c r="P10">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="Q10">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="R10">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="S10">
         <v>2.34</v>
       </c>
       <c r="T10">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V10">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="W10">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X10">
+        <v>32</v>
+      </c>
+      <c r="Y10">
+        <v>38</v>
+      </c>
+      <c r="Z10">
+        <v>80</v>
+      </c>
+      <c r="AA10">
+        <v>230</v>
+      </c>
+      <c r="AB10">
+        <v>12</v>
+      </c>
+      <c r="AC10">
+        <v>13</v>
+      </c>
+      <c r="AD10">
+        <v>950</v>
+      </c>
+      <c r="AE10">
+        <v>110</v>
+      </c>
+      <c r="AF10">
+        <v>11.5</v>
+      </c>
+      <c r="AG10">
+        <v>11</v>
+      </c>
+      <c r="AH10">
+        <v>23</v>
+      </c>
+      <c r="AI10">
+        <v>85</v>
+      </c>
+      <c r="AJ10">
+        <v>14.5</v>
+      </c>
+      <c r="AK10">
+        <v>15.5</v>
+      </c>
+      <c r="AL10">
         <v>34</v>
       </c>
-      <c r="Y10">
-        <v>44</v>
-      </c>
-      <c r="Z10">
-        <v>1000</v>
-      </c>
-      <c r="AA10">
-        <v>1000</v>
-      </c>
-      <c r="AB10">
-        <v>970</v>
-      </c>
-      <c r="AC10">
-        <v>970</v>
-      </c>
-      <c r="AD10">
-        <v>44</v>
-      </c>
-      <c r="AE10">
-        <v>1000</v>
-      </c>
-      <c r="AF10">
-        <v>970</v>
-      </c>
-      <c r="AG10">
-        <v>970</v>
-      </c>
-      <c r="AH10">
-        <v>32</v>
-      </c>
-      <c r="AI10">
-        <v>1000</v>
-      </c>
-      <c r="AJ10">
-        <v>970</v>
-      </c>
-      <c r="AK10">
+      <c r="AM10">
+        <v>110</v>
+      </c>
+      <c r="AN10">
+        <v>5.7</v>
+      </c>
+      <c r="AO10">
+        <v>110</v>
+      </c>
+      <c r="AP10">
         <v>20</v>
       </c>
-      <c r="AL10">
-        <v>46</v>
-      </c>
-      <c r="AM10">
-        <v>1000</v>
-      </c>
-      <c r="AN10">
-        <v>1000</v>
-      </c>
-      <c r="AO10">
-        <v>1000</v>
-      </c>
-      <c r="AP10">
-        <v>1.01</v>
-      </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AT10">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AX10">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY10">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH10" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:60">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F11">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G11">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="H11">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="I11">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="J11">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K11">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L11">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M11">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O11">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P11">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q11">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="R11">
         <v>1.49</v>
       </c>
       <c r="S11">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T11">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="U11">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V11">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W11">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="X11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y11">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Z11">
         <v>24</v>
       </c>
       <c r="AA11">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AB11">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AC11">
         <v>10.5</v>
       </c>
       <c r="AD11">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AE11">
         <v>32</v>
       </c>
       <c r="AF11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG11">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH11">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AI11">
         <v>40</v>
       </c>
       <c r="AJ11">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK11">
         <v>32</v>
       </c>
       <c r="AL11">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM11">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN11">
         <v>21</v>
       </c>
       <c r="AO11">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP11">
-        <v>4.3</v>
+        <v>15.5</v>
       </c>
       <c r="AQ11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR11">
-        <v>4.3</v>
+        <v>15.5</v>
       </c>
       <c r="AS11">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AT11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU11">
         <v>7</v>
       </c>
       <c r="AV11">
+        <v>9.6</v>
+      </c>
+      <c r="AW11">
+        <v>20</v>
+      </c>
+      <c r="AX11">
+        <v>15.5</v>
+      </c>
+      <c r="AY11">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AW11">
-        <v>4.5</v>
-      </c>
-      <c r="AX11">
-        <v>4.3</v>
-      </c>
-      <c r="AY11">
-        <v>9.6</v>
       </c>
       <c r="AZ11">
         <v>11.5</v>
       </c>
       <c r="BA11">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BB11">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BC11">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BD11">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BE11">
-        <v>4.9</v>
+        <v>46</v>
       </c>
       <c r="BF11">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="BG11">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="BH11" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:60">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F12">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="G12">
+        <v>1.52</v>
+      </c>
+      <c r="H12">
         <v>6.8</v>
       </c>
-      <c r="H12">
-        <v>1.74</v>
-      </c>
       <c r="I12">
-        <v>1.9</v>
+        <v>10.5</v>
       </c>
       <c r="J12">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="L12">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="M12">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="P12">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="Q12">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="R12">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="S12">
-        <v>4.1</v>
+        <v>2.34</v>
       </c>
       <c r="T12">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="U12">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="V12">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="W12">
-        <v>1.18</v>
+        <v>2.82</v>
       </c>
       <c r="X12">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="Y12">
-        <v>8.199999999999999</v>
+        <v>950</v>
       </c>
       <c r="Z12">
+        <v>85</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>12</v>
+      </c>
+      <c r="AC12">
+        <v>14</v>
+      </c>
+      <c r="AD12">
+        <v>950</v>
+      </c>
+      <c r="AE12">
+        <v>130</v>
+      </c>
+      <c r="AF12">
         <v>11.5</v>
       </c>
-      <c r="AA12">
+      <c r="AG12">
+        <v>12</v>
+      </c>
+      <c r="AH12">
+        <v>950</v>
+      </c>
+      <c r="AI12">
+        <v>110</v>
+      </c>
+      <c r="AJ12">
+        <v>970</v>
+      </c>
+      <c r="AK12">
+        <v>970</v>
+      </c>
+      <c r="AL12">
+        <v>38</v>
+      </c>
+      <c r="AM12">
+        <v>130</v>
+      </c>
+      <c r="AN12">
+        <v>6.6</v>
+      </c>
+      <c r="AO12">
+        <v>140</v>
+      </c>
+      <c r="AP12">
+        <v>18</v>
+      </c>
+      <c r="AQ12">
         <v>23</v>
       </c>
-      <c r="AB12">
-        <v>18.5</v>
-      </c>
-      <c r="AC12">
-        <v>9.6</v>
-      </c>
-      <c r="AD12">
-        <v>12</v>
-      </c>
-      <c r="AE12">
-        <v>26</v>
-      </c>
-      <c r="AF12">
-        <v>55</v>
-      </c>
-      <c r="AG12">
-        <v>27</v>
-      </c>
-      <c r="AH12">
-        <v>28</v>
-      </c>
-      <c r="AI12">
-        <v>55</v>
-      </c>
-      <c r="AJ12">
-        <v>200</v>
-      </c>
-      <c r="AK12">
-        <v>110</v>
-      </c>
-      <c r="AL12">
-        <v>120</v>
-      </c>
-      <c r="AM12">
-        <v>190</v>
-      </c>
-      <c r="AN12">
-        <v>170</v>
-      </c>
-      <c r="AO12">
-        <v>18</v>
-      </c>
-      <c r="AP12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ12">
-        <v>5.6</v>
-      </c>
       <c r="AR12">
+        <v>4.8</v>
+      </c>
+      <c r="AS12">
+        <v>5</v>
+      </c>
+      <c r="AT12">
+        <v>7.8</v>
+      </c>
+      <c r="AU12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV12">
+        <v>4.4</v>
+      </c>
+      <c r="AW12">
+        <v>4.9</v>
+      </c>
+      <c r="AX12">
         <v>7.6</v>
       </c>
-      <c r="AS12">
-        <v>15</v>
-      </c>
-      <c r="AT12">
-        <v>12</v>
-      </c>
-      <c r="AU12">
-        <v>6.4</v>
-      </c>
-      <c r="AV12">
+      <c r="AY12">
         <v>8</v>
       </c>
-      <c r="AW12">
-        <v>16.5</v>
-      </c>
-      <c r="AX12">
-        <v>4.7</v>
-      </c>
-      <c r="AY12">
-        <v>17.5</v>
-      </c>
       <c r="AZ12">
-        <v>18</v>
+        <v>4.2</v>
       </c>
       <c r="BA12">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB12">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC12">
+        <v>11</v>
+      </c>
+      <c r="BD12">
+        <v>4.4</v>
+      </c>
+      <c r="BE12">
         <v>4.9</v>
       </c>
-      <c r="BD12">
+      <c r="BF12">
+        <v>4.5</v>
+      </c>
+      <c r="BG12">
         <v>4.9</v>
       </c>
-      <c r="BE12">
-        <v>5</v>
-      </c>
-      <c r="BF12">
-        <v>5</v>
-      </c>
-      <c r="BG12">
-        <v>12</v>
-      </c>
       <c r="BH12" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:60">
@@ -2929,67 +2950,67 @@
         <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F13">
         <v>2.02</v>
       </c>
       <c r="G13">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H13">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I13">
         <v>4.3</v>
       </c>
       <c r="J13">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="K13">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L13">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M13">
         <v>1.07</v>
       </c>
       <c r="N13">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O13">
         <v>1.33</v>
       </c>
       <c r="P13">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q13">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R13">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S13">
         <v>3.55</v>
       </c>
       <c r="T13">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U13">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V13">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W13">
         <v>1.78</v>
@@ -3007,22 +3028,22 @@
         <v>100</v>
       </c>
       <c r="AB13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC13">
         <v>9.6</v>
       </c>
       <c r="AD13">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE13">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH13">
         <v>23</v>
@@ -3034,7 +3055,7 @@
         <v>34</v>
       </c>
       <c r="AK13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL13">
         <v>48</v>
@@ -3043,10 +3064,10 @@
         <v>130</v>
       </c>
       <c r="AN13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO13">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP13">
         <v>11</v>
@@ -3055,16 +3076,16 @@
         <v>10</v>
       </c>
       <c r="AR13">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS13">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT13">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU13">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV13">
         <v>11.5</v>
@@ -3073,13 +3094,13 @@
         <v>4</v>
       </c>
       <c r="AX13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY13">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AZ13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA13">
         <v>4.1</v>
@@ -3088,22 +3109,22 @@
         <v>19.5</v>
       </c>
       <c r="BC13">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD13">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="BE13">
         <v>4.2</v>
       </c>
       <c r="BF13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG13">
-        <v>4.1</v>
+        <v>38</v>
       </c>
       <c r="BH13" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:60">
@@ -3111,37 +3132,37 @@
         <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F14">
         <v>7.2</v>
       </c>
       <c r="G14">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H14">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="I14">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="J14">
         <v>3.55</v>
       </c>
       <c r="K14">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L14">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="M14">
         <v>1.11</v>
@@ -3168,13 +3189,13 @@
         <v>2.52</v>
       </c>
       <c r="U14">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="V14">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="W14">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
         <v>970</v>
@@ -3204,10 +3225,10 @@
         <v>80</v>
       </c>
       <c r="AG14">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AH14">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="AI14">
         <v>85</v>
@@ -3228,7 +3249,7 @@
         <v>1000</v>
       </c>
       <c r="AO14">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AP14">
         <v>4.7</v>
@@ -3237,7 +3258,7 @@
         <v>4.9</v>
       </c>
       <c r="AR14">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="AS14">
         <v>11.5</v>
@@ -3258,7 +3279,7 @@
         <v>7.8</v>
       </c>
       <c r="AY14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AZ14">
         <v>7.2</v>
@@ -3267,7 +3288,7 @@
         <v>3.6</v>
       </c>
       <c r="BB14">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BC14">
         <v>2.42</v>
@@ -3276,7 +3297,7 @@
         <v>2.42</v>
       </c>
       <c r="BE14">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BF14">
         <v>1.95</v>
@@ -3285,7 +3306,7 @@
         <v>5.8</v>
       </c>
       <c r="BH14" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:60">
@@ -3293,85 +3314,85 @@
         <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F15">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="G15">
         <v>1.44</v>
       </c>
       <c r="H15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I15">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="J15">
         <v>4.5</v>
       </c>
       <c r="K15">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L15">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M15">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N15">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O15">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P15">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="Q15">
         <v>2.02</v>
       </c>
       <c r="R15">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S15">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="T15">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="U15">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="V15">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W15">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="X15">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y15">
         <v>29</v>
       </c>
       <c r="Z15">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA15">
         <v>1000</v>
       </c>
       <c r="AB15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC15">
         <v>12</v>
@@ -3380,10 +3401,10 @@
         <v>50</v>
       </c>
       <c r="AE15">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="AF15">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AG15">
         <v>11.5</v>
@@ -3392,28 +3413,28 @@
         <v>40</v>
       </c>
       <c r="AI15">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="AJ15">
         <v>12</v>
       </c>
       <c r="AK15">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AL15">
         <v>60</v>
       </c>
       <c r="AM15">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="AN15">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="AP15">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="AQ15">
         <v>7.2</v>
@@ -3422,22 +3443,22 @@
         <v>9</v>
       </c>
       <c r="AS15">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT15">
+        <v>5.7</v>
+      </c>
+      <c r="AU15">
         <v>5.4</v>
       </c>
-      <c r="AU15">
-        <v>9.6</v>
-      </c>
       <c r="AV15">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW15">
         <v>9.4</v>
       </c>
       <c r="AX15">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AY15">
         <v>9.199999999999999</v>
@@ -3452,7 +3473,7 @@
         <v>9.6</v>
       </c>
       <c r="BC15">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD15">
         <v>8.4</v>
@@ -3461,923 +3482,1287 @@
         <v>9.4</v>
       </c>
       <c r="BF15">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BG15">
         <v>9.6</v>
       </c>
       <c r="BH15" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:60">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F16">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="G16">
+        <v>6.8</v>
+      </c>
+      <c r="H16">
+        <v>1.74</v>
+      </c>
+      <c r="I16">
+        <v>1.89</v>
+      </c>
+      <c r="J16">
+        <v>3.5</v>
+      </c>
+      <c r="K16">
+        <v>4</v>
+      </c>
+      <c r="L16">
+        <v>1.46</v>
+      </c>
+      <c r="M16">
+        <v>1.09</v>
+      </c>
+      <c r="N16">
+        <v>3.1</v>
+      </c>
+      <c r="O16">
+        <v>1.4</v>
+      </c>
+      <c r="P16">
+        <v>1.7</v>
+      </c>
+      <c r="Q16">
+        <v>2.18</v>
+      </c>
+      <c r="R16">
+        <v>1.25</v>
+      </c>
+      <c r="S16">
+        <v>4.1</v>
+      </c>
+      <c r="T16">
+        <v>2.06</v>
+      </c>
+      <c r="U16">
+        <v>1.8</v>
+      </c>
+      <c r="V16">
+        <v>2.12</v>
+      </c>
+      <c r="W16">
+        <v>1.17</v>
+      </c>
+      <c r="X16">
         <v>13</v>
       </c>
-      <c r="H16">
-        <v>1.26</v>
-      </c>
-      <c r="I16">
-        <v>1.31</v>
-      </c>
-      <c r="J16">
-        <v>6.8</v>
-      </c>
-      <c r="K16">
-        <v>8</v>
-      </c>
-      <c r="L16">
-        <v>1.18</v>
-      </c>
-      <c r="M16">
-        <v>1.02</v>
-      </c>
-      <c r="N16">
+      <c r="Y16">
         <v>8.199999999999999</v>
       </c>
-      <c r="O16">
-        <v>1.11</v>
-      </c>
-      <c r="P16">
-        <v>3.4</v>
-      </c>
-      <c r="Q16">
-        <v>1.33</v>
-      </c>
-      <c r="R16">
-        <v>1.99</v>
-      </c>
-      <c r="S16">
-        <v>1.83</v>
-      </c>
-      <c r="T16">
-        <v>1.74</v>
-      </c>
-      <c r="U16">
-        <v>2.12</v>
-      </c>
-      <c r="V16">
-        <v>4.2</v>
-      </c>
-      <c r="W16">
-        <v>1.08</v>
-      </c>
-      <c r="X16">
-        <v>50</v>
-      </c>
-      <c r="Y16">
-        <v>16</v>
-      </c>
       <c r="Z16">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA16">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AB16">
-        <v>65</v>
+        <v>18.5</v>
       </c>
       <c r="AC16">
-        <v>19</v>
+        <v>9.6</v>
       </c>
       <c r="AD16">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE16">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AF16">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AG16">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AH16">
         <v>28</v>
       </c>
       <c r="AI16">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AJ16">
-        <v>390</v>
+        <v>200</v>
       </c>
       <c r="AK16">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AL16">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AM16">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="AN16">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AO16">
-        <v>3.35</v>
+        <v>18</v>
       </c>
       <c r="AP16">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ16">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="AR16">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AS16">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="AT16">
-        <v>42</v>
+        <v>13.5</v>
       </c>
       <c r="AU16">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AV16">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW16">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AX16">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="AY16">
-        <v>8</v>
+        <v>17.5</v>
       </c>
       <c r="AZ16">
-        <v>7.2</v>
+        <v>19.5</v>
       </c>
       <c r="BA16">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BB16">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="BC16">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="BD16">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BE16">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BF16">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BG16">
-        <v>2.88</v>
+        <v>12</v>
       </c>
       <c r="BH16" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:60">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F17">
-        <v>1.02</v>
+        <v>2.58</v>
       </c>
       <c r="G17">
-        <v>990</v>
+        <v>2.9</v>
       </c>
       <c r="H17">
-        <v>1.02</v>
+        <v>2.6</v>
       </c>
       <c r="I17">
-        <v>1000</v>
+        <v>2.86</v>
       </c>
       <c r="J17">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="K17">
+        <v>4.4</v>
+      </c>
+      <c r="L17">
+        <v>1.34</v>
+      </c>
+      <c r="M17">
+        <v>1.05</v>
+      </c>
+      <c r="N17">
+        <v>4.6</v>
+      </c>
+      <c r="O17">
+        <v>1.24</v>
+      </c>
+      <c r="P17">
+        <v>2.24</v>
+      </c>
+      <c r="Q17">
+        <v>1.7</v>
+      </c>
+      <c r="R17">
+        <v>1.49</v>
+      </c>
+      <c r="S17">
+        <v>2.62</v>
+      </c>
+      <c r="T17">
+        <v>1.61</v>
+      </c>
+      <c r="U17">
+        <v>2.42</v>
+      </c>
+      <c r="V17">
+        <v>1.54</v>
+      </c>
+      <c r="W17">
+        <v>1.53</v>
+      </c>
+      <c r="X17">
         <v>950</v>
       </c>
-      <c r="L17">
-        <v>1.01</v>
-      </c>
-      <c r="M17">
-        <v>1.01</v>
-      </c>
-      <c r="N17">
-        <v>1.1</v>
-      </c>
-      <c r="O17">
-        <v>1.01</v>
-      </c>
-      <c r="P17">
-        <v>1.08</v>
-      </c>
-      <c r="Q17">
-        <v>1.02</v>
-      </c>
-      <c r="R17">
-        <v>1.08</v>
-      </c>
-      <c r="S17">
-        <v>1.33</v>
-      </c>
-      <c r="T17">
-        <v>1.11</v>
-      </c>
-      <c r="U17">
-        <v>1.11</v>
-      </c>
-      <c r="V17">
-        <v>1.01</v>
-      </c>
-      <c r="W17">
-        <v>1.01</v>
-      </c>
-      <c r="X17">
-        <v>1000</v>
-      </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH17" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:60">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F18">
-        <v>2.26</v>
+        <v>10.5</v>
       </c>
       <c r="G18">
-        <v>2.3</v>
+        <v>12.5</v>
       </c>
       <c r="H18">
-        <v>3.45</v>
+        <v>1.26</v>
       </c>
       <c r="I18">
-        <v>3.55</v>
+        <v>1.32</v>
       </c>
       <c r="J18">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="K18">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M18">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="N18">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="P18">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
       <c r="Q18">
-        <v>2.04</v>
+        <v>1.34</v>
       </c>
       <c r="R18">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="S18">
-        <v>3.7</v>
+        <v>1.84</v>
       </c>
       <c r="T18">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U18">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V18">
-        <v>1.39</v>
+        <v>4.2</v>
       </c>
       <c r="W18">
-        <v>1.76</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>970</v>
+        <v>50</v>
       </c>
       <c r="Y18">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="Z18">
-        <v>24</v>
+        <v>12.5</v>
       </c>
       <c r="AA18">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="AB18">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="AC18">
+        <v>19</v>
+      </c>
+      <c r="AD18">
+        <v>12.5</v>
+      </c>
+      <c r="AE18">
+        <v>14</v>
+      </c>
+      <c r="AF18">
+        <v>120</v>
+      </c>
+      <c r="AG18">
+        <v>44</v>
+      </c>
+      <c r="AH18">
+        <v>28</v>
+      </c>
+      <c r="AI18">
+        <v>28</v>
+      </c>
+      <c r="AJ18">
+        <v>390</v>
+      </c>
+      <c r="AK18">
+        <v>140</v>
+      </c>
+      <c r="AL18">
+        <v>100</v>
+      </c>
+      <c r="AM18">
+        <v>100</v>
+      </c>
+      <c r="AN18">
+        <v>130</v>
+      </c>
+      <c r="AO18">
+        <v>3.35</v>
+      </c>
+      <c r="AP18">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD18">
-        <v>970</v>
-      </c>
-      <c r="AE18">
-        <v>46</v>
-      </c>
-      <c r="AF18">
-        <v>15.5</v>
-      </c>
-      <c r="AG18">
-        <v>11.5</v>
-      </c>
-      <c r="AH18">
-        <v>970</v>
-      </c>
-      <c r="AI18">
-        <v>60</v>
-      </c>
-      <c r="AJ18">
-        <v>38</v>
-      </c>
-      <c r="AK18">
-        <v>30</v>
-      </c>
-      <c r="AL18">
-        <v>44</v>
-      </c>
-      <c r="AM18">
-        <v>110</v>
-      </c>
-      <c r="AN18">
-        <v>970</v>
-      </c>
-      <c r="AO18">
-        <v>44</v>
-      </c>
-      <c r="AP18">
-        <v>6</v>
-      </c>
       <c r="AQ18">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="AR18">
+        <v>10</v>
+      </c>
+      <c r="AS18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT18">
+        <v>8.4</v>
+      </c>
+      <c r="AU18">
+        <v>14</v>
+      </c>
+      <c r="AV18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW18">
+        <v>11</v>
+      </c>
+      <c r="AX18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY18">
+        <v>8</v>
+      </c>
+      <c r="AZ18">
         <v>7.2</v>
       </c>
-      <c r="AS18">
+      <c r="BA18">
+        <v>7.2</v>
+      </c>
+      <c r="BB18">
+        <v>9.6</v>
+      </c>
+      <c r="BC18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD18">
         <v>9</v>
       </c>
-      <c r="AT18">
-        <v>5.2</v>
-      </c>
-      <c r="AU18">
-        <v>4.5</v>
-      </c>
-      <c r="AV18">
-        <v>6</v>
-      </c>
-      <c r="AW18">
-        <v>8.4</v>
-      </c>
-      <c r="AX18">
-        <v>6.2</v>
-      </c>
-      <c r="AY18">
-        <v>5.4</v>
-      </c>
-      <c r="AZ18">
-        <v>6.4</v>
-      </c>
-      <c r="BA18">
-        <v>8.6</v>
-      </c>
-      <c r="BB18">
-        <v>8</v>
-      </c>
-      <c r="BC18">
-        <v>7.6</v>
-      </c>
-      <c r="BD18">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE18">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BF18">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG18">
-        <v>8.199999999999999</v>
+        <v>2.88</v>
       </c>
       <c r="BH18" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:60">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E19" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F19">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="G19">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="H19">
-        <v>2.82</v>
+        <v>3.45</v>
       </c>
       <c r="I19">
+        <v>3.55</v>
+      </c>
+      <c r="J19">
         <v>3.5</v>
       </c>
-      <c r="J19">
-        <v>3</v>
-      </c>
       <c r="K19">
+        <v>3.6</v>
+      </c>
+      <c r="L19">
+        <v>1.41</v>
+      </c>
+      <c r="M19">
+        <v>1.07</v>
+      </c>
+      <c r="N19">
+        <v>3.6</v>
+      </c>
+      <c r="O19">
+        <v>1.32</v>
+      </c>
+      <c r="P19">
+        <v>1.91</v>
+      </c>
+      <c r="Q19">
+        <v>2.04</v>
+      </c>
+      <c r="R19">
+        <v>1.35</v>
+      </c>
+      <c r="S19">
         <v>3.7</v>
       </c>
-      <c r="L19">
-        <v>1.43</v>
-      </c>
-      <c r="M19">
-        <v>1.08</v>
-      </c>
-      <c r="N19">
-        <v>3</v>
-      </c>
-      <c r="O19">
-        <v>1.35</v>
-      </c>
-      <c r="P19">
-        <v>1.7</v>
-      </c>
-      <c r="Q19">
-        <v>1.94</v>
-      </c>
-      <c r="R19">
-        <v>1.29</v>
-      </c>
-      <c r="S19">
-        <v>3.4</v>
-      </c>
       <c r="T19">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="U19">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="V19">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W19">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="X19">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Y19">
         <v>13.5</v>
       </c>
       <c r="Z19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA19">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB19">
+        <v>10.5</v>
+      </c>
+      <c r="AC19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD19">
+        <v>970</v>
+      </c>
+      <c r="AE19">
+        <v>40</v>
+      </c>
+      <c r="AF19">
+        <v>15.5</v>
+      </c>
+      <c r="AG19">
         <v>11.5</v>
       </c>
-      <c r="AC19">
+      <c r="AH19">
+        <v>970</v>
+      </c>
+      <c r="AI19">
+        <v>55</v>
+      </c>
+      <c r="AJ19">
+        <v>32</v>
+      </c>
+      <c r="AK19">
+        <v>26</v>
+      </c>
+      <c r="AL19">
+        <v>44</v>
+      </c>
+      <c r="AM19">
+        <v>110</v>
+      </c>
+      <c r="AN19">
+        <v>970</v>
+      </c>
+      <c r="AO19">
+        <v>38</v>
+      </c>
+      <c r="AP19">
+        <v>6.6</v>
+      </c>
+      <c r="AQ19">
+        <v>6.4</v>
+      </c>
+      <c r="AR19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS19">
+        <v>10</v>
+      </c>
+      <c r="AT19">
+        <v>5.7</v>
+      </c>
+      <c r="AU19">
+        <v>4.9</v>
+      </c>
+      <c r="AV19">
+        <v>6.6</v>
+      </c>
+      <c r="AW19">
+        <v>9.4</v>
+      </c>
+      <c r="AX19">
+        <v>6.8</v>
+      </c>
+      <c r="AY19">
+        <v>5.9</v>
+      </c>
+      <c r="AZ19">
+        <v>7.2</v>
+      </c>
+      <c r="BA19">
+        <v>10</v>
+      </c>
+      <c r="BB19">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD19">
-        <v>16</v>
-      </c>
-      <c r="AE19">
-        <v>46</v>
-      </c>
-      <c r="AF19">
-        <v>18.5</v>
-      </c>
-      <c r="AG19">
-        <v>14</v>
-      </c>
-      <c r="AH19">
-        <v>21</v>
-      </c>
-      <c r="AI19">
-        <v>60</v>
-      </c>
-      <c r="AJ19">
-        <v>42</v>
-      </c>
-      <c r="AK19">
-        <v>34</v>
-      </c>
-      <c r="AL19">
-        <v>55</v>
-      </c>
-      <c r="AM19">
-        <v>120</v>
-      </c>
-      <c r="AN19">
-        <v>30</v>
-      </c>
-      <c r="AO19">
-        <v>46</v>
-      </c>
-      <c r="AP19">
-        <v>3.8</v>
-      </c>
-      <c r="AQ19">
-        <v>3.75</v>
-      </c>
-      <c r="AR19">
-        <v>4.3</v>
-      </c>
-      <c r="AS19">
-        <v>4.8</v>
-      </c>
-      <c r="AT19">
-        <v>3.55</v>
-      </c>
-      <c r="AU19">
-        <v>3.25</v>
-      </c>
-      <c r="AV19">
-        <v>3.9</v>
-      </c>
-      <c r="AW19">
-        <v>4.6</v>
-      </c>
-      <c r="AX19">
-        <v>4</v>
-      </c>
-      <c r="AY19">
-        <v>3.75</v>
-      </c>
-      <c r="AZ19">
-        <v>4.1</v>
-      </c>
-      <c r="BA19">
-        <v>4.7</v>
-      </c>
-      <c r="BB19">
-        <v>4.6</v>
-      </c>
       <c r="BC19">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="BD19">
-        <v>4.7</v>
+        <v>9.6</v>
       </c>
       <c r="BE19">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF19">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG19">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH19" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:60">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E20" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F20">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="G20">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="H20">
-        <v>5.6</v>
+        <v>2.82</v>
       </c>
       <c r="I20">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="J20">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="K20">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L20">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M20">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N20">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="O20">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P20">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="Q20">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R20">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="S20">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T20">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="U20">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="V20">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="X20">
         <v>14.5</v>
       </c>
       <c r="Y20">
+        <v>13.5</v>
+      </c>
+      <c r="Z20">
+        <v>25</v>
+      </c>
+      <c r="AA20">
+        <v>65</v>
+      </c>
+      <c r="AB20">
+        <v>11.5</v>
+      </c>
+      <c r="AC20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD20">
+        <v>16</v>
+      </c>
+      <c r="AE20">
+        <v>46</v>
+      </c>
+      <c r="AF20">
         <v>18.5</v>
       </c>
-      <c r="Z20">
+      <c r="AG20">
+        <v>14</v>
+      </c>
+      <c r="AH20">
+        <v>21</v>
+      </c>
+      <c r="AI20">
+        <v>60</v>
+      </c>
+      <c r="AJ20">
+        <v>42</v>
+      </c>
+      <c r="AK20">
+        <v>34</v>
+      </c>
+      <c r="AL20">
+        <v>55</v>
+      </c>
+      <c r="AM20">
+        <v>120</v>
+      </c>
+      <c r="AN20">
+        <v>30</v>
+      </c>
+      <c r="AO20">
+        <v>46</v>
+      </c>
+      <c r="AP20">
+        <v>3.8</v>
+      </c>
+      <c r="AQ20">
+        <v>3.75</v>
+      </c>
+      <c r="AR20">
+        <v>4.3</v>
+      </c>
+      <c r="AS20">
+        <v>4.8</v>
+      </c>
+      <c r="AT20">
+        <v>3.55</v>
+      </c>
+      <c r="AU20">
+        <v>3.25</v>
+      </c>
+      <c r="AV20">
+        <v>3.9</v>
+      </c>
+      <c r="AW20">
+        <v>4.6</v>
+      </c>
+      <c r="AX20">
+        <v>4</v>
+      </c>
+      <c r="AY20">
+        <v>3.75</v>
+      </c>
+      <c r="AZ20">
+        <v>4.1</v>
+      </c>
+      <c r="BA20">
+        <v>4.7</v>
+      </c>
+      <c r="BB20">
+        <v>4.6</v>
+      </c>
+      <c r="BC20">
+        <v>4.5</v>
+      </c>
+      <c r="BD20">
+        <v>4.7</v>
+      </c>
+      <c r="BE20">
+        <v>4.9</v>
+      </c>
+      <c r="BF20">
+        <v>4.4</v>
+      </c>
+      <c r="BG20">
+        <v>4.6</v>
+      </c>
+      <c r="BH20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:60">
+      <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21">
+        <v>1.04</v>
+      </c>
+      <c r="G21">
+        <v>990</v>
+      </c>
+      <c r="H21">
+        <v>1.04</v>
+      </c>
+      <c r="I21">
+        <v>990</v>
+      </c>
+      <c r="J21">
+        <v>1.03</v>
+      </c>
+      <c r="K21">
+        <v>950</v>
+      </c>
+      <c r="L21">
+        <v>1.01</v>
+      </c>
+      <c r="M21">
+        <v>1.01</v>
+      </c>
+      <c r="N21">
+        <v>1.1</v>
+      </c>
+      <c r="O21">
+        <v>1.01</v>
+      </c>
+      <c r="P21">
+        <v>1.08</v>
+      </c>
+      <c r="Q21">
+        <v>1.02</v>
+      </c>
+      <c r="R21">
+        <v>1.08</v>
+      </c>
+      <c r="S21">
+        <v>1.33</v>
+      </c>
+      <c r="T21">
+        <v>1.11</v>
+      </c>
+      <c r="U21">
+        <v>1.11</v>
+      </c>
+      <c r="V21">
+        <v>1.01</v>
+      </c>
+      <c r="W21">
+        <v>1.01</v>
+      </c>
+      <c r="X21">
+        <v>1000</v>
+      </c>
+      <c r="Y21">
+        <v>1000</v>
+      </c>
+      <c r="Z21">
+        <v>1000</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>1000</v>
+      </c>
+      <c r="AC21">
+        <v>1000</v>
+      </c>
+      <c r="AD21">
+        <v>1000</v>
+      </c>
+      <c r="AE21">
+        <v>1000</v>
+      </c>
+      <c r="AF21">
+        <v>1000</v>
+      </c>
+      <c r="AG21">
+        <v>1000</v>
+      </c>
+      <c r="AH21">
+        <v>1000</v>
+      </c>
+      <c r="AI21">
+        <v>1000</v>
+      </c>
+      <c r="AJ21">
+        <v>1000</v>
+      </c>
+      <c r="AK21">
+        <v>1000</v>
+      </c>
+      <c r="AL21">
+        <v>1000</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>1000</v>
+      </c>
+      <c r="AO21">
+        <v>1000</v>
+      </c>
+      <c r="AP21">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21">
+        <v>1.01</v>
+      </c>
+      <c r="AR21">
+        <v>1.01</v>
+      </c>
+      <c r="AS21">
+        <v>1.01</v>
+      </c>
+      <c r="AT21">
+        <v>1.01</v>
+      </c>
+      <c r="AU21">
+        <v>1.01</v>
+      </c>
+      <c r="AV21">
+        <v>1.01</v>
+      </c>
+      <c r="AW21">
+        <v>1.01</v>
+      </c>
+      <c r="AX21">
+        <v>1.01</v>
+      </c>
+      <c r="AY21">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21">
+        <v>1.01</v>
+      </c>
+      <c r="BA21">
+        <v>1.01</v>
+      </c>
+      <c r="BB21">
+        <v>1.01</v>
+      </c>
+      <c r="BC21">
+        <v>1.01</v>
+      </c>
+      <c r="BD21">
+        <v>1.01</v>
+      </c>
+      <c r="BE21">
+        <v>1.01</v>
+      </c>
+      <c r="BF21">
+        <v>1.01</v>
+      </c>
+      <c r="BG21">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:60">
+      <c r="A22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" t="s">
+        <v>127</v>
+      </c>
+      <c r="F22">
+        <v>1.7</v>
+      </c>
+      <c r="G22">
+        <v>1.71</v>
+      </c>
+      <c r="H22">
+        <v>5.7</v>
+      </c>
+      <c r="I22">
+        <v>5.8</v>
+      </c>
+      <c r="J22">
+        <v>4.2</v>
+      </c>
+      <c r="K22">
+        <v>4.3</v>
+      </c>
+      <c r="L22">
+        <v>1.41</v>
+      </c>
+      <c r="M22">
+        <v>1.07</v>
+      </c>
+      <c r="N22">
+        <v>3.9</v>
+      </c>
+      <c r="O22">
+        <v>1.32</v>
+      </c>
+      <c r="P22">
+        <v>1.98</v>
+      </c>
+      <c r="Q22">
+        <v>1.98</v>
+      </c>
+      <c r="R22">
+        <v>1.37</v>
+      </c>
+      <c r="S22">
+        <v>3.55</v>
+      </c>
+      <c r="T22">
+        <v>1.98</v>
+      </c>
+      <c r="U22">
+        <v>1.97</v>
+      </c>
+      <c r="V22">
+        <v>1.21</v>
+      </c>
+      <c r="W22">
+        <v>2.4</v>
+      </c>
+      <c r="X22">
+        <v>14.5</v>
+      </c>
+      <c r="Y22">
+        <v>19</v>
+      </c>
+      <c r="Z22">
         <v>44</v>
       </c>
-      <c r="AA20">
+      <c r="AA22">
         <v>170</v>
       </c>
-      <c r="AB20">
+      <c r="AB22">
         <v>8.4</v>
       </c>
-      <c r="AC20">
+      <c r="AC22">
         <v>9</v>
       </c>
-      <c r="AD20">
+      <c r="AD22">
         <v>21</v>
       </c>
-      <c r="AE20">
+      <c r="AE22">
         <v>80</v>
       </c>
-      <c r="AF20">
+      <c r="AF22">
         <v>9.4</v>
       </c>
-      <c r="AG20">
+      <c r="AG22">
         <v>9.800000000000001</v>
       </c>
-      <c r="AH20">
+      <c r="AH22">
         <v>22</v>
       </c>
-      <c r="AI20">
+      <c r="AI22">
         <v>85</v>
       </c>
-      <c r="AJ20">
+      <c r="AJ22">
         <v>16</v>
       </c>
-      <c r="AK20">
+      <c r="AK22">
         <v>17.5</v>
       </c>
-      <c r="AL20">
+      <c r="AL22">
         <v>38</v>
       </c>
-      <c r="AM20">
+      <c r="AM22">
         <v>130</v>
       </c>
-      <c r="AN20">
+      <c r="AN22">
         <v>10</v>
       </c>
-      <c r="AO20">
+      <c r="AO22">
         <v>95</v>
       </c>
-      <c r="AP20">
+      <c r="AP22">
         <v>14</v>
       </c>
-      <c r="AQ20">
+      <c r="AQ22">
         <v>17.5</v>
       </c>
-      <c r="AR20">
+      <c r="AR22">
         <v>40</v>
       </c>
-      <c r="AS20">
+      <c r="AS22">
         <v>70</v>
       </c>
-      <c r="AT20">
-        <v>7.8</v>
-      </c>
-      <c r="AU20">
+      <c r="AT22">
+        <v>8</v>
+      </c>
+      <c r="AU22">
         <v>8.6</v>
       </c>
-      <c r="AV20">
+      <c r="AV22">
         <v>20</v>
       </c>
-      <c r="AW20">
+      <c r="AW22">
         <v>70</v>
       </c>
-      <c r="AX20">
+      <c r="AX22">
         <v>9</v>
       </c>
-      <c r="AY20">
+      <c r="AY22">
         <v>9.4</v>
       </c>
-      <c r="AZ20">
+      <c r="AZ22">
         <v>20</v>
       </c>
-      <c r="BA20">
+      <c r="BA22">
         <v>55</v>
       </c>
-      <c r="BB20">
+      <c r="BB22">
         <v>14.5</v>
       </c>
-      <c r="BC20">
+      <c r="BC22">
         <v>16</v>
       </c>
-      <c r="BD20">
+      <c r="BD22">
         <v>34</v>
       </c>
-      <c r="BE20">
-        <v>100</v>
-      </c>
-      <c r="BF20">
+      <c r="BE22">
+        <v>110</v>
+      </c>
+      <c r="BF22">
         <v>9.4</v>
       </c>
-      <c r="BG20">
-        <v>70</v>
-      </c>
-      <c r="BH20" t="s">
-        <v>121</v>
+      <c r="BG22">
+        <v>90</v>
+      </c>
+      <c r="BH22" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -400,7 +400,7 @@
     <t>Atletico Madrid</t>
   </si>
   <si>
-    <t>2026-05-04 04:18:46</t>
+    <t>2026-05-04 06:32:04</t>
   </si>
 </sst>
 </file>
@@ -960,37 +960,37 @@
         <v>107</v>
       </c>
       <c r="F2">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="G2">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H2">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I2">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J2">
         <v>3.25</v>
       </c>
       <c r="K2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O2">
         <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q2">
         <v>2.08</v>
@@ -999,49 +999,49 @@
         <v>1.31</v>
       </c>
       <c r="S2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T2">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U2">
         <v>2.04</v>
       </c>
       <c r="V2">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W2">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA2">
         <v>75</v>
       </c>
       <c r="AB2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE2">
         <v>46</v>
       </c>
       <c r="AF2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
         <v>19</v>
@@ -1050,76 +1050,76 @@
         <v>55</v>
       </c>
       <c r="AJ2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AL2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM2">
         <v>130</v>
       </c>
       <c r="AN2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO2">
         <v>50</v>
       </c>
       <c r="AP2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AS2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AT2">
         <v>8.4</v>
       </c>
       <c r="AU2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY2">
         <v>10</v>
       </c>
       <c r="AZ2">
+        <v>6</v>
+      </c>
+      <c r="BA2">
         <v>7.4</v>
       </c>
-      <c r="BA2">
+      <c r="BB2">
+        <v>7</v>
+      </c>
+      <c r="BC2">
+        <v>6.6</v>
+      </c>
+      <c r="BD2">
+        <v>7.2</v>
+      </c>
+      <c r="BE2">
         <v>8</v>
-      </c>
-      <c r="BB2">
-        <v>7.4</v>
-      </c>
-      <c r="BC2">
-        <v>7</v>
-      </c>
-      <c r="BD2">
-        <v>7.6</v>
-      </c>
-      <c r="BE2">
-        <v>8.6</v>
       </c>
       <c r="BF2">
         <v>18.5</v>
       </c>
       <c r="BG2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH2" t="s">
         <v>128</v>
@@ -1148,10 +1148,10 @@
         <v>2.92</v>
       </c>
       <c r="H3">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I3">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -1160,7 +1160,7 @@
         <v>4.2</v>
       </c>
       <c r="L3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M3">
         <v>1.03</v>
@@ -1190,7 +1190,7 @@
         <v>2.88</v>
       </c>
       <c r="V3">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W3">
         <v>1.52</v>
@@ -1214,7 +1214,7 @@
         <v>11</v>
       </c>
       <c r="AD3">
-        <v>80</v>
+        <v>13.5</v>
       </c>
       <c r="AE3">
         <v>23</v>
@@ -1253,7 +1253,7 @@
         <v>9.4</v>
       </c>
       <c r="AQ3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR3">
         <v>8.4</v>
@@ -1286,7 +1286,7 @@
         <v>9</v>
       </c>
       <c r="BB3">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BC3">
         <v>9</v>
@@ -1336,37 +1336,37 @@
         <v>1.58</v>
       </c>
       <c r="J4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K4">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L4">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M4">
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P4">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q4">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="R4">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S4">
         <v>2.74</v>
       </c>
       <c r="T4">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U4">
         <v>2.06</v>
@@ -1375,22 +1375,22 @@
         <v>2.72</v>
       </c>
       <c r="W4">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X4">
         <v>20</v>
       </c>
       <c r="Y4">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4">
         <v>10</v>
       </c>
       <c r="AA4">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AB4">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AC4">
         <v>10.5</v>
@@ -1414,7 +1414,7 @@
         <v>34</v>
       </c>
       <c r="AJ4">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AK4">
         <v>110</v>
@@ -1426,10 +1426,10 @@
         <v>120</v>
       </c>
       <c r="AN4">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AO4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AP4">
         <v>17</v>
@@ -1450,13 +1450,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV4">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AW4">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY4">
         <v>7.6</v>
@@ -1480,7 +1480,7 @@
         <v>9.6</v>
       </c>
       <c r="BF4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG4">
         <v>6.4</v>
@@ -1506,31 +1506,31 @@
         <v>110</v>
       </c>
       <c r="F5">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="G5">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="H5">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I5">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="J5">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K5">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L5">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="M5">
         <v>1.1</v>
       </c>
       <c r="N5">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="O5">
         <v>1.45</v>
@@ -1542,46 +1542,46 @@
         <v>2.34</v>
       </c>
       <c r="R5">
+        <v>1.23</v>
+      </c>
+      <c r="S5">
+        <v>4.5</v>
+      </c>
+      <c r="T5">
+        <v>2.04</v>
+      </c>
+      <c r="U5">
+        <v>1.81</v>
+      </c>
+      <c r="V5">
         <v>1.22</v>
       </c>
-      <c r="S5">
-        <v>4.1</v>
-      </c>
-      <c r="T5">
-        <v>2.02</v>
-      </c>
-      <c r="U5">
-        <v>1.83</v>
-      </c>
-      <c r="V5">
-        <v>1.23</v>
-      </c>
       <c r="W5">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="X5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y5">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z5">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AA5">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF5">
         <v>15</v>
@@ -1590,10 +1590,10 @@
         <v>13.5</v>
       </c>
       <c r="AH5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ5">
         <v>34</v>
@@ -1605,67 +1605,67 @@
         <v>65</v>
       </c>
       <c r="AM5">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AN5">
         <v>30</v>
       </c>
       <c r="AO5">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AP5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR5">
+        <v>3.65</v>
+      </c>
+      <c r="AS5">
         <v>3.9</v>
       </c>
-      <c r="AS5">
-        <v>4.2</v>
-      </c>
       <c r="AT5">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU5">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AV5">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AW5">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AX5">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AZ5">
+        <v>17.5</v>
+      </c>
+      <c r="BA5">
+        <v>3.85</v>
+      </c>
+      <c r="BB5">
+        <v>17.5</v>
+      </c>
+      <c r="BC5">
         <v>19</v>
       </c>
-      <c r="BA5">
-        <v>4.1</v>
-      </c>
-      <c r="BB5">
-        <v>20</v>
-      </c>
-      <c r="BC5">
-        <v>19.5</v>
-      </c>
       <c r="BD5">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BE5">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BF5">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG5">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BH5" t="s">
         <v>128</v>
@@ -1870,112 +1870,112 @@
         <v>112</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>1.62</v>
       </c>
       <c r="J7">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="O7">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="P7">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="Q7">
-        <v>1.31</v>
+        <v>1.94</v>
       </c>
       <c r="R7">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S7">
-        <v>1.31</v>
+        <v>3.25</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ7">
         <v>1000</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AP7">
         <v>1.03</v>
@@ -2029,7 +2029,7 @@
         <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH7" t="s">
         <v>128</v>
@@ -2052,112 +2052,112 @@
         <v>113</v>
       </c>
       <c r="F8">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>1.64</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N8">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="O8">
         <v>1.29</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>1.93</v>
       </c>
       <c r="Q8">
-        <v>1.29</v>
+        <v>1.81</v>
       </c>
       <c r="R8">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S8">
-        <v>1.29</v>
+        <v>2.96</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE8">
         <v>1000</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK8">
         <v>1000</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM8">
         <v>1000</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP8">
         <v>1.03</v>
@@ -2208,7 +2208,7 @@
         <v>1.03</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG8">
         <v>1.01</v>
@@ -2345,7 +2345,7 @@
         <v>15</v>
       </c>
       <c r="AQ9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR9">
         <v>9.4</v>
@@ -2607,7 +2607,7 @@
         <v>2.52</v>
       </c>
       <c r="I11">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="J11">
         <v>3.6</v>
@@ -2631,7 +2631,7 @@
         <v>2.24</v>
       </c>
       <c r="Q11">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="R11">
         <v>1.49</v>
@@ -2646,7 +2646,7 @@
         <v>2.4</v>
       </c>
       <c r="V11">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W11">
         <v>1.52</v>
@@ -2724,7 +2724,7 @@
         <v>7</v>
       </c>
       <c r="AV11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW11">
         <v>20</v>
@@ -2754,7 +2754,7 @@
         <v>46</v>
       </c>
       <c r="BF11">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="BG11">
         <v>13</v>
@@ -2783,7 +2783,7 @@
         <v>1.4</v>
       </c>
       <c r="G12">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="H12">
         <v>6.8</v>
@@ -2813,13 +2813,13 @@
         <v>2.36</v>
       </c>
       <c r="Q12">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="R12">
         <v>1.54</v>
       </c>
       <c r="S12">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T12">
         <v>1.81</v>
@@ -2888,10 +2888,10 @@
         <v>140</v>
       </c>
       <c r="AP12">
-        <v>18</v>
+        <v>4.3</v>
       </c>
       <c r="AQ12">
-        <v>23</v>
+        <v>4.4</v>
       </c>
       <c r="AR12">
         <v>4.8</v>
@@ -2962,7 +2962,7 @@
         <v>118</v>
       </c>
       <c r="F13">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G13">
         <v>2.3</v>
@@ -2971,16 +2971,16 @@
         <v>3.6</v>
       </c>
       <c r="I13">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J13">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="K13">
         <v>3.8</v>
       </c>
       <c r="L13">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M13">
         <v>1.07</v>
@@ -3022,10 +3022,10 @@
         <v>16.5</v>
       </c>
       <c r="Z13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB13">
         <v>10.5</v>
@@ -3055,7 +3055,7 @@
         <v>34</v>
       </c>
       <c r="AK13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL13">
         <v>48</v>
@@ -3073,19 +3073,19 @@
         <v>11</v>
       </c>
       <c r="AQ13">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT13">
         <v>6.8</v>
       </c>
       <c r="AU13">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AV13">
         <v>11.5</v>
@@ -3097,10 +3097,10 @@
         <v>10</v>
       </c>
       <c r="AY13">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BA13">
         <v>4.1</v>
@@ -3109,19 +3109,19 @@
         <v>19.5</v>
       </c>
       <c r="BC13">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD13">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="BE13">
         <v>4.2</v>
       </c>
       <c r="BF13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG13">
-        <v>38</v>
+        <v>4.1</v>
       </c>
       <c r="BH13" t="s">
         <v>128</v>
@@ -3162,13 +3162,13 @@
         <v>3.9</v>
       </c>
       <c r="L14">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="M14">
         <v>1.11</v>
       </c>
       <c r="N14">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O14">
         <v>1.53</v>
@@ -3511,13 +3511,13 @@
         <v>5.3</v>
       </c>
       <c r="G16">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H16">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="I16">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J16">
         <v>3.5</v>
@@ -3526,7 +3526,7 @@
         <v>4</v>
       </c>
       <c r="L16">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="M16">
         <v>1.09</v>
@@ -3541,7 +3541,7 @@
         <v>1.7</v>
       </c>
       <c r="Q16">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R16">
         <v>1.25</v>
@@ -3550,16 +3550,16 @@
         <v>4.1</v>
       </c>
       <c r="T16">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U16">
         <v>1.8</v>
       </c>
       <c r="V16">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W16">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X16">
         <v>13</v>
@@ -3589,7 +3589,7 @@
         <v>55</v>
       </c>
       <c r="AG16">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH16">
         <v>28</v>
@@ -3616,10 +3616,10 @@
         <v>18</v>
       </c>
       <c r="AP16">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ16">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AR16">
         <v>7.6</v>
@@ -3628,31 +3628,31 @@
         <v>14.5</v>
       </c>
       <c r="AT16">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AU16">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV16">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW16">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX16">
-        <v>32</v>
+        <v>4.7</v>
       </c>
       <c r="AY16">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AZ16">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA16">
-        <v>34</v>
+        <v>4.7</v>
       </c>
       <c r="BB16">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC16">
         <v>5</v>
@@ -3661,7 +3661,7 @@
         <v>5</v>
       </c>
       <c r="BE16">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF16">
         <v>5</v>
@@ -3693,10 +3693,10 @@
         <v>2.58</v>
       </c>
       <c r="G17">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="H17">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I17">
         <v>2.86</v>
@@ -3714,7 +3714,7 @@
         <v>1.05</v>
       </c>
       <c r="N17">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="O17">
         <v>1.24</v>
@@ -3723,16 +3723,16 @@
         <v>2.24</v>
       </c>
       <c r="Q17">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R17">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S17">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T17">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U17">
         <v>2.42</v>
@@ -3741,7 +3741,7 @@
         <v>1.54</v>
       </c>
       <c r="W17">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X17">
         <v>950</v>
@@ -3789,37 +3789,37 @@
         <v>48</v>
       </c>
       <c r="AM17">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN17">
         <v>21</v>
       </c>
       <c r="AO17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP17">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="AQ17">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR17">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="AS17">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT17">
-        <v>10.5</v>
+        <v>3.95</v>
       </c>
       <c r="AU17">
         <v>7</v>
       </c>
       <c r="AV17">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX17">
         <v>4.2</v>
@@ -3831,25 +3831,25 @@
         <v>11.5</v>
       </c>
       <c r="BA17">
+        <v>4.6</v>
+      </c>
+      <c r="BB17">
+        <v>4.7</v>
+      </c>
+      <c r="BC17">
         <v>4.5</v>
       </c>
-      <c r="BB17">
-        <v>4.6</v>
-      </c>
-      <c r="BC17">
-        <v>4.4</v>
-      </c>
       <c r="BD17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE17">
         <v>4.8</v>
       </c>
       <c r="BF17">
+        <v>13.5</v>
+      </c>
+      <c r="BG17">
         <v>14</v>
-      </c>
-      <c r="BG17">
-        <v>13</v>
       </c>
       <c r="BH17" t="s">
         <v>128</v>
@@ -3872,13 +3872,13 @@
         <v>123</v>
       </c>
       <c r="F18">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="G18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="H18">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="I18">
         <v>1.32</v>
@@ -3887,7 +3887,7 @@
         <v>6.6</v>
       </c>
       <c r="K18">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L18">
         <v>1.18</v>
@@ -3917,13 +3917,13 @@
         <v>1.74</v>
       </c>
       <c r="U18">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V18">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X18">
         <v>50</v>
@@ -3962,25 +3962,25 @@
         <v>28</v>
       </c>
       <c r="AJ18">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="AK18">
         <v>140</v>
       </c>
       <c r="AL18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM18">
         <v>100</v>
       </c>
       <c r="AN18">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AO18">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="AP18">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AQ18">
         <v>12.5</v>
@@ -3992,7 +3992,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AT18">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU18">
         <v>14</v>
@@ -4004,31 +4004,31 @@
         <v>11</v>
       </c>
       <c r="AX18">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AY18">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AZ18">
+        <v>5.8</v>
+      </c>
+      <c r="BA18">
+        <v>5.8</v>
+      </c>
+      <c r="BB18">
         <v>7.2</v>
       </c>
-      <c r="BA18">
-        <v>7.2</v>
-      </c>
-      <c r="BB18">
-        <v>9.6</v>
-      </c>
       <c r="BC18">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BD18">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="BE18">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="BF18">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BG18">
         <v>2.88</v>
@@ -4057,31 +4057,31 @@
         <v>2.28</v>
       </c>
       <c r="G19">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="H19">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="I19">
         <v>3.55</v>
       </c>
       <c r="J19">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K19">
         <v>3.6</v>
       </c>
       <c r="L19">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="M19">
         <v>1.07</v>
       </c>
       <c r="N19">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O19">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P19">
         <v>1.91</v>
@@ -4093,10 +4093,10 @@
         <v>1.35</v>
       </c>
       <c r="S19">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T19">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U19">
         <v>2.14</v>
@@ -4105,7 +4105,7 @@
         <v>1.39</v>
       </c>
       <c r="W19">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="X19">
         <v>970</v>
@@ -4123,7 +4123,7 @@
         <v>10.5</v>
       </c>
       <c r="AC19">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD19">
         <v>970</v>
@@ -4150,7 +4150,7 @@
         <v>26</v>
       </c>
       <c r="AL19">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM19">
         <v>110</v>
@@ -4159,19 +4159,19 @@
         <v>970</v>
       </c>
       <c r="AO19">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AP19">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AQ19">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AR19">
-        <v>8.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AS19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT19">
         <v>5.7</v>
@@ -4180,28 +4180,28 @@
         <v>4.9</v>
       </c>
       <c r="AV19">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AW19">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX19">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AY19">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ19">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="BA19">
         <v>10</v>
       </c>
       <c r="BB19">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="BC19">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="BD19">
         <v>9.6</v>
@@ -4213,7 +4213,7 @@
         <v>7.6</v>
       </c>
       <c r="BG19">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH19" t="s">
         <v>128</v>
@@ -4239,13 +4239,13 @@
         <v>2.36</v>
       </c>
       <c r="G20">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="H20">
         <v>2.82</v>
       </c>
       <c r="I20">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J20">
         <v>3</v>
@@ -4254,7 +4254,7 @@
         <v>3.7</v>
       </c>
       <c r="L20">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="M20">
         <v>1.08</v>
@@ -4269,7 +4269,7 @@
         <v>1.77</v>
       </c>
       <c r="Q20">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R20">
         <v>1.29</v>
@@ -4284,10 +4284,10 @@
         <v>2.02</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W20">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="X20">
         <v>14.5</v>
@@ -4430,7 +4430,7 @@
         <v>990</v>
       </c>
       <c r="J21">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K21">
         <v>950</v>
@@ -4642,7 +4642,7 @@
         <v>3.55</v>
       </c>
       <c r="T22">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U22">
         <v>1.97</v>
@@ -4657,13 +4657,13 @@
         <v>14.5</v>
       </c>
       <c r="Y22">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z22">
         <v>44</v>
       </c>
       <c r="AA22">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB22">
         <v>8.4</v>
@@ -4693,19 +4693,19 @@
         <v>16</v>
       </c>
       <c r="AK22">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL22">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM22">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="AN22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO22">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP22">
         <v>14</v>
@@ -4726,7 +4726,7 @@
         <v>8.6</v>
       </c>
       <c r="AV22">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW22">
         <v>70</v>
@@ -4741,10 +4741,10 @@
         <v>20</v>
       </c>
       <c r="BA22">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BB22">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC22">
         <v>16</v>
@@ -4756,7 +4756,7 @@
         <v>110</v>
       </c>
       <c r="BF22">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG22">
         <v>90</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="128">
   <si>
     <t>League</t>
   </si>
@@ -217,24 +217,24 @@
     <t>Israeli Premier League</t>
   </si>
   <si>
+    <t>Swedish Superettan</t>
+  </si>
+  <si>
     <t>Egyptian Premier</t>
   </si>
   <si>
-    <t>Swedish Superettan</t>
-  </si>
-  <si>
     <t>Saudi Professional League</t>
   </si>
   <si>
+    <t>Scottish League Two</t>
+  </si>
+  <si>
     <t>Scottish Championship</t>
   </si>
   <si>
     <t>Scottish League One</t>
   </si>
   <si>
-    <t>Scottish League Two</t>
-  </si>
-  <si>
     <t>UEFA Champions League</t>
   </si>
   <si>
@@ -250,9 +250,6 @@
     <t>11:30:00</t>
   </si>
   <si>
-    <t>12:30:00</t>
-  </si>
-  <si>
     <t>12:45:00</t>
   </si>
   <si>
@@ -289,22 +286,28 @@
     <t>Bihor Oradea</t>
   </si>
   <si>
+    <t>FK Kauno Zalgiris</t>
+  </si>
+  <si>
+    <t>Gnistan</t>
+  </si>
+  <si>
+    <t>Zilina</t>
+  </si>
+  <si>
+    <t>MFk Skalica</t>
+  </si>
+  <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Falkenbergs</t>
+  </si>
+  <si>
     <t>Riteriai</t>
   </si>
   <si>
-    <t>FK Kauno Zalgiris</t>
-  </si>
-  <si>
-    <t>Gnistan</t>
-  </si>
-  <si>
-    <t>Zilina</t>
-  </si>
-  <si>
-    <t>MFk Skalica</t>
-  </si>
-  <si>
-    <t>Maccabi Tel Aviv</t>
+    <t>Ceramica Cleopatra</t>
   </si>
   <si>
     <t>Lokomotiv Sofia</t>
@@ -316,24 +319,18 @@
     <t>Al Ahly Cairo</t>
   </si>
   <si>
-    <t>Ceramica Cleopatra</t>
-  </si>
-  <si>
-    <t>Falkenbergs</t>
-  </si>
-  <si>
     <t>Al-Khaleej Saihat</t>
   </si>
   <si>
+    <t>Clyde</t>
+  </si>
+  <si>
     <t>Dunfermline</t>
   </si>
   <si>
     <t>Queen of South</t>
   </si>
   <si>
-    <t>Clyde</t>
-  </si>
-  <si>
     <t>Arsenal</t>
   </si>
   <si>
@@ -352,22 +349,28 @@
     <t>Chindia Targoviste</t>
   </si>
   <si>
+    <t>FC Dziugas</t>
+  </si>
+  <si>
+    <t>FC Inter</t>
+  </si>
+  <si>
+    <t>Zemplin</t>
+  </si>
+  <si>
+    <t>FC Kosice</t>
+  </si>
+  <si>
+    <t>Hapoel Petach Tikva</t>
+  </si>
+  <si>
+    <t>Norrkoping</t>
+  </si>
+  <si>
     <t>FK Banga Gargzdu</t>
   </si>
   <si>
-    <t>FC Dziugas</t>
-  </si>
-  <si>
-    <t>FC Inter</t>
-  </si>
-  <si>
-    <t>Zemplin</t>
-  </si>
-  <si>
-    <t>FC Kosice</t>
-  </si>
-  <si>
-    <t>Hapoel Petach Tikva</t>
+    <t>Pyramids</t>
   </si>
   <si>
     <t>Botev Vratsa</t>
@@ -379,28 +382,22 @@
     <t>ENPPI</t>
   </si>
   <si>
-    <t>Pyramids</t>
-  </si>
-  <si>
-    <t>Norrkoping</t>
-  </si>
-  <si>
     <t>Al-Hilal</t>
   </si>
   <si>
+    <t>Spartans</t>
+  </si>
+  <si>
     <t>Arbroath</t>
   </si>
   <si>
     <t>Stenhousemuir</t>
   </si>
   <si>
-    <t>Spartans</t>
-  </si>
-  <si>
     <t>Atletico Madrid</t>
   </si>
   <si>
-    <t>2026-05-04 06:32:04</t>
+    <t>2026-05-04 08:43:55</t>
   </si>
 </sst>
 </file>
@@ -954,16 +951,16 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F2">
         <v>2.4</v>
       </c>
       <c r="G2">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="H2">
         <v>3.15</v>
@@ -981,7 +978,7 @@
         <v>1.37</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
         <v>3.3</v>
@@ -990,10 +987,10 @@
         <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R2">
         <v>1.31</v>
@@ -1002,7 +999,7 @@
         <v>3.85</v>
       </c>
       <c r="T2">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U2">
         <v>2.04</v>
@@ -1011,7 +1008,7 @@
         <v>1.41</v>
       </c>
       <c r="W2">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X2">
         <v>12.5</v>
@@ -1026,7 +1023,7 @@
         <v>75</v>
       </c>
       <c r="AB2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC2">
         <v>7.6</v>
@@ -1077,7 +1074,7 @@
         <v>19</v>
       </c>
       <c r="AS2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT2">
         <v>8.4</v>
@@ -1089,7 +1086,7 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX2">
         <v>13.5</v>
@@ -1098,31 +1095,31 @@
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB2">
+        <v>7.2</v>
+      </c>
+      <c r="BC2">
         <v>7</v>
       </c>
-      <c r="BC2">
-        <v>6.6</v>
-      </c>
       <c r="BD2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF2">
         <v>18.5</v>
       </c>
       <c r="BG2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -1136,10 +1133,10 @@
         <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F3">
         <v>2.78</v>
@@ -1304,7 +1301,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BH3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -1318,16 +1315,16 @@
         <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="G4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H4">
         <v>1.53</v>
@@ -1354,19 +1351,19 @@
         <v>1.24</v>
       </c>
       <c r="P4">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q4">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R4">
         <v>1.49</v>
       </c>
       <c r="S4">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="T4">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="U4">
         <v>2.06</v>
@@ -1378,7 +1375,7 @@
         <v>1.15</v>
       </c>
       <c r="X4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Y4">
         <v>9.800000000000001</v>
@@ -1411,7 +1408,7 @@
         <v>24</v>
       </c>
       <c r="AI4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ4">
         <v>220</v>
@@ -1429,7 +1426,7 @@
         <v>120</v>
       </c>
       <c r="AO4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AP4">
         <v>17</v>
@@ -1450,43 +1447,43 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV4">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW4">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="AX4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY4">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AZ4">
         <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB4">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BC4">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BD4">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE4">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BF4">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BG4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:60">
@@ -1500,22 +1497,22 @@
         <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F5">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H5">
         <v>4.5</v>
       </c>
       <c r="I5">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J5">
         <v>3.2</v>
@@ -1533,7 +1530,7 @@
         <v>2.86</v>
       </c>
       <c r="O5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P5">
         <v>1.69</v>
@@ -1545,7 +1542,7 @@
         <v>1.23</v>
       </c>
       <c r="S5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T5">
         <v>2.04</v>
@@ -1554,19 +1551,19 @@
         <v>1.81</v>
       </c>
       <c r="V5">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W5">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X5">
         <v>12.5</v>
       </c>
       <c r="Y5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA5">
         <v>160</v>
@@ -1575,7 +1572,7 @@
         <v>8.6</v>
       </c>
       <c r="AC5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5">
         <v>24</v>
@@ -1593,7 +1590,7 @@
         <v>28</v>
       </c>
       <c r="AI5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ5">
         <v>34</v>
@@ -1614,61 +1611,61 @@
         <v>140</v>
       </c>
       <c r="AP5">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AS5">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AT5">
         <v>6.2</v>
       </c>
       <c r="AU5">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW5">
+        <v>3.95</v>
+      </c>
+      <c r="AX5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY5">
+        <v>9.4</v>
+      </c>
+      <c r="AZ5">
+        <v>19.5</v>
+      </c>
+      <c r="BA5">
+        <v>3.95</v>
+      </c>
+      <c r="BB5">
+        <v>21</v>
+      </c>
+      <c r="BC5">
+        <v>3.65</v>
+      </c>
+      <c r="BD5">
         <v>3.85</v>
       </c>
-      <c r="AX5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY5">
-        <v>8</v>
-      </c>
-      <c r="AZ5">
-        <v>17.5</v>
-      </c>
-      <c r="BA5">
-        <v>3.85</v>
-      </c>
-      <c r="BB5">
-        <v>17.5</v>
-      </c>
-      <c r="BC5">
-        <v>19</v>
-      </c>
-      <c r="BD5">
-        <v>3.75</v>
-      </c>
       <c r="BE5">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BF5">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG5">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BH5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:60">
@@ -1682,175 +1679,175 @@
         <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F6">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="G6">
-        <v>990</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I6">
-        <v>990</v>
+        <v>6.8</v>
       </c>
       <c r="J6">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="O6">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>1.84</v>
       </c>
       <c r="Q6">
-        <v>1.28</v>
+        <v>1.92</v>
       </c>
       <c r="R6">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="S6">
-        <v>1.28</v>
+        <v>2.78</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>1.84</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:60">
@@ -1864,180 +1861,180 @@
         <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F7">
+        <v>1.44</v>
+      </c>
+      <c r="G7">
+        <v>1.56</v>
+      </c>
+      <c r="H7">
         <v>6.2</v>
       </c>
-      <c r="G7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H7">
-        <v>1.51</v>
-      </c>
       <c r="I7">
-        <v>1.62</v>
+        <v>10.5</v>
       </c>
       <c r="J7">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="L7">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N7">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="O7">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="P7">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="Q7">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="R7">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S7">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="T7">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U7">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="V7">
-        <v>2.6</v>
+        <v>1.12</v>
       </c>
       <c r="W7">
-        <v>1.12</v>
+        <v>2.78</v>
       </c>
       <c r="X7">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y7">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="Z7">
-        <v>8.800000000000001</v>
+        <v>85</v>
       </c>
       <c r="AA7">
-        <v>15</v>
+        <v>340</v>
       </c>
       <c r="AB7">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="AC7">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD7">
+        <v>36</v>
+      </c>
+      <c r="AE7">
+        <v>160</v>
+      </c>
+      <c r="AF7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG7">
         <v>12</v>
-      </c>
-      <c r="AE7">
-        <v>19.5</v>
-      </c>
-      <c r="AF7">
-        <v>80</v>
-      </c>
-      <c r="AG7">
-        <v>38</v>
       </c>
       <c r="AH7">
         <v>30</v>
       </c>
       <c r="AI7">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK7">
+        <v>19</v>
+      </c>
+      <c r="AL7">
+        <v>46</v>
+      </c>
+      <c r="AM7">
         <v>180</v>
       </c>
-      <c r="AL7">
-        <v>160</v>
-      </c>
-      <c r="AM7">
+      <c r="AN7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO7">
         <v>230</v>
       </c>
-      <c r="AN7">
-        <v>290</v>
-      </c>
-      <c r="AO7">
-        <v>11</v>
-      </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG7">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="BH7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:60">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
         <v>74</v>
@@ -2046,357 +2043,357 @@
         <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F8">
-        <v>1.51</v>
+        <v>4.9</v>
       </c>
       <c r="G8">
-        <v>1.64</v>
+        <v>5.4</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>1.77</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>1.81</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
       <c r="K8">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M8">
         <v>1.06</v>
       </c>
       <c r="N8">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="O8">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P8">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="Q8">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R8">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S8">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T8">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="U8">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="V8">
-        <v>1.12</v>
+        <v>2.22</v>
       </c>
       <c r="W8">
-        <v>2.56</v>
+        <v>1.23</v>
       </c>
       <c r="X8">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Y8">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="Z8">
+        <v>12</v>
+      </c>
+      <c r="AA8">
+        <v>20</v>
+      </c>
+      <c r="AB8">
+        <v>20</v>
+      </c>
+      <c r="AC8">
+        <v>10.5</v>
+      </c>
+      <c r="AD8">
+        <v>11</v>
+      </c>
+      <c r="AE8">
+        <v>19</v>
+      </c>
+      <c r="AF8">
+        <v>42</v>
+      </c>
+      <c r="AG8">
+        <v>21</v>
+      </c>
+      <c r="AH8">
+        <v>20</v>
+      </c>
+      <c r="AI8">
+        <v>38</v>
+      </c>
+      <c r="AJ8">
+        <v>140</v>
+      </c>
+      <c r="AK8">
         <v>75</v>
       </c>
-      <c r="AA8">
-        <v>270</v>
-      </c>
-      <c r="AB8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC8">
-        <v>11.5</v>
-      </c>
-      <c r="AD8">
-        <v>32</v>
-      </c>
-      <c r="AE8">
-        <v>1000</v>
-      </c>
-      <c r="AF8">
+      <c r="AL8">
+        <v>75</v>
+      </c>
+      <c r="AM8">
+        <v>110</v>
+      </c>
+      <c r="AN8">
+        <v>80</v>
+      </c>
+      <c r="AO8">
         <v>10.5</v>
       </c>
-      <c r="AG8">
-        <v>11.5</v>
-      </c>
-      <c r="AH8">
-        <v>28</v>
-      </c>
-      <c r="AI8">
-        <v>120</v>
-      </c>
-      <c r="AJ8">
-        <v>17</v>
-      </c>
-      <c r="AK8">
-        <v>1000</v>
-      </c>
-      <c r="AL8">
-        <v>46</v>
-      </c>
-      <c r="AM8">
-        <v>1000</v>
-      </c>
-      <c r="AN8">
-        <v>10.5</v>
-      </c>
-      <c r="AO8">
-        <v>180</v>
-      </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BF8">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:60">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F9">
-        <v>4.9</v>
+        <v>1.42</v>
       </c>
       <c r="G9">
-        <v>5.4</v>
+        <v>1.53</v>
       </c>
       <c r="H9">
-        <v>1.77</v>
+        <v>7.2</v>
       </c>
       <c r="I9">
-        <v>1.81</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="K9">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="L9">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="M9">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="O9">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="P9">
-        <v>2.06</v>
+        <v>2.52</v>
       </c>
       <c r="Q9">
-        <v>1.79</v>
+        <v>1.54</v>
       </c>
       <c r="R9">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="S9">
-        <v>2.98</v>
+        <v>2.34</v>
       </c>
       <c r="T9">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U9">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V9">
-        <v>2.22</v>
+        <v>1.13</v>
       </c>
       <c r="W9">
-        <v>1.23</v>
+        <v>2.88</v>
       </c>
       <c r="X9">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="Z9">
+        <v>75</v>
+      </c>
+      <c r="AA9">
+        <v>230</v>
+      </c>
+      <c r="AB9">
         <v>12</v>
       </c>
-      <c r="AA9">
-        <v>20</v>
-      </c>
-      <c r="AB9">
-        <v>20</v>
-      </c>
       <c r="AC9">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AD9">
+        <v>950</v>
+      </c>
+      <c r="AE9">
+        <v>110</v>
+      </c>
+      <c r="AF9">
+        <v>11.5</v>
+      </c>
+      <c r="AG9">
         <v>11</v>
       </c>
-      <c r="AE9">
-        <v>19</v>
-      </c>
-      <c r="AF9">
-        <v>42</v>
-      </c>
-      <c r="AG9">
-        <v>21</v>
-      </c>
       <c r="AH9">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI9">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AJ9">
-        <v>140</v>
+        <v>14.5</v>
       </c>
       <c r="AK9">
-        <v>75</v>
+        <v>15.5</v>
       </c>
       <c r="AL9">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AM9">
         <v>110</v>
       </c>
       <c r="AN9">
-        <v>80</v>
+        <v>5.7</v>
       </c>
       <c r="AO9">
+        <v>110</v>
+      </c>
+      <c r="AP9">
+        <v>20</v>
+      </c>
+      <c r="AQ9">
+        <v>6.2</v>
+      </c>
+      <c r="AR9">
+        <v>7</v>
+      </c>
+      <c r="AS9">
+        <v>7.4</v>
+      </c>
+      <c r="AT9">
+        <v>9.6</v>
+      </c>
+      <c r="AU9">
+        <v>9.4</v>
+      </c>
+      <c r="AV9">
+        <v>21</v>
+      </c>
+      <c r="AW9">
+        <v>7.2</v>
+      </c>
+      <c r="AX9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY9">
+        <v>8</v>
+      </c>
+      <c r="AZ9">
+        <v>16</v>
+      </c>
+      <c r="BA9">
+        <v>7</v>
+      </c>
+      <c r="BB9">
         <v>10.5</v>
       </c>
-      <c r="AP9">
-        <v>15</v>
-      </c>
-      <c r="AQ9">
-        <v>8.4</v>
-      </c>
-      <c r="AR9">
-        <v>9.4</v>
-      </c>
-      <c r="AS9">
-        <v>15</v>
-      </c>
-      <c r="AT9">
-        <v>16.5</v>
-      </c>
-      <c r="AU9">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV9">
-        <v>8.6</v>
-      </c>
-      <c r="AW9">
-        <v>15</v>
-      </c>
-      <c r="AX9">
-        <v>6.6</v>
-      </c>
-      <c r="AY9">
-        <v>17.5</v>
-      </c>
-      <c r="AZ9">
-        <v>16.5</v>
-      </c>
-      <c r="BA9">
-        <v>6.4</v>
-      </c>
-      <c r="BB9">
-        <v>7.4</v>
-      </c>
       <c r="BC9">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BD9">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BE9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF9">
+        <v>4.3</v>
+      </c>
+      <c r="BG9">
         <v>7.2</v>
       </c>
-      <c r="BG9">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BH9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:60">
@@ -2407,183 +2404,183 @@
         <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F10">
-        <v>1.42</v>
+        <v>2.54</v>
       </c>
       <c r="G10">
+        <v>2.94</v>
+      </c>
+      <c r="H10">
+        <v>2.52</v>
+      </c>
+      <c r="I10">
+        <v>2.92</v>
+      </c>
+      <c r="J10">
+        <v>3.6</v>
+      </c>
+      <c r="K10">
+        <v>4.2</v>
+      </c>
+      <c r="L10">
+        <v>1.28</v>
+      </c>
+      <c r="M10">
+        <v>1.04</v>
+      </c>
+      <c r="N10">
+        <v>4.3</v>
+      </c>
+      <c r="O10">
+        <v>1.22</v>
+      </c>
+      <c r="P10">
+        <v>2.24</v>
+      </c>
+      <c r="Q10">
+        <v>1.58</v>
+      </c>
+      <c r="R10">
+        <v>1.49</v>
+      </c>
+      <c r="S10">
+        <v>2.62</v>
+      </c>
+      <c r="T10">
+        <v>1.57</v>
+      </c>
+      <c r="U10">
+        <v>2.4</v>
+      </c>
+      <c r="V10">
         <v>1.53</v>
       </c>
-      <c r="H10">
-        <v>6.8</v>
-      </c>
-      <c r="I10">
-        <v>8.4</v>
-      </c>
-      <c r="J10">
-        <v>4.8</v>
-      </c>
-      <c r="K10">
-        <v>5.7</v>
-      </c>
-      <c r="L10">
-        <v>1.24</v>
-      </c>
-      <c r="M10">
-        <v>1.01</v>
-      </c>
-      <c r="N10">
-        <v>5.5</v>
-      </c>
-      <c r="O10">
-        <v>1.18</v>
-      </c>
-      <c r="P10">
-        <v>2.52</v>
-      </c>
-      <c r="Q10">
-        <v>1.54</v>
-      </c>
-      <c r="R10">
-        <v>1.61</v>
-      </c>
-      <c r="S10">
-        <v>2.34</v>
-      </c>
-      <c r="T10">
-        <v>1.74</v>
-      </c>
-      <c r="U10">
-        <v>2.12</v>
-      </c>
-      <c r="V10">
-        <v>1.13</v>
-      </c>
       <c r="W10">
-        <v>2.88</v>
+        <v>1.52</v>
       </c>
       <c r="X10">
+        <v>24</v>
+      </c>
+      <c r="Y10">
+        <v>17.5</v>
+      </c>
+      <c r="Z10">
+        <v>24</v>
+      </c>
+      <c r="AA10">
+        <v>46</v>
+      </c>
+      <c r="AB10">
+        <v>17</v>
+      </c>
+      <c r="AC10">
+        <v>10.5</v>
+      </c>
+      <c r="AD10">
+        <v>14.5</v>
+      </c>
+      <c r="AE10">
         <v>32</v>
       </c>
-      <c r="Y10">
-        <v>38</v>
-      </c>
-      <c r="Z10">
-        <v>80</v>
-      </c>
-      <c r="AA10">
-        <v>230</v>
-      </c>
-      <c r="AB10">
-        <v>12</v>
-      </c>
-      <c r="AC10">
+      <c r="AF10">
+        <v>24</v>
+      </c>
+      <c r="AG10">
+        <v>14.5</v>
+      </c>
+      <c r="AH10">
+        <v>18</v>
+      </c>
+      <c r="AI10">
+        <v>40</v>
+      </c>
+      <c r="AJ10">
+        <v>46</v>
+      </c>
+      <c r="AK10">
+        <v>32</v>
+      </c>
+      <c r="AL10">
+        <v>40</v>
+      </c>
+      <c r="AM10">
+        <v>75</v>
+      </c>
+      <c r="AN10">
+        <v>21</v>
+      </c>
+      <c r="AO10">
+        <v>20</v>
+      </c>
+      <c r="AP10">
+        <v>15.5</v>
+      </c>
+      <c r="AQ10">
+        <v>11</v>
+      </c>
+      <c r="AR10">
+        <v>15.5</v>
+      </c>
+      <c r="AS10">
+        <v>4.5</v>
+      </c>
+      <c r="AT10">
+        <v>11</v>
+      </c>
+      <c r="AU10">
+        <v>7</v>
+      </c>
+      <c r="AV10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW10">
+        <v>20</v>
+      </c>
+      <c r="AX10">
+        <v>15.5</v>
+      </c>
+      <c r="AY10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ10">
+        <v>11.5</v>
+      </c>
+      <c r="BA10">
+        <v>4.4</v>
+      </c>
+      <c r="BB10">
+        <v>4.5</v>
+      </c>
+      <c r="BC10">
+        <v>20</v>
+      </c>
+      <c r="BD10">
+        <v>4.4</v>
+      </c>
+      <c r="BE10">
+        <v>4.7</v>
+      </c>
+      <c r="BF10">
+        <v>13.5</v>
+      </c>
+      <c r="BG10">
         <v>13</v>
       </c>
-      <c r="AD10">
-        <v>950</v>
-      </c>
-      <c r="AE10">
-        <v>110</v>
-      </c>
-      <c r="AF10">
-        <v>11.5</v>
-      </c>
-      <c r="AG10">
-        <v>11</v>
-      </c>
-      <c r="AH10">
-        <v>23</v>
-      </c>
-      <c r="AI10">
-        <v>85</v>
-      </c>
-      <c r="AJ10">
-        <v>14.5</v>
-      </c>
-      <c r="AK10">
-        <v>15.5</v>
-      </c>
-      <c r="AL10">
-        <v>34</v>
-      </c>
-      <c r="AM10">
-        <v>110</v>
-      </c>
-      <c r="AN10">
-        <v>5.7</v>
-      </c>
-      <c r="AO10">
-        <v>110</v>
-      </c>
-      <c r="AP10">
-        <v>20</v>
-      </c>
-      <c r="AQ10">
-        <v>6.2</v>
-      </c>
-      <c r="AR10">
-        <v>7</v>
-      </c>
-      <c r="AS10">
-        <v>7.4</v>
-      </c>
-      <c r="AT10">
-        <v>9.6</v>
-      </c>
-      <c r="AU10">
-        <v>9.4</v>
-      </c>
-      <c r="AV10">
-        <v>21</v>
-      </c>
-      <c r="AW10">
-        <v>7.2</v>
-      </c>
-      <c r="AX10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY10">
-        <v>8</v>
-      </c>
-      <c r="AZ10">
-        <v>16</v>
-      </c>
-      <c r="BA10">
-        <v>7</v>
-      </c>
-      <c r="BB10">
-        <v>10.5</v>
-      </c>
-      <c r="BC10">
-        <v>11</v>
-      </c>
-      <c r="BD10">
-        <v>21</v>
-      </c>
-      <c r="BE10">
-        <v>7.2</v>
-      </c>
-      <c r="BF10">
-        <v>4.3</v>
-      </c>
-      <c r="BG10">
-        <v>7.2</v>
-      </c>
       <c r="BH10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:60">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
         <v>74</v>
@@ -2592,180 +2589,180 @@
         <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F11">
-        <v>2.54</v>
+        <v>1.42</v>
       </c>
       <c r="G11">
-        <v>2.94</v>
+        <v>1.54</v>
       </c>
       <c r="H11">
-        <v>2.52</v>
+        <v>7.2</v>
       </c>
       <c r="I11">
-        <v>2.94</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J11">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="K11">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="L11">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="O11">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P11">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="Q11">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="R11">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S11">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="T11">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="U11">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="V11">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="W11">
-        <v>1.52</v>
+        <v>2.82</v>
       </c>
       <c r="X11">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="Y11">
-        <v>17.5</v>
+        <v>950</v>
       </c>
       <c r="Z11">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="AA11">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AC11">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD11">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="AE11">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="AF11">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="AG11">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AH11">
-        <v>18</v>
+        <v>950</v>
       </c>
       <c r="AI11">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="AJ11">
-        <v>46</v>
+        <v>970</v>
       </c>
       <c r="AK11">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AL11">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM11">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AN11">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="AO11">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="AP11">
-        <v>15.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ11">
+        <v>4.5</v>
+      </c>
+      <c r="AR11">
+        <v>5</v>
+      </c>
+      <c r="AS11">
+        <v>5.2</v>
+      </c>
+      <c r="AT11">
+        <v>7.8</v>
+      </c>
+      <c r="AU11">
+        <v>9</v>
+      </c>
+      <c r="AV11">
+        <v>4.5</v>
+      </c>
+      <c r="AW11">
+        <v>5.1</v>
+      </c>
+      <c r="AX11">
+        <v>7.6</v>
+      </c>
+      <c r="AY11">
+        <v>8</v>
+      </c>
+      <c r="AZ11">
+        <v>4.4</v>
+      </c>
+      <c r="BA11">
+        <v>5.1</v>
+      </c>
+      <c r="BB11">
+        <v>10</v>
+      </c>
+      <c r="BC11">
         <v>11</v>
       </c>
-      <c r="AR11">
-        <v>15.5</v>
-      </c>
-      <c r="AS11">
-        <v>4.4</v>
-      </c>
-      <c r="AT11">
-        <v>11</v>
-      </c>
-      <c r="AU11">
-        <v>7</v>
-      </c>
-      <c r="AV11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW11">
-        <v>20</v>
-      </c>
-      <c r="AX11">
-        <v>15.5</v>
-      </c>
-      <c r="AY11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ11">
-        <v>11.5</v>
-      </c>
-      <c r="BA11">
-        <v>4.4</v>
-      </c>
-      <c r="BB11">
-        <v>4.4</v>
-      </c>
-      <c r="BC11">
-        <v>20</v>
-      </c>
       <c r="BD11">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE11">
-        <v>46</v>
+        <v>5.1</v>
       </c>
       <c r="BF11">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BG11">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="BH11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:60">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
         <v>74</v>
@@ -2774,574 +2771,574 @@
         <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F12">
-        <v>1.4</v>
+        <v>2.58</v>
       </c>
       <c r="G12">
+        <v>2.8</v>
+      </c>
+      <c r="H12">
+        <v>2.68</v>
+      </c>
+      <c r="I12">
+        <v>2.88</v>
+      </c>
+      <c r="J12">
+        <v>3.7</v>
+      </c>
+      <c r="K12">
+        <v>4.2</v>
+      </c>
+      <c r="L12">
+        <v>1.34</v>
+      </c>
+      <c r="M12">
+        <v>1.05</v>
+      </c>
+      <c r="N12">
+        <v>4.1</v>
+      </c>
+      <c r="O12">
+        <v>1.24</v>
+      </c>
+      <c r="P12">
+        <v>2.24</v>
+      </c>
+      <c r="Q12">
+        <v>1.7</v>
+      </c>
+      <c r="R12">
+        <v>1.5</v>
+      </c>
+      <c r="S12">
+        <v>2.58</v>
+      </c>
+      <c r="T12">
+        <v>1.6</v>
+      </c>
+      <c r="U12">
+        <v>2.42</v>
+      </c>
+      <c r="V12">
+        <v>1.53</v>
+      </c>
+      <c r="W12">
         <v>1.55</v>
-      </c>
-      <c r="H12">
-        <v>6.8</v>
-      </c>
-      <c r="I12">
-        <v>10.5</v>
-      </c>
-      <c r="J12">
-        <v>4.5</v>
-      </c>
-      <c r="K12">
-        <v>5.8</v>
-      </c>
-      <c r="L12">
-        <v>1.26</v>
-      </c>
-      <c r="M12">
-        <v>1.01</v>
-      </c>
-      <c r="N12">
-        <v>5</v>
-      </c>
-      <c r="O12">
-        <v>1.2</v>
-      </c>
-      <c r="P12">
-        <v>2.36</v>
-      </c>
-      <c r="Q12">
-        <v>1.53</v>
-      </c>
-      <c r="R12">
-        <v>1.54</v>
-      </c>
-      <c r="S12">
-        <v>2.32</v>
-      </c>
-      <c r="T12">
-        <v>1.81</v>
-      </c>
-      <c r="U12">
-        <v>1.98</v>
-      </c>
-      <c r="V12">
-        <v>1.11</v>
-      </c>
-      <c r="W12">
-        <v>2.82</v>
       </c>
       <c r="X12">
         <v>950</v>
       </c>
       <c r="Y12">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z12">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB12">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AC12">
+        <v>10.5</v>
+      </c>
+      <c r="AD12">
+        <v>15</v>
+      </c>
+      <c r="AE12">
+        <v>32</v>
+      </c>
+      <c r="AF12">
+        <v>23</v>
+      </c>
+      <c r="AG12">
+        <v>14.5</v>
+      </c>
+      <c r="AH12">
+        <v>970</v>
+      </c>
+      <c r="AI12">
+        <v>40</v>
+      </c>
+      <c r="AJ12">
+        <v>44</v>
+      </c>
+      <c r="AK12">
+        <v>32</v>
+      </c>
+      <c r="AL12">
+        <v>46</v>
+      </c>
+      <c r="AM12">
+        <v>75</v>
+      </c>
+      <c r="AN12">
+        <v>21</v>
+      </c>
+      <c r="AO12">
+        <v>22</v>
+      </c>
+      <c r="AP12">
+        <v>4.2</v>
+      </c>
+      <c r="AQ12">
+        <v>11</v>
+      </c>
+      <c r="AR12">
+        <v>4.2</v>
+      </c>
+      <c r="AS12">
+        <v>4.6</v>
+      </c>
+      <c r="AT12">
+        <v>3.9</v>
+      </c>
+      <c r="AU12">
+        <v>3.45</v>
+      </c>
+      <c r="AV12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW12">
+        <v>4.4</v>
+      </c>
+      <c r="AX12">
+        <v>4.2</v>
+      </c>
+      <c r="AY12">
+        <v>9.6</v>
+      </c>
+      <c r="AZ12">
+        <v>11.5</v>
+      </c>
+      <c r="BA12">
+        <v>4.6</v>
+      </c>
+      <c r="BB12">
+        <v>4.6</v>
+      </c>
+      <c r="BC12">
+        <v>4.4</v>
+      </c>
+      <c r="BD12">
+        <v>4.5</v>
+      </c>
+      <c r="BE12">
+        <v>4.8</v>
+      </c>
+      <c r="BF12">
+        <v>13.5</v>
+      </c>
+      <c r="BG12">
         <v>14</v>
       </c>
-      <c r="AD12">
-        <v>950</v>
-      </c>
-      <c r="AE12">
-        <v>130</v>
-      </c>
-      <c r="AF12">
-        <v>11.5</v>
-      </c>
-      <c r="AG12">
-        <v>12</v>
-      </c>
-      <c r="AH12">
-        <v>950</v>
-      </c>
-      <c r="AI12">
-        <v>110</v>
-      </c>
-      <c r="AJ12">
-        <v>970</v>
-      </c>
-      <c r="AK12">
-        <v>970</v>
-      </c>
-      <c r="AL12">
-        <v>38</v>
-      </c>
-      <c r="AM12">
-        <v>130</v>
-      </c>
-      <c r="AN12">
-        <v>6.6</v>
-      </c>
-      <c r="AO12">
-        <v>140</v>
-      </c>
-      <c r="AP12">
-        <v>4.3</v>
-      </c>
-      <c r="AQ12">
-        <v>4.4</v>
-      </c>
-      <c r="AR12">
-        <v>4.8</v>
-      </c>
-      <c r="AS12">
-        <v>5</v>
-      </c>
-      <c r="AT12">
-        <v>7.8</v>
-      </c>
-      <c r="AU12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV12">
-        <v>4.4</v>
-      </c>
-      <c r="AW12">
-        <v>4.9</v>
-      </c>
-      <c r="AX12">
-        <v>7.6</v>
-      </c>
-      <c r="AY12">
-        <v>8</v>
-      </c>
-      <c r="AZ12">
-        <v>4.2</v>
-      </c>
-      <c r="BA12">
-        <v>4.8</v>
-      </c>
-      <c r="BB12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC12">
-        <v>11</v>
-      </c>
-      <c r="BD12">
-        <v>4.4</v>
-      </c>
-      <c r="BE12">
-        <v>4.9</v>
-      </c>
-      <c r="BF12">
-        <v>4.5</v>
-      </c>
-      <c r="BG12">
-        <v>4.9</v>
-      </c>
       <c r="BH12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:60">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
         <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F13">
-        <v>2.06</v>
+        <v>6.2</v>
       </c>
       <c r="G13">
-        <v>2.3</v>
+        <v>9</v>
       </c>
       <c r="H13">
-        <v>3.6</v>
+        <v>1.51</v>
       </c>
       <c r="I13">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="J13">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K13">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="L13">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M13">
         <v>1.07</v>
       </c>
       <c r="N13">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O13">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P13">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="Q13">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R13">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S13">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="T13">
-        <v>1.79</v>
+        <v>2.12</v>
       </c>
       <c r="U13">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="V13">
-        <v>1.31</v>
+        <v>2.6</v>
       </c>
       <c r="W13">
-        <v>1.78</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y13">
-        <v>16.5</v>
+        <v>7.2</v>
       </c>
       <c r="Z13">
-        <v>34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA13">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="AB13">
+        <v>23</v>
+      </c>
+      <c r="AC13">
         <v>10.5</v>
       </c>
-      <c r="AC13">
-        <v>9.6</v>
-      </c>
       <c r="AD13">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AE13">
-        <v>55</v>
+        <v>19.5</v>
       </c>
       <c r="AF13">
-        <v>16.5</v>
+        <v>75</v>
       </c>
       <c r="AG13">
-        <v>13.5</v>
+        <v>32</v>
       </c>
       <c r="AH13">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AI13">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AJ13">
-        <v>34</v>
+        <v>350</v>
       </c>
       <c r="AK13">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c r="AL13">
-        <v>48</v>
+        <v>160</v>
       </c>
       <c r="AM13">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="AN13">
-        <v>23</v>
+        <v>280</v>
       </c>
       <c r="AO13">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="AP13">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="AQ13">
-        <v>11.5</v>
+        <v>3.7</v>
       </c>
       <c r="AR13">
-        <v>20</v>
+        <v>4.1</v>
       </c>
       <c r="AS13">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT13">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AU13">
+        <v>4.4</v>
+      </c>
+      <c r="AV13">
+        <v>4.7</v>
+      </c>
+      <c r="AW13">
+        <v>5.5</v>
+      </c>
+      <c r="AX13">
+        <v>7</v>
+      </c>
+      <c r="AY13">
+        <v>6.2</v>
+      </c>
+      <c r="AZ13">
         <v>6</v>
       </c>
-      <c r="AV13">
-        <v>11.5</v>
-      </c>
-      <c r="AW13">
-        <v>4</v>
-      </c>
-      <c r="AX13">
-        <v>10</v>
-      </c>
-      <c r="AY13">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ13">
-        <v>13.5</v>
-      </c>
       <c r="BA13">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BB13">
-        <v>19.5</v>
+        <v>7.4</v>
       </c>
       <c r="BC13">
-        <v>17.5</v>
+        <v>7.4</v>
       </c>
       <c r="BD13">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="BE13">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF13">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="BG13">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BH13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:60">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s">
         <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F14">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="G14">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="H14">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="I14">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="J14">
         <v>3.55</v>
       </c>
       <c r="K14">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L14">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="M14">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N14">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="O14">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="P14">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="Q14">
-        <v>2.58</v>
+        <v>2.2</v>
       </c>
       <c r="R14">
+        <v>1.26</v>
+      </c>
+      <c r="S14">
+        <v>4.1</v>
+      </c>
+      <c r="T14">
+        <v>2.06</v>
+      </c>
+      <c r="U14">
+        <v>1.8</v>
+      </c>
+      <c r="V14">
+        <v>2.16</v>
+      </c>
+      <c r="W14">
         <v>1.18</v>
       </c>
-      <c r="S14">
-        <v>5.4</v>
-      </c>
-      <c r="T14">
-        <v>2.52</v>
-      </c>
-      <c r="U14">
-        <v>1.54</v>
-      </c>
-      <c r="V14">
-        <v>2.46</v>
-      </c>
-      <c r="W14">
-        <v>1.13</v>
-      </c>
       <c r="X14">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y14">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="Z14">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AA14">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AB14">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AC14">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AD14">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AE14">
         <v>25</v>
       </c>
       <c r="AF14">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AG14">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AH14">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AI14">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AO14">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AP14">
-        <v>4.7</v>
+        <v>9.6</v>
       </c>
       <c r="AQ14">
+        <v>6</v>
+      </c>
+      <c r="AR14">
+        <v>7.6</v>
+      </c>
+      <c r="AS14">
+        <v>14.5</v>
+      </c>
+      <c r="AT14">
+        <v>12</v>
+      </c>
+      <c r="AU14">
+        <v>7</v>
+      </c>
+      <c r="AV14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW14">
+        <v>16.5</v>
+      </c>
+      <c r="AX14">
         <v>4.9</v>
       </c>
-      <c r="AR14">
-        <v>6.6</v>
-      </c>
-      <c r="AS14">
-        <v>11.5</v>
-      </c>
-      <c r="AT14">
-        <v>5.8</v>
-      </c>
-      <c r="AU14">
-        <v>4.5</v>
-      </c>
-      <c r="AV14">
-        <v>5</v>
-      </c>
-      <c r="AW14">
-        <v>6.4</v>
-      </c>
-      <c r="AX14">
-        <v>7.8</v>
-      </c>
       <c r="AY14">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AZ14">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BA14">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB14">
-        <v>1.95</v>
+        <v>5.3</v>
       </c>
       <c r="BC14">
-        <v>2.42</v>
+        <v>5.2</v>
       </c>
       <c r="BD14">
-        <v>2.42</v>
+        <v>5.2</v>
       </c>
       <c r="BE14">
-        <v>1.95</v>
+        <v>5.3</v>
       </c>
       <c r="BF14">
-        <v>1.95</v>
+        <v>5.3</v>
       </c>
       <c r="BG14">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="BH14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:60">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s">
         <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F15">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="G15">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="H15">
-        <v>10.5</v>
+        <v>3.6</v>
       </c>
       <c r="I15">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="J15">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="K15">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="L15">
         <v>1.35</v>
@@ -3350,327 +3347,327 @@
         <v>1.07</v>
       </c>
       <c r="N15">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O15">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P15">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Q15">
+        <v>1.99</v>
+      </c>
+      <c r="R15">
+        <v>1.31</v>
+      </c>
+      <c r="S15">
+        <v>3.55</v>
+      </c>
+      <c r="T15">
+        <v>1.8</v>
+      </c>
+      <c r="U15">
         <v>2.02</v>
       </c>
-      <c r="R15">
-        <v>1.32</v>
-      </c>
-      <c r="S15">
-        <v>3.65</v>
-      </c>
-      <c r="T15">
-        <v>2.36</v>
-      </c>
-      <c r="U15">
-        <v>1.65</v>
-      </c>
       <c r="V15">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="W15">
-        <v>3.2</v>
+        <v>1.78</v>
       </c>
       <c r="X15">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y15">
+        <v>16.5</v>
+      </c>
+      <c r="Z15">
+        <v>34</v>
+      </c>
+      <c r="AA15">
+        <v>95</v>
+      </c>
+      <c r="AB15">
+        <v>10.5</v>
+      </c>
+      <c r="AC15">
+        <v>9.6</v>
+      </c>
+      <c r="AD15">
+        <v>20</v>
+      </c>
+      <c r="AE15">
+        <v>55</v>
+      </c>
+      <c r="AF15">
+        <v>16.5</v>
+      </c>
+      <c r="AG15">
+        <v>13.5</v>
+      </c>
+      <c r="AH15">
+        <v>23</v>
+      </c>
+      <c r="AI15">
+        <v>75</v>
+      </c>
+      <c r="AJ15">
+        <v>34</v>
+      </c>
+      <c r="AK15">
         <v>29</v>
       </c>
-      <c r="Z15">
-        <v>120</v>
-      </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>6.6</v>
-      </c>
-      <c r="AC15">
-        <v>12</v>
-      </c>
-      <c r="AD15">
-        <v>50</v>
-      </c>
-      <c r="AE15">
-        <v>280</v>
-      </c>
-      <c r="AF15">
-        <v>7.4</v>
-      </c>
-      <c r="AG15">
-        <v>11.5</v>
-      </c>
-      <c r="AH15">
-        <v>40</v>
-      </c>
-      <c r="AI15">
-        <v>230</v>
-      </c>
-      <c r="AJ15">
-        <v>12</v>
-      </c>
-      <c r="AK15">
-        <v>17.5</v>
-      </c>
       <c r="AL15">
+        <v>48</v>
+      </c>
+      <c r="AM15">
+        <v>130</v>
+      </c>
+      <c r="AN15">
+        <v>23</v>
+      </c>
+      <c r="AO15">
         <v>60</v>
-      </c>
-      <c r="AM15">
-        <v>290</v>
-      </c>
-      <c r="AN15">
-        <v>8.4</v>
-      </c>
-      <c r="AO15">
-        <v>520</v>
       </c>
       <c r="AP15">
         <v>11</v>
       </c>
       <c r="AQ15">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="AR15">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="AS15">
-        <v>9.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AT15">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="AU15">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV15">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AW15">
-        <v>9.4</v>
+        <v>4.1</v>
       </c>
       <c r="AX15">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AY15">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="BA15">
-        <v>9.4</v>
+        <v>4.1</v>
       </c>
       <c r="BB15">
-        <v>9.6</v>
+        <v>3.9</v>
       </c>
       <c r="BC15">
-        <v>6.2</v>
+        <v>17.5</v>
       </c>
       <c r="BD15">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="BE15">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="BF15">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BG15">
-        <v>9.6</v>
+        <v>4.1</v>
       </c>
       <c r="BH15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:60">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
         <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F16">
+        <v>7.8</v>
+      </c>
+      <c r="G16">
+        <v>9.4</v>
+      </c>
+      <c r="H16">
+        <v>1.6</v>
+      </c>
+      <c r="I16">
+        <v>1.66</v>
+      </c>
+      <c r="J16">
+        <v>3.6</v>
+      </c>
+      <c r="K16">
+        <v>4.1</v>
+      </c>
+      <c r="L16">
+        <v>1.45</v>
+      </c>
+      <c r="M16">
+        <v>1.11</v>
+      </c>
+      <c r="N16">
+        <v>2.68</v>
+      </c>
+      <c r="O16">
+        <v>1.51</v>
+      </c>
+      <c r="P16">
+        <v>1.55</v>
+      </c>
+      <c r="Q16">
+        <v>2.48</v>
+      </c>
+      <c r="R16">
+        <v>1.19</v>
+      </c>
+      <c r="S16">
         <v>5.3</v>
       </c>
-      <c r="G16">
-        <v>6.4</v>
-      </c>
-      <c r="H16">
-        <v>1.72</v>
-      </c>
-      <c r="I16">
-        <v>1.88</v>
-      </c>
-      <c r="J16">
-        <v>3.5</v>
-      </c>
-      <c r="K16">
-        <v>4</v>
-      </c>
-      <c r="L16">
-        <v>1.41</v>
-      </c>
-      <c r="M16">
-        <v>1.09</v>
-      </c>
-      <c r="N16">
-        <v>3.1</v>
-      </c>
-      <c r="O16">
-        <v>1.4</v>
-      </c>
-      <c r="P16">
-        <v>1.7</v>
-      </c>
-      <c r="Q16">
-        <v>2.2</v>
-      </c>
-      <c r="R16">
-        <v>1.25</v>
-      </c>
-      <c r="S16">
-        <v>4.1</v>
-      </c>
       <c r="T16">
-        <v>2.02</v>
+        <v>2.52</v>
       </c>
       <c r="U16">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="V16">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="W16">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Y16">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="Z16">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AA16">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AB16">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AC16">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AD16">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AE16">
         <v>25</v>
       </c>
       <c r="AF16">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AG16">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AH16">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI16">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AJ16">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AP16">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="AQ16">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="AR16">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AS16">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT16">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="AU16">
+        <v>4.6</v>
+      </c>
+      <c r="AV16">
+        <v>5.1</v>
+      </c>
+      <c r="AW16">
         <v>6.6</v>
       </c>
-      <c r="AV16">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW16">
-        <v>16.5</v>
-      </c>
       <c r="AX16">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="AY16">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="AZ16">
-        <v>18.5</v>
+        <v>7.4</v>
       </c>
       <c r="BA16">
-        <v>4.7</v>
+        <v>2.42</v>
       </c>
       <c r="BB16">
-        <v>5.1</v>
+        <v>1.89</v>
       </c>
       <c r="BC16">
-        <v>5</v>
+        <v>2.46</v>
       </c>
       <c r="BD16">
-        <v>5</v>
+        <v>2.46</v>
       </c>
       <c r="BE16">
-        <v>5.1</v>
+        <v>1.76</v>
       </c>
       <c r="BF16">
-        <v>5</v>
+        <v>1.76</v>
       </c>
       <c r="BG16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:60">
@@ -3681,178 +3678,178 @@
         <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F17">
-        <v>2.58</v>
+        <v>1.38</v>
       </c>
       <c r="G17">
-        <v>2.84</v>
+        <v>1.42</v>
       </c>
       <c r="H17">
-        <v>2.62</v>
+        <v>11.5</v>
       </c>
       <c r="I17">
-        <v>2.86</v>
+        <v>15.5</v>
       </c>
       <c r="J17">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="K17">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="L17">
+        <v>1.35</v>
+      </c>
+      <c r="M17">
+        <v>1.06</v>
+      </c>
+      <c r="N17">
+        <v>3.5</v>
+      </c>
+      <c r="O17">
         <v>1.34</v>
       </c>
-      <c r="M17">
-        <v>1.05</v>
-      </c>
-      <c r="N17">
-        <v>4.1</v>
-      </c>
-      <c r="O17">
-        <v>1.24</v>
-      </c>
       <c r="P17">
-        <v>2.24</v>
+        <v>1.86</v>
       </c>
       <c r="Q17">
-        <v>1.69</v>
+        <v>1.98</v>
       </c>
       <c r="R17">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="S17">
-        <v>2.56</v>
+        <v>3.55</v>
       </c>
       <c r="T17">
-        <v>1.6</v>
+        <v>2.38</v>
       </c>
       <c r="U17">
-        <v>2.42</v>
+        <v>1.62</v>
       </c>
       <c r="V17">
-        <v>1.54</v>
+        <v>1.08</v>
       </c>
       <c r="W17">
-        <v>1.54</v>
+        <v>3.35</v>
       </c>
       <c r="X17">
+        <v>15</v>
+      </c>
+      <c r="Y17">
+        <v>30</v>
+      </c>
+      <c r="Z17">
+        <v>1000</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>6.8</v>
+      </c>
+      <c r="AC17">
+        <v>12</v>
+      </c>
+      <c r="AD17">
         <v>950</v>
       </c>
-      <c r="Y17">
-        <v>970</v>
-      </c>
-      <c r="Z17">
-        <v>24</v>
-      </c>
-      <c r="AA17">
-        <v>46</v>
-      </c>
-      <c r="AB17">
-        <v>16.5</v>
-      </c>
-      <c r="AC17">
-        <v>10.5</v>
-      </c>
-      <c r="AD17">
-        <v>970</v>
-      </c>
       <c r="AE17">
-        <v>32</v>
+        <v>320</v>
       </c>
       <c r="AF17">
-        <v>23</v>
+        <v>7.2</v>
       </c>
       <c r="AG17">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AH17">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AI17">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="AJ17">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="AK17">
-        <v>32</v>
+        <v>17.5</v>
       </c>
       <c r="AL17">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM17">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AN17">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="AO17">
-        <v>21</v>
+        <v>610</v>
       </c>
       <c r="AP17">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="AQ17">
+        <v>8.4</v>
+      </c>
+      <c r="AR17">
+        <v>11.5</v>
+      </c>
+      <c r="AS17">
+        <v>11.5</v>
+      </c>
+      <c r="AT17">
+        <v>5.9</v>
+      </c>
+      <c r="AU17">
+        <v>10</v>
+      </c>
+      <c r="AV17">
+        <v>9.4</v>
+      </c>
+      <c r="AW17">
         <v>11</v>
       </c>
-      <c r="AR17">
-        <v>15.5</v>
-      </c>
-      <c r="AS17">
-        <v>4.7</v>
-      </c>
-      <c r="AT17">
-        <v>3.95</v>
-      </c>
-      <c r="AU17">
-        <v>7</v>
-      </c>
-      <c r="AV17">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW17">
-        <v>4.5</v>
-      </c>
       <c r="AX17">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY17">
+        <v>9.4</v>
+      </c>
+      <c r="AZ17">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA17">
+        <v>11</v>
+      </c>
+      <c r="BB17">
         <v>9.6</v>
       </c>
-      <c r="AZ17">
+      <c r="BC17">
+        <v>15</v>
+      </c>
+      <c r="BD17">
+        <v>9.6</v>
+      </c>
+      <c r="BE17">
+        <v>11</v>
+      </c>
+      <c r="BF17">
+        <v>6.8</v>
+      </c>
+      <c r="BG17">
         <v>11.5</v>
       </c>
-      <c r="BA17">
-        <v>4.6</v>
-      </c>
-      <c r="BB17">
-        <v>4.7</v>
-      </c>
-      <c r="BC17">
-        <v>4.5</v>
-      </c>
-      <c r="BD17">
-        <v>4.5</v>
-      </c>
-      <c r="BE17">
-        <v>4.8</v>
-      </c>
-      <c r="BF17">
-        <v>13.5</v>
-      </c>
-      <c r="BG17">
-        <v>14</v>
-      </c>
       <c r="BH17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:60">
@@ -3863,13 +3860,13 @@
         <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F18">
         <v>10</v>
@@ -4034,7 +4031,7 @@
         <v>2.88</v>
       </c>
       <c r="BH18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:60">
@@ -4045,178 +4042,178 @@
         <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F19">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="G19">
-        <v>2.42</v>
+        <v>990</v>
       </c>
       <c r="H19">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="I19">
-        <v>3.55</v>
+        <v>990</v>
       </c>
       <c r="J19">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="K19">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L19">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>3.65</v>
+        <v>1.1</v>
       </c>
       <c r="O19">
+        <v>1.01</v>
+      </c>
+      <c r="P19">
+        <v>1.08</v>
+      </c>
+      <c r="Q19">
+        <v>1.02</v>
+      </c>
+      <c r="R19">
+        <v>1.08</v>
+      </c>
+      <c r="S19">
         <v>1.33</v>
       </c>
-      <c r="P19">
-        <v>1.91</v>
-      </c>
-      <c r="Q19">
-        <v>2.04</v>
-      </c>
-      <c r="R19">
-        <v>1.35</v>
-      </c>
-      <c r="S19">
-        <v>3.6</v>
-      </c>
       <c r="T19">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="U19">
-        <v>2.14</v>
+        <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="W19">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:60">
@@ -4227,178 +4224,178 @@
         <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F20">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="G20">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="H20">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="I20">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="K20">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L20">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M20">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="O20">
+        <v>1.33</v>
+      </c>
+      <c r="P20">
+        <v>1.91</v>
+      </c>
+      <c r="Q20">
+        <v>2.04</v>
+      </c>
+      <c r="R20">
         <v>1.35</v>
-      </c>
-      <c r="P20">
-        <v>1.77</v>
-      </c>
-      <c r="Q20">
-        <v>1.94</v>
-      </c>
-      <c r="R20">
-        <v>1.29</v>
       </c>
       <c r="S20">
         <v>3.4</v>
       </c>
       <c r="T20">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U20">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="V20">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W20">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="X20">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Y20">
         <v>13.5</v>
       </c>
       <c r="Z20">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA20">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB20">
+        <v>10.5</v>
+      </c>
+      <c r="AC20">
+        <v>8</v>
+      </c>
+      <c r="AD20">
+        <v>970</v>
+      </c>
+      <c r="AE20">
+        <v>40</v>
+      </c>
+      <c r="AF20">
+        <v>15.5</v>
+      </c>
+      <c r="AG20">
         <v>11.5</v>
       </c>
-      <c r="AC20">
+      <c r="AH20">
+        <v>970</v>
+      </c>
+      <c r="AI20">
+        <v>55</v>
+      </c>
+      <c r="AJ20">
+        <v>32</v>
+      </c>
+      <c r="AK20">
+        <v>26</v>
+      </c>
+      <c r="AL20">
+        <v>38</v>
+      </c>
+      <c r="AM20">
+        <v>110</v>
+      </c>
+      <c r="AN20">
+        <v>970</v>
+      </c>
+      <c r="AO20">
+        <v>42</v>
+      </c>
+      <c r="AP20">
+        <v>11</v>
+      </c>
+      <c r="AQ20">
+        <v>10</v>
+      </c>
+      <c r="AR20">
+        <v>18</v>
+      </c>
+      <c r="AS20">
+        <v>10.5</v>
+      </c>
+      <c r="AT20">
+        <v>5.8</v>
+      </c>
+      <c r="AU20">
+        <v>4.9</v>
+      </c>
+      <c r="AV20">
+        <v>11</v>
+      </c>
+      <c r="AW20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX20">
+        <v>11.5</v>
+      </c>
+      <c r="AY20">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD20">
-        <v>16</v>
-      </c>
-      <c r="AE20">
-        <v>46</v>
-      </c>
-      <c r="AF20">
-        <v>18.5</v>
-      </c>
-      <c r="AG20">
-        <v>14</v>
-      </c>
-      <c r="AH20">
-        <v>21</v>
-      </c>
-      <c r="AI20">
-        <v>60</v>
-      </c>
-      <c r="AJ20">
-        <v>42</v>
-      </c>
-      <c r="AK20">
-        <v>34</v>
-      </c>
-      <c r="AL20">
-        <v>55</v>
-      </c>
-      <c r="AM20">
-        <v>120</v>
-      </c>
-      <c r="AN20">
-        <v>30</v>
-      </c>
-      <c r="AO20">
-        <v>46</v>
-      </c>
-      <c r="AP20">
-        <v>3.8</v>
-      </c>
-      <c r="AQ20">
-        <v>3.75</v>
-      </c>
-      <c r="AR20">
-        <v>4.3</v>
-      </c>
-      <c r="AS20">
-        <v>4.8</v>
-      </c>
-      <c r="AT20">
-        <v>3.55</v>
-      </c>
-      <c r="AU20">
-        <v>3.25</v>
-      </c>
-      <c r="AV20">
-        <v>3.9</v>
-      </c>
-      <c r="AW20">
-        <v>4.6</v>
-      </c>
-      <c r="AX20">
-        <v>4</v>
-      </c>
-      <c r="AY20">
-        <v>3.75</v>
-      </c>
       <c r="AZ20">
-        <v>4.1</v>
+        <v>15.5</v>
       </c>
       <c r="BA20">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="BB20">
-        <v>4.6</v>
+        <v>24</v>
       </c>
       <c r="BC20">
-        <v>4.5</v>
+        <v>19</v>
       </c>
       <c r="BD20">
-        <v>4.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE20">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF20">
-        <v>4.4</v>
+        <v>17</v>
       </c>
       <c r="BG20">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="BH20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:60">
@@ -4409,178 +4406,178 @@
         <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F21">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="G21">
-        <v>990</v>
+        <v>2.76</v>
       </c>
       <c r="H21">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="I21">
-        <v>990</v>
+        <v>3.7</v>
       </c>
       <c r="J21">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="K21">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M21">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N21">
-        <v>1.1</v>
+        <v>3.25</v>
       </c>
       <c r="O21">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="P21">
-        <v>1.08</v>
+        <v>1.77</v>
       </c>
       <c r="Q21">
-        <v>1.02</v>
+        <v>1.94</v>
       </c>
       <c r="R21">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="S21">
-        <v>1.33</v>
+        <v>3.4</v>
       </c>
       <c r="T21">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="U21">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V21">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W21">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="X21">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y21">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z21">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB21">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC21">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD21">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF21">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG21">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ21">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK21">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL21">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN21">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP21">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ21">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR21">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS21">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT21">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU21">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV21">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW21">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX21">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY21">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ21">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA21">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB21">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC21">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD21">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE21">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:60">
@@ -4591,25 +4588,25 @@
         <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F22">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G22">
         <v>1.71</v>
       </c>
       <c r="H22">
+        <v>5.6</v>
+      </c>
+      <c r="I22">
         <v>5.7</v>
-      </c>
-      <c r="I22">
-        <v>5.8</v>
       </c>
       <c r="J22">
         <v>4.2</v>
@@ -4645,7 +4642,7 @@
         <v>1.99</v>
       </c>
       <c r="U22">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V22">
         <v>1.21</v>
@@ -4654,7 +4651,7 @@
         <v>2.4</v>
       </c>
       <c r="X22">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y22">
         <v>18.5</v>
@@ -4663,22 +4660,22 @@
         <v>44</v>
       </c>
       <c r="AA22">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AB22">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE22">
         <v>80</v>
       </c>
       <c r="AF22">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG22">
         <v>9.800000000000001</v>
@@ -4699,19 +4696,19 @@
         <v>36</v>
       </c>
       <c r="AM22">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="AN22">
         <v>10.5</v>
       </c>
       <c r="AO22">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP22">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ22">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR22">
         <v>40</v>
@@ -4726,7 +4723,7 @@
         <v>8.6</v>
       </c>
       <c r="AV22">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW22">
         <v>70</v>
@@ -4735,7 +4732,7 @@
         <v>9</v>
       </c>
       <c r="AY22">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ22">
         <v>20</v>
@@ -4744,7 +4741,7 @@
         <v>70</v>
       </c>
       <c r="BB22">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC22">
         <v>16</v>
@@ -4762,7 +4759,7 @@
         <v>90</v>
       </c>
       <c r="BH22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G2" t="n">
         <v>4.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="I2" t="n">
         <v>2.58</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G3" t="n">
         <v>2.4</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I3" t="n">
         <v>4.2</v>
@@ -984,7 +984,7 @@
         <v>1.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="R3" t="n">
         <v>1.25</v>
@@ -1035,7 +1035,7 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
         <v>80</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -1253,52 +1253,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="J5" t="n">
         <v>3.25</v>
@@ -1360,10 +1360,10 @@
         <v>1.37</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O5" t="n">
         <v>1.37</v>
@@ -1372,31 +1372,31 @@
         <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R5" t="n">
         <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U5" t="n">
         <v>2.04</v>
       </c>
       <c r="V5" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X5" t="n">
         <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="Z5" t="n">
         <v>24</v>
@@ -1411,22 +1411,22 @@
         <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AF5" t="n">
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="n">
         <v>36</v>
@@ -1456,7 +1456,7 @@
         <v>19</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT5" t="n">
         <v>8.4</v>
@@ -1468,41 +1468,41 @@
         <v>12.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
         <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
         <v>18.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -1542,10 +1542,10 @@
         <v>2.58</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="J6" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
         <v>3.35</v>
@@ -1560,13 +1560,13 @@
         <v>2.32</v>
       </c>
       <c r="O6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P6" t="n">
         <v>1.49</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1581,7 +1581,7 @@
         <v>1.73</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
         <v>1.4</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="G7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H7" t="n">
         <v>1.74</v>
       </c>
       <c r="I7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J7" t="n">
         <v>2.88</v>
       </c>
       <c r="K7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L7" t="n">
         <v>1.33</v>
@@ -1754,13 +1754,13 @@
         <v>2.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P7" t="n">
         <v>1.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="R7" t="n">
         <v>1.21</v>
@@ -1775,10 +1775,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="W7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1835,52 +1835,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -1933,13 +1933,13 @@
         <v>2.52</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M8" t="n">
         <v>1.03</v>
@@ -1951,16 +1951,16 @@
         <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q8" t="n">
         <v>1.51</v>
       </c>
       <c r="R8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S8" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T8" t="n">
         <v>1.47</v>
@@ -1972,22 +1972,22 @@
         <v>1.65</v>
       </c>
       <c r="W8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
         <v>48</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="Z8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA8" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AB8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC8" t="n">
         <v>10</v>
@@ -1996,19 +1996,19 @@
         <v>12.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF8" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AG8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ8" t="n">
         <v>55</v>
@@ -2020,31 +2020,31 @@
         <v>50</v>
       </c>
       <c r="AM8" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AN8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR8" t="n">
         <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
         <v>15.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV8" t="n">
         <v>11</v>
@@ -2053,22 +2053,22 @@
         <v>16</v>
       </c>
       <c r="AX8" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AY8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ8" t="n">
         <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD8" t="n">
         <v>19.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -2148,13 +2148,13 @@
         <v>2.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R9" t="n">
         <v>1.51</v>
       </c>
       <c r="S9" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T9" t="n">
         <v>1.82</v>
@@ -2190,7 +2190,7 @@
         <v>10.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AF9" t="n">
         <v>65</v>
@@ -2253,7 +2253,7 @@
         <v>7.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="BA9" t="n">
         <v>7.4</v>
@@ -2268,17 +2268,17 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG9" t="n">
         <v>6.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H10" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>1.54</v>
+        <v>990</v>
       </c>
       <c r="J10" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="K10" t="n">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,31 +2333,31 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>2.04</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
         <v>1.19</v>
       </c>
       <c r="P10" t="n">
-        <v>2.04</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.54</v>
+        <v>1.18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>2.36</v>
+        <v>1.19</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
         <v>1.01</v>
@@ -2417,52 +2417,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="G11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N11" t="n">
         <v>3.1</v>
       </c>
-      <c r="H11" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3</v>
-      </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="V11" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X11" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AA11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>50</v>
       </c>
-      <c r="AB11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="AK11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR11" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AS11" t="n">
-        <v>3.7</v>
+        <v>30</v>
       </c>
       <c r="AT11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>3.6</v>
+        <v>25</v>
       </c>
       <c r="AX11" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>3.75</v>
+        <v>40</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.75</v>
+        <v>30</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.65</v>
+        <v>28</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.75</v>
+        <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="BF11" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="BG11" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G12" t="n">
         <v>2.08</v>
@@ -2742,7 +2742,7 @@
         <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V12" t="n">
         <v>1.24</v>
@@ -2793,7 +2793,7 @@
         <v>34</v>
       </c>
       <c r="AL12" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM12" t="n">
         <v>210</v>
@@ -2826,7 +2826,7 @@
         <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX12" t="n">
         <v>9.800000000000001</v>
@@ -2838,19 +2838,19 @@
         <v>19.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB12" t="n">
         <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD12" t="n">
         <v>4.1</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF12" t="n">
         <v>18.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -2924,13 +2924,13 @@
         <v>1.84</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="R13" t="n">
         <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="T13" t="n">
         <v>1.86</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -3085,46 +3085,46 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="G14" t="n">
         <v>1.58</v>
       </c>
       <c r="H14" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
         <v>1.97</v>
@@ -3133,40 +3133,40 @@
         <v>1.84</v>
       </c>
       <c r="V14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W14" t="n">
         <v>2.74</v>
       </c>
       <c r="X14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z14" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AA14" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AE14" t="n">
         <v>150</v>
       </c>
       <c r="AF14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
         <v>29</v>
@@ -3175,7 +3175,7 @@
         <v>130</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK14" t="n">
         <v>19</v>
@@ -3187,68 +3187,68 @@
         <v>170</v>
       </c>
       <c r="AN14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO14" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AP14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AR14" t="n">
         <v>5</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA14" t="n">
         <v>5.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BC14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>2.58</v>
       </c>
       <c r="G15" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H15" t="n">
         <v>2.48</v>
       </c>
       <c r="I15" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J15" t="n">
         <v>3.65</v>
@@ -3300,7 +3300,7 @@
         <v>1.28</v>
       </c>
       <c r="M15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
         <v>4.6</v>
@@ -3420,13 +3420,13 @@
         <v>11.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB15" t="n">
         <v>4.8</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BD15" t="n">
         <v>5.1</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>1.75</v>
       </c>
       <c r="I16" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>4</v>
@@ -3497,16 +3497,16 @@
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
         <v>1.27</v>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R16" t="n">
         <v>1.42</v>
@@ -3521,16 +3521,16 @@
         <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="W16" t="n">
         <v>1.23</v>
       </c>
       <c r="X16" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z16" t="n">
         <v>12</v>
@@ -3542,7 +3542,7 @@
         <v>20</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD16" t="n">
         <v>11</v>
@@ -3560,7 +3560,7 @@
         <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ16" t="n">
         <v>140</v>
@@ -3605,7 +3605,7 @@
         <v>15</v>
       </c>
       <c r="AX16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY16" t="n">
         <v>17.5</v>
@@ -3614,29 +3614,29 @@
         <v>16.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BG16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -3673,13 +3673,13 @@
         <v>1.51</v>
       </c>
       <c r="H17" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K17" t="n">
         <v>5.7</v>
@@ -3697,10 +3697,10 @@
         <v>1.18</v>
       </c>
       <c r="P17" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R17" t="n">
         <v>1.61</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G18" t="n">
         <v>1.52</v>
@@ -3870,13 +3870,13 @@
         <v>7.2</v>
       </c>
       <c r="I18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J18" t="n">
         <v>4.5</v>
       </c>
       <c r="K18" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L18" t="n">
         <v>1.26</v>
@@ -3948,7 +3948,7 @@
         <v>950</v>
       </c>
       <c r="AI18" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ18" t="n">
         <v>15</v>
@@ -3966,7 +3966,7 @@
         <v>6.8</v>
       </c>
       <c r="AO18" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP18" t="n">
         <v>4.9</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G19" t="n">
         <v>2.14</v>
       </c>
       <c r="H19" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I19" t="n">
         <v>4.4</v>
@@ -4073,7 +4073,7 @@
         <v>3.75</v>
       </c>
       <c r="L19" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
@@ -4103,7 +4103,7 @@
         <v>2.02</v>
       </c>
       <c r="V19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
         <v>1.87</v>
@@ -4139,7 +4139,7 @@
         <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AI19" t="n">
         <v>75</v>
@@ -4169,10 +4169,10 @@
         <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT19" t="n">
         <v>7.8</v>
@@ -4184,7 +4184,7 @@
         <v>11.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX19" t="n">
         <v>11</v>
@@ -4196,29 +4196,29 @@
         <v>15.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BC19" t="n">
         <v>17.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF19" t="n">
         <v>13</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
         <v>9.4</v>
@@ -4258,7 +4258,7 @@
         <v>1.55</v>
       </c>
       <c r="I20" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="J20" t="n">
         <v>3.7</v>
@@ -4267,7 +4267,7 @@
         <v>4.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="M20" t="n">
         <v>1.11</v>
@@ -4276,13 +4276,13 @@
         <v>2.72</v>
       </c>
       <c r="O20" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P20" t="n">
         <v>1.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R20" t="n">
         <v>1.2</v>
@@ -4297,25 +4297,25 @@
         <v>1.55</v>
       </c>
       <c r="V20" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="W20" t="n">
         <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AA20" t="n">
         <v>970</v>
       </c>
       <c r="AB20" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AC20" t="n">
         <v>970</v>
@@ -4336,7 +4336,7 @@
         <v>950</v>
       </c>
       <c r="AI20" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="n">
         <v>1000</v>
@@ -4369,50 +4369,50 @@
         <v>11.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AW20" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AY20" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AZ20" t="n">
         <v>7.2</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="BG20" t="n">
         <v>12.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -4482,10 +4482,10 @@
         <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U21" t="n">
         <v>1.62</v>
@@ -4494,7 +4494,7 @@
         <v>1.08</v>
       </c>
       <c r="W21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="X21" t="n">
         <v>15</v>
@@ -4548,19 +4548,19 @@
         <v>7.8</v>
       </c>
       <c r="AO21" t="n">
-        <v>610</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR21" t="n">
         <v>11.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT21" t="n">
         <v>5.9</v>
@@ -4569,10 +4569,10 @@
         <v>10</v>
       </c>
       <c r="AV21" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX21" t="n">
         <v>6.4</v>
@@ -4581,7 +4581,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BA21" t="n">
         <v>12</v>
@@ -4593,7 +4593,7 @@
         <v>15</v>
       </c>
       <c r="BD21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BE21" t="n">
         <v>12</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
         <v>3.55</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L22" t="n">
         <v>1.46</v>
@@ -4706,7 +4706,7 @@
         <v>18.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD22" t="n">
         <v>12</v>
@@ -4724,7 +4724,7 @@
         <v>28</v>
       </c>
       <c r="AI22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ22" t="n">
         <v>200</v>
@@ -4769,7 +4769,7 @@
         <v>16.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="AY22" t="n">
         <v>17</v>
@@ -4778,29 +4778,29 @@
         <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG22" t="n">
         <v>12</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="G23" t="n">
         <v>9</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="J23" t="n">
         <v>4</v>
@@ -4861,16 +4861,16 @@
         <v>1.34</v>
       </c>
       <c r="P23" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="R23" t="n">
         <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T23" t="n">
         <v>2.06</v>
@@ -4885,40 +4885,40 @@
         <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AC23" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD23" t="n">
         <v>11.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AF23" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH23" t="n">
         <v>32</v>
       </c>
-      <c r="AH23" t="n">
-        <v>30</v>
-      </c>
       <c r="AI23" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ23" t="n">
         <v>340</v>
@@ -4939,62 +4939,62 @@
         <v>11</v>
       </c>
       <c r="AP23" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR23" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS23" t="n">
         <v>10.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AU23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV23" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV23" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AW23" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="AY23" t="n">
-        <v>23</v>
+        <v>6.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA23" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BB23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG23" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -5025,31 +5025,31 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G24" t="n">
         <v>2.78</v>
       </c>
       <c r="H24" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I24" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L24" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M24" t="n">
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
         <v>1.24</v>
@@ -5064,16 +5064,16 @@
         <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="T24" t="n">
         <v>1.6</v>
       </c>
       <c r="U24" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V24" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W24" t="n">
         <v>1.56</v>
@@ -5091,10 +5091,10 @@
         <v>46</v>
       </c>
       <c r="AB24" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AC24" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD24" t="n">
         <v>15</v>
@@ -5121,7 +5121,7 @@
         <v>32</v>
       </c>
       <c r="AL24" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM24" t="n">
         <v>75</v>
@@ -5130,55 +5130,55 @@
         <v>21</v>
       </c>
       <c r="AO24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AQ24" t="n">
         <v>11</v>
       </c>
       <c r="AR24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT24" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AU24" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AV24" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AX24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY24" t="n">
         <v>4.2</v>
       </c>
-      <c r="AY24" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AZ24" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF24" t="n">
         <v>13.5</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="G25" t="n">
         <v>12</v>
@@ -5228,7 +5228,7 @@
         <v>1.29</v>
       </c>
       <c r="I25" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>6.6</v>
@@ -5243,31 +5243,31 @@
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="O25" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P25" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="R25" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="S25" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="T25" t="n">
         <v>1.74</v>
       </c>
       <c r="U25" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V25" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="W25" t="n">
         <v>1.09</v>
@@ -5276,34 +5276,34 @@
         <v>50</v>
       </c>
       <c r="Y25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA25" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>13</v>
       </c>
       <c r="AB25" t="n">
         <v>55</v>
       </c>
       <c r="AC25" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AF25" t="n">
         <v>120</v>
       </c>
       <c r="AG25" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AH25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI25" t="n">
         <v>28</v>
@@ -5315,7 +5315,7 @@
         <v>140</v>
       </c>
       <c r="AL25" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AM25" t="n">
         <v>100</v>
@@ -5324,22 +5324,22 @@
         <v>120</v>
       </c>
       <c r="AO25" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AP25" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ25" t="n">
         <v>12.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AS25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.6</v>
+        <v>38</v>
       </c>
       <c r="AU25" t="n">
         <v>14</v>
@@ -5351,38 +5351,38 @@
         <v>11</v>
       </c>
       <c r="AX25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY25" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BC25" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BD25" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BF25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BG25" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
         <v>990</v>
       </c>
       <c r="J26" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K26" t="n">
         <v>950</v>
@@ -5434,22 +5434,22 @@
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N26" t="n">
         <v>1.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="P26" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="R26" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S26" t="n">
         <v>1.33</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>2.28</v>
       </c>
       <c r="G27" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H27" t="n">
         <v>3.35</v>
@@ -5622,7 +5622,7 @@
         <v>3.4</v>
       </c>
       <c r="K27" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L27" t="n">
         <v>1.35</v>
@@ -5658,7 +5658,7 @@
         <v>1.39</v>
       </c>
       <c r="W27" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X27" t="n">
         <v>970</v>
@@ -5670,7 +5670,7 @@
         <v>24</v>
       </c>
       <c r="AA27" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AB27" t="n">
         <v>10.5</v>
@@ -5694,7 +5694,7 @@
         <v>970</v>
       </c>
       <c r="AI27" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ27" t="n">
         <v>32</v>
@@ -5703,7 +5703,7 @@
         <v>26</v>
       </c>
       <c r="AL27" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -5727,16 +5727,16 @@
         <v>10.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AU27" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AV27" t="n">
         <v>11</v>
       </c>
       <c r="AW27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX27" t="n">
         <v>11.5</v>
@@ -5751,26 +5751,26 @@
         <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="BC27" t="n">
         <v>19</v>
       </c>
       <c r="BD27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF27" t="n">
         <v>17</v>
       </c>
       <c r="BG27" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -5801,103 +5801,103 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="G28" t="n">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="I28" t="n">
-        <v>3.45</v>
+        <v>2.92</v>
       </c>
       <c r="J28" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K28" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="L28" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M28" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T28" t="n">
         <v>1.77</v>
       </c>
-      <c r="Q28" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.79</v>
-      </c>
       <c r="U28" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V28" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="W28" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="X28" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Y28" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AA28" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AB28" t="n">
         <v>11.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI28" t="n">
         <v>46</v>
       </c>
-      <c r="AF28" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>60</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AK28" t="n">
         <v>34</v>
       </c>
       <c r="AL28" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM28" t="n">
         <v>120</v>
@@ -5906,65 +5906,65 @@
         <v>30</v>
       </c>
       <c r="AO28" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="AP28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY28" t="n">
         <v>9.6</v>
       </c>
-      <c r="AQ28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ28" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.9</v>
+        <v>32</v>
       </c>
       <c r="BB28" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="BC28" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.9</v>
+        <v>32</v>
       </c>
       <c r="BE28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BF28" t="n">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="G29" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="H29" t="n">
         <v>5.9</v>
@@ -6007,103 +6007,103 @@
         <v>6</v>
       </c>
       <c r="J29" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K29" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P29" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R29" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
         <v>2.04</v>
       </c>
       <c r="U29" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="V29" t="n">
         <v>1.2</v>
       </c>
       <c r="W29" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="X29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y29" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA29" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD29" t="n">
         <v>23</v>
       </c>
       <c r="AE29" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN29" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AG29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AO29" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ29" t="n">
         <v>17</v>
@@ -6112,53 +6112,53 @@
         <v>40</v>
       </c>
       <c r="AS29" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AT29" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV29" t="n">
         <v>21</v>
       </c>
       <c r="AW29" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AX29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>75</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF29" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>70</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>110</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BG29" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -760,16 +760,16 @@
         <v>3.4</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I2" t="n">
         <v>2.58</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K2" t="n">
         <v>3.5</v>
@@ -790,13 +790,13 @@
         <v>1.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
         <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.05</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
         <v>1.97</v>
@@ -808,10 +808,10 @@
         <v>1.63</v>
       </c>
       <c r="W2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y2" t="n">
         <v>9</v>
@@ -823,7 +823,7 @@
         <v>40</v>
       </c>
       <c r="AB2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
         <v>8.199999999999999</v>
@@ -835,16 +835,16 @@
         <v>38</v>
       </c>
       <c r="AF2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG2" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH2" t="n">
         <v>25</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
         <v>90</v>
@@ -865,62 +865,62 @@
         <v>38</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BC2" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G3" t="n">
         <v>2.4</v>
@@ -960,7 +960,7 @@
         <v>3.4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
         <v>3.05</v>
@@ -990,7 +990,7 @@
         <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="T3" t="n">
         <v>1.87</v>
@@ -999,7 +999,7 @@
         <v>1.88</v>
       </c>
       <c r="V3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
         <v>1.72</v>
@@ -1011,16 +1011,16 @@
         <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA3" t="n">
         <v>90</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
         <v>970</v>
@@ -1041,10 +1041,10 @@
         <v>80</v>
       </c>
       <c r="AJ3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL3" t="n">
         <v>55</v>
@@ -1053,68 +1053,68 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AS3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX3" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AY3" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.9</v>
+        <v>2.34</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="G4" t="n">
         <v>990</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1169,22 +1169,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P4" t="n">
         <v>1.25</v>
       </c>
-      <c r="O4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S4" t="n">
-        <v>1.39</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1193,10 +1193,10 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -1342,94 +1342,94 @@
         <v>2.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I5" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
         <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
         <v>3.35</v>
       </c>
       <c r="O5" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="U5" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="V5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="X5" t="n">
         <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA5" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AF5" t="n">
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH5" t="n">
         <v>970</v>
       </c>
       <c r="AI5" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1444,65 +1444,65 @@
         <v>25</v>
       </c>
       <c r="AO5" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AP5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>10</v>
       </c>
       <c r="AR5" t="n">
         <v>19</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX5" t="n">
         <v>12.5</v>
       </c>
-      <c r="AW5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>11</v>
-      </c>
       <c r="AY5" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5" t="n">
         <v>18.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -1542,10 +1542,10 @@
         <v>2.58</v>
       </c>
       <c r="I6" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J6" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K6" t="n">
         <v>3.35</v>
@@ -1557,16 +1557,16 @@
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="O6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P6" t="n">
         <v>1.49</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1581,7 +1581,7 @@
         <v>1.73</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
         <v>1.4</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="G7" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="I7" t="n">
         <v>2.2</v>
@@ -1742,7 +1742,7 @@
         <v>2.88</v>
       </c>
       <c r="K7" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L7" t="n">
         <v>1.33</v>
@@ -1751,10 +1751,10 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P7" t="n">
         <v>1.64</v>
@@ -1775,10 +1775,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="H8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I8" t="n">
         <v>2.42</v>
       </c>
-      <c r="I8" t="n">
-        <v>2.52</v>
-      </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
         <v>4.1</v>
@@ -1951,43 +1951,43 @@
         <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S8" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T8" t="n">
         <v>1.47</v>
       </c>
       <c r="U8" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="V8" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="X8" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="Y8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA8" t="n">
         <v>40</v>
       </c>
       <c r="AB8" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AC8" t="n">
         <v>10</v>
@@ -2002,55 +2002,55 @@
         <v>38</v>
       </c>
       <c r="AG8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH8" t="n">
         <v>13.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ8" t="n">
         <v>55</v>
       </c>
       <c r="AK8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AM8" t="n">
         <v>55</v>
       </c>
       <c r="AN8" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
         <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AX8" t="n">
         <v>18</v>
@@ -2071,20 +2071,20 @@
         <v>19</v>
       </c>
       <c r="BD8" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BE8" t="n">
         <v>25</v>
       </c>
       <c r="BF8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="G9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="H9" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="I9" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.29</v>
@@ -2139,22 +2139,22 @@
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R9" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S9" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T9" t="n">
         <v>1.82</v>
@@ -2163,13 +2163,13 @@
         <v>2.08</v>
       </c>
       <c r="V9" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="W9" t="n">
         <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y9" t="n">
         <v>9.800000000000001</v>
@@ -2178,19 +2178,19 @@
         <v>10</v>
       </c>
       <c r="AA9" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AB9" t="n">
         <v>28</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
         <v>10.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF9" t="n">
         <v>65</v>
@@ -2205,10 +2205,10 @@
         <v>34</v>
       </c>
       <c r="AJ9" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AK9" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL9" t="n">
         <v>85</v>
@@ -2220,65 +2220,65 @@
         <v>120</v>
       </c>
       <c r="AO9" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AP9" t="n">
         <v>6.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AV9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX9" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AY9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC9" t="n">
         <v>7.6</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA9" t="n">
+      <c r="BD9" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE9" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
         <v>990</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="I10" t="n">
-        <v>990</v>
+        <v>1.52</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="K10" t="n">
         <v>950</v>
@@ -2333,22 +2333,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>1.19</v>
+        <v>2.36</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2357,7 +2357,7 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="W10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -2506,73 +2506,73 @@
         <v>2.88</v>
       </c>
       <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N11" t="n">
         <v>3.05</v>
       </c>
-      <c r="H11" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.1</v>
-      </c>
       <c r="O11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P11" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="U11" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W11" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z11" t="n">
         <v>18</v>
       </c>
       <c r="AA11" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD11" t="n">
         <v>13</v>
@@ -2581,7 +2581,7 @@
         <v>36</v>
       </c>
       <c r="AF11" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG11" t="n">
         <v>13.5</v>
@@ -2602,7 +2602,7 @@
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN11" t="n">
         <v>40</v>
@@ -2611,16 +2611,16 @@
         <v>36</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR11" t="n">
         <v>15.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AT11" t="n">
         <v>8.800000000000001</v>
@@ -2629,44 +2629,44 @@
         <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AX11" t="n">
         <v>16.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ11" t="n">
         <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BB11" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BC11" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BD11" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BE11" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="BF11" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BG11" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.94</v>
       </c>
       <c r="G12" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H12" t="n">
         <v>4.5</v>
@@ -2709,7 +2709,7 @@
         <v>5.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
         <v>3.55</v>
@@ -2721,7 +2721,7 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O12" t="n">
         <v>1.46</v>
@@ -2730,10 +2730,10 @@
         <v>1.69</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
         <v>4.6</v>
@@ -2742,7 +2742,7 @@
         <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V12" t="n">
         <v>1.24</v>
@@ -2751,7 +2751,7 @@
         <v>1.94</v>
       </c>
       <c r="X12" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="n">
         <v>16</v>
@@ -2766,7 +2766,7 @@
         <v>8.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
         <v>24</v>
@@ -2775,31 +2775,31 @@
         <v>95</v>
       </c>
       <c r="AF12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI12" t="n">
         <v>110</v>
       </c>
       <c r="AJ12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM12" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
         <v>140</v>
@@ -2811,10 +2811,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT12" t="n">
         <v>6.2</v>
@@ -2826,7 +2826,7 @@
         <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX12" t="n">
         <v>9.800000000000001</v>
@@ -2838,29 +2838,29 @@
         <v>19.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BB12" t="n">
         <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.2</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BF12" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>1.92</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
         <v>7</v>
@@ -3014,7 +3014,7 @@
         <v>3.05</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AV13" t="n">
         <v>3.7</v>
@@ -3026,7 +3026,7 @@
         <v>3.25</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AZ13" t="n">
         <v>3.7</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>1.44</v>
       </c>
       <c r="G14" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="H14" t="n">
         <v>7.6</v>
@@ -3115,7 +3115,7 @@
         <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
         <v>1.79</v>
@@ -3136,13 +3136,13 @@
         <v>1.11</v>
       </c>
       <c r="W14" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="X14" t="n">
         <v>20</v>
       </c>
       <c r="Y14" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="Z14" t="n">
         <v>85</v>
@@ -3151,10 +3151,10 @@
         <v>320</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD14" t="n">
         <v>36</v>
@@ -3187,7 +3187,7 @@
         <v>170</v>
       </c>
       <c r="AN14" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AO14" t="n">
         <v>210</v>
@@ -3196,59 +3196,59 @@
         <v>13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AR14" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AX14" t="n">
         <v>6.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
         <v>10</v>
       </c>
       <c r="BC14" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BF14" t="n">
         <v>6.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H15" t="n">
         <v>2.58</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.48</v>
-      </c>
       <c r="I15" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J15" t="n">
         <v>3.65</v>
@@ -3309,7 +3309,7 @@
         <v>1.22</v>
       </c>
       <c r="P15" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
         <v>1.65</v>
@@ -3330,7 +3330,7 @@
         <v>1.56</v>
       </c>
       <c r="W15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X15" t="n">
         <v>24</v>
@@ -3423,13 +3423,13 @@
         <v>5.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC15" t="n">
         <v>4.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BE15" t="n">
         <v>4.8</v>
@@ -3438,11 +3438,11 @@
         <v>13.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
         <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
         <v>1.06</v>
@@ -3503,10 +3503,10 @@
         <v>1.27</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R16" t="n">
         <v>1.42</v>
@@ -3515,7 +3515,7 @@
         <v>2.98</v>
       </c>
       <c r="T16" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U16" t="n">
         <v>2.1</v>
@@ -3566,16 +3566,16 @@
         <v>140</v>
       </c>
       <c r="AK16" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL16" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
       </c>
       <c r="AN16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO16" t="n">
         <v>10.5</v>
@@ -3605,7 +3605,7 @@
         <v>15</v>
       </c>
       <c r="AX16" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY16" t="n">
         <v>17.5</v>
@@ -3620,7 +3620,7 @@
         <v>8.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD16" t="n">
         <v>8.4</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>1.42</v>
       </c>
       <c r="G17" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="H17" t="n">
         <v>7.6</v>
@@ -3682,7 +3682,7 @@
         <v>4.9</v>
       </c>
       <c r="K17" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.24</v>
@@ -3691,40 +3691,40 @@
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O17" t="n">
         <v>1.18</v>
       </c>
       <c r="P17" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q17" t="n">
         <v>1.48</v>
       </c>
       <c r="R17" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="S17" t="n">
         <v>2.34</v>
       </c>
       <c r="T17" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="U17" t="n">
         <v>2.12</v>
       </c>
       <c r="V17" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
         <v>30</v>
       </c>
       <c r="Y17" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="Z17" t="n">
         <v>75</v>
@@ -3781,10 +3781,10 @@
         <v>7</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT17" t="n">
         <v>9.6</v>
@@ -3796,7 +3796,7 @@
         <v>21</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX17" t="n">
         <v>8.199999999999999</v>
@@ -3808,7 +3808,7 @@
         <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BB17" t="n">
         <v>10.5</v>
@@ -3820,17 +3820,17 @@
         <v>21</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF17" t="n">
         <v>4.7</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>1.43</v>
       </c>
       <c r="G18" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="H18" t="n">
         <v>7.2</v>
@@ -3873,7 +3873,7 @@
         <v>9.6</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="K18" t="n">
         <v>5.6</v>
@@ -3885,7 +3885,7 @@
         <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
         <v>1.21</v>
@@ -3909,10 +3909,10 @@
         <v>1.98</v>
       </c>
       <c r="V18" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W18" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="X18" t="n">
         <v>950</v>
@@ -3969,7 +3969,7 @@
         <v>130</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AQ18" t="n">
         <v>4.6</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -4061,13 +4061,13 @@
         <v>2.14</v>
       </c>
       <c r="H19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I19" t="n">
         <v>4.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
         <v>3.75</v>
@@ -4118,7 +4118,7 @@
         <v>34</v>
       </c>
       <c r="AA19" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB19" t="n">
         <v>9.4</v>
@@ -4157,7 +4157,7 @@
         <v>130</v>
       </c>
       <c r="AN19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="n">
         <v>60</v>
@@ -4169,10 +4169,10 @@
         <v>11.5</v>
       </c>
       <c r="AR19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS19" t="n">
         <v>4.8</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>4.7</v>
       </c>
       <c r="AT19" t="n">
         <v>7.8</v>
@@ -4184,7 +4184,7 @@
         <v>11.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX19" t="n">
         <v>11</v>
@@ -4199,26 +4199,26 @@
         <v>5.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC19" t="n">
         <v>17.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF19" t="n">
         <v>13</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -4249,43 +4249,43 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="G20" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="H20" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="I20" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O20" t="n">
         <v>1.53</v>
       </c>
-      <c r="M20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.51</v>
-      </c>
       <c r="P20" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S20" t="n">
         <v>5.2</v>
@@ -4297,13 +4297,13 @@
         <v>1.55</v>
       </c>
       <c r="V20" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
@@ -4312,7 +4312,7 @@
         <v>7.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AB20" t="n">
         <v>970</v>
@@ -4324,7 +4324,7 @@
         <v>970</v>
       </c>
       <c r="AE20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF20" t="n">
         <v>80</v>
@@ -4339,7 +4339,7 @@
         <v>75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AK20" t="n">
         <v>1000</v>
@@ -4354,10 +4354,10 @@
         <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AP20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ20" t="n">
         <v>4.9</v>
@@ -4369,50 +4369,50 @@
         <v>11.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU20" t="n">
         <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX20" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.8</v>
+        <v>3.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BC20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BG20" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G21" t="n">
         <v>1.41</v>
@@ -4452,43 +4452,43 @@
         <v>11.5</v>
       </c>
       <c r="I21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J21" t="n">
         <v>4.8</v>
       </c>
       <c r="K21" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.34</v>
       </c>
-      <c r="P21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.32</v>
-      </c>
       <c r="S21" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T21" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U21" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V21" t="n">
         <v>1.08</v>
@@ -4503,7 +4503,7 @@
         <v>30</v>
       </c>
       <c r="Z21" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
@@ -4515,10 +4515,10 @@
         <v>12</v>
       </c>
       <c r="AD21" t="n">
-        <v>950</v>
+        <v>46</v>
       </c>
       <c r="AE21" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AF21" t="n">
         <v>7.2</v>
@@ -4530,7 +4530,7 @@
         <v>950</v>
       </c>
       <c r="AI21" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AJ21" t="n">
         <v>11</v>
@@ -4548,19 +4548,19 @@
         <v>7.8</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AP21" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR21" t="n">
         <v>11.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT21" t="n">
         <v>5.9</v>
@@ -4569,10 +4569,10 @@
         <v>10</v>
       </c>
       <c r="AV21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX21" t="n">
         <v>6.4</v>
@@ -4581,10 +4581,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB21" t="n">
         <v>9.6</v>
@@ -4593,10 +4593,10 @@
         <v>15</v>
       </c>
       <c r="BD21" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="BE21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF21" t="n">
         <v>6.8</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="G22" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="H22" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="I22" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K22" t="n">
         <v>3.9</v>
@@ -4670,7 +4670,7 @@
         <v>1.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="R22" t="n">
         <v>1.26</v>
@@ -4685,13 +4685,13 @@
         <v>1.8</v>
       </c>
       <c r="V22" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y22" t="n">
         <v>8</v>
@@ -4703,10 +4703,10 @@
         <v>22</v>
       </c>
       <c r="AB22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
         <v>12</v>
@@ -4715,19 +4715,19 @@
         <v>25</v>
       </c>
       <c r="AF22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI22" t="n">
         <v>50</v>
       </c>
       <c r="AJ22" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AK22" t="n">
         <v>110</v>
@@ -4739,7 +4739,7 @@
         <v>190</v>
       </c>
       <c r="AN22" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AO22" t="n">
         <v>17.5</v>
@@ -4748,7 +4748,7 @@
         <v>9.6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR22" t="n">
         <v>7.6</v>
@@ -4778,29 +4778,29 @@
         <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG22" t="n">
         <v>12</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>9</v>
       </c>
       <c r="H23" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I23" t="n">
         <v>1.58</v>
@@ -4861,16 +4861,16 @@
         <v>1.34</v>
       </c>
       <c r="P23" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R23" t="n">
         <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="T23" t="n">
         <v>2.06</v>
@@ -4888,34 +4888,34 @@
         <v>16.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA23" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AC23" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD23" t="n">
         <v>11.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF23" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AG23" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AH23" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI23" t="n">
         <v>55</v>
@@ -4951,7 +4951,7 @@
         <v>10.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU23" t="n">
         <v>7.8</v>
@@ -4963,38 +4963,38 @@
         <v>13.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY23" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="AZ23" t="n">
         <v>20</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.8</v>
+        <v>32</v>
       </c>
       <c r="BB23" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BC23" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H24" t="n">
         <v>2.62</v>
       </c>
-      <c r="G24" t="n">
+      <c r="I24" t="n">
         <v>2.78</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>3.75</v>
@@ -5079,16 +5079,16 @@
         <v>1.56</v>
       </c>
       <c r="X24" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="Y24" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Z24" t="n">
         <v>24</v>
       </c>
       <c r="AA24" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB24" t="n">
         <v>970</v>
@@ -5106,7 +5106,7 @@
         <v>23</v>
       </c>
       <c r="AG24" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH24" t="n">
         <v>970</v>
@@ -5118,7 +5118,7 @@
         <v>44</v>
       </c>
       <c r="AK24" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL24" t="n">
         <v>40</v>
@@ -5133,62 +5133,62 @@
         <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AQ24" t="n">
         <v>11</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AV24" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AX24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY24" t="n">
         <v>4.6</v>
       </c>
-      <c r="AY24" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AZ24" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF24" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>13.5</v>
       </c>
       <c r="BG24" t="n">
         <v>14</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
         <v>12</v>
       </c>
       <c r="H25" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="I25" t="n">
         <v>1.3</v>
       </c>
       <c r="J25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="K25" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L25" t="n">
         <v>1.18</v>
@@ -5255,10 +5255,10 @@
         <v>1.37</v>
       </c>
       <c r="R25" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="S25" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="T25" t="n">
         <v>1.74</v>
@@ -5267,13 +5267,13 @@
         <v>2.12</v>
       </c>
       <c r="V25" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="W25" t="n">
         <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y25" t="n">
         <v>15</v>
@@ -5285,7 +5285,7 @@
         <v>12.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="AC25" t="n">
         <v>17.5</v>
@@ -5303,7 +5303,7 @@
         <v>42</v>
       </c>
       <c r="AH25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI25" t="n">
         <v>28</v>
@@ -5315,7 +5315,7 @@
         <v>140</v>
       </c>
       <c r="AL25" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM25" t="n">
         <v>100</v>
@@ -5339,7 +5339,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AT25" t="n">
-        <v>38</v>
+        <v>8.6</v>
       </c>
       <c r="AU25" t="n">
         <v>14</v>
@@ -5351,38 +5351,38 @@
         <v>11</v>
       </c>
       <c r="AX25" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>7.2</v>
+        <v>18.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="BB25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD25" t="n">
         <v>9.4</v>
       </c>
-      <c r="BC25" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD25" t="n">
+      <c r="BE25" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BE25" t="n">
-        <v>9</v>
-      </c>
       <c r="BF25" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
         <v>990</v>
       </c>
       <c r="J26" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K26" t="n">
         <v>950</v>
@@ -5437,31 +5437,31 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>1.1</v>
+        <v>1.39</v>
       </c>
       <c r="O26" t="n">
         <v>1.06</v>
       </c>
       <c r="P26" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="R26" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="S26" t="n">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="T26" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U26" t="n">
         <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W26" t="n">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G27" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H27" t="n">
         <v>3.35</v>
@@ -5658,13 +5658,13 @@
         <v>1.39</v>
       </c>
       <c r="W27" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X27" t="n">
         <v>970</v>
       </c>
       <c r="Y27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z27" t="n">
         <v>24</v>
@@ -5703,7 +5703,7 @@
         <v>26</v>
       </c>
       <c r="AL27" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -5712,7 +5712,7 @@
         <v>970</v>
       </c>
       <c r="AO27" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AP27" t="n">
         <v>11</v>
@@ -5724,10 +5724,10 @@
         <v>18</v>
       </c>
       <c r="AS27" t="n">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="AT27" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AU27" t="n">
         <v>7</v>
@@ -5736,7 +5736,7 @@
         <v>11</v>
       </c>
       <c r="AW27" t="n">
-        <v>9.4</v>
+        <v>30</v>
       </c>
       <c r="AX27" t="n">
         <v>11.5</v>
@@ -5748,10 +5748,10 @@
         <v>15.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BB27" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="BC27" t="n">
         <v>19</v>
@@ -5766,11 +5766,11 @@
         <v>17</v>
       </c>
       <c r="BG27" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -5801,25 +5801,25 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G28" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H28" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I28" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="J28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M28" t="n">
         <v>1.07</v>
@@ -5834,7 +5834,7 @@
         <v>1.84</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="R28" t="n">
         <v>1.31</v>
@@ -5843,22 +5843,22 @@
         <v>3.55</v>
       </c>
       <c r="T28" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U28" t="n">
         <v>2.06</v>
       </c>
       <c r="V28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W28" t="n">
         <v>1.52</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.51</v>
       </c>
       <c r="X28" t="n">
         <v>16</v>
       </c>
       <c r="Y28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z28" t="n">
         <v>19</v>
@@ -5867,10 +5867,10 @@
         <v>44</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD28" t="n">
         <v>13</v>
@@ -5885,7 +5885,7 @@
         <v>13</v>
       </c>
       <c r="AH28" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI28" t="n">
         <v>46</v>
@@ -5924,13 +5924,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV28" t="n">
         <v>9.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX28" t="n">
         <v>14</v>
@@ -5942,16 +5942,16 @@
         <v>14</v>
       </c>
       <c r="BA28" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="BB28" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="BC28" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="BE28" t="n">
         <v>8</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G29" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H29" t="n">
         <v>5.9</v>
@@ -6019,52 +6019,52 @@
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O29" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P29" t="n">
         <v>1.99</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T29" t="n">
         <v>2.04</v>
       </c>
       <c r="U29" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V29" t="n">
         <v>1.2</v>
       </c>
       <c r="W29" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="X29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y29" t="n">
         <v>18.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA29" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD29" t="n">
         <v>23</v>
@@ -6073,7 +6073,7 @@
         <v>90</v>
       </c>
       <c r="AF29" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG29" t="n">
         <v>10</v>
@@ -6082,28 +6082,28 @@
         <v>25</v>
       </c>
       <c r="AI29" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP29" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>14</v>
       </c>
       <c r="AQ29" t="n">
         <v>17</v>
@@ -6112,19 +6112,19 @@
         <v>40</v>
       </c>
       <c r="AS29" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AT29" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU29" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV29" t="n">
         <v>21</v>
       </c>
       <c r="AW29" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AX29" t="n">
         <v>8.4</v>
@@ -6139,10 +6139,10 @@
         <v>75</v>
       </c>
       <c r="BB29" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD29" t="n">
         <v>40</v>
@@ -6151,14 +6151,14 @@
         <v>120</v>
       </c>
       <c r="BF29" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG29" t="n">
         <v>95</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH29"/>
+  <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,7 +760,7 @@
         <v>3.4</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="H2" t="n">
         <v>2.24</v>
@@ -814,13 +814,13 @@
         <v>10</v>
       </c>
       <c r="Y2" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB2" t="n">
         <v>11.5</v>
@@ -829,10 +829,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF2" t="n">
         <v>27</v>
@@ -841,7 +841,7 @@
         <v>17.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
         <v>60</v>
@@ -853,7 +853,7 @@
         <v>65</v>
       </c>
       <c r="AL2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="n">
         <v>190</v>
@@ -862,65 +862,65 @@
         <v>85</v>
       </c>
       <c r="AO2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AR2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT2" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4</v>
-      </c>
       <c r="AU2" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G3" t="n">
         <v>2.4</v>
@@ -960,7 +960,7 @@
         <v>3.4</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J3" t="n">
         <v>3.05</v>
@@ -999,13 +999,13 @@
         <v>1.88</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
         <v>1.72</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
         <v>970</v>
@@ -1065,7 +1065,7 @@
         <v>4.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="AS3" t="n">
         <v>6.6</v>
@@ -1098,13 +1098,13 @@
         <v>6</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.55</v>
+        <v>5.8</v>
       </c>
       <c r="BD3" t="n">
         <v>6.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.34</v>
+        <v>3.45</v>
       </c>
       <c r="BF3" t="n">
         <v>5.7</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.46</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
         <v>990</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="I4" t="n">
         <v>19</v>
@@ -1166,7 +1166,7 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
         <v>1.1</v>
@@ -1184,7 +1184,7 @@
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1196,10 +1196,10 @@
         <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
         <v>1000</v>
@@ -1256,59 +1256,59 @@
         <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G5" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="H5" t="n">
         <v>3.55</v>
@@ -1351,7 +1351,7 @@
         <v>3.75</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
         <v>3.45</v>
@@ -1363,13 +1363,13 @@
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q5" t="n">
         <v>2.2</v>
@@ -1384,25 +1384,25 @@
         <v>1.88</v>
       </c>
       <c r="U5" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
         <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="X5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y5" t="n">
         <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AA5" t="n">
-        <v>90</v>
+        <v>340</v>
       </c>
       <c r="AB5" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
         <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
         <v>60</v>
@@ -1423,28 +1423,28 @@
         <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
         <v>38</v>
       </c>
       <c r="AK5" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="AL5" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
         <v>25</v>
       </c>
       <c r="AO5" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AP5" t="n">
         <v>10</v>
@@ -1456,19 +1456,19 @@
         <v>19</v>
       </c>
       <c r="AS5" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5" t="n">
         <v>7.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
         <v>13</v>
       </c>
       <c r="AW5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AX5" t="n">
         <v>12.5</v>
@@ -1477,32 +1477,32 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD5" t="n">
         <v>8</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF5" t="n">
         <v>18.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>2.58</v>
       </c>
       <c r="I6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J6" t="n">
         <v>2.8</v>
@@ -1557,16 +1557,16 @@
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="O6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P6" t="n">
         <v>1.49</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1581,13 +1581,13 @@
         <v>1.73</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
         <v>1.4</v>
       </c>
       <c r="X6" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="Y6" t="n">
         <v>9.4</v>
@@ -1596,22 +1596,22 @@
         <v>19.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
         <v>17</v>
@@ -1620,19 +1620,19 @@
         <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ6" t="n">
         <v>75</v>
       </c>
       <c r="AK6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL6" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AM6" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
         <v>75</v>
@@ -1641,62 +1641,62 @@
         <v>60</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AS6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY6" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>4</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
         <v>1.76</v>
@@ -1742,7 +1742,7 @@
         <v>2.88</v>
       </c>
       <c r="K7" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.33</v>
@@ -1751,7 +1751,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
         <v>1.34</v>
@@ -1781,116 +1781,116 @@
         <v>1.19</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -1930,10 +1930,10 @@
         <v>2.34</v>
       </c>
       <c r="I8" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
         <v>4.1</v>
@@ -1951,16 +1951,16 @@
         <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R8" t="n">
         <v>1.75</v>
       </c>
       <c r="S8" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T8" t="n">
         <v>1.47</v>
@@ -1969,25 +1969,25 @@
         <v>2.96</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W8" t="n">
         <v>1.47</v>
       </c>
       <c r="X8" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="Y8" t="n">
         <v>24</v>
       </c>
       <c r="Z8" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
         <v>40</v>
       </c>
       <c r="AB8" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AC8" t="n">
         <v>10</v>
@@ -1999,7 +1999,7 @@
         <v>29</v>
       </c>
       <c r="AF8" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AG8" t="n">
         <v>14.5</v>
@@ -2014,31 +2014,31 @@
         <v>55</v>
       </c>
       <c r="AK8" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AL8" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
         <v>55</v>
       </c>
       <c r="AN8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO8" t="n">
         <v>10.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AQ8" t="n">
         <v>15.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AT8" t="n">
         <v>18.5</v>
@@ -2053,7 +2053,7 @@
         <v>18.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AY8" t="n">
         <v>12.5</v>
@@ -2062,19 +2062,19 @@
         <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BC8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BD8" t="n">
         <v>22</v>
       </c>
       <c r="BE8" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BF8" t="n">
         <v>14</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -2118,22 +2118,22 @@
         <v>6.4</v>
       </c>
       <c r="G9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
         <v>1.57</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="J9" t="n">
         <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
@@ -2145,7 +2145,7 @@
         <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
         <v>1.73</v>
@@ -2154,28 +2154,28 @@
         <v>1.48</v>
       </c>
       <c r="S9" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="T9" t="n">
         <v>1.82</v>
       </c>
       <c r="U9" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V9" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="W9" t="n">
         <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA9" t="n">
         <v>17.5</v>
@@ -2187,55 +2187,55 @@
         <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AE9" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AG9" t="n">
         <v>28</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
         <v>34</v>
       </c>
       <c r="AJ9" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AK9" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AL9" t="n">
-        <v>85</v>
+        <v>700</v>
       </c>
       <c r="AM9" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AN9" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AO9" t="n">
         <v>7.8</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR9" t="n">
         <v>9</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AU9" t="n">
         <v>9</v>
@@ -2247,38 +2247,38 @@
         <v>14</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.2</v>
+        <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG9" t="n">
         <v>7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>990</v>
       </c>
       <c r="H10" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="I10" t="n">
         <v>1.52</v>
@@ -2324,28 +2324,28 @@
         <v>4.5</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
         <v>1.54</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
         <v>2.36</v>
@@ -2366,25 +2366,25 @@
         <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB10" t="n">
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF10" t="n">
         <v>1000</v>
@@ -2396,7 +2396,7 @@
         <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
         <v>1000</v>
@@ -2414,65 +2414,65 @@
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G11" t="n">
         <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="I11" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J11" t="n">
         <v>3.1</v>
@@ -2527,13 +2527,13 @@
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.44</v>
       </c>
       <c r="P11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q11" t="n">
         <v>2.38</v>
@@ -2545,19 +2545,19 @@
         <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U11" t="n">
         <v>1.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W11" t="n">
         <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
         <v>9.6</v>
@@ -2566,7 +2566,7 @@
         <v>18</v>
       </c>
       <c r="AA11" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AB11" t="n">
         <v>9.800000000000001</v>
@@ -2593,16 +2593,16 @@
         <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>50</v>
+        <v>320</v>
       </c>
       <c r="AK11" t="n">
         <v>80</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM11" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
         <v>40</v>
@@ -2647,7 +2647,7 @@
         <v>29</v>
       </c>
       <c r="BB11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC11" t="n">
         <v>23</v>
@@ -2656,17 +2656,17 @@
         <v>29</v>
       </c>
       <c r="BE11" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="BF11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BG11" t="n">
         <v>22</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -2703,13 +2703,13 @@
         <v>2.06</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
         <v>3.55</v>
@@ -2727,10 +2727,10 @@
         <v>1.46</v>
       </c>
       <c r="P12" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
@@ -2796,7 +2796,7 @@
         <v>50</v>
       </c>
       <c r="AM12" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
         <v>21</v>
@@ -2811,7 +2811,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
         <v>5.3</v>
@@ -2826,7 +2826,7 @@
         <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX12" t="n">
         <v>9.800000000000001</v>
@@ -2847,20 +2847,20 @@
         <v>21</v>
       </c>
       <c r="BD12" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF12" t="n">
         <v>14.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>1.69</v>
       </c>
       <c r="G13" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="J13" t="n">
         <v>3.65</v>
@@ -2924,7 +2924,7 @@
         <v>1.84</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R13" t="n">
         <v>1.32</v>
@@ -2939,13 +2939,13 @@
         <v>1.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W13" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y13" t="n">
         <v>22</v>
@@ -2954,107 +2954,107 @@
         <v>55</v>
       </c>
       <c r="AA13" t="n">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD13" t="n">
         <v>26</v>
       </c>
       <c r="AE13" t="n">
-        <v>95</v>
+        <v>700</v>
       </c>
       <c r="AF13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>230</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN13" t="n">
         <v>13</v>
       </c>
-      <c r="AG13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>15</v>
-      </c>
       <c r="AO13" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="AR13" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="AS13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX13" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW13" t="n">
+      <c r="AY13" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>7.6</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="J14" t="n">
         <v>4.3</v>
@@ -3139,13 +3139,13 @@
         <v>2.82</v>
       </c>
       <c r="X14" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="Z14" t="n">
-        <v>85</v>
+        <v>420</v>
       </c>
       <c r="AA14" t="n">
         <v>320</v>
@@ -3163,25 +3163,25 @@
         <v>150</v>
       </c>
       <c r="AF14" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG14" t="n">
         <v>12</v>
       </c>
       <c r="AH14" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI14" t="n">
-        <v>130</v>
+        <v>470</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL14" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AM14" t="n">
         <v>170</v>
@@ -3193,16 +3193,16 @@
         <v>210</v>
       </c>
       <c r="AP14" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>21</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT14" t="n">
         <v>7</v>
@@ -3211,10 +3211,10 @@
         <v>9</v>
       </c>
       <c r="AV14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AW14" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AX14" t="n">
         <v>6.8</v>
@@ -3226,7 +3226,7 @@
         <v>21</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BB14" t="n">
         <v>10</v>
@@ -3235,20 +3235,20 @@
         <v>13.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.6</v>
+        <v>19.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BF14" t="n">
         <v>6.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MFk Skalica</t>
+          <t>Zilina</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FC Kosice</t>
+          <t>Zemplin</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P15" t="n">
         <v>2.62</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Q15" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="U15" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.56</v>
+        <v>1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="X15" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Y15" t="n">
-        <v>16.5</v>
+        <v>75</v>
       </c>
       <c r="Z15" t="n">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="AA15" t="n">
-        <v>44</v>
+        <v>230</v>
       </c>
       <c r="AB15" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AC15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>240</v>
+      </c>
+      <c r="AF15" t="n">
         <v>11</v>
       </c>
-      <c r="AD15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>24</v>
-      </c>
       <c r="AG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK15" t="n">
         <v>15</v>
       </c>
-      <c r="AH15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>32</v>
-      </c>
       <c r="AL15" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AM15" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AN15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV15" t="n">
         <v>21</v>
       </c>
-      <c r="AO15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AP15" t="n">
+      <c r="AW15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>16</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR15" t="n">
+      <c r="BA15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG15" t="n">
         <v>15</v>
       </c>
-      <c r="AS15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Slovakian Super League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>MFk Skalica</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FC Inter</t>
+          <t>FC Kosice</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.9</v>
+        <v>2.62</v>
       </c>
       <c r="G16" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="H16" t="n">
-        <v>1.75</v>
+        <v>2.58</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="V16" t="n">
-        <v>2.24</v>
+        <v>1.56</v>
       </c>
       <c r="W16" t="n">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="X16" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO16" t="n">
         <v>19.5</v>
       </c>
-      <c r="Y16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z16" t="n">
+      <c r="AP16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>12</v>
       </c>
-      <c r="AA16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AR16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT16" t="n">
         <v>11</v>
       </c>
-      <c r="AE16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>140</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO16" t="n">
+      <c r="AU16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AP16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AW16" t="n">
-        <v>15</v>
+        <v>5.6</v>
       </c>
       <c r="AX16" t="n">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BD16" t="n">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Slovakian Super League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Zilina</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zemplin</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.42</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.49</v>
+        <v>5.3</v>
       </c>
       <c r="H17" t="n">
-        <v>7.6</v>
+        <v>1.75</v>
       </c>
       <c r="I17" t="n">
-        <v>8.800000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="J17" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>2.58</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="R17" t="n">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="T17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>2.28</v>
       </c>
       <c r="W17" t="n">
-        <v>3</v>
+        <v>1.23</v>
       </c>
       <c r="X17" t="n">
-        <v>30</v>
+        <v>19.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>950</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN17" t="n">
         <v>75</v>
       </c>
-      <c r="AA17" t="n">
-        <v>230</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AO17" t="n">
-        <v>110</v>
+        <v>10.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="AT17" t="n">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY17" t="n">
-        <v>8</v>
+        <v>17.5</v>
       </c>
       <c r="AZ17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA17" t="n">
         <v>16</v>
       </c>
-      <c r="BA17" t="n">
-        <v>7</v>
-      </c>
       <c r="BB17" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -3882,10 +3882,10 @@
         <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
         <v>1.21</v>
@@ -3900,13 +3900,13 @@
         <v>1.54</v>
       </c>
       <c r="S18" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="T18" t="n">
         <v>1.81</v>
       </c>
       <c r="U18" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>1.12</v>
@@ -3915,52 +3915,52 @@
         <v>3.1</v>
       </c>
       <c r="X18" t="n">
-        <v>950</v>
+        <v>50</v>
       </c>
       <c r="Y18" t="n">
         <v>950</v>
       </c>
       <c r="Z18" t="n">
-        <v>80</v>
+        <v>540</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC18" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD18" t="n">
         <v>950</v>
       </c>
       <c r="AE18" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AF18" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
         <v>950</v>
       </c>
       <c r="AI18" t="n">
-        <v>100</v>
+        <v>390</v>
       </c>
       <c r="AJ18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AK18" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AM18" t="n">
-        <v>130</v>
+        <v>380</v>
       </c>
       <c r="AN18" t="n">
         <v>6.8</v>
@@ -3969,16 +3969,16 @@
         <v>130</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.8</v>
+        <v>12.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
         <v>7.8</v>
@@ -3987,10 +3987,10 @@
         <v>9</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
         <v>7.6</v>
@@ -4002,7 +4002,7 @@
         <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BB18" t="n">
         <v>10</v>
@@ -4011,27 +4011,27 @@
         <v>11</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BF18" t="n">
         <v>5.1</v>
       </c>
       <c r="BG18" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.02</v>
+        <v>1.37</v>
       </c>
       <c r="G19" t="n">
-        <v>2.14</v>
+        <v>1.39</v>
       </c>
       <c r="H19" t="n">
-        <v>3.8</v>
+        <v>13.5</v>
       </c>
       <c r="I19" t="n">
-        <v>4.4</v>
+        <v>15.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="K19" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="O19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.34</v>
       </c>
-      <c r="P19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.31</v>
-      </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="W19" t="n">
-        <v>1.87</v>
+        <v>3.55</v>
       </c>
       <c r="X19" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>16.5</v>
+        <v>42</v>
       </c>
       <c r="Z19" t="n">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="AA19" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>360</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY19" t="n">
         <v>9.4</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AZ19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB19" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP19" t="n">
+      <c r="BC19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE19" t="n">
         <v>11</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="BF19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG19" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,106 +4240,106 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Smouha</t>
+          <t>SV Wildon</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>FC Schladming</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="G20" t="n">
-        <v>8.6</v>
+        <v>990</v>
       </c>
       <c r="H20" t="n">
-        <v>1.61</v>
+        <v>1.03</v>
       </c>
       <c r="I20" t="n">
-        <v>1.66</v>
+        <v>990</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>1.09</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L20" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>2.58</v>
+        <v>1.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="P20" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.62</v>
+        <v>1.14</v>
       </c>
       <c r="R20" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>5.2</v>
+        <v>1.14</v>
       </c>
       <c r="T20" t="n">
-        <v>2.52</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
         <v>1000</v>
@@ -4354,72 +4354,72 @@
         <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>SV Union Gnas</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>SV Lebring</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="G21" t="n">
-        <v>1.41</v>
+        <v>990</v>
       </c>
       <c r="H21" t="n">
-        <v>11.5</v>
+        <v>1.02</v>
       </c>
       <c r="I21" t="n">
-        <v>13</v>
+        <v>990</v>
       </c>
       <c r="J21" t="n">
-        <v>4.8</v>
+        <v>1.09</v>
       </c>
       <c r="K21" t="n">
-        <v>5.3</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>3.55</v>
+        <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.98</v>
+        <v>1.12</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>3.55</v>
+        <v>1.12</v>
       </c>
       <c r="T21" t="n">
-        <v>2.38</v>
+        <v>1.11</v>
       </c>
       <c r="U21" t="n">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="V21" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>570</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>TUS Bad Waltersdorf</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>SC Furstenfeld</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5.2</v>
+        <v>1.02</v>
       </c>
       <c r="G22" t="n">
-        <v>5.8</v>
+        <v>990</v>
       </c>
       <c r="H22" t="n">
-        <v>1.81</v>
+        <v>1.02</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>990</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>1.09</v>
       </c>
       <c r="K22" t="n">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="P22" t="n">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.28</v>
+        <v>1.14</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1</v>
+        <v>1.14</v>
       </c>
       <c r="T22" t="n">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Riteriai</t>
+          <t>SV Tillmitsch</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>FSC Eggendorf Hartberg II</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>7.4</v>
+        <v>1.02</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>990</v>
       </c>
       <c r="H23" t="n">
-        <v>1.49</v>
+        <v>1.02</v>
       </c>
       <c r="I23" t="n">
-        <v>1.58</v>
+        <v>990</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>1.09</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8</v>
+        <v>950</v>
       </c>
       <c r="L23" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>1.25</v>
       </c>
       <c r="O23" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="P23" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.98</v>
+        <v>1.15</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5</v>
+        <v>1.15</v>
       </c>
       <c r="T23" t="n">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.64</v>
+        <v>2.06</v>
       </c>
       <c r="G24" t="n">
-        <v>2.8</v>
+        <v>2.14</v>
       </c>
       <c r="H24" t="n">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="I24" t="n">
-        <v>2.78</v>
+        <v>4.4</v>
       </c>
       <c r="J24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K24" t="n">
         <v>3.75</v>
       </c>
-      <c r="K24" t="n">
-        <v>3.95</v>
-      </c>
       <c r="L24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R24" t="n">
         <v>1.29</v>
       </c>
-      <c r="M24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.5</v>
-      </c>
       <c r="S24" t="n">
-        <v>2.68</v>
+        <v>3.7</v>
       </c>
       <c r="T24" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="U24" t="n">
-        <v>2.44</v>
+        <v>2.02</v>
       </c>
       <c r="V24" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="W24" t="n">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="X24" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="Y24" t="n">
         <v>16.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AA24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL24" t="n">
         <v>44</v>
       </c>
-      <c r="AB24" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>40</v>
-      </c>
       <c r="AM24" t="n">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="AN24" t="n">
         <v>21</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="AP24" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="AQ24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX24" t="n">
         <v>11</v>
       </c>
-      <c r="AR24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV24" t="n">
+      <c r="AY24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG24" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AW24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>14</v>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Al-Khaleej Saihat</t>
+          <t>Smouha</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="G25" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="H25" t="n">
-        <v>1.27</v>
+        <v>1.61</v>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="J25" t="n">
-        <v>6.4</v>
+        <v>3.65</v>
       </c>
       <c r="K25" t="n">
-        <v>7.4</v>
+        <v>3.95</v>
       </c>
       <c r="L25" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="M25" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="N25" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>490</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>230</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>450</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW25" t="n">
         <v>7.6</v>
       </c>
-      <c r="O25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X25" t="n">
-        <v>44</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>120</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>360</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>140</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>11</v>
-      </c>
       <c r="AX25" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY25" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>18.5</v>
+        <v>8.6</v>
       </c>
       <c r="BA25" t="n">
-        <v>18.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE25" t="n">
         <v>10</v>
       </c>
-      <c r="BC25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BF25" t="n">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.2</v>
+        <v>13.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Scottish League Two</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Clyde</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spartans</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M26" t="n">
         <v>1.09</v>
       </c>
-      <c r="G26" t="n">
-        <v>990</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I26" t="n">
-        <v>990</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K26" t="n">
-        <v>950</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.06</v>
-      </c>
       <c r="N26" t="n">
-        <v>1.39</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.06</v>
+        <v>1.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.34</v>
+        <v>1.68</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.32</v>
+        <v>2.28</v>
       </c>
       <c r="R26" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="S26" t="n">
-        <v>1.79</v>
+        <v>4.1</v>
       </c>
       <c r="T26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.8</v>
       </c>
-      <c r="U26" t="n">
-        <v>1.11</v>
-      </c>
       <c r="V26" t="n">
-        <v>1.32</v>
+        <v>2.08</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Riteriai</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.3</v>
+        <v>7.4</v>
       </c>
       <c r="G27" t="n">
-        <v>2.4</v>
+        <v>9</v>
       </c>
       <c r="H27" t="n">
-        <v>3.35</v>
+        <v>1.49</v>
       </c>
       <c r="I27" t="n">
-        <v>3.55</v>
+        <v>1.59</v>
       </c>
       <c r="J27" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="O27" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P27" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q27" t="n">
         <v>2.04</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>2.14</v>
+        <v>1.76</v>
       </c>
       <c r="V27" t="n">
-        <v>1.39</v>
+        <v>2.66</v>
       </c>
       <c r="W27" t="n">
-        <v>1.71</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="Z27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB27" t="n">
         <v>24</v>
       </c>
-      <c r="AA27" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="AC27" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC27" t="n">
-        <v>8</v>
-      </c>
       <c r="AD27" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AF27" t="n">
-        <v>15.5</v>
+        <v>80</v>
       </c>
       <c r="AG27" t="n">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="AH27" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AI27" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ27" t="n">
+        <v>340</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>170</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>270</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA27" t="n">
         <v>32</v>
       </c>
-      <c r="AK27" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>36</v>
-      </c>
       <c r="BB27" t="n">
-        <v>24</v>
+        <v>7.2</v>
       </c>
       <c r="BC27" t="n">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="BD27" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>17</v>
+        <v>7.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,378 +5787,1154 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Queen of South</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="G28" t="n">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="H28" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="I28" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="K28" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L28" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="O28" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="P28" t="n">
-        <v>1.84</v>
+        <v>2.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>3.55</v>
+        <v>2.68</v>
       </c>
       <c r="T28" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="U28" t="n">
-        <v>2.06</v>
+        <v>2.48</v>
       </c>
       <c r="V28" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W28" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="X28" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Y28" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>19</v>
+        <v>500</v>
       </c>
       <c r="AA28" t="n">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AC28" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AD28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC28" t="n">
         <v>13</v>
       </c>
-      <c r="AE28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ28" t="n">
+      <c r="BD28" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AR28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS28" t="n">
+      <c r="BE28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG28" t="n">
         <v>7.2</v>
       </c>
-      <c r="AT28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>21</v>
-      </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Al-Khaleej Saihat</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Al-Hilal</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>11</v>
+      </c>
+      <c r="G29" t="n">
+        <v>13</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X29" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>120</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>46</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>360</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>240</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>150</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>42</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-05-04 20:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Scottish League One</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Queen of South</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Stenhousemuir</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>290</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>180</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>26</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-05-04 20:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Scottish League Two</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Clyde</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Spartans</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-05-04 20:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Scottish Championship</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Dunfermline</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Arbroath</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X32" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-05-04 20:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>UEFA Champions League</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>16:00:00</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Arsenal</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Atletico Madrid</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="F33" t="n">
         <v>1.65</v>
       </c>
-      <c r="H29" t="n">
+      <c r="G33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H33" t="n">
         <v>5.9</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I33" t="n">
         <v>6</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J33" t="n">
         <v>4.4</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K33" t="n">
         <v>4.5</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L33" t="n">
         <v>1.42</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M33" t="n">
         <v>1.07</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N33" t="n">
         <v>3.95</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O33" t="n">
         <v>1.32</v>
       </c>
-      <c r="P29" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="P33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q33" t="n">
         <v>2</v>
       </c>
-      <c r="R29" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="R33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S33" t="n">
         <v>3.55</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T33" t="n">
         <v>2.04</v>
       </c>
-      <c r="U29" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V29" t="n">
+      <c r="U33" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V33" t="n">
         <v>1.2</v>
       </c>
-      <c r="W29" t="n">
+      <c r="W33" t="n">
         <v>2.52</v>
       </c>
-      <c r="X29" t="n">
+      <c r="X33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>130</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>75</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB33" t="n">
         <v>14</v>
       </c>
-      <c r="Y29" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>40</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>120</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU29" t="n">
+      <c r="BC33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF33" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AV29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>75</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>75</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>120</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG29" t="n">
+      <c r="BG33" t="n">
         <v>95</v>
       </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>2026-05-04 17:51:34</t>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH33"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I2" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J2" t="n">
         <v>2.94</v>
@@ -775,13 +775,13 @@
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M2" t="n">
         <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O2" t="n">
         <v>1.46</v>
@@ -790,13 +790,13 @@
         <v>1.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="T2" t="n">
         <v>1.97</v>
@@ -805,10 +805,10 @@
         <v>1.79</v>
       </c>
       <c r="V2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
         <v>10</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -954,16 +954,16 @@
         <v>2.14</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="H3" t="n">
         <v>3.4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
         <v>3.75</v>
@@ -987,7 +987,7 @@
         <v>2.14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
         <v>3.75</v>
@@ -999,10 +999,10 @@
         <v>1.88</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="X3" t="n">
         <v>13</v>
@@ -1038,7 +1038,7 @@
         <v>950</v>
       </c>
       <c r="AI3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="n">
         <v>34</v>
@@ -1062,13 +1062,13 @@
         <v>4.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AR3" t="n">
         <v>5.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT3" t="n">
         <v>4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G4" t="n">
         <v>990</v>
       </c>
       <c r="H4" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="I4" t="n">
         <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>2.68</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1166,22 +1166,22 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="O4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
         <v>1.05</v>
@@ -1199,7 +1199,7 @@
         <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Y4" t="n">
         <v>1000</v>
@@ -1256,59 +1256,59 @@
         <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G5" t="n">
         <v>2.4</v>
@@ -1354,10 +1354,10 @@
         <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
@@ -1369,7 +1369,7 @@
         <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q5" t="n">
         <v>2.2</v>
@@ -1381,10 +1381,10 @@
         <v>4.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
         <v>1.36</v>
@@ -1396,13 +1396,13 @@
         <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
         <v>44</v>
       </c>
       <c r="AA5" t="n">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="AB5" t="n">
         <v>10</v>
@@ -1411,16 +1411,16 @@
         <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE5" t="n">
         <v>60</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AG5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
         <v>32</v>
@@ -1429,10 +1429,10 @@
         <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AK5" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1441,10 +1441,10 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AO5" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
         <v>10</v>
@@ -1453,10 +1453,10 @@
         <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AT5" t="n">
         <v>7.8</v>
@@ -1468,7 +1468,7 @@
         <v>13</v>
       </c>
       <c r="AW5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX5" t="n">
         <v>12.5</v>
@@ -1480,29 +1480,29 @@
         <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BD5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BF5" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.58</v>
+        <v>2.22</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L6" t="n">
         <v>1.51</v>
@@ -1560,13 +1560,13 @@
         <v>2.36</v>
       </c>
       <c r="O6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1578,125 +1578,125 @@
         <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="X6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AF6" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AG6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="AJ6" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AL6" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
         <v>3.95</v>
       </c>
       <c r="AR6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>5.9</v>
       </c>
-      <c r="AT6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="BD6" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BE6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG6" t="n">
         <v>6.4</v>
       </c>
-      <c r="BF6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>6</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -1727,64 +1727,64 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J7" t="n">
         <v>3.2</v>
       </c>
-      <c r="G7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.88</v>
-      </c>
       <c r="K7" t="n">
-        <v>8.6</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="R7" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>2.66</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="V7" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="W7" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="X7" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="Y7" t="n">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="Z7" t="n">
         <v>500</v>
@@ -1793,13 +1793,13 @@
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
@@ -1808,16 +1808,16 @@
         <v>500</v>
       </c>
       <c r="AG7" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
         <v>500</v>
@@ -1826,71 +1826,71 @@
         <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.15</v>
+        <v>5.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.11</v>
+        <v>4.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.16</v>
+        <v>5.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.16</v>
+        <v>6.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.16</v>
+        <v>5.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.13</v>
+        <v>4.1</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.12</v>
+        <v>4.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.14</v>
+        <v>6.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.16</v>
+        <v>5.7</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.16</v>
+        <v>5.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.16</v>
+        <v>5.9</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.16</v>
+        <v>6</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.16</v>
+        <v>4.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.16</v>
+        <v>5</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.16</v>
+        <v>5.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.16</v>
+        <v>3.85</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.55</v>
+        <v>5.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.16</v>
+        <v>5.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
         <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
         <v>1.03</v>
@@ -1966,7 +1966,7 @@
         <v>1.47</v>
       </c>
       <c r="U8" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="V8" t="n">
         <v>1.71</v>
@@ -1984,7 +1984,7 @@
         <v>500</v>
       </c>
       <c r="AA8" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AB8" t="n">
         <v>22</v>
@@ -2023,7 +2023,7 @@
         <v>55</v>
       </c>
       <c r="AN8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="n">
         <v>10.5</v>
@@ -2035,7 +2035,7 @@
         <v>15.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
         <v>25</v>
@@ -2065,13 +2065,13 @@
         <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BC8" t="n">
         <v>22</v>
       </c>
       <c r="BD8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BE8" t="n">
         <v>38</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -2118,19 +2118,19 @@
         <v>6.4</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="I9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.33</v>
@@ -2139,22 +2139,22 @@
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S9" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T9" t="n">
         <v>1.82</v>
@@ -2163,25 +2163,25 @@
         <v>2.12</v>
       </c>
       <c r="V9" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="W9" t="n">
         <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y9" t="n">
         <v>9.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA9" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AB9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC9" t="n">
         <v>10.5</v>
@@ -2190,19 +2190,19 @@
         <v>9.6</v>
       </c>
       <c r="AE9" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AG9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AH9" t="n">
         <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ9" t="n">
         <v>700</v>
@@ -2217,16 +2217,16 @@
         <v>700</v>
       </c>
       <c r="AN9" t="n">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="AO9" t="n">
         <v>7.8</v>
       </c>
       <c r="AP9" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR9" t="n">
         <v>9</v>
@@ -2235,50 +2235,50 @@
         <v>13.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="AU9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV9" t="n">
         <v>9</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AW9" t="n">
         <v>14</v>
       </c>
       <c r="AX9" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.4</v>
+        <v>22</v>
       </c>
       <c r="AZ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB9" t="n">
         <v>14</v>
       </c>
-      <c r="BA9" t="n">
-        <v>19</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BC9" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="BG9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -2309,91 +2309,91 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>990</v>
+        <v>14</v>
       </c>
       <c r="H10" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="I10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.52</v>
       </c>
-      <c r="J10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
       <c r="S10" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="V10" t="n">
-        <v>2.94</v>
+        <v>3.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="Z10" t="n">
         <v>970</v>
       </c>
       <c r="AA10" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC10" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
@@ -2414,65 +2414,65 @@
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>470</v>
+        <v>9.6</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.57</v>
+        <v>6.4</v>
       </c>
       <c r="AQ10" t="n">
         <v>5.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS10" t="n">
         <v>5.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.57</v>
+        <v>5.3</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.45</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.45</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.57</v>
+        <v>4.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.57</v>
+        <v>7.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.57</v>
+        <v>6.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.56</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.57</v>
+        <v>4.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.57</v>
+        <v>4.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.57</v>
+        <v>4.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.57</v>
+        <v>3.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.57</v>
+        <v>8.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.73</v>
+        <v>4.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -2503,25 +2503,25 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H11" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I11" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J11" t="n">
         <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
@@ -2536,13 +2536,13 @@
         <v>1.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R11" t="n">
         <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T11" t="n">
         <v>1.93</v>
@@ -2554,10 +2554,10 @@
         <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y11" t="n">
         <v>9.6</v>
@@ -2569,7 +2569,7 @@
         <v>95</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
         <v>7.2</v>
@@ -2620,19 +2620,19 @@
         <v>15.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU11" t="n">
         <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AX11" t="n">
         <v>16.5</v>
@@ -2647,26 +2647,26 @@
         <v>29</v>
       </c>
       <c r="BB11" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BC11" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BD11" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BE11" t="n">
         <v>65</v>
       </c>
       <c r="BF11" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BG11" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -2709,10 +2709,10 @@
         <v>5.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.52</v>
@@ -2721,7 +2721,7 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="O12" t="n">
         <v>1.46</v>
@@ -2730,7 +2730,7 @@
         <v>1.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
@@ -2754,7 +2754,7 @@
         <v>11</v>
       </c>
       <c r="Y12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z12" t="n">
         <v>42</v>
@@ -2766,7 +2766,7 @@
         <v>8.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AD12" t="n">
         <v>24</v>
@@ -2778,7 +2778,7 @@
         <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
         <v>26</v>
@@ -2793,7 +2793,7 @@
         <v>30</v>
       </c>
       <c r="AL12" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
@@ -2814,7 +2814,7 @@
         <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AT12" t="n">
         <v>6.2</v>
@@ -2826,7 +2826,7 @@
         <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX12" t="n">
         <v>9.800000000000001</v>
@@ -2838,7 +2838,7 @@
         <v>19.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB12" t="n">
         <v>21</v>
@@ -2847,20 +2847,20 @@
         <v>21</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF12" t="n">
         <v>14.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
         <v>3.85</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AW13" t="n">
         <v>6</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Slovakian Super League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Zilina</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zemplin</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.42</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>1.49</v>
+        <v>5.4</v>
       </c>
       <c r="H15" t="n">
-        <v>7.6</v>
+        <v>1.75</v>
       </c>
       <c r="I15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV15" t="n">
         <v>8.6</v>
       </c>
-      <c r="J15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3</v>
-      </c>
-      <c r="X15" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>75</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>160</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>230</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>240</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>190</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK15" t="n">
+      <c r="AW15" t="n">
         <v>15</v>
       </c>
-      <c r="AL15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR15" t="n">
+      <c r="AX15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB15" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BC15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE15" t="n">
         <v>9.6</v>
       </c>
-      <c r="AT15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>9</v>
-      </c>
       <c r="BF15" t="n">
-        <v>4.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MFk Skalica</t>
+          <t>Zilina</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FC Kosice</t>
+          <t>Zemplin</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.62</v>
+        <v>1.42</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9</v>
+        <v>1.49</v>
       </c>
       <c r="H16" t="n">
-        <v>2.58</v>
+        <v>7.4</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>8.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="P16" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U16" t="n">
         <v>2.26</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.42</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.56</v>
+        <v>1.13</v>
       </c>
       <c r="W16" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="X16" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Y16" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="Z16" t="n">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="AA16" t="n">
-        <v>900</v>
+        <v>230</v>
       </c>
       <c r="AB16" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AC16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>240</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG16" t="n">
         <v>11</v>
       </c>
-      <c r="AD16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>15</v>
-      </c>
       <c r="AH16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>40</v>
+        <v>190</v>
       </c>
       <c r="AJ16" t="n">
-        <v>900</v>
+        <v>14</v>
       </c>
       <c r="AK16" t="n">
-        <v>32</v>
+        <v>14.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AM16" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="AO16" t="n">
-        <v>19.5</v>
+        <v>110</v>
       </c>
       <c r="AP16" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AT16" t="n">
         <v>11</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AV16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BC16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="BG16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Slovakian Super League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>MFk Skalica</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FC Inter</t>
+          <t>FC Kosice</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="G17" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="H17" t="n">
-        <v>1.75</v>
+        <v>2.58</v>
       </c>
       <c r="I17" t="n">
-        <v>1.78</v>
+        <v>2.8</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="U17" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="V17" t="n">
-        <v>2.28</v>
+        <v>1.56</v>
       </c>
       <c r="W17" t="n">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="X17" t="n">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="Z17" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.5</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD17" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="AF17" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AG17" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AH17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI17" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AJ17" t="n">
         <v>900</v>
       </c>
       <c r="AK17" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="AL17" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AN17" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV17" t="n">
         <v>10.5</v>
       </c>
-      <c r="AP17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AW17" t="n">
-        <v>15</v>
+        <v>5.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>8.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA17" t="n">
         <v>16</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="BD17" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BE17" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="BF17" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>1.43</v>
       </c>
       <c r="G18" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="H18" t="n">
         <v>7.2</v>
@@ -3873,7 +3873,7 @@
         <v>9.6</v>
       </c>
       <c r="J18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K18" t="n">
         <v>5.6</v>
@@ -3906,13 +3906,13 @@
         <v>1.81</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V18" t="n">
         <v>1.12</v>
       </c>
       <c r="W18" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="X18" t="n">
         <v>50</v>
@@ -3969,7 +3969,7 @@
         <v>130</v>
       </c>
       <c r="AP18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>13</v>
@@ -3999,7 +3999,7 @@
         <v>8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>17</v>
+        <v>6.6</v>
       </c>
       <c r="BA18" t="n">
         <v>7</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,179 +4046,179 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>SV Wildon</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>FC Schladming</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.37</v>
+        <v>1.03</v>
       </c>
       <c r="G19" t="n">
-        <v>1.39</v>
+        <v>990</v>
       </c>
       <c r="H19" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>15.5</v>
+        <v>990</v>
       </c>
       <c r="J19" t="n">
-        <v>4.7</v>
+        <v>1.09</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="P19" t="n">
-        <v>1.93</v>
+        <v>1.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.98</v>
+        <v>1.14</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>3.55</v>
+        <v>1.14</v>
       </c>
       <c r="T19" t="n">
-        <v>2.38</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SV Wildon</t>
+          <t>SV Union Gnas</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Schladming</t>
+          <t>SV Lebring</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4276,19 +4276,19 @@
         <v>1.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P20" t="n">
         <v>1.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="R20" t="n">
         <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -4434,22 +4434,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SV Union Gnas</t>
+          <t>TUS Bad Waltersdorf</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SV Lebring</t>
+          <t>SC Furstenfeld</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G21" t="n">
         <v>990</v>
       </c>
       <c r="H21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I21" t="n">
         <v>990</v>
@@ -4467,22 +4467,22 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P21" t="n">
         <v>1.25</v>
       </c>
-      <c r="O21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q21" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="R21" t="n">
         <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="T21" t="n">
         <v>1.11</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TUS Bad Waltersdorf</t>
+          <t>SV Tillmitsch</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SC Furstenfeld</t>
+          <t>FSC Eggendorf Hartberg II</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4661,22 +4661,22 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P22" t="n">
         <v>1.25</v>
       </c>
-      <c r="O22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q22" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="R22" t="n">
         <v>1.24</v>
       </c>
       <c r="S22" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T22" t="n">
         <v>1.11</v>
@@ -4800,14 +4800,14 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SV Tillmitsch</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FSC Eggendorf Hartberg II</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.02</v>
+        <v>2.06</v>
       </c>
       <c r="G23" t="n">
-        <v>990</v>
+        <v>2.14</v>
       </c>
       <c r="H23" t="n">
-        <v>1.02</v>
+        <v>3.8</v>
       </c>
       <c r="I23" t="n">
-        <v>990</v>
+        <v>4.4</v>
       </c>
       <c r="J23" t="n">
-        <v>1.09</v>
+        <v>3.35</v>
       </c>
       <c r="K23" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>1.25</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="P23" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.15</v>
+        <v>2.02</v>
       </c>
       <c r="R23" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>1.15</v>
+        <v>3.7</v>
       </c>
       <c r="T23" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="U23" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,179 +5016,179 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Smouha</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.06</v>
+        <v>7.2</v>
       </c>
       <c r="G24" t="n">
-        <v>2.14</v>
+        <v>8.6</v>
       </c>
       <c r="H24" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="I24" t="n">
-        <v>4.4</v>
+        <v>1.66</v>
       </c>
       <c r="J24" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="L24" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M24" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="O24" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="P24" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="S24" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.83</v>
+        <v>2.52</v>
       </c>
       <c r="U24" t="n">
-        <v>2.02</v>
+        <v>1.55</v>
       </c>
       <c r="V24" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.87</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>16.5</v>
+        <v>5.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="AB24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>490</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>230</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>450</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX24" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AC24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>11</v>
-      </c>
       <c r="AY24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BA24" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>28</v>
-      </c>
       <c r="BB24" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="BC24" t="n">
-        <v>17.5</v>
+        <v>6</v>
       </c>
       <c r="BD24" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BE24" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="BF24" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BG24" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -5210,179 +5210,179 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Smouha</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>360</v>
+      </c>
+      <c r="AF25" t="n">
         <v>7.2</v>
       </c>
-      <c r="G25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Z25" t="n">
+      <c r="AG25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN25" t="n">
         <v>7.8</v>
       </c>
-      <c r="AA25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>490</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>230</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>450</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO25" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS25" t="n">
         <v>11.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>14.5</v>
+        <v>5.9</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AV25" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AX25" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AY25" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
         <v>8.6</v>
       </c>
       <c r="BA25" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BB25" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="BD25" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="BE25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF25" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG25" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -5419,16 +5419,16 @@
         <v>5.8</v>
       </c>
       <c r="H26" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="I26" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="J26" t="n">
         <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L26" t="n">
         <v>1.46</v>
@@ -5491,7 +5491,7 @@
         <v>24</v>
       </c>
       <c r="AF26" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AG26" t="n">
         <v>23</v>
@@ -5506,7 +5506,7 @@
         <v>900</v>
       </c>
       <c r="AK26" t="n">
-        <v>700</v>
+        <v>470</v>
       </c>
       <c r="AL26" t="n">
         <v>700</v>
@@ -5527,34 +5527,34 @@
         <v>6.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS26" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="AT26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU26" t="n">
         <v>7</v>
       </c>
       <c r="AV26" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW26" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>32</v>
+        <v>7.8</v>
       </c>
       <c r="AY26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ26" t="n">
         <v>20</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="BB26" t="n">
         <v>8.199999999999999</v>
@@ -5572,11 +5572,11 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
         <v>1.76</v>
       </c>
       <c r="V27" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="W27" t="n">
         <v>1.12</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -5801,19 +5801,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="G28" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="H28" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I28" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J28" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K28" t="n">
         <v>3.9</v>
@@ -5831,16 +5831,16 @@
         <v>1.24</v>
       </c>
       <c r="P28" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R28" t="n">
         <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="T28" t="n">
         <v>1.6</v>
@@ -5867,7 +5867,7 @@
         <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AC28" t="n">
         <v>14</v>
@@ -5876,13 +5876,13 @@
         <v>15</v>
       </c>
       <c r="AE28" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG28" t="n">
         <v>500</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>21</v>
       </c>
       <c r="AH28" t="n">
         <v>26</v>
@@ -5897,7 +5897,7 @@
         <v>500</v>
       </c>
       <c r="AL28" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AM28" t="n">
         <v>580</v>
@@ -5909,7 +5909,7 @@
         <v>42</v>
       </c>
       <c r="AP28" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ28" t="n">
         <v>7.6</v>
@@ -5918,60 +5918,60 @@
         <v>10.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT28" t="n">
         <v>7.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AV28" t="n">
         <v>7</v>
       </c>
       <c r="AW28" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
         <v>8.4</v>
       </c>
       <c r="BA28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB28" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>8.6</v>
       </c>
       <c r="BC28" t="n">
         <v>13</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BE28" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BF28" t="n">
         <v>6.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5986,186 +5986,186 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Al-Khaleej Saihat</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>1.95</v>
       </c>
       <c r="G29" t="n">
-        <v>13</v>
+        <v>2.2</v>
       </c>
       <c r="H29" t="n">
-        <v>1.27</v>
+        <v>3.95</v>
       </c>
       <c r="I29" t="n">
-        <v>1.32</v>
+        <v>980</v>
       </c>
       <c r="J29" t="n">
-        <v>6.4</v>
+        <v>3.05</v>
       </c>
       <c r="K29" t="n">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="M29" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="N29" t="n">
-        <v>7.8</v>
+        <v>2.22</v>
       </c>
       <c r="O29" t="n">
-        <v>1.12</v>
+        <v>1.41</v>
       </c>
       <c r="P29" t="n">
-        <v>3.25</v>
+        <v>1.49</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.38</v>
+        <v>2.38</v>
       </c>
       <c r="R29" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="S29" t="n">
-        <v>1.93</v>
+        <v>1.05</v>
       </c>
       <c r="T29" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="U29" t="n">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="V29" t="n">
-        <v>4.1</v>
+        <v>1.17</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.69</v>
       </c>
       <c r="X29" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>46</v>
+        <v>990</v>
       </c>
       <c r="AH29" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>44</v>
+        <v>5.9</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR29" t="n">
-        <v>9.4</v>
+        <v>1.3</v>
       </c>
       <c r="AS29" t="n">
-        <v>9.800000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="AT29" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="AU29" t="n">
-        <v>14</v>
+        <v>5.3</v>
       </c>
       <c r="AV29" t="n">
-        <v>9.800000000000001</v>
+        <v>1.51</v>
       </c>
       <c r="AW29" t="n">
-        <v>11</v>
+        <v>1.34</v>
       </c>
       <c r="AX29" t="n">
-        <v>9.4</v>
+        <v>1.41</v>
       </c>
       <c r="AY29" t="n">
-        <v>18</v>
+        <v>1.25</v>
       </c>
       <c r="AZ29" t="n">
-        <v>20</v>
+        <v>1.33</v>
       </c>
       <c r="BA29" t="n">
-        <v>18.5</v>
+        <v>1.33</v>
       </c>
       <c r="BB29" t="n">
-        <v>10</v>
+        <v>1.33</v>
       </c>
       <c r="BC29" t="n">
-        <v>9.6</v>
+        <v>1.33</v>
       </c>
       <c r="BD29" t="n">
-        <v>9.4</v>
+        <v>1.34</v>
       </c>
       <c r="BE29" t="n">
-        <v>9.4</v>
+        <v>1.33</v>
       </c>
       <c r="BF29" t="n">
-        <v>10.5</v>
+        <v>1.33</v>
       </c>
       <c r="BG29" t="n">
-        <v>3.2</v>
+        <v>1.34</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Queen of South</t>
+          <t>Al-Khaleej Saihat</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.72</v>
+        <v>12</v>
       </c>
       <c r="G30" t="n">
-        <v>2.92</v>
+        <v>14</v>
       </c>
       <c r="H30" t="n">
-        <v>2.58</v>
+        <v>1.27</v>
       </c>
       <c r="I30" t="n">
-        <v>2.82</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="K30" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="M30" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="N30" t="n">
-        <v>3.35</v>
+        <v>7.8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="P30" t="n">
-        <v>1.84</v>
+        <v>3.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.02</v>
+        <v>1.37</v>
       </c>
       <c r="R30" t="n">
-        <v>1.31</v>
+        <v>1.9</v>
       </c>
       <c r="S30" t="n">
-        <v>3.55</v>
+        <v>1.93</v>
       </c>
       <c r="T30" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="U30" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V30" t="n">
-        <v>1.55</v>
+        <v>4.3</v>
       </c>
       <c r="W30" t="n">
-        <v>1.52</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y30" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y30" t="n">
-        <v>11</v>
-      </c>
       <c r="Z30" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>220</v>
+        <v>12.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.6</v>
+        <v>17</v>
       </c>
       <c r="AD30" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>34</v>
+        <v>13.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="AG30" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="AH30" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AI30" t="n">
-        <v>290</v>
+        <v>28</v>
       </c>
       <c r="AJ30" t="n">
+        <v>430</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>170</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>390</v>
+      </c>
+      <c r="AM30" t="n">
         <v>100</v>
       </c>
-      <c r="AK30" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>180</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>580</v>
-      </c>
       <c r="AN30" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AO30" t="n">
-        <v>30</v>
+        <v>3.65</v>
       </c>
       <c r="AP30" t="n">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="AQ30" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="AS30" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT30" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="AV30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB30" t="n">
         <v>9.4</v>
       </c>
-      <c r="AW30" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>32</v>
-      </c>
       <c r="BC30" t="n">
-        <v>14.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD30" t="n">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE30" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BF30" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>21</v>
+        <v>3.2</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Scottish League Two</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6374,186 +6374,186 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Clyde</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spartans</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="G31" t="n">
-        <v>3.1</v>
+        <v>2.34</v>
       </c>
       <c r="H31" t="n">
-        <v>2.54</v>
+        <v>3.4</v>
       </c>
       <c r="I31" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J31" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="K31" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="L31" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="M31" t="n">
         <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="O31" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="P31" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="T31" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U31" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="V31" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="W31" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="X31" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Y31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z31" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AA31" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AB31" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD31" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AF31" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AG31" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="AI31" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="AJ31" t="n">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="AK31" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="AM31" t="n">
         <v>500</v>
       </c>
       <c r="AN31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW31" t="n">
         <v>30</v>
       </c>
-      <c r="AO31" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AX31" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ31" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.7</v>
+        <v>36</v>
       </c>
       <c r="BB31" t="n">
-        <v>5.7</v>
+        <v>24</v>
       </c>
       <c r="BC31" t="n">
-        <v>5.4</v>
+        <v>19</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.7</v>
+        <v>29</v>
       </c>
       <c r="BE31" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BF31" t="n">
-        <v>5.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6568,186 +6568,186 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Queen of South</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.28</v>
+        <v>2.72</v>
       </c>
       <c r="G32" t="n">
-        <v>2.34</v>
+        <v>2.92</v>
       </c>
       <c r="H32" t="n">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="I32" t="n">
-        <v>3.6</v>
+        <v>2.82</v>
       </c>
       <c r="J32" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K32" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="L32" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M32" t="n">
         <v>1.07</v>
       </c>
       <c r="N32" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="O32" t="n">
         <v>1.34</v>
       </c>
       <c r="P32" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S32" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="T32" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U32" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="V32" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="W32" t="n">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="X32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>290</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>180</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX32" t="n">
         <v>14</v>
       </c>
-      <c r="Y32" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK32" t="n">
+      <c r="AY32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE32" t="n">
         <v>26</v>
       </c>
-      <c r="AL32" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT32" t="n">
+      <c r="BF32" t="n">
         <v>7.8</v>
       </c>
-      <c r="AU32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>17</v>
-      </c>
       <c r="BG32" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,184 +6757,378 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Clyde</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Spartans</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="G33" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="H33" t="n">
-        <v>5.9</v>
+        <v>2.54</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="J33" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="K33" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="L33" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M33" t="n">
         <v>1.07</v>
       </c>
       <c r="N33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-05-04 22:09:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N34" t="n">
         <v>3.95</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O34" t="n">
         <v>1.32</v>
       </c>
-      <c r="P33" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="P34" t="n">
         <v>2</v>
       </c>
-      <c r="R33" t="n">
+      <c r="Q34" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R34" t="n">
         <v>1.38</v>
       </c>
-      <c r="S33" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T33" t="n">
+      <c r="S34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T34" t="n">
         <v>2.04</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U34" t="n">
         <v>1.93</v>
       </c>
-      <c r="V33" t="n">
+      <c r="V34" t="n">
         <v>1.2</v>
       </c>
-      <c r="W33" t="n">
+      <c r="W34" t="n">
         <v>2.52</v>
       </c>
-      <c r="X33" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z33" t="n">
+      <c r="X34" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z34" t="n">
         <v>46</v>
       </c>
-      <c r="AA33" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="AA34" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB34" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AC34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN34" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AO34" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>130</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ34" t="n">
         <v>22</v>
       </c>
-      <c r="AE33" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>130</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>75</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA33" t="n">
+      <c r="BA34" t="n">
         <v>70</v>
       </c>
-      <c r="BB33" t="n">
+      <c r="BB34" t="n">
         <v>14</v>
       </c>
-      <c r="BC33" t="n">
+      <c r="BC34" t="n">
         <v>15.5</v>
       </c>
-      <c r="BD33" t="n">
+      <c r="BD34" t="n">
         <v>38</v>
       </c>
-      <c r="BE33" t="n">
+      <c r="BE34" t="n">
         <v>110</v>
       </c>
-      <c r="BF33" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG33" t="n">
+      <c r="BF34" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG34" t="n">
         <v>95</v>
       </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>2026-05-04 20:01:00</t>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G2" t="n">
         <v>4.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J2" t="n">
         <v>2.94</v>
@@ -775,13 +775,13 @@
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
         <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O2" t="n">
         <v>1.46</v>
@@ -868,7 +868,7 @@
         <v>4.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AR2" t="n">
         <v>4.9</v>
@@ -910,7 +910,7 @@
         <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="BF2" t="n">
         <v>6.6</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H3" t="n">
         <v>3.4</v>
       </c>
       <c r="I3" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
         <v>3.75</v>
@@ -975,13 +975,13 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="O3" t="n">
         <v>1.39</v>
       </c>
       <c r="P3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q3" t="n">
         <v>2.14</v>
@@ -990,19 +990,19 @@
         <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V3" t="n">
         <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X3" t="n">
         <v>13</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="G4" t="n">
         <v>990</v>
@@ -1154,28 +1154,28 @@
         <v>1.41</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="J4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O4" t="n">
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="Q4" t="n">
         <v>1.85</v>
@@ -1193,10 +1193,10 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.05</v>
+        <v>1.83</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>17</v>
@@ -1298,7 +1298,7 @@
         <v>1.07</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.07</v>
+        <v>120</v>
       </c>
       <c r="BF4" t="n">
         <v>1.07</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
         <v>1.9</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V5" t="n">
         <v>1.36</v>
@@ -1399,10 +1399,10 @@
         <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA5" t="n">
-        <v>500</v>
+        <v>340</v>
       </c>
       <c r="AB5" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
         <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
         <v>60</v>
@@ -1423,25 +1423,25 @@
         <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AJ5" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AK5" t="n">
         <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AO5" t="n">
         <v>600</v>
@@ -1474,7 +1474,7 @@
         <v>12.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>16.5</v>
@@ -1498,11 +1498,11 @@
         <v>21</v>
       </c>
       <c r="BG5" t="n">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>2.22</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -1557,7 +1557,7 @@
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O6" t="n">
         <v>1.51</v>
@@ -1581,10 +1581,10 @@
         <v>1.72</v>
       </c>
       <c r="V6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X6" t="n">
         <v>9.199999999999999</v>
@@ -1644,7 +1644,7 @@
         <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR6" t="n">
         <v>5.1</v>
@@ -1653,7 +1653,7 @@
         <v>6.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU6" t="n">
         <v>4</v>
@@ -1662,13 +1662,13 @@
         <v>4.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX6" t="n">
         <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AZ6" t="n">
         <v>5.9</v>
@@ -1677,26 +1677,26 @@
         <v>7</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC6" t="n">
         <v>9</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE6" t="n">
         <v>7.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG6" t="n">
         <v>6.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J7" t="n">
         <v>3.2</v>
@@ -1751,13 +1751,13 @@
         <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="O7" t="n">
         <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
         <v>1.92</v>
@@ -1769,16 +1769,16 @@
         <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U7" t="n">
         <v>1.93</v>
       </c>
       <c r="V7" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="W7" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X7" t="n">
         <v>28</v>
@@ -1835,7 +1835,7 @@
         <v>85</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AQ7" t="n">
         <v>4.3</v>
@@ -1847,7 +1847,7 @@
         <v>6.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AU7" t="n">
         <v>4.1</v>
@@ -1862,7 +1862,7 @@
         <v>5.7</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AZ7" t="n">
         <v>5.9</v>
@@ -1871,7 +1871,7 @@
         <v>6</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BC7" t="n">
         <v>5</v>
@@ -1880,7 +1880,7 @@
         <v>5.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="BF7" t="n">
         <v>5.1</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
         <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="I8" t="n">
         <v>2.4</v>
@@ -1945,22 +1945,22 @@
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O8" t="n">
         <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="S8" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T8" t="n">
         <v>1.47</v>
@@ -1972,7 +1972,7 @@
         <v>1.71</v>
       </c>
       <c r="W8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X8" t="n">
         <v>46</v>
@@ -1981,13 +1981,13 @@
         <v>24</v>
       </c>
       <c r="Z8" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
         <v>500</v>
       </c>
       <c r="AB8" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AC8" t="n">
         <v>10</v>
@@ -1996,7 +1996,7 @@
         <v>12.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF8" t="n">
         <v>500</v>
@@ -2008,7 +2008,7 @@
         <v>13.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ8" t="n">
         <v>55</v>
@@ -2023,22 +2023,22 @@
         <v>55</v>
       </c>
       <c r="AN8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO8" t="n">
         <v>10.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR8" t="n">
         <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
         <v>18.5</v>
@@ -2065,26 +2065,26 @@
         <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BC8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD8" t="n">
         <v>24</v>
       </c>
       <c r="BE8" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BF8" t="n">
         <v>14</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I9" t="n">
         <v>1.56</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.6</v>
       </c>
       <c r="J9" t="n">
         <v>4.5</v>
@@ -2133,40 +2133,40 @@
         <v>4.7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
         <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R9" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S9" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="U9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
         <v>19.5</v>
@@ -2181,7 +2181,7 @@
         <v>15</v>
       </c>
       <c r="AB9" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AC9" t="n">
         <v>10.5</v>
@@ -2193,49 +2193,49 @@
         <v>15.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AG9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AH9" t="n">
         <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ9" t="n">
-        <v>700</v>
+        <v>220</v>
       </c>
       <c r="AK9" t="n">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="AL9" t="n">
-        <v>700</v>
+        <v>95</v>
       </c>
       <c r="AM9" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO9" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AP9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AR9" t="n">
-        <v>9</v>
-      </c>
       <c r="AS9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU9" t="n">
         <v>9.199999999999999</v>
@@ -2244,41 +2244,41 @@
         <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>12.5</v>
+        <v>27</v>
       </c>
       <c r="AY9" t="n">
         <v>22</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA9" t="n">
         <v>27</v>
       </c>
       <c r="BB9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD9" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE9" t="n">
         <v>12.5</v>
       </c>
-      <c r="BE9" t="n">
-        <v>13</v>
-      </c>
       <c r="BF9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -2309,70 +2309,70 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H10" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="I10" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="J10" t="n">
         <v>4.9</v>
       </c>
       <c r="K10" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O10" t="n">
         <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S10" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
         <v>950</v>
       </c>
       <c r="Y10" t="n">
-        <v>24</v>
+        <v>9.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AA10" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AB10" t="n">
         <v>950</v>
@@ -2381,13 +2381,13 @@
         <v>42</v>
       </c>
       <c r="AD10" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="AG10" t="n">
         <v>950</v>
@@ -2408,19 +2408,19 @@
         <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN10" t="n">
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>9.6</v>
+        <v>5.2</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AR10" t="n">
         <v>4.5</v>
@@ -2429,28 +2429,28 @@
         <v>5.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AX10" t="n">
         <v>4.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>16.5</v>
       </c>
       <c r="BB10" t="n">
         <v>4.2</v>
@@ -2462,17 +2462,17 @@
         <v>4.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="BF10" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG10" t="n">
         <v>4.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G11" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H11" t="n">
         <v>2.82</v>
@@ -2515,91 +2515,91 @@
         <v>2.94</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="U11" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="V11" t="n">
         <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="X11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y11" t="n">
         <v>10.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>9.6</v>
       </c>
       <c r="Z11" t="n">
         <v>18</v>
       </c>
       <c r="AA11" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AF11" t="n">
         <v>19</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AJ11" t="n">
         <v>320</v>
       </c>
       <c r="AK11" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AL11" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="AM11" t="n">
         <v>580</v>
@@ -2608,19 +2608,19 @@
         <v>40</v>
       </c>
       <c r="AO11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR11" t="n">
         <v>15.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AT11" t="n">
         <v>9</v>
@@ -2632,7 +2632,7 @@
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AX11" t="n">
         <v>16.5</v>
@@ -2641,32 +2641,32 @@
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA11" t="n">
         <v>29</v>
       </c>
       <c r="BB11" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BC11" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="BD11" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BE11" t="n">
         <v>65</v>
       </c>
       <c r="BF11" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BG11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.94</v>
       </c>
       <c r="G12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H12" t="n">
         <v>4.6</v>
@@ -2709,13 +2709,13 @@
         <v>5.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
         <v>3.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="M12" t="n">
         <v>1.1</v>
@@ -2724,7 +2724,7 @@
         <v>2.86</v>
       </c>
       <c r="O12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P12" t="n">
         <v>1.64</v>
@@ -2748,7 +2748,7 @@
         <v>1.24</v>
       </c>
       <c r="W12" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X12" t="n">
         <v>11</v>
@@ -2802,7 +2802,7 @@
         <v>21</v>
       </c>
       <c r="AO12" t="n">
-        <v>140</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
         <v>8.800000000000001</v>
@@ -2847,20 +2847,20 @@
         <v>21</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF12" t="n">
         <v>14.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>1.88</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I13" t="n">
         <v>6.2</v>
@@ -2909,7 +2909,7 @@
         <v>4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
@@ -2927,10 +2927,10 @@
         <v>1.92</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="T13" t="n">
         <v>1.86</v>
@@ -2939,13 +2939,13 @@
         <v>1.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
         <v>2.12</v>
       </c>
       <c r="X13" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Y13" t="n">
         <v>22</v>
@@ -3002,59 +3002,59 @@
         <v>4.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AV13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC13" t="n">
         <v>5.3</v>
       </c>
-      <c r="AW13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>5</v>
-      </c>
       <c r="BD13" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
         <v>1.97</v>
       </c>
       <c r="U14" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V14" t="n">
         <v>1.11</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G15" t="n">
         <v>5.4</v>
@@ -3291,10 +3291,10 @@
         <v>1.78</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.35</v>
@@ -3324,7 +3324,7 @@
         <v>1.76</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
         <v>2.28</v>
@@ -3354,7 +3354,7 @@
         <v>10.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF15" t="n">
         <v>42</v>
@@ -3384,7 +3384,7 @@
         <v>75</v>
       </c>
       <c r="AO15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AP15" t="n">
         <v>15</v>
@@ -3423,26 +3423,26 @@
         <v>16</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BD15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
         <v>8.6</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K16" t="n">
         <v>5.8</v>
@@ -3515,7 +3515,7 @@
         <v>2.16</v>
       </c>
       <c r="T16" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U16" t="n">
         <v>2.26</v>
@@ -3530,7 +3530,7 @@
         <v>34</v>
       </c>
       <c r="Y16" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="Z16" t="n">
         <v>160</v>
@@ -3584,10 +3584,10 @@
         <v>20</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AS16" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
         <v>11</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AV16" t="n">
         <v>21</v>
@@ -3608,16 +3608,16 @@
         <v>10</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="BB16" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BC16" t="n">
         <v>12</v>
@@ -3626,17 +3626,17 @@
         <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BG16" t="n">
         <v>15</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="G17" t="n">
         <v>2.9</v>
       </c>
       <c r="H17" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="I17" t="n">
         <v>2.8</v>
@@ -3784,7 +3784,7 @@
         <v>15</v>
       </c>
       <c r="AS17" t="n">
-        <v>18</v>
+        <v>5.7</v>
       </c>
       <c r="AT17" t="n">
         <v>11</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
         <v>1.81</v>
       </c>
       <c r="U18" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>1.12</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
         <v>4.4</v>
       </c>
       <c r="J23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
         <v>3.75</v>
@@ -4969,7 +4969,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA23" t="n">
         <v>28</v>
@@ -4984,7 +4984,7 @@
         <v>20</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BF23" t="n">
         <v>13</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -5025,40 +5025,40 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G24" t="n">
         <v>8.6</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="I24" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K24" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M24" t="n">
         <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
         <v>1.53</v>
       </c>
       <c r="P24" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="R24" t="n">
         <v>1.19</v>
@@ -5073,13 +5073,13 @@
         <v>1.55</v>
       </c>
       <c r="V24" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="W24" t="n">
         <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="Y24" t="n">
         <v>5.8</v>
@@ -5097,7 +5097,7 @@
         <v>14</v>
       </c>
       <c r="AD24" t="n">
-        <v>24</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE24" t="n">
         <v>40</v>
@@ -5130,10 +5130,10 @@
         <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ24" t="n">
         <v>5</v>
@@ -5151,44 +5151,44 @@
         <v>7.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX24" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB24" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AZ24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>6</v>
-      </c>
       <c r="BC24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BE24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF24" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG24" t="n">
         <v>13.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -5225,16 +5225,16 @@
         <v>1.39</v>
       </c>
       <c r="H25" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="I25" t="n">
         <v>15.5</v>
       </c>
       <c r="J25" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K25" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L25" t="n">
         <v>1.4</v>
@@ -5243,28 +5243,28 @@
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O25" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P25" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q25" t="n">
         <v>1.98</v>
       </c>
       <c r="R25" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="T25" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="U25" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V25" t="n">
         <v>1.07</v>
@@ -5273,10 +5273,10 @@
         <v>3.55</v>
       </c>
       <c r="X25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y25" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Z25" t="n">
         <v>130</v>
@@ -5285,22 +5285,22 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC25" t="n">
         <v>11.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>65</v>
+        <v>950</v>
       </c>
       <c r="AE25" t="n">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="AF25" t="n">
         <v>7.2</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AH25" t="n">
         <v>80</v>
@@ -5312,16 +5312,16 @@
         <v>11</v>
       </c>
       <c r="AK25" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM25" t="n">
         <v>310</v>
       </c>
       <c r="AN25" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
@@ -5330,13 +5330,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AS25" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="AT25" t="n">
         <v>5.9</v>
@@ -5345,44 +5345,44 @@
         <v>10</v>
       </c>
       <c r="AV25" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AX25" t="n">
         <v>6.4</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>44</v>
+        <v>12.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BF25" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="G26" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H26" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="I26" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="J26" t="n">
         <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L26" t="n">
         <v>1.46</v>
@@ -5440,13 +5440,13 @@
         <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P26" t="n">
         <v>1.68</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R26" t="n">
         <v>1.26</v>
@@ -5458,13 +5458,13 @@
         <v>2.04</v>
       </c>
       <c r="U26" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="V26" t="n">
         <v>2.08</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X26" t="n">
         <v>12</v>
@@ -5485,7 +5485,7 @@
         <v>8.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AE26" t="n">
         <v>24</v>
@@ -5500,7 +5500,7 @@
         <v>24</v>
       </c>
       <c r="AI26" t="n">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="AJ26" t="n">
         <v>900</v>
@@ -5545,7 +5545,7 @@
         <v>10.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY26" t="n">
         <v>18</v>
@@ -5557,26 +5557,26 @@
         <v>34</v>
       </c>
       <c r="BB26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC26" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD26" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>13.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
         <v>4.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
@@ -5652,10 +5652,10 @@
         <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V27" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="W27" t="n">
         <v>1.12</v>
@@ -5682,10 +5682,10 @@
         <v>10.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF27" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AG27" t="n">
         <v>32</v>
@@ -5754,13 +5754,13 @@
         <v>7.2</v>
       </c>
       <c r="BC27" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF27" t="n">
         <v>7.2</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
         <v>3.65</v>
       </c>
       <c r="K28" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L28" t="n">
         <v>1.29</v>
@@ -5825,22 +5825,22 @@
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
         <v>1.24</v>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R28" t="n">
         <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="T28" t="n">
         <v>1.6</v>
@@ -5858,13 +5858,13 @@
         <v>23</v>
       </c>
       <c r="Y28" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Z28" t="n">
         <v>500</v>
       </c>
       <c r="AA28" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB28" t="n">
         <v>500</v>
@@ -5879,7 +5879,7 @@
         <v>60</v>
       </c>
       <c r="AF28" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AG28" t="n">
         <v>500</v>
@@ -5897,7 +5897,7 @@
         <v>500</v>
       </c>
       <c r="AL28" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM28" t="n">
         <v>580</v>
@@ -5906,10 +5906,10 @@
         <v>55</v>
       </c>
       <c r="AO28" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="AP28" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ28" t="n">
         <v>7.6</v>
@@ -5918,22 +5918,22 @@
         <v>10.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT28" t="n">
         <v>7.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AV28" t="n">
         <v>7</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX28" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
@@ -5942,29 +5942,29 @@
         <v>8.4</v>
       </c>
       <c r="BA28" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB28" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC28" t="n">
         <v>13</v>
       </c>
       <c r="BD28" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BF28" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG28" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -6201,13 +6201,13 @@
         <v>1.3</v>
       </c>
       <c r="J30" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K30" t="n">
         <v>7.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M30" t="n">
         <v>1.02</v>
@@ -6324,7 +6324,7 @@
         <v>9</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ30" t="n">
         <v>20</v>
@@ -6336,7 +6336,7 @@
         <v>9.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BD30" t="n">
         <v>8.800000000000001</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G31" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H31" t="n">
         <v>3.4</v>
@@ -6398,13 +6398,13 @@
         <v>3.4</v>
       </c>
       <c r="K31" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L31" t="n">
         <v>1.41</v>
       </c>
       <c r="M31" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N31" t="n">
         <v>3.6</v>
@@ -6416,28 +6416,28 @@
         <v>1.88</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T31" t="n">
         <v>1.79</v>
       </c>
       <c r="U31" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V31" t="n">
         <v>1.38</v>
       </c>
       <c r="W31" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X31" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y31" t="n">
         <v>13</v>
@@ -6446,16 +6446,16 @@
         <v>500</v>
       </c>
       <c r="AA31" t="n">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AB31" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC31" t="n">
         <v>8</v>
       </c>
       <c r="AD31" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AE31" t="n">
         <v>42</v>
@@ -6470,7 +6470,7 @@
         <v>29</v>
       </c>
       <c r="AI31" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="AJ31" t="n">
         <v>32</v>
@@ -6482,10 +6482,10 @@
         <v>40</v>
       </c>
       <c r="AM31" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AN31" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AO31" t="n">
         <v>50</v>
@@ -6527,26 +6527,26 @@
         <v>36</v>
       </c>
       <c r="BB31" t="n">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="BC31" t="n">
         <v>19</v>
       </c>
       <c r="BD31" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="BE31" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="BF31" t="n">
         <v>17.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6589,7 @@
         <v>2.82</v>
       </c>
       <c r="J32" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K32" t="n">
         <v>4</v>
@@ -6646,7 +6646,7 @@
         <v>11</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD32" t="n">
         <v>13</v>
@@ -6661,13 +6661,13 @@
         <v>13</v>
       </c>
       <c r="AH32" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI32" t="n">
         <v>290</v>
       </c>
       <c r="AJ32" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AK32" t="n">
         <v>75</v>
@@ -6718,16 +6718,16 @@
         <v>14</v>
       </c>
       <c r="BA32" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="BB32" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="BC32" t="n">
         <v>14.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="BE32" t="n">
         <v>26</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
         <v>1.31</v>
       </c>
       <c r="S33" t="n">
-        <v>1.05</v>
+        <v>3.25</v>
       </c>
       <c r="T33" t="n">
         <v>1.8</v>
@@ -6861,7 +6861,7 @@
         <v>130</v>
       </c>
       <c r="AJ33" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="AK33" t="n">
         <v>36</v>
@@ -6885,10 +6885,10 @@
         <v>6.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT33" t="n">
         <v>5.8</v>
@@ -6900,10 +6900,10 @@
         <v>7.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX33" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="AY33" t="n">
         <v>7</v>
@@ -6918,13 +6918,13 @@
         <v>5.7</v>
       </c>
       <c r="BC33" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD33" t="n">
         <v>5.7</v>
       </c>
       <c r="BE33" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF33" t="n">
         <v>5.5</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="F34" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G34" t="n">
         <v>1.65</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1.66</v>
       </c>
       <c r="H34" t="n">
         <v>5.9</v>
@@ -6989,28 +6989,28 @@
         <v>1.07</v>
       </c>
       <c r="N34" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="R34" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S34" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T34" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U34" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V34" t="n">
         <v>1.2</v>
@@ -7019,22 +7019,22 @@
         <v>2.52</v>
       </c>
       <c r="X34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y34" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z34" t="n">
         <v>46</v>
       </c>
       <c r="AA34" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AB34" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD34" t="n">
         <v>22</v>
@@ -7055,10 +7055,10 @@
         <v>85</v>
       </c>
       <c r="AJ34" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK34" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL34" t="n">
         <v>40</v>
@@ -7067,16 +7067,16 @@
         <v>130</v>
       </c>
       <c r="AN34" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO34" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP34" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ34" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AR34" t="n">
         <v>42</v>
@@ -7085,19 +7085,19 @@
         <v>130</v>
       </c>
       <c r="AT34" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW34" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AX34" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY34" t="n">
         <v>9.800000000000001</v>
@@ -7124,11 +7124,11 @@
         <v>9</v>
       </c>
       <c r="BG34" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G2" t="n">
         <v>4.2</v>
@@ -766,28 +766,28 @@
         <v>2.28</v>
       </c>
       <c r="I2" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J2" t="n">
         <v>2.94</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M2" t="n">
         <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="O2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q2" t="n">
         <v>2.46</v>
@@ -796,28 +796,28 @@
         <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U2" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V2" t="n">
         <v>1.64</v>
       </c>
       <c r="W2" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
         <v>10</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA2" t="n">
         <v>38</v>
@@ -826,7 +826,7 @@
         <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
         <v>13</v>
@@ -835,7 +835,7 @@
         <v>34</v>
       </c>
       <c r="AF2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AG2" t="n">
         <v>17.5</v>
@@ -862,65 +862,65 @@
         <v>85</v>
       </c>
       <c r="AO2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AR2" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AS2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX2" t="n">
         <v>6</v>
       </c>
-      <c r="AT2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW2" t="n">
+      <c r="AY2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>6</v>
       </c>
-      <c r="AX2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC2" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC2" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
         <v>130</v>
       </c>
       <c r="BF2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG2" t="n">
         <v>6.6</v>
       </c>
-      <c r="BG2" t="n">
-        <v>6</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -957,16 +957,16 @@
         <v>2.44</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
         <v>1.46</v>
@@ -978,31 +978,31 @@
         <v>2.96</v>
       </c>
       <c r="O3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q3" t="n">
         <v>2.14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
         <v>1.89</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="X3" t="n">
         <v>13</v>
@@ -1011,22 +1011,22 @@
         <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB3" t="n">
         <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
@@ -1038,10 +1038,10 @@
         <v>950</v>
       </c>
       <c r="AI3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK3" t="n">
         <v>29</v>
@@ -1059,62 +1059,62 @@
         <v>70</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AW3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE3" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BF3" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -1145,61 +1145,61 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J4" t="n">
         <v>3.15</v>
       </c>
-      <c r="G4" t="n">
-        <v>990</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="I4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.7</v>
-      </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="Q4" t="n">
         <v>1.85</v>
       </c>
       <c r="R4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
         <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V4" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -1339,34 +1339,34 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="H5" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P5" t="n">
         <v>1.79</v>
@@ -1375,134 +1375,134 @@
         <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
         <v>4.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U5" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="X5" t="n">
         <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>340</v>
+        <v>90</v>
       </c>
       <c r="AB5" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
         <v>60</v>
       </c>
       <c r="AF5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>29</v>
+        <v>19.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="AJ5" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="AK5" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AO5" t="n">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AS5" t="n">
         <v>20</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="AX5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BB5" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BC5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BE5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BF5" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.199999999999999</v>
+        <v>48</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -1536,16 +1536,16 @@
         <v>3.45</v>
       </c>
       <c r="G6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H6" t="n">
         <v>2.22</v>
       </c>
       <c r="I6" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
         <v>3.45</v>
@@ -1584,7 +1584,7 @@
         <v>1.64</v>
       </c>
       <c r="W6" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X6" t="n">
         <v>9.199999999999999</v>
@@ -1614,7 +1614,7 @@
         <v>27</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AH6" t="n">
         <v>26</v>
@@ -1641,62 +1641,62 @@
         <v>40</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV6" t="n">
         <v>4.7</v>
       </c>
-      <c r="AU6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AW6" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ6" t="n">
         <v>5.9</v>
       </c>
       <c r="BA6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB6" t="n">
         <v>7</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BC6" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC6" t="n">
-        <v>9</v>
-      </c>
       <c r="BD6" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="J7" t="n">
         <v>3.2</v>
@@ -1751,16 +1751,16 @@
         <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="R7" t="n">
         <v>1.29</v>
@@ -1775,19 +1775,19 @@
         <v>1.93</v>
       </c>
       <c r="V7" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="W7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X7" t="n">
         <v>28</v>
       </c>
       <c r="Y7" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="Z7" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
@@ -1799,7 +1799,7 @@
         <v>14</v>
       </c>
       <c r="AD7" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
@@ -1838,59 +1838,59 @@
         <v>5.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
         <v>5.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AW7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX7" t="n">
         <v>6.2</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AY7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC7" t="n">
         <v>5.7</v>
       </c>
-      <c r="AY7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA7" t="n">
+      <c r="BD7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE7" t="n">
         <v>6</v>
       </c>
-      <c r="BB7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5</v>
-      </c>
       <c r="BF7" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -1921,25 +1921,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
         <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M8" t="n">
         <v>1.03</v>
@@ -1951,10 +1951,10 @@
         <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R8" t="n">
         <v>1.77</v>
@@ -1963,31 +1963,31 @@
         <v>2.22</v>
       </c>
       <c r="T8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U8" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="W8" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="X8" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="Y8" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AB8" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AC8" t="n">
         <v>10</v>
@@ -1996,49 +1996,49 @@
         <v>12.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AF8" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AG8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
         <v>13.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AJ8" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AK8" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AL8" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AN8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>16.5</v>
       </c>
-      <c r="AO8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP8" t="n">
+      <c r="AR8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS8" t="n">
         <v>24</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>21</v>
       </c>
       <c r="AT8" t="n">
         <v>18.5</v>
@@ -2047,13 +2047,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW8" t="n">
         <v>18.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AY8" t="n">
         <v>12.5</v>
@@ -2071,20 +2071,20 @@
         <v>21</v>
       </c>
       <c r="BD8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BE8" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BF8" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -2115,25 +2115,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="G9" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="H9" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="I9" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
@@ -2142,143 +2142,143 @@
         <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="R9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="T9" t="n">
         <v>1.86</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD9" t="n">
         <v>9.6</v>
       </c>
       <c r="AE9" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AG9" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI9" t="n">
         <v>34</v>
       </c>
       <c r="AJ9" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="AK9" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AL9" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AM9" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AN9" t="n">
         <v>110</v>
       </c>
       <c r="AO9" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AP9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AS9" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AT9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AU9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV9" t="n">
         <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY9" t="n">
         <v>22</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BB9" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -2309,67 +2309,67 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="G10" t="n">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="H10" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="I10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="J10" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="K10" t="n">
         <v>6.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="R10" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="V10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
         <v>950</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA10" t="n">
         <v>25</v>
@@ -2381,13 +2381,13 @@
         <v>42</v>
       </c>
       <c r="AD10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AF10" t="n">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="AG10" t="n">
         <v>950</v>
@@ -2396,83 +2396,83 @@
         <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="n">
         <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AM10" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="AN10" t="n">
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="AU10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV10" t="n">
         <v>7</v>
       </c>
-      <c r="AV10" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AW10" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="BA10" t="n">
         <v>16.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.2</v>
+        <v>19.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -2503,127 +2503,127 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="G11" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="H11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I11" t="n">
         <v>2.82</v>
       </c>
-      <c r="I11" t="n">
-        <v>2.94</v>
-      </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
         <v>3.35</v>
       </c>
       <c r="L11" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="U11" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="V11" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="X11" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA11" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC11" t="n">
         <v>7.4</v>
       </c>
       <c r="AD11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG11" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AH11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI11" t="n">
         <v>60</v>
       </c>
-      <c r="AF11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>290</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>320</v>
+        <v>55</v>
       </c>
       <c r="AK11" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AL11" t="n">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="AM11" t="n">
         <v>580</v>
       </c>
       <c r="AN11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO11" t="n">
         <v>40</v>
       </c>
-      <c r="AO11" t="n">
-        <v>34</v>
-      </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS11" t="n">
         <v>25</v>
       </c>
       <c r="AT11" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AU11" t="n">
         <v>6.6</v>
@@ -2632,41 +2632,41 @@
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AX11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BB11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD11" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BE11" t="n">
         <v>65</v>
       </c>
       <c r="BF11" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG11" t="n">
         <v>23</v>
       </c>
-      <c r="BG11" t="n">
-        <v>22</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G12" t="n">
         <v>2.04</v>
@@ -2706,52 +2706,52 @@
         <v>4.6</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="n">
         <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L12" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P12" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T12" t="n">
         <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
         <v>1.96</v>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Y12" t="n">
         <v>15.5</v>
@@ -2760,7 +2760,7 @@
         <v>42</v>
       </c>
       <c r="AA12" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB12" t="n">
         <v>8.6</v>
@@ -2769,40 +2769,40 @@
         <v>7.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE12" t="n">
-        <v>95</v>
+        <v>480</v>
       </c>
       <c r="AF12" t="n">
         <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
-        <v>110</v>
+        <v>380</v>
       </c>
       <c r="AJ12" t="n">
         <v>30</v>
       </c>
       <c r="AK12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL12" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AP12" t="n">
         <v>8.800000000000001</v>
@@ -2814,7 +2814,7 @@
         <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT12" t="n">
         <v>6.2</v>
@@ -2826,7 +2826,7 @@
         <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AX12" t="n">
         <v>9.800000000000001</v>
@@ -2835,10 +2835,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB12" t="n">
         <v>21</v>
@@ -2847,20 +2847,20 @@
         <v>21</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BF12" t="n">
         <v>14.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -2891,170 +2891,170 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="G13" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.39</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="V13" t="n">
         <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z13" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA13" t="n">
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="AE13" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI13" t="n">
         <v>700</v>
       </c>
-      <c r="AF13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>230</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AK13" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AL13" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AO13" t="n">
         <v>700</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="AQ13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV13" t="n">
         <v>5.4</v>
       </c>
-      <c r="AR13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AW13" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BD13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE13" t="n">
         <v>6.4</v>
       </c>
-      <c r="BE13" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BF13" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -3085,61 +3085,61 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G14" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="H14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I14" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K14" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="T14" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="U14" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="X14" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="Y14" t="n">
         <v>55</v>
@@ -3148,107 +3148,107 @@
         <v>420</v>
       </c>
       <c r="AA14" t="n">
-        <v>320</v>
+        <v>250</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AC14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD14" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AE14" t="n">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="AF14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG14" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
         <v>470</v>
       </c>
       <c r="AJ14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AL14" t="n">
         <v>85</v>
       </c>
       <c r="AM14" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AO14" t="n">
         <v>170</v>
       </c>
-      <c r="AN14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>210</v>
-      </c>
       <c r="AP14" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AQ14" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AT14" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AU14" t="n">
         <v>9</v>
       </c>
       <c r="AV14" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX14" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
         <v>10</v>
       </c>
       <c r="BC14" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>5.1</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H15" t="n">
         <v>1.75</v>
@@ -3294,37 +3294,37 @@
         <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U15" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V15" t="n">
         <v>2.28</v>
@@ -3333,116 +3333,116 @@
         <v>1.23</v>
       </c>
       <c r="X15" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AB15" t="n">
         <v>20</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE15" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AF15" t="n">
         <v>42</v>
       </c>
       <c r="AG15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ15" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AK15" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL15" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM15" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="AN15" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AO15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR15" t="n">
         <v>10</v>
       </c>
-      <c r="AP15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AS15" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="AY15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ15" t="n">
         <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.4</v>
+        <v>40</v>
       </c>
       <c r="BC15" t="n">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BD15" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="BF15" t="n">
-        <v>9.4</v>
+        <v>32</v>
       </c>
       <c r="BG15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -3473,25 +3473,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="G16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I16" t="n">
         <v>8.6</v>
       </c>
       <c r="J16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K16" t="n">
         <v>5.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
@@ -3503,28 +3503,28 @@
         <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="R16" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="S16" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U16" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="V16" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X16" t="n">
         <v>34</v>
@@ -3542,7 +3542,7 @@
         <v>13.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD16" t="n">
         <v>65</v>
@@ -3551,7 +3551,7 @@
         <v>240</v>
       </c>
       <c r="AF16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
@@ -3575,13 +3575,13 @@
         <v>80</v>
       </c>
       <c r="AN16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO16" t="n">
         <v>110</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>8.6</v>
       </c>
       <c r="AQ16" t="n">
         <v>17.5</v>
@@ -3590,19 +3590,19 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU16" t="n">
         <v>11</v>
       </c>
       <c r="AV16" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX16" t="n">
         <v>10</v>
@@ -3611,7 +3611,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA16" t="n">
         <v>23</v>
@@ -3626,7 +3626,7 @@
         <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF16" t="n">
         <v>4.2</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J17" t="n">
         <v>3.65</v>
@@ -3685,94 +3685,94 @@
         <v>4.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="T17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U17" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X17" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="Y17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AA17" t="n">
         <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AC17" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
         <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AF17" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="AG17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AJ17" t="n">
         <v>900</v>
       </c>
       <c r="AK17" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AL17" t="n">
         <v>500</v>
       </c>
       <c r="AM17" t="n">
-        <v>250</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="AO17" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP17" t="n">
         <v>16</v>
@@ -3784,7 +3784,7 @@
         <v>15</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT17" t="n">
         <v>11</v>
@@ -3796,7 +3796,7 @@
         <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AX17" t="n">
         <v>15.5</v>
@@ -3811,7 +3811,7 @@
         <v>16</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC17" t="n">
         <v>13</v>
@@ -3820,17 +3820,17 @@
         <v>18</v>
       </c>
       <c r="BE17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BF17" t="n">
         <v>13.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -3861,61 +3861,61 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G18" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="H18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I18" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="J18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K18" t="n">
         <v>5.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O18" t="n">
         <v>1.21</v>
       </c>
       <c r="P18" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R18" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S18" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="T18" t="n">
         <v>1.81</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
         <v>1.12</v>
       </c>
       <c r="W18" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="X18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="Y18" t="n">
         <v>950</v>
@@ -3924,10 +3924,10 @@
         <v>540</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB18" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AC18" t="n">
         <v>17.5</v>
@@ -3939,13 +3939,13 @@
         <v>260</v>
       </c>
       <c r="AF18" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AH18" t="n">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="AI18" t="n">
         <v>390</v>
@@ -3957,74 +3957,74 @@
         <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AM18" t="n">
         <v>380</v>
       </c>
       <c r="AN18" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AO18" t="n">
         <v>130</v>
       </c>
       <c r="AP18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB18" t="n">
         <v>11.5</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS18" t="n">
+      <c r="BC18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD18" t="n">
         <v>7.2</v>
       </c>
-      <c r="AT18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BE18" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG18" t="n">
         <v>15</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -4055,170 +4055,170 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="G19" t="n">
-        <v>990</v>
+        <v>1.4</v>
       </c>
       <c r="H19" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="I19" t="n">
-        <v>990</v>
+        <v>12.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1.09</v>
+        <v>4.9</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>7.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="O19" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P19" t="n">
-        <v>1.25</v>
+        <v>2.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="S19" t="n">
-        <v>1.14</v>
+        <v>1.98</v>
       </c>
       <c r="T19" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -4249,170 +4249,170 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.03</v>
+        <v>2.78</v>
       </c>
       <c r="G20" t="n">
-        <v>990</v>
+        <v>3.8</v>
       </c>
       <c r="H20" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="I20" t="n">
-        <v>990</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
-        <v>1.09</v>
+        <v>3.45</v>
       </c>
       <c r="K20" t="n">
-        <v>950</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="O20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>2.72</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="S20" t="n">
-        <v>1.12</v>
+        <v>1.92</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>2.72</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -4443,25 +4443,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.03</v>
+        <v>2.72</v>
       </c>
       <c r="G21" t="n">
-        <v>990</v>
+        <v>3.4</v>
       </c>
       <c r="H21" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>990</v>
+        <v>2.54</v>
       </c>
       <c r="J21" t="n">
-        <v>1.09</v>
+        <v>3.2</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M21" t="n">
         <v>1.01</v>
@@ -4470,143 +4470,143 @@
         <v>1.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P21" t="n">
         <v>1.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="R21" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="S21" t="n">
-        <v>1.14</v>
+        <v>2.14</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="U21" t="n">
-        <v>1.11</v>
+        <v>2.56</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AM21" t="n">
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -4637,177 +4637,177 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.02</v>
+        <v>1.92</v>
       </c>
       <c r="G22" t="n">
-        <v>990</v>
+        <v>2.32</v>
       </c>
       <c r="H22" t="n">
-        <v>1.02</v>
+        <v>2.98</v>
       </c>
       <c r="I22" t="n">
-        <v>990</v>
+        <v>3.55</v>
       </c>
       <c r="J22" t="n">
-        <v>1.09</v>
+        <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M22" t="n">
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.1</v>
+        <v>3.55</v>
       </c>
       <c r="O22" t="n">
         <v>1.15</v>
       </c>
       <c r="P22" t="n">
-        <v>1.25</v>
+        <v>2.84</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="R22" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="S22" t="n">
-        <v>1.15</v>
+        <v>1.98</v>
       </c>
       <c r="T22" t="n">
         <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>1.11</v>
+        <v>2.72</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="G23" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="H23" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="I23" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BB23" t="n">
         <v>3.3</v>
       </c>
-      <c r="K23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="X23" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BC23" t="n">
-        <v>20</v>
+        <v>9.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>20</v>
+        <v>3.15</v>
       </c>
       <c r="BE23" t="n">
-        <v>28</v>
+        <v>3.25</v>
       </c>
       <c r="BF23" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BG23" t="n">
-        <v>9.800000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,179 +5016,179 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Smouha</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X24" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT24" t="n">
         <v>7.4</v>
       </c>
-      <c r="G24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V24" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X24" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC24" t="n">
+      <c r="AU24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV24" t="n">
         <v>14</v>
       </c>
-      <c r="AD24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>490</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>230</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>450</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AW24" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX24" t="n">
         <v>10</v>
       </c>
       <c r="AY24" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ24" t="n">
-        <v>8.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="BC24" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BD24" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BE24" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BF24" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BG24" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -5210,179 +5210,179 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Smouha</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.35</v>
+        <v>7.4</v>
       </c>
       <c r="G25" t="n">
-        <v>1.39</v>
+        <v>8.6</v>
       </c>
       <c r="H25" t="n">
-        <v>12.5</v>
+        <v>1.62</v>
       </c>
       <c r="I25" t="n">
-        <v>15.5</v>
+        <v>1.66</v>
       </c>
       <c r="J25" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="K25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S25" t="n">
         <v>5.4</v>
       </c>
-      <c r="L25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.45</v>
-      </c>
       <c r="T25" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="U25" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="V25" t="n">
-        <v>1.07</v>
+        <v>2.52</v>
       </c>
       <c r="W25" t="n">
-        <v>3.55</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>490</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>220</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>230</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>430</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>230</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>230</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>490</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT25" t="n">
         <v>15</v>
       </c>
-      <c r="Y25" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC25" t="n">
+      <c r="AU25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW25" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD25" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>330</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>80</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>310</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>16</v>
-      </c>
       <c r="AX25" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="AZ25" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="BA25" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="BB25" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="BD25" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="BE25" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BG25" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5.2</v>
+        <v>1.37</v>
       </c>
       <c r="G26" t="n">
-        <v>5.6</v>
+        <v>1.4</v>
       </c>
       <c r="H26" t="n">
-        <v>1.83</v>
+        <v>12</v>
       </c>
       <c r="I26" t="n">
-        <v>1.92</v>
+        <v>14</v>
       </c>
       <c r="J26" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="K26" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M26" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="O26" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="P26" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="R26" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="T26" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="U26" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="V26" t="n">
-        <v>2.08</v>
+        <v>1.08</v>
       </c>
       <c r="W26" t="n">
-        <v>1.21</v>
+        <v>3.5</v>
       </c>
       <c r="X26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>95</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC26" t="n">
         <v>12</v>
       </c>
-      <c r="Y26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z26" t="n">
+      <c r="AD26" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>310</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>80</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>11</v>
       </c>
-      <c r="AA26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>100</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI26" t="n">
+      <c r="AK26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL26" t="n">
         <v>120</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>470</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>700</v>
-      </c>
       <c r="AM26" t="n">
-        <v>580</v>
+        <v>310</v>
       </c>
       <c r="AN26" t="n">
-        <v>700</v>
+        <v>7.4</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>560</v>
       </c>
       <c r="AP26" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="AQ26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT26" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>13</v>
-      </c>
       <c r="AU26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AV26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY26" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AW26" t="n">
+      <c r="AZ26" t="n">
         <v>10.5</v>
       </c>
-      <c r="AX26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>20</v>
-      </c>
       <c r="BA26" t="n">
-        <v>34</v>
+        <v>14.5</v>
       </c>
       <c r="BB26" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC26" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>9.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="BE26" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Riteriai</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y27" t="n">
         <v>7.4</v>
       </c>
-      <c r="G27" t="n">
-        <v>9</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="J27" t="n">
-        <v>4</v>
-      </c>
-      <c r="K27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V27" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>7.6</v>
-      </c>
       <c r="Z27" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AB27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>120</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH27" t="n">
         <v>24</v>
       </c>
-      <c r="AC27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>160</v>
-      </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>700</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>700</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>700</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX27" t="n">
         <v>32</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AY27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC27" t="n">
         <v>28</v>
       </c>
-      <c r="AI27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>340</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>170</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>270</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW27" t="n">
+      <c r="BD27" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG27" t="n">
         <v>13.5</v>
       </c>
-      <c r="AX27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,186 +5792,186 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Riteriai</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.58</v>
+        <v>7.6</v>
       </c>
       <c r="G28" t="n">
+        <v>9</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V28" t="n">
         <v>2.72</v>
       </c>
-      <c r="H28" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.54</v>
-      </c>
       <c r="W28" t="n">
-        <v>1.59</v>
+        <v>1.12</v>
       </c>
       <c r="X28" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>500</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA28" t="n">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AC28" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="AF28" t="n">
-        <v>970</v>
+        <v>75</v>
       </c>
       <c r="AG28" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AH28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI28" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AJ28" t="n">
-        <v>900</v>
+        <v>340</v>
       </c>
       <c r="AK28" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AL28" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AM28" t="n">
-        <v>580</v>
+        <v>190</v>
       </c>
       <c r="AN28" t="n">
-        <v>55</v>
+        <v>260</v>
       </c>
       <c r="AO28" t="n">
-        <v>21</v>
+        <v>9.6</v>
       </c>
       <c r="AP28" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS28" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS28" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AT28" t="n">
-        <v>7.6</v>
+        <v>19</v>
       </c>
       <c r="AU28" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AV28" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AW28" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY28" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="BA28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC28" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG28" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,184 +5981,184 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.95</v>
+        <v>2.64</v>
       </c>
       <c r="G29" t="n">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="H29" t="n">
-        <v>3.95</v>
+        <v>2.76</v>
       </c>
       <c r="I29" t="n">
-        <v>980</v>
+        <v>2.82</v>
       </c>
       <c r="J29" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="K29" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="L29" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="M29" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>2.22</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="P29" t="n">
-        <v>1.49</v>
+        <v>2.32</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.38</v>
+        <v>1.72</v>
       </c>
       <c r="R29" t="n">
-        <v>1.1</v>
+        <v>1.52</v>
       </c>
       <c r="S29" t="n">
-        <v>1.05</v>
+        <v>2.84</v>
       </c>
       <c r="T29" t="n">
-        <v>1.96</v>
+        <v>1.6</v>
       </c>
       <c r="U29" t="n">
-        <v>1.68</v>
+        <v>2.48</v>
       </c>
       <c r="V29" t="n">
-        <v>1.17</v>
+        <v>1.54</v>
       </c>
       <c r="W29" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG29" t="n">
-        <v>990</v>
+        <v>13.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM29" t="n">
         <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE29" t="n">
         <v>5.9</v>
       </c>
-      <c r="AQ29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AT29" t="n">
+      <c r="BF29" t="n">
         <v>5</v>
       </c>
-      <c r="AU29" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BG29" t="n">
-        <v>1.34</v>
+        <v>16</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -6192,10 +6192,10 @@
         <v>12</v>
       </c>
       <c r="G30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="H30" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="I30" t="n">
         <v>1.3</v>
@@ -6207,34 +6207,34 @@
         <v>7.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M30" t="n">
         <v>1.02</v>
       </c>
       <c r="N30" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="O30" t="n">
         <v>1.12</v>
       </c>
       <c r="P30" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q30" t="n">
         <v>1.37</v>
       </c>
       <c r="R30" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="T30" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U30" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="V30" t="n">
         <v>4.3</v>
@@ -6243,13 +6243,13 @@
         <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Y30" t="n">
         <v>14.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA30" t="n">
         <v>12.5</v>
@@ -6258,101 +6258,101 @@
         <v>65</v>
       </c>
       <c r="AC30" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AF30" t="n">
         <v>150</v>
       </c>
       <c r="AG30" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AH30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI30" t="n">
         <v>26</v>
       </c>
-      <c r="AI30" t="n">
-        <v>28</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>430</v>
+        <v>390</v>
       </c>
       <c r="AK30" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AL30" t="n">
-        <v>390</v>
+        <v>110</v>
       </c>
       <c r="AM30" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AN30" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AO30" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AP30" t="n">
         <v>44</v>
       </c>
       <c r="AQ30" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>8.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="AU30" t="n">
         <v>14</v>
       </c>
       <c r="AV30" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW30" t="n">
         <v>11</v>
       </c>
       <c r="AX30" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AY30" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA30" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BB30" t="n">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BG30" t="n">
         <v>3.2</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -6383,52 +6383,52 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G31" t="n">
         <v>2.36</v>
       </c>
       <c r="H31" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I31" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J31" t="n">
         <v>3.4</v>
       </c>
       <c r="K31" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L31" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M31" t="n">
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R31" t="n">
         <v>1.34</v>
       </c>
-      <c r="P31" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.33</v>
-      </c>
       <c r="S31" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T31" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U31" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V31" t="n">
         <v>1.38</v>
@@ -6437,28 +6437,28 @@
         <v>1.73</v>
       </c>
       <c r="X31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y31" t="n">
         <v>13</v>
       </c>
       <c r="Z31" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AA31" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD31" t="n">
         <v>15</v>
       </c>
       <c r="AE31" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF31" t="n">
         <v>15</v>
@@ -6470,7 +6470,7 @@
         <v>29</v>
       </c>
       <c r="AI31" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="AJ31" t="n">
         <v>32</v>
@@ -6479,46 +6479,46 @@
         <v>26</v>
       </c>
       <c r="AL31" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AM31" t="n">
         <v>320</v>
       </c>
       <c r="AN31" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO31" t="n">
         <v>50</v>
       </c>
       <c r="AP31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR31" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="AS31" t="n">
         <v>23</v>
       </c>
       <c r="AT31" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU31" t="n">
         <v>7</v>
       </c>
       <c r="AV31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW31" t="n">
         <v>30</v>
       </c>
       <c r="AX31" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AY31" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
         <v>15.5</v>
@@ -6530,23 +6530,23 @@
         <v>14.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="BD31" t="n">
         <v>18</v>
       </c>
       <c r="BE31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BF31" t="n">
-        <v>17.5</v>
+        <v>9.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -6577,97 +6577,97 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="G32" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="H32" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I32" t="n">
         <v>2.82</v>
       </c>
       <c r="J32" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K32" t="n">
         <v>4</v>
       </c>
       <c r="L32" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M32" t="n">
         <v>1.07</v>
       </c>
       <c r="N32" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="P32" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="R32" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="S32" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="T32" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="U32" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="V32" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W32" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="X32" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="Y32" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AA32" t="n">
         <v>220</v>
       </c>
       <c r="AB32" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AC32" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD32" t="n">
         <v>13</v>
       </c>
       <c r="AE32" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AF32" t="n">
         <v>19</v>
       </c>
       <c r="AG32" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AI32" t="n">
         <v>290</v>
       </c>
       <c r="AJ32" t="n">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="AK32" t="n">
         <v>75</v>
@@ -6676,71 +6676,71 @@
         <v>180</v>
       </c>
       <c r="AM32" t="n">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="AN32" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="AO32" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AP32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT32" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="AU32" t="n">
         <v>7.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB32" t="n">
         <v>16</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>32</v>
       </c>
       <c r="BC32" t="n">
         <v>14.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE32" t="n">
         <v>26</v>
       </c>
       <c r="BF32" t="n">
-        <v>7.8</v>
+        <v>17.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -6771,112 +6771,112 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="G33" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="H33" t="n">
-        <v>2.54</v>
+        <v>2.06</v>
       </c>
       <c r="I33" t="n">
-        <v>3.2</v>
+        <v>10.5</v>
       </c>
       <c r="J33" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="K33" t="n">
         <v>3.8</v>
       </c>
       <c r="L33" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N33" t="n">
-        <v>3.05</v>
+        <v>1.1</v>
       </c>
       <c r="O33" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="P33" t="n">
-        <v>1.75</v>
+        <v>1.08</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.85</v>
+        <v>1.34</v>
       </c>
       <c r="R33" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="S33" t="n">
-        <v>3.25</v>
+        <v>1.86</v>
       </c>
       <c r="T33" t="n">
         <v>1.8</v>
       </c>
       <c r="U33" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="V33" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="W33" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="X33" t="n">
-        <v>15.5</v>
+        <v>34</v>
       </c>
       <c r="Y33" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Z33" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AA33" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AB33" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="AD33" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AE33" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AF33" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AG33" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH33" t="n">
-        <v>19</v>
+        <v>500</v>
       </c>
       <c r="AI33" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AJ33" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AK33" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AL33" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AM33" t="n">
         <v>580</v>
       </c>
       <c r="AN33" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AO33" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AP33" t="n">
         <v>7.6</v>
@@ -6885,10 +6885,10 @@
         <v>6.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>5.5</v>
+        <v>2.16</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.8</v>
+        <v>2.24</v>
       </c>
       <c r="AT33" t="n">
         <v>5.8</v>
@@ -6897,13 +6897,13 @@
         <v>6.2</v>
       </c>
       <c r="AV33" t="n">
-        <v>7.6</v>
+        <v>2.06</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.6</v>
+        <v>2.22</v>
       </c>
       <c r="AX33" t="n">
-        <v>8.4</v>
+        <v>2.14</v>
       </c>
       <c r="AY33" t="n">
         <v>7</v>
@@ -6912,19 +6912,19 @@
         <v>10.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.7</v>
+        <v>2.24</v>
       </c>
       <c r="BB33" t="n">
-        <v>5.7</v>
+        <v>2.24</v>
       </c>
       <c r="BC33" t="n">
-        <v>5.5</v>
+        <v>2.14</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.7</v>
+        <v>2.24</v>
       </c>
       <c r="BE33" t="n">
-        <v>6.8</v>
+        <v>2.26</v>
       </c>
       <c r="BF33" t="n">
         <v>5.5</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -6965,16 +6965,16 @@
         </is>
       </c>
       <c r="F34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G34" t="n">
         <v>1.64</v>
       </c>
-      <c r="G34" t="n">
-        <v>1.65</v>
-      </c>
       <c r="H34" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J34" t="n">
         <v>4.4</v>
@@ -6992,55 +6992,55 @@
         <v>4</v>
       </c>
       <c r="O34" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T34" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="U34" t="n">
         <v>1.94</v>
       </c>
-      <c r="R34" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.95</v>
-      </c>
       <c r="V34" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W34" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X34" t="n">
         <v>15</v>
       </c>
       <c r="Y34" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z34" t="n">
         <v>46</v>
       </c>
       <c r="AA34" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB34" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE34" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF34" t="n">
         <v>8.800000000000001</v>
@@ -7049,7 +7049,7 @@
         <v>10</v>
       </c>
       <c r="AH34" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI34" t="n">
         <v>85</v>
@@ -7064,16 +7064,16 @@
         <v>40</v>
       </c>
       <c r="AM34" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN34" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO34" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AP34" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ34" t="n">
         <v>17.5</v>
@@ -7082,19 +7082,19 @@
         <v>42</v>
       </c>
       <c r="AS34" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AT34" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU34" t="n">
         <v>9.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW34" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AX34" t="n">
         <v>8.4</v>
@@ -7103,10 +7103,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ34" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA34" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BB34" t="n">
         <v>14</v>
@@ -7118,17 +7118,17 @@
         <v>38</v>
       </c>
       <c r="BE34" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BF34" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG34" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2.28</v>
+        <v>2.68</v>
       </c>
       <c r="I2" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="J2" t="n">
-        <v>2.94</v>
+        <v>2.38</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>2.48</v>
       </c>
       <c r="L2" t="n">
-        <v>1.52</v>
+        <v>3.15</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="N2" t="n">
-        <v>2.66</v>
+        <v>1.57</v>
       </c>
       <c r="O2" t="n">
-        <v>1.47</v>
+        <v>2.64</v>
       </c>
       <c r="P2" t="n">
-        <v>1.56</v>
+        <v>1.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.46</v>
+        <v>6.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7</v>
+        <v>23</v>
       </c>
       <c r="T2" t="n">
-        <v>1.99</v>
+        <v>3.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.81</v>
+        <v>1.31</v>
       </c>
       <c r="V2" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="W2" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X2" t="n">
-        <v>10</v>
+        <v>3.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="Z2" t="n">
         <v>16</v>
       </c>
       <c r="AA2" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="AF2" t="n">
         <v>30</v>
       </c>
       <c r="AG2" t="n">
-        <v>17.5</v>
+        <v>34</v>
       </c>
       <c r="AH2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>370</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>260</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>550</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>590</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>230</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX2" t="n">
         <v>24</v>
       </c>
-      <c r="AI2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>6</v>
-      </c>
       <c r="AY2" t="n">
-        <v>5.5</v>
+        <v>25</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.8</v>
+        <v>210</v>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.8</v>
+        <v>120</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BE2" t="n">
-        <v>130</v>
+        <v>300</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.6</v>
+        <v>75</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="G3" t="n">
-        <v>2.44</v>
+        <v>2.06</v>
       </c>
       <c r="H3" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="R3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.27</v>
       </c>
-      <c r="S3" t="n">
-        <v>4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.32</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="X3" t="n">
         <v>13</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Z3" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AH3" t="n">
         <v>950</v>
       </c>
       <c r="AI3" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AJ3" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AK3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD3" t="n">
         <v>26</v>
       </c>
-      <c r="AO3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>6</v>
-      </c>
       <c r="BE3" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF3" t="n">
         <v>6.4</v>
       </c>
-      <c r="BF3" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BG3" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>270</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR4" t="n">
         <v>8</v>
       </c>
-      <c r="H4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X4" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AS4" t="n">
-        <v>1.07</v>
+        <v>15.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.07</v>
+        <v>11</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.07</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.07</v>
+        <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.07</v>
+        <v>17.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.07</v>
+        <v>7.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.07</v>
+        <v>17</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.07</v>
+        <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.07</v>
+        <v>36</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.07</v>
+        <v>9</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.07</v>
+        <v>9.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.07</v>
+        <v>8.4</v>
       </c>
       <c r="BE4" t="n">
         <v>120</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.07</v>
+        <v>9</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.07</v>
+        <v>13</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G5" t="n">
         <v>2.14</v>
@@ -1348,49 +1348,49 @@
         <v>4.1</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
         <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X5" t="n">
         <v>11.5</v>
@@ -1399,16 +1399,16 @@
         <v>13.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA5" t="n">
         <v>90</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
         <v>17</v>
@@ -1423,16 +1423,16 @@
         <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI5" t="n">
         <v>130</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
         <v>44</v>
@@ -1441,13 +1441,13 @@
         <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO5" t="n">
         <v>70</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
         <v>12.5</v>
@@ -1459,10 +1459,10 @@
         <v>20</v>
       </c>
       <c r="AT5" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
         <v>15</v>
@@ -1474,35 +1474,35 @@
         <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
         <v>17.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF5" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BG5" t="n">
         <v>48</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -1533,31 +1533,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="H6" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="J6" t="n">
         <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
         <v>1.51</v>
@@ -1575,16 +1575,16 @@
         <v>1.05</v>
       </c>
       <c r="T6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V6" t="n">
         <v>1.64</v>
       </c>
       <c r="W6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X6" t="n">
         <v>9.199999999999999</v>
@@ -1593,10 +1593,10 @@
         <v>7.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB6" t="n">
         <v>11</v>
@@ -1608,19 +1608,19 @@
         <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF6" t="n">
         <v>27</v>
       </c>
       <c r="AG6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AH6" t="n">
         <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="AJ6" t="n">
         <v>900</v>
@@ -1638,65 +1638,65 @@
         <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AR6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF6" t="n">
         <v>7.8</v>
       </c>
-      <c r="BD6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7</v>
-      </c>
       <c r="BG6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="G7" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="I7" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
         <v>1.42</v>
@@ -1754,7 +1754,7 @@
         <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P7" t="n">
         <v>1.73</v>
@@ -1763,28 +1763,28 @@
         <v>2.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V7" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
         <v>28</v>
       </c>
       <c r="Y7" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="Z7" t="n">
         <v>970</v>
@@ -1811,7 +1811,7 @@
         <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
@@ -1838,59 +1838,59 @@
         <v>5.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT7" t="n">
         <v>5.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AV7" t="n">
         <v>4.7</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BA7" t="n">
         <v>6.6</v>
       </c>
       <c r="BB7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG7" t="n">
         <v>5.9</v>
       </c>
-      <c r="BC7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="G8" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H8" t="n">
         <v>2.46</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J8" t="n">
         <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
         <v>1.27</v>
@@ -1945,7 +1945,7 @@
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="O8" t="n">
         <v>1.16</v>
@@ -1954,31 +1954,31 @@
         <v>2.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="S8" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U8" t="n">
         <v>3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W8" t="n">
         <v>1.51</v>
       </c>
       <c r="X8" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Y8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z8" t="n">
         <v>22</v>
@@ -1987,43 +1987,43 @@
         <v>36</v>
       </c>
       <c r="AB8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8" t="n">
         <v>12.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF8" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AG8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
         <v>13.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AJ8" t="n">
         <v>120</v>
       </c>
       <c r="AK8" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AN8" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AO8" t="n">
         <v>11</v>
@@ -2035,56 +2035,56 @@
         <v>16.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AT8" t="n">
         <v>18.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV8" t="n">
         <v>11</v>
       </c>
       <c r="AW8" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AY8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ8" t="n">
         <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB8" t="n">
         <v>40</v>
       </c>
       <c r="BC8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BE8" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BF8" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -2115,61 +2115,61 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="I9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="T9" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V9" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y9" t="n">
         <v>9.199999999999999</v>
@@ -2178,52 +2178,52 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AB9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
         <v>9.6</v>
       </c>
       <c r="AE9" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AG9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
         <v>34</v>
       </c>
       <c r="AJ9" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AK9" t="n">
-        <v>230</v>
+        <v>95</v>
       </c>
       <c r="AL9" t="n">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="AM9" t="n">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
         <v>110</v>
       </c>
       <c r="AO9" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>8.4</v>
@@ -2232,19 +2232,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV9" t="n">
         <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX9" t="n">
         <v>28</v>
@@ -2253,32 +2253,32 @@
         <v>22</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC9" t="n">
-        <v>17.5</v>
+        <v>42</v>
       </c>
       <c r="BD9" t="n">
         <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>17.5</v>
+        <v>48</v>
       </c>
       <c r="BF9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="H10" t="n">
         <v>1.31</v>
@@ -2327,49 +2327,49 @@
         <v>6.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="R10" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="V10" t="n">
         <v>3.85</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
         <v>950</v>
       </c>
       <c r="Y10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA10" t="n">
         <v>25</v>
@@ -2381,98 +2381,98 @@
         <v>42</v>
       </c>
       <c r="AD10" t="n">
-        <v>17.5</v>
+        <v>30</v>
       </c>
       <c r="AE10" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="n">
         <v>950</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="AI10" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
         <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AM10" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AN10" t="n">
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AP10" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AQ10" t="n">
         <v>8.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="AS10" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="AU10" t="n">
         <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD10" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AX10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BE10" t="n">
-        <v>23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF10" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -2503,127 +2503,127 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="H11" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N11" t="n">
         <v>2.82</v>
       </c>
-      <c r="J11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="O11" t="n">
         <v>1.53</v>
       </c>
-      <c r="M11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.48</v>
-      </c>
       <c r="P11" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W11" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="X11" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD11" t="n">
         <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF11" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH11" t="n">
         <v>23</v>
       </c>
       <c r="AI11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>60</v>
       </c>
-      <c r="AJ11" t="n">
-        <v>55</v>
-      </c>
       <c r="AK11" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL11" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AM11" t="n">
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AO11" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AQ11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT11" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8.4</v>
       </c>
       <c r="AU11" t="n">
         <v>6.6</v>
@@ -2632,41 +2632,41 @@
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AX11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA11" t="n">
         <v>32</v>
       </c>
       <c r="BB11" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BC11" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="BD11" t="n">
         <v>32</v>
       </c>
       <c r="BE11" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="BF11" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="BG11" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
         <v>3.3</v>
@@ -2724,7 +2724,7 @@
         <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P12" t="n">
         <v>1.66</v>
@@ -2742,13 +2742,13 @@
         <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="V12" t="n">
         <v>1.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="X12" t="n">
         <v>12.5</v>
@@ -2772,7 +2772,7 @@
         <v>23</v>
       </c>
       <c r="AE12" t="n">
-        <v>480</v>
+        <v>75</v>
       </c>
       <c r="AF12" t="n">
         <v>13</v>
@@ -2790,7 +2790,7 @@
         <v>30</v>
       </c>
       <c r="AK12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AL12" t="n">
         <v>290</v>
@@ -2826,7 +2826,7 @@
         <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AX12" t="n">
         <v>9.800000000000001</v>
@@ -2838,7 +2838,7 @@
         <v>19</v>
       </c>
       <c r="BA12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BB12" t="n">
         <v>21</v>
@@ -2847,7 +2847,7 @@
         <v>21</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE12" t="n">
         <v>6.8</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -2891,64 +2891,64 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
         <v>4.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="U13" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W13" t="n">
         <v>2.28</v>
       </c>
       <c r="X13" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="Y13" t="n">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="Z13" t="n">
         <v>500</v>
@@ -2957,25 +2957,25 @@
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AE13" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AF13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG13" t="n">
         <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AI13" t="n">
         <v>700</v>
@@ -2984,77 +2984,77 @@
         <v>38</v>
       </c>
       <c r="AK13" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="AL13" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AM13" t="n">
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO13" t="n">
         <v>700</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AQ13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU13" t="n">
         <v>5.2</v>
       </c>
-      <c r="AR13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AV13" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AZ13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB13" t="n">
         <v>7.2</v>
       </c>
-      <c r="BA13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BC13" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -3085,73 +3085,73 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G14" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="H14" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I14" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="J14" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="K14" t="n">
         <v>5.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R14" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S14" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T14" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V14" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W14" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="X14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y14" t="n">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="Z14" t="n">
         <v>420</v>
       </c>
       <c r="AA14" t="n">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="AB14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
         <v>12</v>
@@ -3169,13 +3169,13 @@
         <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="AI14" t="n">
         <v>470</v>
       </c>
       <c r="AJ14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK14" t="n">
         <v>15.5</v>
@@ -3184,10 +3184,10 @@
         <v>85</v>
       </c>
       <c r="AM14" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN14" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AO14" t="n">
         <v>170</v>
@@ -3199,22 +3199,22 @@
         <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS14" t="n">
         <v>10</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV14" t="n">
         <v>23</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="AX14" t="n">
         <v>8.199999999999999</v>
@@ -3223,32 +3223,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC14" t="n">
         <v>12.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE14" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BG14" t="n">
         <v>15</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -3279,28 +3279,28 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="G15" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="H15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="I15" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
         <v>4.5</v>
@@ -3312,7 +3312,7 @@
         <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R15" t="n">
         <v>1.47</v>
@@ -3321,22 +3321,22 @@
         <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U15" t="n">
         <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="W15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="X15" t="n">
         <v>17.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z15" t="n">
         <v>11</v>
@@ -3345,10 +3345,10 @@
         <v>18</v>
       </c>
       <c r="AB15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD15" t="n">
         <v>9.800000000000001</v>
@@ -3357,10 +3357,10 @@
         <v>17</v>
       </c>
       <c r="AF15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AG15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH15" t="n">
         <v>19</v>
@@ -3369,10 +3369,10 @@
         <v>32</v>
       </c>
       <c r="AJ15" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK15" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL15" t="n">
         <v>65</v>
@@ -3381,10 +3381,10 @@
         <v>95</v>
       </c>
       <c r="AN15" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AO15" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AP15" t="n">
         <v>16</v>
@@ -3396,10 +3396,10 @@
         <v>10</v>
       </c>
       <c r="AS15" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AU15" t="n">
         <v>8.6</v>
@@ -3408,41 +3408,41 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX15" t="n">
         <v>36</v>
       </c>
       <c r="AY15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BB15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD15" t="n">
         <v>36</v>
       </c>
       <c r="BE15" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BF15" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="G16" t="n">
         <v>1.48</v>
       </c>
       <c r="H16" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I16" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
         <v>5.2</v>
       </c>
       <c r="K16" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.25</v>
@@ -3497,28 +3497,28 @@
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O16" t="n">
         <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="n">
         <v>1.47</v>
       </c>
       <c r="R16" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="S16" t="n">
         <v>2.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U16" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="V16" t="n">
         <v>1.14</v>
@@ -3530,7 +3530,7 @@
         <v>34</v>
       </c>
       <c r="Y16" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="Z16" t="n">
         <v>160</v>
@@ -3575,22 +3575,22 @@
         <v>80</v>
       </c>
       <c r="AN16" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AO16" t="n">
         <v>110</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="AQ16" t="n">
         <v>17.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AS16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT16" t="n">
         <v>11.5</v>
@@ -3599,7 +3599,7 @@
         <v>11</v>
       </c>
       <c r="AV16" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW16" t="n">
         <v>10</v>
@@ -3626,7 +3626,7 @@
         <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="BF16" t="n">
         <v>4.2</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H17" t="n">
         <v>2.6</v>
       </c>
-      <c r="G17" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2.56</v>
-      </c>
       <c r="I17" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="J17" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K17" t="n">
         <v>4.1</v>
@@ -3691,7 +3691,7 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O17" t="n">
         <v>1.23</v>
@@ -3700,13 +3700,13 @@
         <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R17" t="n">
         <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T17" t="n">
         <v>1.59</v>
@@ -3715,31 +3715,31 @@
         <v>2.44</v>
       </c>
       <c r="V17" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W17" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X17" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="Y17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z17" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AA17" t="n">
         <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE17" t="n">
         <v>75</v>
@@ -3769,10 +3769,10 @@
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AP17" t="n">
         <v>16</v>
@@ -3784,7 +3784,7 @@
         <v>15</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AT17" t="n">
         <v>11</v>
@@ -3811,7 +3811,7 @@
         <v>16</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="BC17" t="n">
         <v>13</v>
@@ -3820,7 +3820,7 @@
         <v>18</v>
       </c>
       <c r="BE17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF17" t="n">
         <v>13.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G18" t="n">
         <v>1.49</v>
@@ -3870,16 +3870,16 @@
         <v>7.4</v>
       </c>
       <c r="I18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K18" t="n">
         <v>5.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
@@ -3888,25 +3888,25 @@
         <v>5.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R18" t="n">
         <v>1.56</v>
       </c>
       <c r="S18" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="U18" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>1.12</v>
@@ -3915,7 +3915,7 @@
         <v>3.05</v>
       </c>
       <c r="X18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="Y18" t="n">
         <v>950</v>
@@ -3927,7 +3927,7 @@
         <v>240</v>
       </c>
       <c r="AB18" t="n">
-        <v>16.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC18" t="n">
         <v>17.5</v>
@@ -3939,7 +3939,7 @@
         <v>260</v>
       </c>
       <c r="AF18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG18" t="n">
         <v>10</v>
@@ -3957,7 +3957,7 @@
         <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM18" t="n">
         <v>380</v>
@@ -3975,13 +3975,13 @@
         <v>22</v>
       </c>
       <c r="AR18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AU18" t="n">
         <v>9.4</v>
@@ -3990,19 +3990,19 @@
         <v>22</v>
       </c>
       <c r="AW18" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="AY18" t="n">
         <v>5.8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB18" t="n">
         <v>11.5</v>
@@ -4011,10 +4011,10 @@
         <v>7.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF18" t="n">
         <v>5.3</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -4055,100 +4055,100 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="I19" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="J19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.15</v>
       </c>
       <c r="P19" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="Q19" t="n">
         <v>1.41</v>
       </c>
       <c r="R19" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="S19" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="T19" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V19" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W19" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="X19" t="n">
         <v>38</v>
       </c>
       <c r="Y19" t="n">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="Z19" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA19" t="n">
-        <v>380</v>
+        <v>440</v>
       </c>
       <c r="AB19" t="n">
         <v>13.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>950</v>
+        <v>95</v>
       </c>
       <c r="AE19" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AF19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG19" t="n">
         <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI19" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AJ19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL19" t="n">
         <v>34</v>
@@ -4157,68 +4157,68 @@
         <v>130</v>
       </c>
       <c r="AN19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB19" t="n">
         <v>4.4</v>
       </c>
-      <c r="AO19" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BC19" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -4249,170 +4249,170 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
         <v>3.8</v>
       </c>
       <c r="H20" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="J20" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="P20" t="n">
-        <v>2.72</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="S20" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="T20" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="U20" t="n">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="V20" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="W20" t="n">
         <v>1.36</v>
       </c>
       <c r="X20" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="Y20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN20" t="n">
         <v>23</v>
       </c>
-      <c r="Z20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>21</v>
-      </c>
       <c r="AO20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.82</v>
+        <v>5.7</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2.52</v>
+        <v>4.9</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.56</v>
+        <v>5.1</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.64</v>
+        <v>5.7</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.58</v>
+        <v>5.3</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.56</v>
+        <v>5.2</v>
       </c>
       <c r="AX20" t="n">
-        <v>2.66</v>
+        <v>5.8</v>
       </c>
       <c r="AY20" t="n">
-        <v>2.72</v>
+        <v>5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.48</v>
+        <v>4.9</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB20" t="n">
-        <v>2.72</v>
+        <v>6.2</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.64</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.66</v>
+        <v>6</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.24</v>
+        <v>4.2</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -4449,43 +4449,43 @@
         <v>3.4</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="I21" t="n">
         <v>2.54</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="O21" t="n">
         <v>1.16</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>2.42</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="R21" t="n">
         <v>1.62</v>
       </c>
       <c r="S21" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T21" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U21" t="n">
         <v>2.56</v>
@@ -4494,16 +4494,16 @@
         <v>1.64</v>
       </c>
       <c r="W21" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="X21" t="n">
         <v>950</v>
       </c>
       <c r="Y21" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z21" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AA21" t="n">
         <v>900</v>
@@ -4515,34 +4515,34 @@
         <v>95</v>
       </c>
       <c r="AD21" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AF21" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AG21" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH21" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI21" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AJ21" t="n">
         <v>900</v>
       </c>
       <c r="AK21" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AL21" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
         <v>600</v>
@@ -4551,62 +4551,62 @@
         <v>600</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.05</v>
+        <v>1.93</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.3</v>
+        <v>2.12</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.92</v>
+        <v>3.95</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.05</v>
+        <v>5.3</v>
       </c>
       <c r="AW21" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="AX21" t="n">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="AZ21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD21" t="n">
         <v>3.15</v>
       </c>
-      <c r="BA21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BE21" t="n">
-        <v>1.93</v>
+        <v>2.56</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.96</v>
+        <v>4.2</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -4637,28 +4637,28 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="G22" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H22" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="I22" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K22" t="n">
         <v>4.8</v>
       </c>
       <c r="L22" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N22" t="n">
         <v>3.55</v>
@@ -4679,19 +4679,19 @@
         <v>1.98</v>
       </c>
       <c r="T22" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="U22" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V22" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y22" t="n">
         <v>950</v>
@@ -4703,13 +4703,13 @@
         <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC22" t="n">
         <v>42</v>
       </c>
       <c r="AD22" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE22" t="n">
         <v>200</v>
@@ -4718,13 +4718,13 @@
         <v>70</v>
       </c>
       <c r="AG22" t="n">
-        <v>950</v>
+        <v>50</v>
       </c>
       <c r="AH22" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI22" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AJ22" t="n">
         <v>900</v>
@@ -4733,81 +4733,81 @@
         <v>160</v>
       </c>
       <c r="AL22" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AO22" t="n">
-        <v>600</v>
+        <v>970</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AQ22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF22" t="n">
         <v>4.6</v>
       </c>
-      <c r="AR22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BG22" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G23" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="H23" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J23" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="K23" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="M23" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="P23" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.66</v>
+        <v>2.08</v>
       </c>
       <c r="R23" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>5.7</v>
+        <v>3.75</v>
       </c>
       <c r="T23" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="U23" t="n">
-        <v>1.69</v>
+        <v>1.98</v>
       </c>
       <c r="V23" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X23" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB23" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Y23" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1000</v>
-      </c>
       <c r="AC23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU23" t="n">
         <v>7.4</v>
       </c>
-      <c r="AD23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AV23" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>3.2</v>
+        <v>20</v>
       </c>
       <c r="AX23" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9.4</v>
+        <v>17</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.25</v>
+        <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>3.3</v>
+        <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.15</v>
+        <v>20</v>
       </c>
       <c r="BE23" t="n">
-        <v>3.25</v>
+        <v>29</v>
       </c>
       <c r="BF23" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.25</v>
+        <v>19</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,179 +5016,179 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Smouha</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.08</v>
+        <v>7.6</v>
       </c>
       <c r="G24" t="n">
-        <v>2.14</v>
+        <v>8.6</v>
       </c>
       <c r="H24" t="n">
-        <v>3.95</v>
+        <v>1.62</v>
       </c>
       <c r="I24" t="n">
-        <v>4.4</v>
+        <v>1.65</v>
       </c>
       <c r="J24" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="K24" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L24" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="M24" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="O24" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="P24" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="S24" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.84</v>
+        <v>2.48</v>
       </c>
       <c r="U24" t="n">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="V24" t="n">
-        <v>1.3</v>
+        <v>2.52</v>
       </c>
       <c r="W24" t="n">
-        <v>1.87</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>17</v>
+        <v>5.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA24" t="n">
-        <v>290</v>
+        <v>16.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="AC24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>490</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>220</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>230</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>430</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>230</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>230</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>490</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP24" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH24" t="n">
+      <c r="AQ24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>21</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>16.5</v>
       </c>
       <c r="BA24" t="n">
         <v>29</v>
       </c>
       <c r="BB24" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>20</v>
+        <v>7.8</v>
       </c>
       <c r="BD24" t="n">
-        <v>20</v>
+        <v>7.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="BG24" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -5210,179 +5210,179 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Smouha</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H25" t="n">
+        <v>12</v>
+      </c>
+      <c r="I25" t="n">
+        <v>14</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X25" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>95</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>310</v>
+      </c>
+      <c r="AF25" t="n">
         <v>7.4</v>
       </c>
-      <c r="G25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V25" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA25" t="n">
+      <c r="AG25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK25" t="n">
         <v>16.5</v>
       </c>
-      <c r="AB25" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC25" t="n">
+      <c r="AL25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>540</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR25" t="n">
         <v>14</v>
       </c>
-      <c r="AD25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>490</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>220</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>230</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>430</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>230</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>230</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>490</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR25" t="n">
+      <c r="AS25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX25" t="n">
         <v>6.6</v>
       </c>
-      <c r="AS25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT25" t="n">
+      <c r="AY25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA25" t="n">
         <v>15</v>
       </c>
-      <c r="AU25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>28</v>
-      </c>
       <c r="BB25" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="BE25" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BF25" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.37</v>
+        <v>5.2</v>
       </c>
       <c r="G26" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="H26" t="n">
-        <v>12</v>
+        <v>1.82</v>
       </c>
       <c r="I26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>700</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>700</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>700</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE26" t="n">
         <v>14</v>
       </c>
-      <c r="J26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K26" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>95</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>310</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>80</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>310</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>560</v>
-      </c>
-      <c r="AP26" t="n">
+      <c r="BF26" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG26" t="n">
         <v>13.5</v>
       </c>
-      <c r="AQ26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>15</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Riteriai</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="G27" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="H27" t="n">
-        <v>1.83</v>
+        <v>1.49</v>
       </c>
       <c r="I27" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="J27" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="K27" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="O27" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="R27" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="U27" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="V27" t="n">
-        <v>2.12</v>
+        <v>2.84</v>
       </c>
       <c r="W27" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="X27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>280</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>260</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>190</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS27" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD27" t="n">
+      <c r="AT27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB27" t="n">
         <v>9.6</v>
       </c>
-      <c r="AE27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>120</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>700</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>700</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>700</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV27" t="n">
+      <c r="BC27" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AW27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>32</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>28</v>
-      </c>
       <c r="BD27" t="n">
-        <v>29</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE27" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,186 +5792,186 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Riteriai</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>7.6</v>
+        <v>2.66</v>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>2.72</v>
       </c>
       <c r="H28" t="n">
-        <v>1.53</v>
+        <v>2.76</v>
       </c>
       <c r="I28" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W28" t="n">
         <v>1.58</v>
       </c>
-      <c r="J28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V28" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.12</v>
-      </c>
       <c r="X28" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX28" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="AY28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB28" t="n">
         <v>24</v>
       </c>
-      <c r="AC28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>32</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>340</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>150</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>260</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>19</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BC28" t="n">
-        <v>9.4</v>
+        <v>21</v>
       </c>
       <c r="BD28" t="n">
-        <v>9.4</v>
+        <v>26</v>
       </c>
       <c r="BE28" t="n">
-        <v>9.6</v>
+        <v>30</v>
       </c>
       <c r="BF28" t="n">
-        <v>9.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,184 +5981,184 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="G29" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="H29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N29" t="n">
         <v>2.76</v>
       </c>
-      <c r="I29" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5</v>
-      </c>
       <c r="O29" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="P29" t="n">
-        <v>2.32</v>
+        <v>1.58</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.72</v>
+        <v>2.58</v>
       </c>
       <c r="R29" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>2.84</v>
+        <v>5.3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.6</v>
+        <v>2.06</v>
       </c>
       <c r="U29" t="n">
-        <v>2.48</v>
+        <v>1.8</v>
       </c>
       <c r="V29" t="n">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="W29" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="X29" t="n">
-        <v>23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y29" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>230</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR29" t="n">
         <v>22</v>
       </c>
-      <c r="Z29" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG29" t="n">
+      <c r="AS29" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH29" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AT29" t="n">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>7</v>
+        <v>15.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>9.4</v>
+        <v>36</v>
       </c>
       <c r="AX29" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY29" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>8.6</v>
+        <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BB29" t="n">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="BC29" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BD29" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.9</v>
+        <v>13.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="BG29" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G30" t="n">
         <v>12</v>
       </c>
-      <c r="G30" t="n">
-        <v>13.5</v>
-      </c>
       <c r="H30" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="J30" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="K30" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L30" t="n">
         <v>1.22</v>
@@ -6213,34 +6213,34 @@
         <v>1.02</v>
       </c>
       <c r="N30" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="O30" t="n">
         <v>1.12</v>
       </c>
       <c r="P30" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S30" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="T30" t="n">
         <v>1.73</v>
       </c>
       <c r="U30" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V30" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
         <v>60</v>
@@ -6252,58 +6252,58 @@
         <v>11</v>
       </c>
       <c r="AA30" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AB30" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AC30" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AF30" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AG30" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AH30" t="n">
         <v>25</v>
       </c>
       <c r="AI30" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AJ30" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="AK30" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AL30" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM30" t="n">
-        <v>320</v>
+        <v>100</v>
       </c>
       <c r="AN30" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AO30" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AP30" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AQ30" t="n">
         <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS30" t="n">
         <v>10.5</v>
@@ -6312,19 +6312,19 @@
         <v>25</v>
       </c>
       <c r="AU30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AV30" t="n">
         <v>10</v>
       </c>
       <c r="AW30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX30" t="n">
         <v>11</v>
       </c>
-      <c r="AX30" t="n">
-        <v>15</v>
-      </c>
       <c r="AY30" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="AZ30" t="n">
         <v>21</v>
@@ -6333,26 +6333,26 @@
         <v>23</v>
       </c>
       <c r="BB30" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="BC30" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BD30" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="BE30" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="BF30" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -6386,118 +6386,118 @@
         <v>2.28</v>
       </c>
       <c r="G31" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H31" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I31" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>3.4</v>
       </c>
       <c r="K31" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L31" t="n">
         <v>1.43</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N31" t="n">
         <v>3.7</v>
       </c>
       <c r="O31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R31" t="n">
         <v>1.35</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.34</v>
       </c>
       <c r="S31" t="n">
         <v>3.7</v>
       </c>
       <c r="T31" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U31" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V31" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W31" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X31" t="n">
         <v>13</v>
       </c>
       <c r="Y31" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="AA31" t="n">
         <v>160</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH31" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AI31" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ31" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL31" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AM31" t="n">
         <v>320</v>
       </c>
       <c r="AN31" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO31" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ31" t="n">
         <v>12</v>
       </c>
       <c r="AR31" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="AS31" t="n">
         <v>23</v>
@@ -6509,10 +6509,10 @@
         <v>7</v>
       </c>
       <c r="AV31" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="AX31" t="n">
         <v>13</v>
@@ -6521,32 +6521,32 @@
         <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="BB31" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="BC31" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="BD31" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="BE31" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="BF31" t="n">
-        <v>9.4</v>
+        <v>17</v>
       </c>
       <c r="BG31" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -6580,70 +6580,70 @@
         <v>2.68</v>
       </c>
       <c r="G32" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H32" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I32" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J32" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K32" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L32" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M32" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="O32" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P32" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="R32" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S32" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="T32" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="U32" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V32" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W32" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X32" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA32" t="n">
         <v>220</v>
       </c>
       <c r="AB32" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC32" t="n">
         <v>8.800000000000001</v>
@@ -6661,7 +6661,7 @@
         <v>12.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI32" t="n">
         <v>290</v>
@@ -6673,22 +6673,22 @@
         <v>75</v>
       </c>
       <c r="AL32" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="AM32" t="n">
         <v>450</v>
       </c>
       <c r="AN32" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP32" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="AQ32" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AR32" t="n">
         <v>16.5</v>
@@ -6706,16 +6706,16 @@
         <v>10.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="AY32" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA32" t="n">
         <v>30</v>
@@ -6724,7 +6724,7 @@
         <v>16</v>
       </c>
       <c r="BC32" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD32" t="n">
         <v>30</v>
@@ -6733,14 +6733,14 @@
         <v>26</v>
       </c>
       <c r="BF32" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -6771,112 +6771,112 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.87</v>
+        <v>2.68</v>
       </c>
       <c r="G33" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="H33" t="n">
-        <v>2.06</v>
+        <v>2.74</v>
       </c>
       <c r="I33" t="n">
-        <v>10.5</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="K33" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M33" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N33" t="n">
-        <v>1.1</v>
+        <v>3.55</v>
       </c>
       <c r="O33" t="n">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="P33" t="n">
-        <v>1.08</v>
+        <v>1.86</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.34</v>
+        <v>2.04</v>
       </c>
       <c r="R33" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="S33" t="n">
-        <v>1.86</v>
+        <v>3.7</v>
       </c>
       <c r="T33" t="n">
         <v>1.8</v>
       </c>
       <c r="U33" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V33" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="W33" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="X33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE33" t="n">
         <v>34</v>
       </c>
-      <c r="Y33" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>500</v>
-      </c>
       <c r="AF33" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AG33" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH33" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AI33" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AJ33" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AK33" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AL33" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AM33" t="n">
         <v>580</v>
       </c>
       <c r="AN33" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AO33" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AP33" t="n">
         <v>7.6</v>
@@ -6885,10 +6885,10 @@
         <v>6.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.16</v>
+        <v>5.7</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.24</v>
+        <v>5.9</v>
       </c>
       <c r="AT33" t="n">
         <v>5.8</v>
@@ -6897,13 +6897,13 @@
         <v>6.2</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.06</v>
+        <v>7.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.22</v>
+        <v>5.8</v>
       </c>
       <c r="AX33" t="n">
-        <v>2.14</v>
+        <v>8.4</v>
       </c>
       <c r="AY33" t="n">
         <v>7</v>
@@ -6912,29 +6912,29 @@
         <v>10.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.24</v>
+        <v>5.9</v>
       </c>
       <c r="BB33" t="n">
-        <v>2.24</v>
+        <v>5.9</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.14</v>
+        <v>5.7</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.24</v>
+        <v>5.9</v>
       </c>
       <c r="BE33" t="n">
-        <v>2.26</v>
+        <v>7.4</v>
       </c>
       <c r="BF33" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -6965,16 +6965,16 @@
         </is>
       </c>
       <c r="F34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G34" t="n">
         <v>1.63</v>
       </c>
-      <c r="G34" t="n">
-        <v>1.64</v>
-      </c>
       <c r="H34" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I34" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J34" t="n">
         <v>4.4</v>
@@ -6983,7 +6983,7 @@
         <v>4.5</v>
       </c>
       <c r="L34" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M34" t="n">
         <v>1.07</v>
@@ -6995,13 +6995,13 @@
         <v>1.32</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R34" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S34" t="n">
         <v>3.5</v>
@@ -7013,122 +7013,122 @@
         <v>1.94</v>
       </c>
       <c r="V34" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W34" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X34" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z34" t="n">
         <v>46</v>
       </c>
       <c r="AA34" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB34" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC34" t="n">
         <v>9.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE34" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF34" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG34" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH34" t="n">
         <v>25</v>
       </c>
       <c r="AI34" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ34" t="n">
         <v>14.5</v>
       </c>
       <c r="AK34" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL34" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM34" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO34" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP34" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ34" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AS34" t="n">
         <v>140</v>
       </c>
       <c r="AT34" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU34" t="n">
         <v>9.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW34" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AX34" t="n">
         <v>8.4</v>
       </c>
       <c r="AY34" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ34" t="n">
         <v>24</v>
       </c>
       <c r="BA34" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BB34" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC34" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD34" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE34" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="BF34" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG34" t="n">
         <v>100</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH25"/>
+  <dimension ref="A1:BH24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Chongqing Tonglianglong</t>
+          <t>Beroe Stara Za</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Henan Songshan Longmen</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>4.2</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>4.6</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="I2" t="n">
-        <v>65</v>
+        <v>7.6</v>
       </c>
       <c r="J2" t="n">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="K2" t="n">
-        <v>1.09</v>
+        <v>1.59</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,16 +787,16 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -826,7 +826,7 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.06</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -841,10 +841,10 @@
         <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>1.67</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -853,22 +853,22 @@
         <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP2" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AR2" t="n">
         <v>1000</v>
@@ -877,57 +877,57 @@
         <v>1000</v>
       </c>
       <c r="AT2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AV2" t="n">
         <v>1000</v>
       </c>
-      <c r="AU2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AW2" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="AX2" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AY2" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.24</v>
+        <v>1.62</v>
       </c>
       <c r="BA2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BB2" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.24</v>
+        <v>27</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.24</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.24</v>
+        <v>25</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.24</v>
+        <v>30</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.24</v>
+        <v>38</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -942,186 +942,186 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Beroe Stara Za</t>
+          <t>Bihor Oradea</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="G3" t="n">
-        <v>2.02</v>
+        <v>1.02</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7</v>
+        <v>140</v>
       </c>
       <c r="I3" t="n">
+        <v>240</v>
+      </c>
+      <c r="J3" t="n">
+        <v>50</v>
+      </c>
+      <c r="K3" t="n">
+        <v>950</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>50</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AN3" t="n">
         <v>5.1</v>
       </c>
-      <c r="J3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>110</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>110</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF3" t="n">
         <v>3.45</v>
       </c>
-      <c r="L3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>210</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>130</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>18</v>
-      </c>
       <c r="BG3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bihor Oradea</t>
+          <t>FK Kauno Zalgiris</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>FC Dziugas</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.69</v>
+        <v>1.17</v>
       </c>
       <c r="G4" t="n">
-        <v>1.75</v>
+        <v>1.19</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7</v>
+        <v>24</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>28</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>9.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="P4" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="U4" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>2.32</v>
+        <v>6.2</v>
       </c>
       <c r="X4" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>280</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM4" t="n">
         <v>120</v>
       </c>
-      <c r="AB4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>95</v>
-      </c>
       <c r="AN4" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="AO4" t="n">
         <v>280</v>
       </c>
       <c r="AP4" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>32</v>
+        <v>13.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>65</v>
+        <v>13.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AV4" t="n">
-        <v>16.5</v>
+        <v>42</v>
       </c>
       <c r="AW4" t="n">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="BB4" t="n">
-        <v>15.5</v>
+        <v>7.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD4" t="n">
         <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.4</v>
+        <v>3.65</v>
       </c>
       <c r="BG4" t="n">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FK Kauno Zalgiris</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Dziugas</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L5" t="n">
         <v>1.47</v>
       </c>
-      <c r="G5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="H5" t="n">
-        <v>7</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="M5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X5" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU5" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="J5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="X5" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>30</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AV5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB5" t="n">
         <v>110</v>
       </c>
-      <c r="AA5" t="n">
-        <v>240</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>470</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL5" t="n">
+      <c r="BC5" t="n">
+        <v>60</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF5" t="n">
         <v>85</v>
       </c>
-      <c r="AM5" t="n">
-        <v>510</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BG5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Slovakian Super League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,179 +1524,179 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Zilina</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Inter</t>
+          <t>Zemplin</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.2</v>
+        <v>1.93</v>
       </c>
       <c r="G6" t="n">
-        <v>5.4</v>
+        <v>2.86</v>
       </c>
       <c r="H6" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.74</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.24</v>
+        <v>1.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
-        <v>1.49</v>
+        <v>3.7</v>
       </c>
       <c r="S6" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="T6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>2.34</v>
+        <v>1.16</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>2.78</v>
       </c>
       <c r="X6" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
         <v>11</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AL6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE6" t="n">
         <v>17.5</v>
       </c>
-      <c r="AB6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>50</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>46</v>
-      </c>
       <c r="BF6" t="n">
-        <v>55</v>
+        <v>2.88</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.199999999999999</v>
+        <v>2.18</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Zilina</t>
+          <t>MFk Skalica</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zemplin</t>
+          <t>FC Kosice</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.46</v>
+        <v>2.36</v>
       </c>
       <c r="G7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L7" t="n">
         <v>1.51</v>
       </c>
-      <c r="H7" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.26</v>
-      </c>
       <c r="M7" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="P7" t="n">
-        <v>2.9</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.48</v>
+        <v>2.14</v>
       </c>
       <c r="R7" t="n">
-        <v>1.76</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>2.22</v>
+        <v>3.85</v>
       </c>
       <c r="T7" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>2.96</v>
+        <v>1.74</v>
       </c>
       <c r="X7" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE7" t="n">
         <v>48</v>
       </c>
-      <c r="Y7" t="n">
-        <v>75</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>160</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>240</v>
-      </c>
       <c r="AF7" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="AK7" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AL7" t="n">
         <v>46</v>
       </c>
       <c r="AM7" t="n">
-        <v>790</v>
+        <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>5.1</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AP7" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>30</v>
+        <v>10.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>38</v>
+        <v>19.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.5</v>
+        <v>46</v>
       </c>
       <c r="AT7" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="AX7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY7" t="n">
         <v>10</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.4</v>
       </c>
       <c r="AZ7" t="n">
         <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="BC7" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="BE7" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG7" t="n">
         <v>34</v>
       </c>
-      <c r="BF7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>15</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Slovakian Super League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MFk Skalica</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Kosice</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.74</v>
+        <v>1.39</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8</v>
+        <v>1.42</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>2.64</v>
+        <v>9.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="R8" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="S8" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="U8" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>3.35</v>
       </c>
       <c r="X8" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>230</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD8" t="n">
         <v>21</v>
       </c>
-      <c r="Y8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BE8" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BF8" t="n">
-        <v>15</v>
+        <v>4.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.41</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>1.45</v>
+        <v>3.15</v>
       </c>
       <c r="H9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC9" t="n">
         <v>7.8</v>
       </c>
-      <c r="I9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X9" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>75</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>540</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>250</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AD9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP9" t="n">
         <v>15</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AQ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG9" t="n">
         <v>17</v>
       </c>
-      <c r="AD9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>390</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>380</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>15</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Riteriai</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="G10" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="I10" t="n">
-        <v>2.46</v>
+        <v>1.55</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="U10" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="V10" t="n">
-        <v>1.69</v>
+        <v>2.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE10" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y10" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="AF10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>290</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW10" t="n">
         <v>14</v>
       </c>
-      <c r="AC10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE10" t="n">
+      <c r="AX10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY10" t="n">
         <v>25</v>
       </c>
-      <c r="AF10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG10" t="n">
+      <c r="AZ10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>60</v>
+      </c>
+      <c r="BD10" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>42</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>34</v>
-      </c>
       <c r="BE10" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="BF10" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="BG10" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Riteriai</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="G11" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.54</v>
+        <v>1.87</v>
       </c>
       <c r="I11" t="n">
-        <v>1.59</v>
+        <v>1.91</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.91</v>
+        <v>2.44</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="T11" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="V11" t="n">
-        <v>2.68</v>
+        <v>2.08</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X11" t="n">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="Z11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD11" t="n">
         <v>9.4</v>
       </c>
-      <c r="AA11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="AE11" t="n">
         <v>24</v>
       </c>
-      <c r="AC11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>17</v>
-      </c>
       <c r="AF11" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AG11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AH11" t="n">
         <v>25</v>
       </c>
       <c r="AI11" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AJ11" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="AK11" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AL11" t="n">
-        <v>260</v>
+        <v>170</v>
       </c>
       <c r="AM11" t="n">
-        <v>790</v>
+        <v>190</v>
       </c>
       <c r="AN11" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AO11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV11" t="n">
         <v>9</v>
       </c>
-      <c r="AP11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AW11" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AX11" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AY11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA11" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.6</v>
+        <v>29</v>
       </c>
       <c r="BC11" t="n">
-        <v>9.4</v>
+        <v>55</v>
       </c>
       <c r="BD11" t="n">
-        <v>9.6</v>
+        <v>29</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.4</v>
+        <v>29</v>
       </c>
       <c r="BF11" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.6</v>
+        <v>17</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.2</v>
+        <v>1.34</v>
       </c>
       <c r="G12" t="n">
-        <v>5.5</v>
+        <v>1.37</v>
       </c>
       <c r="H12" t="n">
-        <v>1.88</v>
+        <v>12</v>
       </c>
       <c r="I12" t="n">
-        <v>1.91</v>
+        <v>13</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>1.67</v>
+        <v>2.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.42</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U12" t="n">
         <v>1.77</v>
       </c>
       <c r="V12" t="n">
-        <v>2.1</v>
+        <v>1.08</v>
       </c>
       <c r="W12" t="n">
-        <v>1.22</v>
+        <v>3.7</v>
       </c>
       <c r="X12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>230</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>310</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AK12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>350</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>95</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>27</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC12" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>140</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX12" t="n">
+      <c r="BD12" t="n">
         <v>32</v>
       </c>
-      <c r="AY12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>29</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>38</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>55</v>
-      </c>
       <c r="BE12" t="n">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="BF12" t="n">
-        <v>23</v>
+        <v>5.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Smouha</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.35</v>
+        <v>6.6</v>
       </c>
       <c r="G13" t="n">
-        <v>1.37</v>
+        <v>7</v>
       </c>
       <c r="H13" t="n">
-        <v>13</v>
+        <v>1.73</v>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>1.74</v>
       </c>
       <c r="J13" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="N13" t="n">
-        <v>3.95</v>
+        <v>2.62</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>1.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.96</v>
+        <v>2.78</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="V13" t="n">
-        <v>1.07</v>
+        <v>2.34</v>
       </c>
       <c r="W13" t="n">
-        <v>3.7</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB13" t="n">
         <v>16</v>
       </c>
-      <c r="Y13" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>690</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>7</v>
-      </c>
       <c r="AC13" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF13" t="n">
         <v>55</v>
       </c>
-      <c r="AE13" t="n">
-        <v>300</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AG13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>270</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>700</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>190</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>320</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV13" t="n">
         <v>9.6</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AW13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX13" t="n">
         <v>38</v>
       </c>
-      <c r="AI13" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>310</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>490</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AY13" t="n">
-        <v>9.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="AZ13" t="n">
         <v>30</v>
       </c>
       <c r="BA13" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB13" t="n">
         <v>20</v>
       </c>
-      <c r="BB13" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BC13" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BD13" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="BE13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.6</v>
+        <v>19.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Smouha</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6.6</v>
+        <v>1.81</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>1.85</v>
       </c>
       <c r="H14" t="n">
-        <v>1.73</v>
+        <v>5.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.75</v>
+        <v>5.7</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K14" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="L14" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="P14" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>1.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.42</v>
+        <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="V14" t="n">
-        <v>2.32</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
       <c r="X14" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.8</v>
+        <v>19.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="AA14" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH14" t="n">
         <v>18.5</v>
       </c>
-      <c r="AB14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AH14" t="n">
+      <c r="AI14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL14" t="n">
         <v>34</v>
       </c>
-      <c r="AI14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>700</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>160</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>180</v>
-      </c>
       <c r="AM14" t="n">
-        <v>300</v>
+        <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>320</v>
+        <v>12</v>
       </c>
       <c r="AO14" t="n">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="AP14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.4</v>
+        <v>17</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="AS14" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU14" t="n">
         <v>8</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.4</v>
+        <v>17.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="AX14" t="n">
-        <v>46</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY14" t="n">
-        <v>26</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD14" t="n">
         <v>29</v>
       </c>
-      <c r="BA14" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BE14" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="BF14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BG14" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
@@ -3279,34 +3279,34 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="H15" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M15" t="n">
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="P15" t="n">
         <v>3</v>
@@ -3315,28 +3315,28 @@
         <v>1.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="S15" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="T15" t="n">
         <v>1.41</v>
       </c>
       <c r="U15" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W15" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="X15" t="n">
         <v>950</v>
       </c>
       <c r="Y15" t="n">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="Z15" t="n">
         <v>500</v>
@@ -3363,13 +3363,13 @@
         <v>50</v>
       </c>
       <c r="AH15" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="n">
         <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK15" t="n">
         <v>500</v>
@@ -3378,22 +3378,22 @@
         <v>500</v>
       </c>
       <c r="AM15" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="AO15" t="n">
         <v>970</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AQ15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR15" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>6.8</v>
       </c>
       <c r="AS15" t="n">
         <v>6.4</v>
@@ -3402,47 +3402,47 @@
         <v>7</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AW15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX15" t="n">
         <v>6.8</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="AY15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD15" t="n">
         <v>7</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>6.8</v>
       </c>
       <c r="BE15" t="n">
         <v>6.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
@@ -3476,61 +3476,61 @@
         <v>2.74</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I16" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J16" t="n">
         <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
         <v>1.18</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="R16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="T16" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V16" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W16" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X16" t="n">
         <v>500</v>
       </c>
       <c r="Y16" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="Z16" t="n">
         <v>970</v>
@@ -3554,7 +3554,7 @@
         <v>500</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH16" t="n">
         <v>80</v>
@@ -3578,10 +3578,10 @@
         <v>970</v>
       </c>
       <c r="AO16" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AP16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ16" t="n">
         <v>6.8</v>
@@ -3590,53 +3590,53 @@
         <v>7.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AV16" t="n">
         <v>5.3</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AZ16" t="n">
         <v>6.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="BF16" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
@@ -3670,19 +3670,19 @@
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H17" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="I17" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="K17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.19</v>
@@ -3691,19 +3691,19 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O17" t="n">
         <v>1.1</v>
       </c>
-      <c r="O17" t="n">
-        <v>1.14</v>
-      </c>
       <c r="P17" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="R17" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="S17" t="n">
         <v>1.79</v>
@@ -3712,22 +3712,22 @@
         <v>1.37</v>
       </c>
       <c r="U17" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X17" t="n">
         <v>48</v>
       </c>
       <c r="Y17" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z17" t="n">
         <v>23</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>24</v>
       </c>
       <c r="AA17" t="n">
         <v>30</v>
@@ -3742,19 +3742,19 @@
         <v>13.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF17" t="n">
         <v>38</v>
       </c>
       <c r="AG17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH17" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ17" t="n">
         <v>65</v>
@@ -3763,74 +3763,74 @@
         <v>34</v>
       </c>
       <c r="AL17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM17" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AN17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO17" t="n">
         <v>7.4</v>
       </c>
       <c r="AP17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>5.8</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AR17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY17" t="n">
         <v>5.4</v>
       </c>
-      <c r="AS17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX17" t="n">
+      <c r="AZ17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA17" t="n">
         <v>5.8</v>
       </c>
-      <c r="AY17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ17" t="n">
+      <c r="BB17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF17" t="n">
         <v>5</v>
       </c>
-      <c r="BA17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG17" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
@@ -3864,55 +3864,55 @@
         <v>1.33</v>
       </c>
       <c r="G18" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I18" t="n">
         <v>10.5</v>
       </c>
       <c r="J18" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K18" t="n">
         <v>6.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="O18" t="n">
         <v>1.16</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q18" t="n">
         <v>1.44</v>
       </c>
       <c r="R18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T18" t="n">
         <v>1.73</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V18" t="n">
         <v>1.11</v>
       </c>
       <c r="W18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X18" t="n">
         <v>34</v>
@@ -3927,7 +3927,7 @@
         <v>290</v>
       </c>
       <c r="AB18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC18" t="n">
         <v>15</v>
@@ -3945,7 +3945,7 @@
         <v>12</v>
       </c>
       <c r="AH18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI18" t="n">
         <v>260</v>
@@ -3954,84 +3954,84 @@
         <v>13.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL18" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AM18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AO18" t="n">
         <v>120</v>
       </c>
-      <c r="AN18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>130</v>
-      </c>
       <c r="AP18" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT18" t="n">
         <v>5</v>
       </c>
       <c r="AU18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX18" t="n">
         <v>4.7</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>4.4</v>
       </c>
       <c r="AY18" t="n">
         <v>4.7</v>
       </c>
       <c r="AZ18" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BA18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD18" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BE18" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="G19" t="n">
-        <v>1.84</v>
+        <v>2.28</v>
       </c>
       <c r="H19" t="n">
-        <v>5.3</v>
+        <v>3.95</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="K19" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>3.75</v>
+        <v>2.84</v>
       </c>
       <c r="O19" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="P19" t="n">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="S19" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="U19" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="W19" t="n">
-        <v>2.18</v>
+        <v>1.78</v>
       </c>
       <c r="X19" t="n">
-        <v>14.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.5</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="AA19" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>230</v>
+        <v>65</v>
       </c>
       <c r="AF19" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ19" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AK19" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="AL19" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AM19" t="n">
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>12.5</v>
+        <v>32</v>
       </c>
       <c r="AO19" t="n">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="AP19" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ19" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AS19" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW19" t="n">
         <v>40</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG19" t="n">
         <v>16</v>
       </c>
-      <c r="BA19" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>29</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>10</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Al-Khaleej Saihat</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.24</v>
       </c>
-      <c r="G20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="V20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>140</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>490</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>75</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>90</v>
+      </c>
+      <c r="BG20" t="n">
         <v>3.25</v>
       </c>
-      <c r="L20" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="X20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>25</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>15</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Al-Khaleej Saihat</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X21" t="n">
         <v>12</v>
       </c>
-      <c r="G21" t="n">
+      <c r="Y21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD21" t="n">
         <v>14</v>
       </c>
-      <c r="H21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="AE21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU21" t="n">
         <v>7</v>
       </c>
-      <c r="K21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X21" t="n">
-        <v>48</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>140</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>46</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>430</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>160</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>160</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AP21" t="n">
+      <c r="AV21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA21" t="n">
         <v>44</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>36</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>23</v>
-      </c>
       <c r="BB21" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="BC21" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="BD21" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE21" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="BF21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.15</v>
+        <v>17.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Scottish League Two</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,133 +4628,133 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Clyde</t>
+          <t>Queen of South</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spartans</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G22" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="H22" t="n">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="I22" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
         <v>1.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q22" t="n">
         <v>1.92</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U22" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="V22" t="n">
         <v>1.53</v>
       </c>
       <c r="W22" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="X22" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB22" t="n">
         <v>12</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>12.5</v>
       </c>
       <c r="AC22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AF22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AJ22" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AL22" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM22" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN22" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="AO22" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AP22" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR22" t="n">
         <v>16</v>
       </c>
       <c r="AS22" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AT22" t="n">
         <v>10</v>
@@ -4763,51 +4763,51 @@
         <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AX22" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
         <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB22" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="BC22" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BD22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG22" t="n">
         <v>20</v>
       </c>
-      <c r="BE22" t="n">
-        <v>19</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Clyde</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Spartans</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="G23" t="n">
-        <v>2.34</v>
+        <v>2.92</v>
       </c>
       <c r="H23" t="n">
-        <v>3.55</v>
+        <v>2.68</v>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>2.92</v>
       </c>
       <c r="J23" t="n">
         <v>3.35</v>
       </c>
       <c r="K23" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M23" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O23" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U23" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V23" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="W23" t="n">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="X23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y23" t="n">
         <v>12</v>
       </c>
-      <c r="Y23" t="n">
-        <v>13.5</v>
-      </c>
       <c r="Z23" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE23" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AF23" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
         <v>18</v>
       </c>
       <c r="AI23" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="AK23" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AL23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM23" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="AO23" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AP23" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AR23" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AS23" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU23" t="n">
         <v>7</v>
       </c>
       <c r="AV23" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="AX23" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AY23" t="n">
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB23" t="n">
         <v>16</v>
       </c>
-      <c r="BA23" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>27</v>
-      </c>
       <c r="BC23" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BD23" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="BE23" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="BF23" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,378 +5011,184 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Queen of South</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.64</v>
+        <v>1.63</v>
       </c>
       <c r="G24" t="n">
-        <v>2.76</v>
+        <v>1.64</v>
       </c>
       <c r="H24" t="n">
-        <v>2.78</v>
+        <v>5.8</v>
       </c>
       <c r="I24" t="n">
-        <v>2.88</v>
+        <v>5.9</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="K24" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U24" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.2</v>
-      </c>
       <c r="V24" t="n">
-        <v>1.54</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.57</v>
+        <v>2.56</v>
       </c>
       <c r="X24" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y24" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.5</v>
+        <v>44</v>
       </c>
       <c r="AA24" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO24" t="n">
         <v>100</v>
       </c>
-      <c r="AB24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI24" t="n">
+      <c r="AP24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>75</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE24" t="n">
         <v>100</v>
       </c>
-      <c r="AJ24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>29</v>
-      </c>
       <c r="BF24" t="n">
-        <v>18.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG24" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Atletico Madrid</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="H25" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="I25" t="n">
-        <v>6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>40</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>140</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>80</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>85</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>100</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>95</v>
-      </c>
-      <c r="BH25" t="inlineStr">
-        <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH18"/>
+  <dimension ref="A1:BH20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="H2" t="n">
+        <v>32</v>
+      </c>
+      <c r="I2" t="n">
         <v>150</v>
       </c>
-      <c r="I2" t="n">
-        <v>1000</v>
-      </c>
       <c r="J2" t="n">
-        <v>100</v>
+        <v>1.08</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>1.1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -799,16 +799,16 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>280</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -841,7 +841,7 @@
         <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>1.3</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -859,34 +859,34 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>220</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>220</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>220</v>
+        <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>220</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
-        <v>220</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>220</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="n">
-        <v>220</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>220</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
         <v>11</v>
@@ -895,10 +895,10 @@
         <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>100</v>
+        <v>17.5</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
@@ -907,27 +907,27 @@
         <v>11</v>
       </c>
       <c r="BD2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.35</v>
+        <v>5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -942,31 +942,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Smouha</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.5</v>
+        <v>110</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>3.45</v>
+        <v>1.1</v>
       </c>
       <c r="J3" t="n">
-        <v>2.04</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1</v>
+        <v>13.5</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -975,40 +975,40 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.56</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.48</v>
+        <v>3.85</v>
       </c>
       <c r="P3" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="R3" t="n">
         <v>1.01</v>
       </c>
       <c r="S3" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="T3" t="n">
-        <v>6.2</v>
+        <v>1.41</v>
       </c>
       <c r="U3" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="V3" t="n">
-        <v>1.06</v>
+        <v>10.5</v>
       </c>
       <c r="W3" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1017,111 +1017,111 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.78</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>12.5</v>
+        <v>5.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.5</v>
+        <v>1.18</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>12.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.64</v>
+        <v>5.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>5.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>5.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AY3" t="n">
-        <v>10.5</v>
+        <v>95</v>
       </c>
       <c r="AZ3" t="n">
-        <v>36</v>
+        <v>7.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>12</v>
+        <v>5.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>30</v>
+        <v>5.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>55</v>
+        <v>5.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>12.5</v>
+        <v>5.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>12.5</v>
+        <v>5.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1136,31 +1136,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Riteriai</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>190</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
-        <v>590</v>
+        <v>1.01</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02</v>
+        <v>610</v>
       </c>
       <c r="I4" t="n">
-        <v>1.03</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,28 +1175,28 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36</v>
+        <v>1.06</v>
       </c>
       <c r="V4" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>100</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1205,10 +1205,10 @@
         <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
         <v>1000</v>
@@ -1217,10 +1217,10 @@
         <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
         <v>1000</v>
@@ -1229,86 +1229,86 @@
         <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>1.37</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.55</v>
+        <v>8.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AV4" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>60</v>
+        <v>8.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>11.5</v>
+        <v>1.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>130</v>
+        <v>7.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="BF4" t="n">
-        <v>130</v>
+        <v>4.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
@@ -1330,186 +1330,186 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G5" t="n">
+        <v>270</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.01</v>
       </c>
-      <c r="G5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="H5" t="n">
-        <v>140</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>50</v>
-      </c>
-      <c r="K5" t="n">
-        <v>710</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>850</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>850</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>220</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW5" t="n">
         <v>4.7</v>
       </c>
-      <c r="S5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>100</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AX5" t="n">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="AY5" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BC5" t="n">
         <v>8</v>
       </c>
       <c r="BD5" t="n">
-        <v>24</v>
+        <v>7.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>42</v>
+        <v>4.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.42</v>
+        <v>8.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>11.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>South African Premier Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Smouha</t>
+          <t>Stellenbosch FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Orlando Pirates (SA)</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="G6" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>1.87</v>
+        <v>1.02</v>
       </c>
       <c r="J6" t="n">
-        <v>2.72</v>
+        <v>34</v>
       </c>
       <c r="K6" t="n">
+        <v>130</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V6" t="n">
+        <v>38</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>780</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>990</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>990</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>220</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>220</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>220</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>2.9</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="S6" t="n">
-        <v>34</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>820</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>990</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>990</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>990</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>990</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BA6" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.6</v>
+        <v>220</v>
       </c>
       <c r="BC6" t="n">
-        <v>8.6</v>
+        <v>19</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.2</v>
+        <v>2.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="BG6" t="n">
-        <v>46</v>
+        <v>2.82</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>South African Premier Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Magesi FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Orbit College FC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6.4</v>
+        <v>2.78</v>
       </c>
       <c r="G7" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="I7" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="J7" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="K7" t="n">
-        <v>2.36</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,28 +1757,28 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="W7" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1796,108 +1796,108 @@
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>12.5</v>
+        <v>980</v>
       </c>
       <c r="AF7" t="n">
         <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>11</v>
+        <v>740</v>
       </c>
       <c r="AI7" t="n">
-        <v>32</v>
+        <v>990</v>
       </c>
       <c r="AJ7" t="n">
         <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>75</v>
+        <v>840</v>
       </c>
       <c r="AM7" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>38</v>
+        <v>990</v>
       </c>
       <c r="AP7" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>140</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>150</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>South African Premier Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SV Tillmitsch</t>
+          <t>Siwelele FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FSC Eggendorf Hartberg II</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="G8" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="H8" t="n">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="I8" t="n">
-        <v>15.5</v>
+        <v>55</v>
       </c>
       <c r="J8" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1957,10 +1957,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>4.2</v>
+        <v>1.66</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>2.42</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1969,10 +1969,10 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2002,19 +2002,19 @@
         <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.6</v>
+        <v>1.79</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AI8" t="n">
-        <v>930</v>
+        <v>970</v>
       </c>
       <c r="AJ8" t="n">
         <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AL8" t="n">
         <v>990</v>
@@ -2023,75 +2023,75 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.16</v>
+        <v>220</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.16</v>
+        <v>220</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.16</v>
+        <v>220</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.16</v>
+        <v>220</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.16</v>
+        <v>220</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.16</v>
+        <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.16</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.16</v>
+        <v>15</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.16</v>
+        <v>6.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.85</v>
+        <v>1.71</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.16</v>
+        <v>6.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="BE8" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.18</v>
+        <v>7.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.18</v>
+        <v>60</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,78 +2101,78 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TUS Bad Waltersdorf</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SC Furstenfeld</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6</v>
+        <v>1.39</v>
       </c>
       <c r="G9" t="n">
-        <v>3.95</v>
+        <v>1.43</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1</v>
+        <v>13.5</v>
       </c>
       <c r="I9" t="n">
+        <v>15</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W9" t="n">
         <v>3.3</v>
       </c>
-      <c r="J9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="S9" t="n">
-        <v>27</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X9" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2181,111 +2181,111 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF9" t="n">
         <v>6.6</v>
       </c>
-      <c r="AC9" t="n">
-        <v>990</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>990</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
       <c r="AG9" t="n">
-        <v>990</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH9" t="n">
-        <v>990</v>
+        <v>34</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>610</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.52</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.55</v>
+        <v>9.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS9" t="n">
-        <v>50</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AX9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB9" t="n">
         <v>14</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>23</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>46</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>55</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>46</v>
-      </c>
       <c r="BD9" t="n">
-        <v>2.66</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.66</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.62</v>
+        <v>30</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.66</v>
+        <v>10</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,72 +2295,72 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SV Union Gnas</t>
+          <t>Al-Khaleej Saihat</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SV Lebring</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.51</v>
+        <v>9.4</v>
       </c>
       <c r="G10" t="n">
-        <v>1.74</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6</v>
+        <v>1.52</v>
       </c>
       <c r="I10" t="n">
-        <v>9.800000000000001</v>
+        <v>1.53</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.57</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.96</v>
+        <v>1.13</v>
       </c>
       <c r="R10" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="S10" t="n">
-        <v>19</v>
+        <v>1.69</v>
       </c>
       <c r="T10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.66</v>
+        <v>2.84</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2378,108 +2378,108 @@
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>990</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>990</v>
+        <v>4.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AF10" t="n">
         <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>990</v>
+        <v>17.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AJ10" t="n">
         <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>95</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SV Wildon</t>
+          <t>Clyde</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Schladming</t>
+          <t>Spartans</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.11</v>
+        <v>2.58</v>
       </c>
       <c r="G11" t="n">
-        <v>1.12</v>
+        <v>2.72</v>
       </c>
       <c r="H11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y11" t="n">
         <v>10.5</v>
       </c>
-      <c r="I11" t="n">
-        <v>680</v>
-      </c>
-      <c r="J11" t="n">
+      <c r="Z11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB11" t="n">
         <v>10</v>
       </c>
-      <c r="K11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG11" t="n">
-        <v>990</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN11" t="n">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP11" t="n">
-        <v>3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.22</v>
+        <v>16</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.22</v>
+        <v>38</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.22</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.2</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.2</v>
+        <v>34</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.22</v>
+        <v>14</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.73</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.2</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.2</v>
+        <v>50</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.73</v>
+        <v>34</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.2</v>
+        <v>30</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.2</v>
+        <v>50</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.23</v>
+        <v>120</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.23</v>
+        <v>28</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.22</v>
+        <v>38</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,72 +2683,72 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>7.8</v>
+        <v>1.4</v>
       </c>
       <c r="G12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.43</v>
       </c>
       <c r="H12" t="n">
-        <v>1.61</v>
+        <v>11</v>
       </c>
       <c r="I12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T12" t="n">
         <v>1.65</v>
       </c>
-      <c r="J12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V12" t="n">
-        <v>2.58</v>
+        <v>1.09</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>3.3</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2763,111 +2763,111 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.75</v>
+        <v>22</v>
       </c>
       <c r="AE12" t="n">
-        <v>7.6</v>
+        <v>110</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.6</v>
+        <v>16.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>9.800000000000001</v>
+        <v>70</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AL12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN12" t="n">
         <v>12</v>
       </c>
-      <c r="AM12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>38</v>
-      </c>
       <c r="AO12" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>14.5</v>
       </c>
-      <c r="AP12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BA12" t="n">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="BB12" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BC12" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="BE12" t="n">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="BF12" t="n">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Queen of South</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I13" t="n">
         <v>4.1</v>
       </c>
-      <c r="I13" t="n">
-        <v>4.5</v>
-      </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="L13" t="n">
-        <v>1.93</v>
+        <v>1.69</v>
       </c>
       <c r="M13" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.34</v>
+        <v>2.92</v>
       </c>
       <c r="O13" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="R13" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="U13" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X13" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z13" t="n">
         <v>32</v>
       </c>
       <c r="AA13" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AB13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU13" t="n">
         <v>6.4</v>
       </c>
-      <c r="AC13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>370</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AV13" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>9.4</v>
+        <v>48</v>
       </c>
       <c r="AX13" t="n">
         <v>10.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="BB13" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BC13" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BD13" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="BE13" t="n">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="BF13" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="BG13" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Al-Khaleej Saihat</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.3</v>
+        <v>1.62</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4</v>
+        <v>1.63</v>
       </c>
       <c r="H14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.9</v>
       </c>
-      <c r="I14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="V14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH14" t="n">
         <v>27</v>
       </c>
-      <c r="O14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="P14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="U14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AI14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>130</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AX14" t="n">
         <v>7.8</v>
       </c>
-      <c r="AE14" t="n">
-        <v>290</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>370</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI14" t="n">
+      <c r="AY14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>25</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="BA14" t="n">
+        <v>85</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE14" t="n">
         <v>120</v>
       </c>
-      <c r="AK14" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>28</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>75</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>27</v>
-      </c>
       <c r="BF14" t="n">
-        <v>25</v>
+        <v>9.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.5</v>
+        <v>100</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Scottish League Two</t>
+          <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Clyde</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spartans</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V15" t="n">
         <v>2.7</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.57</v>
-      </c>
       <c r="W15" t="n">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>250</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>190</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS15" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="AT15" t="n">
         <v>20</v>
       </c>
-      <c r="AG15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI15" t="n">
+      <c r="AU15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX15" t="n">
         <v>50</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AY15" t="n">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BA15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB15" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BC15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BD15" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BE15" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="BF15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG15" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.22</v>
+        <v>1.33</v>
       </c>
       <c r="G16" t="n">
-        <v>2.28</v>
+        <v>1.36</v>
       </c>
       <c r="H16" t="n">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="I16" t="n">
-        <v>3.9</v>
+        <v>13.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="T16" t="n">
-        <v>1.92</v>
+        <v>2.36</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="W16" t="n">
-        <v>1.78</v>
+        <v>3.75</v>
       </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="Y16" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>620</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC16" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AD16" t="n">
-        <v>15.5</v>
+        <v>46</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>260</v>
       </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
       </c>
       <c r="AH16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>390</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AS16" t="n">
         <v>19</v>
       </c>
-      <c r="AI16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>65</v>
-      </c>
       <c r="AT16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU16" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="AW16" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="AY16" t="n">
         <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="BA16" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="BB16" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="BC16" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="BD16" t="n">
         <v>36</v>
       </c>
       <c r="BE16" t="n">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="BF16" t="n">
-        <v>20</v>
+        <v>5.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Queen of South</t>
+          <t>Universidad de Venezuela</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2</v>
+        <v>1.76</v>
       </c>
       <c r="I17" t="n">
-        <v>3.35</v>
+        <v>1.79</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="K17" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="O17" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="U17" t="n">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>2.26</v>
       </c>
       <c r="W17" t="n">
-        <v>1.71</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT17" t="n">
         <v>15</v>
       </c>
-      <c r="Y17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="AU17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG17" t="n">
         <v>11</v>
       </c>
-      <c r="AC17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>27</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,184 +3847,572 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Barcelona (Ecu)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L18" t="n">
         <v>1.64</v>
       </c>
-      <c r="G18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="H18" t="n">
+      <c r="M18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S18" t="n">
         <v>5.7</v>
       </c>
-      <c r="I18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="T18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V18" t="n">
         <v>2</v>
       </c>
-      <c r="Q18" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.2</v>
-      </c>
       <c r="W18" t="n">
-        <v>2.54</v>
+        <v>1.23</v>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y18" t="n">
-        <v>19</v>
+        <v>6.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>40</v>
+        <v>10.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>170</v>
+        <v>23</v>
       </c>
       <c r="AB18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>160</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP18" t="n">
         <v>7.8</v>
       </c>
-      <c r="AC18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG18" t="n">
+      <c r="AQ18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV18" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>150</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>20</v>
-      </c>
       <c r="AW18" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="AX18" t="n">
-        <v>8.4</v>
+        <v>30</v>
       </c>
       <c r="AY18" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="AZ18" t="n">
         <v>24</v>
       </c>
       <c r="BA18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:03:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Always Ready</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL19" t="n">
         <v>70</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="AM19" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:03:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CONCACAF Champions League</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Tigres</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X20" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>14</v>
       </c>
-      <c r="BC18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>110</v>
-      </c>
-      <c r="BF18" t="n">
+      <c r="AR20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY20" t="n">
         <v>9.4</v>
       </c>
-      <c r="BG18" t="n">
-        <v>95</v>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>2026-05-05 15:23:41</t>
+      <c r="AZ20" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7.2</v>
+        <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>7.4</v>
+        <v>300</v>
       </c>
       <c r="H2" t="n">
-        <v>1.58</v>
+        <v>1.02</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6</v>
+        <v>1.03</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>38</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>42</v>
       </c>
       <c r="L2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>3.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.04</v>
+        <v>1.45</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="S2" t="n">
-        <v>3.65</v>
+        <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>2.06</v>
+        <v>2.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="V2" t="n">
-        <v>2.66</v>
+        <v>34</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AA2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AE2" t="n">
-        <v>16.5</v>
+        <v>9.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AI2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>310</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>430</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA2" t="n">
         <v>40</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>270</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>210</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>36</v>
-      </c>
       <c r="BB2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BC2" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BD2" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="BE2" t="n">
-        <v>65</v>
+        <v>230</v>
       </c>
       <c r="BF2" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="G3" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="I3" t="n">
-        <v>12.5</v>
+        <v>170</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>5.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>1.39</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.83</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>440</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>880</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>770</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AU3" t="n">
         <v>1.44</v>
       </c>
-      <c r="S3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>590</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>410</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>360</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>370</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>11</v>
-      </c>
       <c r="AV3" t="n">
-        <v>40</v>
+        <v>1.45</v>
       </c>
       <c r="AW3" t="n">
-        <v>38</v>
+        <v>1.45</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.4</v>
+        <v>1.47</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>1.45</v>
       </c>
       <c r="AZ3" t="n">
-        <v>32</v>
+        <v>1.45</v>
       </c>
       <c r="BA3" t="n">
-        <v>50</v>
+        <v>1.45</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.6</v>
+        <v>1.45</v>
       </c>
       <c r="BC3" t="n">
-        <v>15</v>
+        <v>1.45</v>
       </c>
       <c r="BD3" t="n">
-        <v>44</v>
+        <v>1.45</v>
       </c>
       <c r="BE3" t="n">
-        <v>65</v>
+        <v>1.45</v>
       </c>
       <c r="BF3" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>15</v>
+        <v>1.45</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -1148,79 +1148,79 @@
         <v>5.5</v>
       </c>
       <c r="G4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="H4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I4" t="n">
         <v>1.74</v>
       </c>
-      <c r="I4" t="n">
-        <v>1.76</v>
-      </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O4" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="U4" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="W4" t="n">
         <v>1.2</v>
       </c>
       <c r="X4" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z4" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AB4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF4" t="n">
         <v>46</v>
@@ -1229,58 +1229,58 @@
         <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ4" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AK4" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL4" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AM4" t="n">
         <v>140</v>
       </c>
       <c r="AN4" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AT4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW4" t="n">
         <v>17</v>
       </c>
       <c r="AX4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AY4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ4" t="n">
         <v>20</v>
@@ -1289,26 +1289,26 @@
         <v>34</v>
       </c>
       <c r="BB4" t="n">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="BC4" t="n">
         <v>65</v>
       </c>
       <c r="BD4" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BE4" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BF4" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="BG4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="G5" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="H5" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
         <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="O5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="R5" t="n">
         <v>1.21</v>
       </c>
       <c r="S5" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="T5" t="n">
         <v>2.24</v>
       </c>
       <c r="U5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="W5" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="Z5" t="n">
         <v>10.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>27</v>
       </c>
       <c r="AF5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AK5" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AL5" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AM5" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AO5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT5" t="n">
         <v>11.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AY5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA5" t="n">
         <v>50</v>
       </c>
       <c r="BB5" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BC5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BD5" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="BE5" t="n">
-        <v>19.5</v>
+        <v>150</v>
       </c>
       <c r="BF5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H6" t="n">
         <v>5.8</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K6" t="n">
         <v>4.1</v>
@@ -1557,13 +1557,13 @@
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O6" t="n">
         <v>1.39</v>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
         <v>2.18</v>
@@ -1572,61 +1572,61 @@
         <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="V6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X6" t="n">
         <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AA6" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB6" t="n">
         <v>7.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF6" t="n">
         <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ6" t="n">
         <v>16.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL6" t="n">
         <v>44</v>
@@ -1641,22 +1641,22 @@
         <v>150</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>15.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AS6" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="AT6" t="n">
         <v>6.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV6" t="n">
         <v>21</v>
@@ -1665,38 +1665,38 @@
         <v>80</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA6" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="BB6" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD6" t="n">
         <v>40</v>
       </c>
       <c r="BE6" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="BF6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG6" t="n">
         <v>100</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="G7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
         <v>4</v>
@@ -1745,46 +1745,46 @@
         <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P7" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U7" t="n">
         <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="X7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z7" t="n">
         <v>40</v>
@@ -1793,13 +1793,13 @@
         <v>130</v>
       </c>
       <c r="AB7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC7" t="n">
         <v>9</v>
       </c>
       <c r="AD7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="n">
         <v>70</v>
@@ -1820,7 +1820,7 @@
         <v>18.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL7" t="n">
         <v>55</v>
@@ -1829,7 +1829,7 @@
         <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO7" t="n">
         <v>85</v>
@@ -1838,7 +1838,7 @@
         <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="n">
         <v>34</v>
@@ -1847,19 +1847,19 @@
         <v>65</v>
       </c>
       <c r="AT7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU7" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AU7" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AV7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW7" t="n">
         <v>44</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY7" t="n">
         <v>9.199999999999999</v>
@@ -1883,14 +1883,14 @@
         <v>70</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG7" t="n">
         <v>55</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH7"/>
+  <dimension ref="A1:BH5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>Universidad de Venezuela</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>200</v>
+        <v>1.16</v>
       </c>
       <c r="G2" t="n">
-        <v>300</v>
+        <v>1.17</v>
       </c>
       <c r="H2" t="n">
-        <v>1.02</v>
+        <v>34</v>
       </c>
       <c r="I2" t="n">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="J2" t="n">
-        <v>38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,140 +787,140 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>360</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>320</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AY2" t="n">
         <v>3.15</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V2" t="n">
-        <v>34</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>310</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>430</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1000</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="BA2" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BB2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>190</v>
+        <v>42</v>
       </c>
       <c r="BE2" t="n">
-        <v>230</v>
+        <v>160</v>
       </c>
       <c r="BF2" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.8</v>
+        <v>120</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -937,105 +937,105 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Barcelona (Ecu)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.15</v>
+        <v>6.6</v>
       </c>
       <c r="G3" t="n">
-        <v>1.17</v>
+        <v>7.2</v>
       </c>
       <c r="H3" t="n">
-        <v>36</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>170</v>
+        <v>3.8</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>1.69</v>
       </c>
       <c r="K3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.71</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="N3" t="n">
-        <v>2.88</v>
+        <v>1.17</v>
       </c>
       <c r="O3" t="n">
-        <v>1.52</v>
+        <v>6.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>36</v>
       </c>
       <c r="R3" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>230</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>13.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>6.8</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>1.95</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>440</v>
+        <v>17.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>880</v>
+        <v>100</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>770</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.6</v>
+        <v>1.89</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.45</v>
+        <v>4.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.800000000000001</v>
+        <v>160</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.84</v>
+        <v>8</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.44</v>
+        <v>17</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.45</v>
+        <v>80</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.45</v>
+        <v>300</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.47</v>
+        <v>65</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.45</v>
+        <v>120</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.45</v>
+        <v>310</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.45</v>
+        <v>150</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.45</v>
+        <v>320</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.45</v>
+        <v>250</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.45</v>
+        <v>130</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.45</v>
+        <v>1000</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.3</v>
+        <v>60</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.45</v>
+        <v>160</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>5.9</v>
+        <v>1.05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7</v>
+        <v>150</v>
       </c>
       <c r="I4" t="n">
-        <v>1.74</v>
+        <v>230</v>
       </c>
       <c r="J4" t="n">
+        <v>29</v>
+      </c>
+      <c r="K4" t="n">
+        <v>32</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>4</v>
       </c>
-      <c r="K4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>1.32</v>
       </c>
-      <c r="P4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>2.48</v>
       </c>
       <c r="T4" t="n">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.96</v>
+        <v>1.61</v>
       </c>
       <c r="V4" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2</v>
+        <v>26</v>
       </c>
       <c r="X4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>46</v>
+        <v>4.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AI4" t="n">
-        <v>38</v>
+        <v>280</v>
       </c>
       <c r="AJ4" t="n">
-        <v>160</v>
+        <v>4.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="AL4" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM4" t="n">
+        <v>390</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>200</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE4" t="n">
         <v>140</v>
       </c>
-      <c r="AN4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>65</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>70</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>95</v>
-      </c>
       <c r="BF4" t="n">
-        <v>24</v>
+        <v>4.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>10</v>
+        <v>240</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>CONCACAF Champions League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,572 +1325,184 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Barcelona (Ecu)</t>
+          <t>Tigres</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.6</v>
+        <v>1.78</v>
       </c>
       <c r="G5" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="H5" t="n">
-        <v>2.04</v>
+        <v>5.1</v>
       </c>
       <c r="I5" t="n">
-        <v>2.06</v>
+        <v>5.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.78</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="P5" t="n">
-        <v>1.54</v>
+        <v>1.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.78</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W5" t="n">
         <v>2.24</v>
       </c>
-      <c r="U5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.27</v>
-      </c>
       <c r="X5" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC5" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Y5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AD5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF5" t="n">
         <v>10.5</v>
       </c>
-      <c r="AA5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR5" t="n">
         <v>34</v>
       </c>
-      <c r="AG5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI5" t="n">
+      <c r="AS5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW5" t="n">
         <v>60</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>25</v>
-      </c>
       <c r="AX5" t="n">
-        <v>30</v>
+        <v>9.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>18.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BA5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB5" t="n">
-        <v>100</v>
+        <v>16.5</v>
       </c>
       <c r="BC5" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG5" t="n">
         <v>65</v>
       </c>
-      <c r="BD5" t="n">
-        <v>75</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>150</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>22</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CONMEBOL Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Always Ready</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Lanus</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>120</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>100</v>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2026-05-05 20:26:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CONCACAF Champions League</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Tigres</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X7" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>55</v>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
